--- a/docs/RALK_Preise_Plaene_Vertrieb.xlsx
+++ b/docs/RALK_Preise_Plaene_Vertrieb.xlsx
@@ -9,14 +9,15 @@
   </bookViews>
   <sheets>
     <sheet name="Legende" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Preise &amp; Pläne" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Mit Anwalts-Funnel" sheetId="3" state="visible" r:id="rId5"/>
-    <sheet name="Ohne Anwalt (Direkt)" sheetId="4" state="visible" r:id="rId6"/>
-    <sheet name="Vergleich" sheetId="5" state="visible" r:id="rId7"/>
-    <sheet name="Zielkunden – Register" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Marktvergleich" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Preise &amp; Pläne" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Mit Anwalts-Funnel" sheetId="4" state="visible" r:id="rId6"/>
+    <sheet name="Ohne Anwalt (Direkt)" sheetId="5" state="visible" r:id="rId7"/>
+    <sheet name="Vergleich" sheetId="6" state="visible" r:id="rId8"/>
+    <sheet name="Zielkunden – Register" sheetId="7" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">'Zielkunden – Register'!$B$5:$L$130</definedName>
+    <definedName function="false" hidden="true" localSheetId="6" name="_xlnm._FilterDatabase" vbProcedure="false">'Zielkunden – Register'!$B$5:$L$130</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -27,7 +28,7 @@
 </workbook>
 </file>
 
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <authors>
     <author>Unknown Author</author>
@@ -157,7 +158,7 @@
 </comments>
 </file>
 
-<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <authors>
     <author>Unknown Author</author>
@@ -311,7 +312,7 @@
 </comments>
 </file>
 
-<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <authors>
     <author>Unknown Author</author>
@@ -478,7 +479,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1576" uniqueCount="708">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1618" uniqueCount="749">
   <si>
     <t xml:space="preserve">RALK – Preise, Pläne &amp; Vertriebsmodell</t>
   </si>
@@ -561,10 +562,16 @@
     <t xml:space="preserve">1) Antworten = Zugestellt × Antwortquote (alte Datei zeigte −1.878). 2) Einheitlich USD statt €/$ gemischt; € nur über den Wechselkurs. 3) Kein Ø-Preis von 35 € mehr – jeder Vertrag wird mit der echten Staffel gerechnet.</t>
   </si>
   <si>
-    <t xml:space="preserve">Hinweis Preisstaffel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Der Satz gilt für ALLE Mitarbeitenden des Kunden. Dadurch zahlt eine Firma mit 4.001 MA (200.050 $) weniger als eine mit 4.000 MA (260.000 $). Siehe Blatt „Preise &amp; Pläne“ – ggf. Übergangsregel festlegen.</t>
+    <t xml:space="preserve">Preisstaffel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Der Satz gilt für alle Mitarbeitenden des Kunden. Übergangsregel: Wer in eine günstigere Klasse rutscht, zahlt nie weniger als die größte Organisation der Klasse darunter – kein Preissprung nach unten.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preispolitik</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feste, veröffentlichte Preisliste wie bei Google Workspace, Microsoft 365, Atlassian und KnowBe4: gleicher Preis für alle, Mengenrabatt steckt in den Klassen, keine Einzelrabatte. Siehe Blatt „Marktvergleich“.</t>
   </si>
   <si>
     <t xml:space="preserve">Beispiel-Eingabe</t>
@@ -573,6 +580,114 @@
     <t xml:space="preserve">← so sehen Eingabezellen aus</t>
   </si>
   <si>
+    <t xml:space="preserve">Marktvergleich – wie andere Lizenzanbieter Preise machen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stand Oktober 2026, Listenpreise laut öffentlichen Quellen (Drittanbieter-Übersichten, nicht von den Herstellern bestätigt).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anbieter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preismodell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Listenpreis pro Nutzer/Jahr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Was RALK übernimmt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google Workspace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pläne nach Funktionsumfang, gleicher Preis pro Nutzer für alle; Jahresvertrag günstiger als monatlich; Enterprise auf Anfrage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ca. 84–264 $ (7–22 $/Monat)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ein öffentlicher Preis für alle, keine Verhandlung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft 365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Business-Pläne für kleinere Firmen, Enterprise-Pläne (E3/E5) für große; Preis pro Nutzer, Jahresbindung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ca. 84–720 $ (7–60 $/Monat)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feste Preisliste; Preiserhöhungen mit Vorankündigung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Atlassian (Jira)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jahresabos in festen Nutzerstufen; jede Nutzerzahl innerhalb einer Stufe zahlt gleich viel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">stufenabhängig</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Übergangsregel an den Klassengrenzen statt Preissprung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KnowBe4 (Security-Awareness)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Staffelpreis pro Platz nach Mengenband, günstiger bei längerer Laufzeit; ab 1.001 Plätzen Angebot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ca. 20–45 $ (Liste, 3-Jahres-Vertrag)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mengenrabatt über Größenklassen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AML-/Compliance-E-Learning (UK u. a.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pro Kurs oder pro Nutzer, Mengenstaffel; große Anbieter (NAVEX, LRN, Thomson Reuters) nur auf Anfrage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ca. 8–13 $ pro Kurs bzw. 60–200 $ pro Plattform-Nutzer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RALK liegt mit 45–65 $ im Mittelfeld – für alle 13 Module</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Klassische Präsenzschulung (dein Modell)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Einmalig pro Person</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ca. 462 $ für 5 Tage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RALK: dauerhaft, nachweisbar, Bruchteil der Kosten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.cloudwards.net/google-workspace-plans-and-pricing/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://sanka.com/docs/migrate/tco/microsoft-365/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://community.atlassian.com/forums/discussion/3284604/jira-pricing-how-much-does-jira-cost-in-2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.knowbe4.com/products/security-awareness-training-quote</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://coggno.com/blog/compliance-training-pricing-2026/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.kyclookup.com/knowledgebase/best-aml-training-courses-uk/</t>
+  </si>
+  <si>
     <t xml:space="preserve">Preise &amp; Pläne – Jahreslizenz pro Mitarbeiter</t>
   </si>
   <si>
@@ -657,7 +772,7 @@
     <t xml:space="preserve">Listenpreis (MA × Satz)</t>
   </si>
   <si>
-    <t xml:space="preserve">Jahreslizenz (mind. Mindestlizenz)</t>
+    <t xml:space="preserve">Jahreslizenz (mit Mindestlizenz &amp; Übergangsregel)</t>
   </si>
   <si>
     <t xml:space="preserve">Jahreslizenz in €</t>
@@ -702,10 +817,16 @@
     <t xml:space="preserve">Klassengrenze</t>
   </si>
   <si>
-    <t xml:space="preserve">⚠ günstiger als 4.000 MA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">⚠ günstiger als 7.999 MA</t>
+    <t xml:space="preserve">Übergangsregel: wie 4.000 MA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ab hier normaler 50-$-Satz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Übergangsregel: wie 7.999 MA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ab hier normaler 45-$-Satz</t>
   </si>
   <si>
     <t xml:space="preserve">Verband</t>
@@ -714,7 +835,10 @@
     <t xml:space="preserve">z. B. Law Society of Kenya</t>
   </si>
   <si>
-    <t xml:space="preserve">⚠ Preissprung: Weil der Satz für alle Mitarbeitenden gilt, zahlt ein Kunde knapp über einer Klassengrenze insgesamt weniger als einer knapp darunter (4.000 MA = 260.000 $, 4.001 MA = 200.050 $). Möglicher Ausgleich: Jahreslizenz = MAX(eigene Klasse, Obergrenze der günstigeren Klasse × deren Satz) – das entscheidest du.</t>
+    <t xml:space="preserve">Übergangsregel (wie bei Atlassian-Stufen): Wer in eine günstigere Klasse rutscht, zahlt nie weniger als die größte Organisation der Klasse darunter. 4.001–5.200 MA zahlen also 260.000 $ (wie 4.000 MA), 8.000–8.888 MA zahlen 399.950 $ (wie 7.999 MA). Danach gilt der normale Satz. So gibt es keinen Preissprung nach unten.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feste Preisliste wie Google Workspace / Microsoft 365: gleicher Preis für alle, Mengenrabatt steckt in den Klassen, keine Einzelrabatte, keine Verhandlung.</t>
   </si>
   <si>
     <t xml:space="preserve">Leistungsumfang (in allen Klassen gleich)</t>
@@ -2685,6 +2809,14 @@
       <charset val="1"/>
     </font>
     <font>
+      <u val="single"/>
+      <sz val="11"/>
+      <color rgb="FF0563C1"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -2692,14 +2824,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF008000"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <u val="single"/>
-      <sz val="11"/>
-      <color rgb="FF0563C1"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -2780,7 +2904,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2811,6 +2935,10 @@
     </xf>
     <xf numFmtId="164" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
@@ -2849,6 +2977,10 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -2873,7 +3005,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2885,11 +3017,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="171" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="171" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -3182,7 +3314,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:C24"/>
+  <dimension ref="B2:C27"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
@@ -3322,12 +3454,20 @@
         <v>28</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="6" t="s">
+    <row r="22" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C22" s="4" t="s">
         <v>30</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -3346,7 +3486,184 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:G55"/>
+  <dimension ref="B2:E19"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="52"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="1" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B6" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B7" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B8" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E8" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B9" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B10" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B11" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="8" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="8" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="8" t="s">
+        <v>68</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="B14" r:id="rId1" display="https://www.cloudwards.net/google-workspace-plans-and-pricing/"/>
+    <hyperlink ref="B15" r:id="rId2" display="https://sanka.com/docs/migrate/tco/microsoft-365/"/>
+    <hyperlink ref="B16" r:id="rId3" display="https://community.atlassian.com/forums/discussion/3284604/jira-pricing-how-much-does-jira-cost-in-2026"/>
+    <hyperlink ref="B17" r:id="rId4" display="https://www.knowbe4.com/products/security-awareness-training-quote"/>
+    <hyperlink ref="B18" r:id="rId5" display="https://coggno.com/blog/compliance-training-pricing-2026/"/>
+    <hyperlink ref="B19" r:id="rId6" display="https://www.kyclookup.com/knowledgebase/best-aml-training-courses-uk/"/>
+  </hyperlinks>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B2:G58"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
@@ -3357,1179 +3674,708 @@
   <sheetData>
     <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
-        <v>32</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="7" t="s">
-        <v>33</v>
+        <v>71</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>34</v>
+        <v>72</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>35</v>
+        <v>73</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>36</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" s="8" t="n">
+        <v>75</v>
+      </c>
+      <c r="C6" s="9" t="n">
         <v>4000</v>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="D6" s="10" t="n">
         <v>65</v>
       </c>
-      <c r="E6" s="10" t="n">
+      <c r="E6" s="11" t="n">
         <f aca="false">D6*$C$12</f>
         <v>59.8</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C7" s="8" t="n">
+        <v>76</v>
+      </c>
+      <c r="C7" s="9" t="n">
         <v>7999</v>
       </c>
-      <c r="D7" s="9" t="n">
+      <c r="D7" s="10" t="n">
         <v>50</v>
       </c>
-      <c r="E7" s="10" t="n">
+      <c r="E7" s="11" t="n">
         <f aca="false">D7*$C$12</f>
         <v>46</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" s="8" t="n">
+        <v>77</v>
+      </c>
+      <c r="C8" s="9" t="n">
         <v>999999999</v>
       </c>
-      <c r="D8" s="9" t="n">
+      <c r="D8" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="E8" s="10" t="n">
+      <c r="E8" s="11" t="n">
         <f aca="false">D8*$C$12</f>
         <v>41.4</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="2" t="s">
-        <v>40</v>
+        <v>78</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="C11" s="9" t="n">
+        <v>79</v>
+      </c>
+      <c r="C11" s="10" t="n">
         <v>5000</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C12" s="11" t="n">
+        <v>80</v>
+      </c>
+      <c r="C12" s="12" t="n">
         <v>0.92</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="C13" s="9" t="n">
+        <v>81</v>
+      </c>
+      <c r="C13" s="10" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="5" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>45</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="5" t="s">
-        <v>46</v>
+        <v>84</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>47</v>
+        <v>85</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="3" t="s">
-        <v>48</v>
+        <v>86</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
+        <v>87</v>
+      </c>
+      <c r="C18" s="13" t="s">
+        <v>88</v>
+      </c>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
     </row>
     <row r="19" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B19" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>52</v>
-      </c>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
+        <v>89</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="D19" s="13"/>
+      <c r="E19" s="13"/>
+      <c r="F19" s="13"/>
+      <c r="G19" s="13"/>
     </row>
     <row r="20" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="D20" s="12"/>
-      <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12"/>
+        <v>91</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="D20" s="13"/>
+      <c r="E20" s="13"/>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="3" t="s">
-        <v>55</v>
+        <v>93</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C23" s="8" t="n">
+        <v>94</v>
+      </c>
+      <c r="C23" s="9" t="n">
         <v>400</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C24" s="13" t="n">
+        <v>95</v>
+      </c>
+      <c r="C24" s="14" t="n">
         <f aca="false">IF(C23&lt;=$C$6,$D$6,IF(C23&lt;=$C$7,$D$7,$D$8))</f>
         <v>65</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C25" s="13" t="n">
+        <v>96</v>
+      </c>
+      <c r="C25" s="14" t="n">
         <f aca="false">C23*C24</f>
         <v>26000</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C26" s="14" t="n">
-        <f aca="false">MAX(C25,$C$11)</f>
+        <v>97</v>
+      </c>
+      <c r="C26" s="15" t="n">
+        <f aca="false">MAX(C25,$C$11,IF(C23&gt;$C$6,$C$6*$D$6,0),IF(C23&gt;$C$7,$C$7*$D$7,0))</f>
         <v>26000</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C27" s="10" t="n">
+        <v>98</v>
+      </c>
+      <c r="C27" s="11" t="n">
         <f aca="false">C26*$C$12</f>
         <v>23920</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C28" s="15" t="n">
+        <v>99</v>
+      </c>
+      <c r="C28" s="16" t="n">
         <f aca="false">IF(C23&gt;0,C26/C23,0)</f>
         <v>65</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="3" t="s">
-        <v>62</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="7" t="s">
-        <v>63</v>
+        <v>101</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>64</v>
+        <v>102</v>
       </c>
       <c r="D31" s="7" t="s">
-        <v>65</v>
+        <v>103</v>
       </c>
       <c r="E31" s="7" t="s">
-        <v>66</v>
+        <v>104</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>67</v>
+        <v>105</v>
       </c>
       <c r="G31" s="7" t="s">
-        <v>68</v>
+        <v>106</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="8" t="n">
+      <c r="B32" s="9" t="n">
         <v>10</v>
       </c>
-      <c r="C32" s="13" t="n">
+      <c r="C32" s="14" t="n">
         <f aca="false">IF(B32&lt;=$C$6,$D$6,IF(B32&lt;=$C$7,$D$7,$D$8))</f>
         <v>65</v>
       </c>
-      <c r="D32" s="13" t="n">
-        <f aca="false">MAX(B32*C32,$C$11)</f>
+      <c r="D32" s="14" t="n">
+        <f aca="false">MAX(B32*C32,$C$11,IF(B32&gt;$C$6,$C$6*$D$6,0),IF(B32&gt;$C$7,$C$7*$D$7,0))</f>
         <v>5000</v>
       </c>
-      <c r="E32" s="10" t="n">
+      <c r="E32" s="11" t="n">
         <f aca="false">D32*$C$12</f>
         <v>4600</v>
       </c>
-      <c r="F32" s="15" t="n">
+      <c r="F32" s="16" t="n">
         <f aca="false">IF(B32&gt;0,D32/B32,0)</f>
         <v>500</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>69</v>
+        <v>107</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="8" t="n">
+      <c r="B33" s="9" t="n">
         <v>50</v>
       </c>
-      <c r="C33" s="13" t="n">
+      <c r="C33" s="14" t="n">
         <f aca="false">IF(B33&lt;=$C$6,$D$6,IF(B33&lt;=$C$7,$D$7,$D$8))</f>
         <v>65</v>
       </c>
-      <c r="D33" s="13" t="n">
-        <f aca="false">MAX(B33*C33,$C$11)</f>
+      <c r="D33" s="14" t="n">
+        <f aca="false">MAX(B33*C33,$C$11,IF(B33&gt;$C$6,$C$6*$D$6,0),IF(B33&gt;$C$7,$C$7*$D$7,0))</f>
         <v>5000</v>
       </c>
-      <c r="E33" s="10" t="n">
+      <c r="E33" s="11" t="n">
         <f aca="false">D33*$C$12</f>
         <v>4600</v>
       </c>
-      <c r="F33" s="15" t="n">
+      <c r="F33" s="16" t="n">
         <f aca="false">IF(B33&gt;0,D33/B33,0)</f>
         <v>100</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>69</v>
+        <v>107</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="8" t="n">
+      <c r="B34" s="9" t="n">
         <v>77</v>
       </c>
-      <c r="C34" s="13" t="n">
+      <c r="C34" s="14" t="n">
         <f aca="false">IF(B34&lt;=$C$6,$D$6,IF(B34&lt;=$C$7,$D$7,$D$8))</f>
         <v>65</v>
       </c>
-      <c r="D34" s="13" t="n">
-        <f aca="false">MAX(B34*C34,$C$11)</f>
+      <c r="D34" s="14" t="n">
+        <f aca="false">MAX(B34*C34,$C$11,IF(B34&gt;$C$6,$C$6*$D$6,0),IF(B34&gt;$C$7,$C$7*$D$7,0))</f>
         <v>5005</v>
       </c>
-      <c r="E34" s="10" t="n">
+      <c r="E34" s="11" t="n">
         <f aca="false">D34*$C$12</f>
         <v>4604.6</v>
       </c>
-      <c r="F34" s="15" t="n">
+      <c r="F34" s="16" t="n">
         <f aca="false">IF(B34&gt;0,D34/B34,0)</f>
         <v>65</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>70</v>
+        <v>108</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="8" t="n">
+      <c r="B35" s="9" t="n">
         <v>100</v>
       </c>
-      <c r="C35" s="13" t="n">
+      <c r="C35" s="14" t="n">
         <f aca="false">IF(B35&lt;=$C$6,$D$6,IF(B35&lt;=$C$7,$D$7,$D$8))</f>
         <v>65</v>
       </c>
-      <c r="D35" s="13" t="n">
-        <f aca="false">MAX(B35*C35,$C$11)</f>
+      <c r="D35" s="14" t="n">
+        <f aca="false">MAX(B35*C35,$C$11,IF(B35&gt;$C$6,$C$6*$D$6,0),IF(B35&gt;$C$7,$C$7*$D$7,0))</f>
         <v>6500</v>
       </c>
-      <c r="E35" s="10" t="n">
+      <c r="E35" s="11" t="n">
         <f aca="false">D35*$C$12</f>
         <v>5980</v>
       </c>
-      <c r="F35" s="15" t="n">
+      <c r="F35" s="16" t="n">
         <f aca="false">IF(B35&gt;0,D35/B35,0)</f>
         <v>65</v>
       </c>
       <c r="G35" s="2"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="8" t="n">
+      <c r="B36" s="9" t="n">
         <v>400</v>
       </c>
-      <c r="C36" s="13" t="n">
+      <c r="C36" s="14" t="n">
         <f aca="false">IF(B36&lt;=$C$6,$D$6,IF(B36&lt;=$C$7,$D$7,$D$8))</f>
         <v>65</v>
       </c>
-      <c r="D36" s="13" t="n">
-        <f aca="false">MAX(B36*C36,$C$11)</f>
+      <c r="D36" s="14" t="n">
+        <f aca="false">MAX(B36*C36,$C$11,IF(B36&gt;$C$6,$C$6*$D$6,0),IF(B36&gt;$C$7,$C$7*$D$7,0))</f>
         <v>26000</v>
       </c>
-      <c r="E36" s="10" t="n">
+      <c r="E36" s="11" t="n">
         <f aca="false">D36*$C$12</f>
         <v>23920</v>
       </c>
-      <c r="F36" s="15" t="n">
+      <c r="F36" s="16" t="n">
         <f aca="false">IF(B36&gt;0,D36/B36,0)</f>
         <v>65</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>71</v>
+        <v>109</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="8" t="n">
+      <c r="B37" s="9" t="n">
         <v>1000</v>
       </c>
-      <c r="C37" s="13" t="n">
+      <c r="C37" s="14" t="n">
         <f aca="false">IF(B37&lt;=$C$6,$D$6,IF(B37&lt;=$C$7,$D$7,$D$8))</f>
         <v>65</v>
       </c>
-      <c r="D37" s="13" t="n">
-        <f aca="false">MAX(B37*C37,$C$11)</f>
+      <c r="D37" s="14" t="n">
+        <f aca="false">MAX(B37*C37,$C$11,IF(B37&gt;$C$6,$C$6*$D$6,0),IF(B37&gt;$C$7,$C$7*$D$7,0))</f>
         <v>65000</v>
       </c>
-      <c r="E37" s="10" t="n">
+      <c r="E37" s="11" t="n">
         <f aca="false">D37*$C$12</f>
         <v>59800</v>
       </c>
-      <c r="F37" s="15" t="n">
+      <c r="F37" s="16" t="n">
         <f aca="false">IF(B37&gt;0,D37/B37,0)</f>
         <v>65</v>
       </c>
       <c r="G37" s="2"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B38" s="8" t="n">
+      <c r="B38" s="9" t="n">
         <v>3000</v>
       </c>
-      <c r="C38" s="13" t="n">
+      <c r="C38" s="14" t="n">
         <f aca="false">IF(B38&lt;=$C$6,$D$6,IF(B38&lt;=$C$7,$D$7,$D$8))</f>
         <v>65</v>
       </c>
-      <c r="D38" s="13" t="n">
-        <f aca="false">MAX(B38*C38,$C$11)</f>
+      <c r="D38" s="14" t="n">
+        <f aca="false">MAX(B38*C38,$C$11,IF(B38&gt;$C$6,$C$6*$D$6,0),IF(B38&gt;$C$7,$C$7*$D$7,0))</f>
         <v>195000</v>
       </c>
-      <c r="E38" s="10" t="n">
+      <c r="E38" s="11" t="n">
         <f aca="false">D38*$C$12</f>
         <v>179400</v>
       </c>
-      <c r="F38" s="15" t="n">
+      <c r="F38" s="16" t="n">
         <f aca="false">IF(B38&gt;0,D38/B38,0)</f>
         <v>65</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>72</v>
+        <v>110</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="8" t="n">
+      <c r="B39" s="9" t="n">
         <v>4000</v>
       </c>
-      <c r="C39" s="13" t="n">
+      <c r="C39" s="14" t="n">
         <f aca="false">IF(B39&lt;=$C$6,$D$6,IF(B39&lt;=$C$7,$D$7,$D$8))</f>
         <v>65</v>
       </c>
-      <c r="D39" s="13" t="n">
-        <f aca="false">MAX(B39*C39,$C$11)</f>
+      <c r="D39" s="14" t="n">
+        <f aca="false">MAX(B39*C39,$C$11,IF(B39&gt;$C$6,$C$6*$D$6,0),IF(B39&gt;$C$7,$C$7*$D$7,0))</f>
         <v>260000</v>
       </c>
-      <c r="E39" s="10" t="n">
+      <c r="E39" s="11" t="n">
         <f aca="false">D39*$C$12</f>
         <v>239200</v>
       </c>
-      <c r="F39" s="15" t="n">
+      <c r="F39" s="16" t="n">
         <f aca="false">IF(B39&gt;0,D39/B39,0)</f>
         <v>65</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>73</v>
+        <v>111</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="8" t="n">
+      <c r="B40" s="9" t="n">
         <v>4001</v>
       </c>
-      <c r="C40" s="13" t="n">
+      <c r="C40" s="14" t="n">
         <f aca="false">IF(B40&lt;=$C$6,$D$6,IF(B40&lt;=$C$7,$D$7,$D$8))</f>
         <v>50</v>
       </c>
-      <c r="D40" s="13" t="n">
-        <f aca="false">MAX(B40*C40,$C$11)</f>
-        <v>200050</v>
-      </c>
-      <c r="E40" s="10" t="n">
+      <c r="D40" s="14" t="n">
+        <f aca="false">MAX(B40*C40,$C$11,IF(B40&gt;$C$6,$C$6*$D$6,0),IF(B40&gt;$C$7,$C$7*$D$7,0))</f>
+        <v>260000</v>
+      </c>
+      <c r="E40" s="11" t="n">
         <f aca="false">D40*$C$12</f>
-        <v>184046</v>
-      </c>
-      <c r="F40" s="15" t="n">
+        <v>239200</v>
+      </c>
+      <c r="F40" s="16" t="n">
         <f aca="false">IF(B40&gt;0,D40/B40,0)</f>
-        <v>50</v>
+        <v>64.9837540614846</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>74</v>
+        <v>112</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="8" t="n">
-        <v>7999</v>
-      </c>
-      <c r="C41" s="13" t="n">
+      <c r="B41" s="9" t="n">
+        <v>5200</v>
+      </c>
+      <c r="C41" s="14" t="n">
         <f aca="false">IF(B41&lt;=$C$6,$D$6,IF(B41&lt;=$C$7,$D$7,$D$8))</f>
         <v>50</v>
       </c>
-      <c r="D41" s="13" t="n">
-        <f aca="false">MAX(B41*C41,$C$11)</f>
-        <v>399950</v>
-      </c>
-      <c r="E41" s="10" t="n">
+      <c r="D41" s="14" t="n">
+        <f aca="false">MAX(B41*C41,$C$11,IF(B41&gt;$C$6,$C$6*$D$6,0),IF(B41&gt;$C$7,$C$7*$D$7,0))</f>
+        <v>260000</v>
+      </c>
+      <c r="E41" s="11" t="n">
         <f aca="false">D41*$C$12</f>
-        <v>367954</v>
-      </c>
-      <c r="F41" s="15" t="n">
+        <v>239200</v>
+      </c>
+      <c r="F41" s="16" t="n">
         <f aca="false">IF(B41&gt;0,D41/B41,0)</f>
         <v>50</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>73</v>
+        <v>113</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="8" t="n">
+      <c r="B42" s="9" t="n">
+        <v>7999</v>
+      </c>
+      <c r="C42" s="14" t="n">
+        <f aca="false">IF(B42&lt;=$C$6,$D$6,IF(B42&lt;=$C$7,$D$7,$D$8))</f>
+        <v>50</v>
+      </c>
+      <c r="D42" s="14" t="n">
+        <f aca="false">MAX(B42*C42,$C$11,IF(B42&gt;$C$6,$C$6*$D$6,0),IF(B42&gt;$C$7,$C$7*$D$7,0))</f>
+        <v>399950</v>
+      </c>
+      <c r="E42" s="11" t="n">
+        <f aca="false">D42*$C$12</f>
+        <v>367954</v>
+      </c>
+      <c r="F42" s="16" t="n">
+        <f aca="false">IF(B42&gt;0,D42/B42,0)</f>
+        <v>50</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B43" s="9" t="n">
         <v>8000</v>
       </c>
-      <c r="C42" s="13" t="n">
-        <f aca="false">IF(B42&lt;=$C$6,$D$6,IF(B42&lt;=$C$7,$D$7,$D$8))</f>
-        <v>45</v>
-      </c>
-      <c r="D42" s="13" t="n">
-        <f aca="false">MAX(B42*C42,$C$11)</f>
-        <v>360000</v>
-      </c>
-      <c r="E42" s="10" t="n">
-        <f aca="false">D42*$C$12</f>
-        <v>331200</v>
-      </c>
-      <c r="F42" s="15" t="n">
-        <f aca="false">IF(B42&gt;0,D42/B42,0)</f>
-        <v>45</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="8" t="n">
-        <v>15000</v>
-      </c>
-      <c r="C43" s="13" t="n">
+      <c r="C43" s="14" t="n">
         <f aca="false">IF(B43&lt;=$C$6,$D$6,IF(B43&lt;=$C$7,$D$7,$D$8))</f>
         <v>45</v>
       </c>
-      <c r="D43" s="13" t="n">
-        <f aca="false">MAX(B43*C43,$C$11)</f>
-        <v>675000</v>
-      </c>
-      <c r="E43" s="10" t="n">
+      <c r="D43" s="14" t="n">
+        <f aca="false">MAX(B43*C43,$C$11,IF(B43&gt;$C$6,$C$6*$D$6,0),IF(B43&gt;$C$7,$C$7*$D$7,0))</f>
+        <v>399950</v>
+      </c>
+      <c r="E43" s="11" t="n">
         <f aca="false">D43*$C$12</f>
-        <v>621000</v>
-      </c>
-      <c r="F43" s="15" t="n">
+        <v>367954</v>
+      </c>
+      <c r="F43" s="16" t="n">
         <f aca="false">IF(B43&gt;0,D43/B43,0)</f>
-        <v>45</v>
+        <v>49.99375</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>76</v>
+        <v>114</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="8" t="n">
-        <v>30000</v>
-      </c>
-      <c r="C44" s="13" t="n">
+      <c r="B44" s="9" t="n">
+        <v>8889</v>
+      </c>
+      <c r="C44" s="14" t="n">
         <f aca="false">IF(B44&lt;=$C$6,$D$6,IF(B44&lt;=$C$7,$D$7,$D$8))</f>
         <v>45</v>
       </c>
-      <c r="D44" s="13" t="n">
-        <f aca="false">MAX(B44*C44,$C$11)</f>
-        <v>1350000</v>
-      </c>
-      <c r="E44" s="10" t="n">
+      <c r="D44" s="14" t="n">
+        <f aca="false">MAX(B44*C44,$C$11,IF(B44&gt;$C$6,$C$6*$D$6,0),IF(B44&gt;$C$7,$C$7*$D$7,0))</f>
+        <v>400005</v>
+      </c>
+      <c r="E44" s="11" t="n">
         <f aca="false">D44*$C$12</f>
-        <v>1242000</v>
-      </c>
-      <c r="F44" s="15" t="n">
+        <v>368004.6</v>
+      </c>
+      <c r="F44" s="16" t="n">
         <f aca="false">IF(B44&gt;0,D44/B44,0)</f>
         <v>45</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B46" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="C46" s="16"/>
-      <c r="D46" s="16"/>
-      <c r="E46" s="16"/>
-      <c r="F46" s="16"/>
-      <c r="G46" s="16"/>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="3" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B49" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="C49" s="17"/>
-      <c r="D49" s="17"/>
-      <c r="E49" s="17"/>
-      <c r="F49" s="17"/>
-      <c r="G49" s="17"/>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B50" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="C50" s="17"/>
-      <c r="D50" s="17"/>
-      <c r="E50" s="17"/>
-      <c r="F50" s="17"/>
-      <c r="G50" s="17"/>
+        <v>115</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B45" s="9" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C45" s="14" t="n">
+        <f aca="false">IF(B45&lt;=$C$6,$D$6,IF(B45&lt;=$C$7,$D$7,$D$8))</f>
+        <v>45</v>
+      </c>
+      <c r="D45" s="14" t="n">
+        <f aca="false">MAX(B45*C45,$C$11,IF(B45&gt;$C$6,$C$6*$D$6,0),IF(B45&gt;$C$7,$C$7*$D$7,0))</f>
+        <v>675000</v>
+      </c>
+      <c r="E45" s="11" t="n">
+        <f aca="false">D45*$C$12</f>
+        <v>621000</v>
+      </c>
+      <c r="F45" s="16" t="n">
+        <f aca="false">IF(B45&gt;0,D45/B45,0)</f>
+        <v>45</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B46" s="9" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C46" s="14" t="n">
+        <f aca="false">IF(B46&lt;=$C$6,$D$6,IF(B46&lt;=$C$7,$D$7,$D$8))</f>
+        <v>45</v>
+      </c>
+      <c r="D46" s="14" t="n">
+        <f aca="false">MAX(B46*C46,$C$11,IF(B46&gt;$C$6,$C$6*$D$6,0),IF(B46&gt;$C$7,$C$7*$D$7,0))</f>
+        <v>1350000</v>
+      </c>
+      <c r="E46" s="11" t="n">
+        <f aca="false">D46*$C$12</f>
+        <v>1242000</v>
+      </c>
+      <c r="F46" s="16" t="n">
+        <f aca="false">IF(B46&gt;0,D46/B46,0)</f>
+        <v>45</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B48" s="17" t="s">
+        <v>118</v>
+      </c>
+      <c r="C48" s="17"/>
+      <c r="D48" s="17"/>
+      <c r="E48" s="17"/>
+      <c r="F48" s="17"/>
+      <c r="G48" s="17"/>
+    </row>
+    <row r="49" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B49" s="18" t="s">
+        <v>119</v>
+      </c>
+      <c r="C49" s="18"/>
+      <c r="D49" s="18"/>
+      <c r="E49" s="18"/>
+      <c r="F49" s="18"/>
+      <c r="G49" s="18"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B51" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="C51" s="17"/>
-      <c r="D51" s="17"/>
-      <c r="E51" s="17"/>
-      <c r="F51" s="17"/>
-      <c r="G51" s="17"/>
+      <c r="B51" s="3" t="s">
+        <v>120</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B52" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="C52" s="17"/>
-      <c r="D52" s="17"/>
-      <c r="E52" s="17"/>
-      <c r="F52" s="17"/>
-      <c r="G52" s="17"/>
+      <c r="B52" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="C52" s="19"/>
+      <c r="D52" s="19"/>
+      <c r="E52" s="19"/>
+      <c r="F52" s="19"/>
+      <c r="G52" s="19"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B53" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="C53" s="17"/>
-      <c r="D53" s="17"/>
-      <c r="E53" s="17"/>
-      <c r="F53" s="17"/>
-      <c r="G53" s="17"/>
+      <c r="B53" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="C53" s="19"/>
+      <c r="D53" s="19"/>
+      <c r="E53" s="19"/>
+      <c r="F53" s="19"/>
+      <c r="G53" s="19"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B54" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="C54" s="17"/>
-      <c r="D54" s="17"/>
-      <c r="E54" s="17"/>
-      <c r="F54" s="17"/>
-      <c r="G54" s="17"/>
+      <c r="B54" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="C54" s="19"/>
+      <c r="D54" s="19"/>
+      <c r="E54" s="19"/>
+      <c r="F54" s="19"/>
+      <c r="G54" s="19"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B55" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="C55" s="17"/>
-      <c r="D55" s="17"/>
-      <c r="E55" s="17"/>
-      <c r="F55" s="17"/>
-      <c r="G55" s="17"/>
+      <c r="B55" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="C55" s="19"/>
+      <c r="D55" s="19"/>
+      <c r="E55" s="19"/>
+      <c r="F55" s="19"/>
+      <c r="G55" s="19"/>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B56" s="19" t="s">
+        <v>125</v>
+      </c>
+      <c r="C56" s="19"/>
+      <c r="D56" s="19"/>
+      <c r="E56" s="19"/>
+      <c r="F56" s="19"/>
+      <c r="G56" s="19"/>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B57" s="19" t="s">
+        <v>126</v>
+      </c>
+      <c r="C57" s="19"/>
+      <c r="D57" s="19"/>
+      <c r="E57" s="19"/>
+      <c r="F57" s="19"/>
+      <c r="G57" s="19"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B58" s="19" t="s">
+        <v>127</v>
+      </c>
+      <c r="C58" s="19"/>
+      <c r="D58" s="19"/>
+      <c r="E58" s="19"/>
+      <c r="F58" s="19"/>
+      <c r="G58" s="19"/>
     </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="12">
     <mergeCell ref="C18:G18"/>
     <mergeCell ref="C19:G19"/>
     <mergeCell ref="C20:G20"/>
-    <mergeCell ref="B46:G46"/>
+    <mergeCell ref="B48:G48"/>
     <mergeCell ref="B49:G49"/>
-    <mergeCell ref="B50:G50"/>
-    <mergeCell ref="B51:G51"/>
     <mergeCell ref="B52:G52"/>
     <mergeCell ref="B53:G53"/>
     <mergeCell ref="B54:G54"/>
     <mergeCell ref="B55:G55"/>
+    <mergeCell ref="B56:G56"/>
+    <mergeCell ref="B57:G57"/>
+    <mergeCell ref="B58:G58"/>
   </mergeCells>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <legacyDrawing r:id="rId2"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="B2:G43"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="40"/>
-  </cols>
-  <sheetData>
-    <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="1" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="2" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="3" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B6" s="5" t="s">
-        <v>90</v>
-      </c>
-      <c r="C6" s="8" t="n">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="C7" s="8" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="5" t="s">
-        <v>92</v>
-      </c>
-      <c r="C8" s="18" t="n">
-        <f aca="false">C6-C7</f>
-        <v>307</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="5" t="s">
-        <v>93</v>
-      </c>
-      <c r="C9" s="19" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="5" t="s">
-        <v>94</v>
-      </c>
-      <c r="C10" s="20" t="n">
-        <f aca="false">C8*C9</f>
-        <v>30.7</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="5" t="s">
-        <v>95</v>
-      </c>
-      <c r="C11" s="19" t="n">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="C12" s="21" t="n">
-        <f aca="false">C10*C11</f>
-        <v>9.21</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="5" t="s">
-        <v>97</v>
-      </c>
-      <c r="C13" s="8" t="n">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="3" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="5" t="s">
-        <v>99</v>
-      </c>
-      <c r="C16" s="22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="C17" s="8" t="n">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="C18" s="23" t="n">
-        <f aca="false">MAX(C17*IF(C17&lt;='Preise &amp; Pläne'!$C$6,'Preise &amp; Pläne'!$D$6,IF(C17&lt;='Preise &amp; Pläne'!$C$7,'Preise &amp; Pläne'!$D$7,'Preise &amp; Pläne'!$D$8)),'Preise &amp; Pläne'!$C$11)</f>
-        <v>26000</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="C19" s="19" t="n">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="C20" s="19" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="5" t="s">
-        <v>104</v>
-      </c>
-      <c r="C21" s="19" t="n">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="C22" s="24" t="n">
-        <v>1.5</v>
-      </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="C23" s="9" t="n">
-        <v>6130</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="C25" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="C26" s="20" t="n">
-        <f aca="false">$C$12*$C$16</f>
-        <v>9.21</v>
-      </c>
-      <c r="D26" s="20" t="n">
-        <f aca="false">$C$12*$C$16</f>
-        <v>9.21</v>
-      </c>
-      <c r="E26" s="20" t="n">
-        <f aca="false">$C$12*$C$16</f>
-        <v>9.21</v>
-      </c>
-      <c r="F26" s="20" t="n">
-        <f aca="false">$C$12*$C$16</f>
-        <v>9.21</v>
-      </c>
-      <c r="G26" s="20" t="n">
-        <f aca="false">$C$12*$C$16</f>
-        <v>9.21</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="5" t="s">
-        <v>114</v>
-      </c>
-      <c r="C27" s="20" t="n">
-        <f aca="false">C26+C28</f>
-        <v>9.21</v>
-      </c>
-      <c r="D27" s="20" t="n">
-        <f aca="false">D26+D28</f>
-        <v>17.0385</v>
-      </c>
-      <c r="E27" s="20" t="n">
-        <f aca="false">E26+E28</f>
-        <v>23.692725</v>
-      </c>
-      <c r="F27" s="20" t="n">
-        <f aca="false">F26+F28</f>
-        <v>29.34881625</v>
-      </c>
-      <c r="G27" s="20" t="n">
-        <f aca="false">G26+G28</f>
-        <v>34.1564938125</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="C28" s="20" t="n">
-        <f aca="false">0</f>
-        <v>0</v>
-      </c>
-      <c r="D28" s="20" t="n">
-        <f aca="false">C27*$C$19</f>
-        <v>7.8285</v>
-      </c>
-      <c r="E28" s="20" t="n">
-        <f aca="false">D27*$C$19</f>
-        <v>14.482725</v>
-      </c>
-      <c r="F28" s="20" t="n">
-        <f aca="false">E27*$C$19</f>
-        <v>20.13881625</v>
-      </c>
-      <c r="G28" s="20" t="n">
-        <f aca="false">F27*$C$19</f>
-        <v>24.9464938125</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="C29" s="18" t="n">
-        <f aca="false">C27*$C$17</f>
-        <v>3684</v>
-      </c>
-      <c r="D29" s="18" t="n">
-        <f aca="false">D27*$C$17</f>
-        <v>6815.4</v>
-      </c>
-      <c r="E29" s="18" t="n">
-        <f aca="false">E27*$C$17</f>
-        <v>9477.09</v>
-      </c>
-      <c r="F29" s="18" t="n">
-        <f aca="false">F27*$C$17</f>
-        <v>11739.5265</v>
-      </c>
-      <c r="G29" s="18" t="n">
-        <f aca="false">G27*$C$17</f>
-        <v>13662.597525</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C30" s="13" t="n">
-        <f aca="false">C26*$C$18</f>
-        <v>239460</v>
-      </c>
-      <c r="D30" s="13" t="n">
-        <f aca="false">D26*$C$18</f>
-        <v>239460</v>
-      </c>
-      <c r="E30" s="13" t="n">
-        <f aca="false">E26*$C$18</f>
-        <v>239460</v>
-      </c>
-      <c r="F30" s="13" t="n">
-        <f aca="false">F26*$C$18</f>
-        <v>239460</v>
-      </c>
-      <c r="G30" s="13" t="n">
-        <f aca="false">G26*$C$18</f>
-        <v>239460</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="C31" s="13" t="n">
-        <f aca="false">C28*$C$18</f>
-        <v>0</v>
-      </c>
-      <c r="D31" s="13" t="n">
-        <f aca="false">D28*$C$18</f>
-        <v>203541</v>
-      </c>
-      <c r="E31" s="13" t="n">
-        <f aca="false">E28*$C$18</f>
-        <v>376550.85</v>
-      </c>
-      <c r="F31" s="13" t="n">
-        <f aca="false">F28*$C$18</f>
-        <v>523609.2225</v>
-      </c>
-      <c r="G31" s="13" t="n">
-        <f aca="false">G28*$C$18</f>
-        <v>648608.839125</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="C32" s="14" t="n">
-        <f aca="false">C30+C31</f>
-        <v>239460</v>
-      </c>
-      <c r="D32" s="14" t="n">
-        <f aca="false">D30+D31</f>
-        <v>443001</v>
-      </c>
-      <c r="E32" s="14" t="n">
-        <f aca="false">E30+E31</f>
-        <v>616010.85</v>
-      </c>
-      <c r="F32" s="14" t="n">
-        <f aca="false">F30+F31</f>
-        <v>763069.2225</v>
-      </c>
-      <c r="G32" s="14" t="n">
-        <f aca="false">G30+G31</f>
-        <v>888068.839125</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="C33" s="13" t="n">
-        <f aca="false">-(C30*$C$20+C31*$C$21)</f>
-        <v>-23946</v>
-      </c>
-      <c r="D33" s="13" t="n">
-        <f aca="false">-(D30*$C$20+D31*$C$21)</f>
-        <v>-34123.05</v>
-      </c>
-      <c r="E33" s="13" t="n">
-        <f aca="false">-(E30*$C$20+E31*$C$21)</f>
-        <v>-42773.5425</v>
-      </c>
-      <c r="F33" s="13" t="n">
-        <f aca="false">-(F30*$C$20+F31*$C$21)</f>
-        <v>-50126.461125</v>
-      </c>
-      <c r="G33" s="13" t="n">
-        <f aca="false">-(G30*$C$20+G31*$C$21)</f>
-        <v>-56376.44195625</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="C34" s="13" t="n">
-        <f aca="false">-C29*$C$22</f>
-        <v>-5526</v>
-      </c>
-      <c r="D34" s="13" t="n">
-        <f aca="false">-D29*$C$22</f>
-        <v>-10223.1</v>
-      </c>
-      <c r="E34" s="13" t="n">
-        <f aca="false">-E29*$C$22</f>
-        <v>-14215.635</v>
-      </c>
-      <c r="F34" s="13" t="n">
-        <f aca="false">-F29*$C$22</f>
-        <v>-17609.28975</v>
-      </c>
-      <c r="G34" s="13" t="n">
-        <f aca="false">-G29*$C$22</f>
-        <v>-20493.8962875</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="C35" s="13" t="n">
-        <f aca="false">-$C$23</f>
-        <v>-6130</v>
-      </c>
-      <c r="D35" s="13" t="n">
-        <f aca="false">-$C$23</f>
-        <v>-6130</v>
-      </c>
-      <c r="E35" s="13" t="n">
-        <f aca="false">-$C$23</f>
-        <v>-6130</v>
-      </c>
-      <c r="F35" s="13" t="n">
-        <f aca="false">-$C$23</f>
-        <v>-6130</v>
-      </c>
-      <c r="G35" s="13" t="n">
-        <f aca="false">-$C$23</f>
-        <v>-6130</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="C36" s="14" t="n">
-        <f aca="false">SUM(C32:C35)</f>
-        <v>203858</v>
-      </c>
-      <c r="D36" s="14" t="n">
-        <f aca="false">SUM(D32:D35)</f>
-        <v>392524.85</v>
-      </c>
-      <c r="E36" s="14" t="n">
-        <f aca="false">SUM(E32:E35)</f>
-        <v>552891.6725</v>
-      </c>
-      <c r="F36" s="14" t="n">
-        <f aca="false">SUM(F32:F35)</f>
-        <v>689203.471625</v>
-      </c>
-      <c r="G36" s="14" t="n">
-        <f aca="false">SUM(G32:G35)</f>
-        <v>805068.50088125</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="C37" s="25" t="n">
-        <f aca="false">IF(C32&lt;&gt;0,C36/C32,0)</f>
-        <v>0.851323811910131</v>
-      </c>
-      <c r="D37" s="25" t="n">
-        <f aca="false">IF(D32&lt;&gt;0,D36/D32,0)</f>
-        <v>0.886058609348512</v>
-      </c>
-      <c r="E37" s="25" t="n">
-        <f aca="false">IF(E32&lt;&gt;0,E36/E32,0)</f>
-        <v>0.89753560753029</v>
-      </c>
-      <c r="F37" s="25" t="n">
-        <f aca="false">IF(F32&lt;&gt;0,F36/F32,0)</f>
-        <v>0.90319914799735</v>
-      </c>
-      <c r="G37" s="25" t="n">
-        <f aca="false">IF(G32&lt;&gt;0,G36/G32,0)</f>
-        <v>0.906538395913622</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="C39" s="14" t="n">
-        <f aca="false">SUM(C32:G32)</f>
-        <v>2949609.911625</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="C40" s="13" t="n">
-        <f aca="false">SUM(C33:G33)</f>
-        <v>-207345.49558125</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="C41" s="14" t="n">
-        <f aca="false">SUM(C36:G36)</f>
-        <v>2643546.49500625</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="2" t="s">
-        <v>128</v>
-      </c>
-    </row>
-  </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -4557,473 +4403,506 @@
   <sheetData>
     <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="C6" s="8" t="n">
-        <v>600</v>
+        <v>131</v>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>313</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="C7" s="19" t="n">
-        <v>0.05</v>
+        <v>132</v>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="5" t="s">
-        <v>134</v>
-      </c>
-      <c r="C8" s="19" t="n">
-        <v>0.15</v>
+        <v>133</v>
+      </c>
+      <c r="C8" s="20" t="n">
+        <f aca="false">C6-C7</f>
+        <v>307</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="5" t="s">
-        <v>135</v>
-      </c>
-      <c r="C9" s="20" t="n">
-        <f aca="false">C6*C7*C8</f>
-        <v>4.5</v>
+        <v>134</v>
+      </c>
+      <c r="C9" s="21" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="C10" s="9" t="n">
-        <v>6000</v>
+        <v>135</v>
+      </c>
+      <c r="C10" s="22" t="n">
+        <f aca="false">C8*C9</f>
+        <v>30.7</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="5" t="s">
-        <v>137</v>
-      </c>
-      <c r="C11" s="9" t="n">
-        <v>40</v>
+        <v>136</v>
+      </c>
+      <c r="C11" s="21" t="n">
+        <v>0.3</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="5" t="s">
-        <v>138</v>
-      </c>
-      <c r="C12" s="19" t="n">
-        <v>0.05</v>
+        <v>137</v>
+      </c>
+      <c r="C12" s="23" t="n">
+        <f aca="false">C10*C11</f>
+        <v>9.21</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="3" t="s">
         <v>139</v>
-      </c>
-      <c r="C13" s="20" t="n">
-        <f aca="false">IF(C11&gt;0,C10/C11*C12,0)</f>
-        <v>7.5</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="5" t="s">
-        <v>140</v>
-      </c>
-      <c r="C14" s="8" t="n">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="C15" s="19" t="n">
-        <v>0.1</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="5" t="s">
-        <v>142</v>
-      </c>
-      <c r="C16" s="20" t="n">
-        <f aca="false">C14*C15</f>
-        <v>6</v>
+        <v>140</v>
+      </c>
+      <c r="C16" s="24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="5" t="s">
-        <v>143</v>
-      </c>
-      <c r="C17" s="21" t="n">
-        <f aca="false">C9+C13+C16</f>
-        <v>18</v>
+        <v>141</v>
+      </c>
+      <c r="C17" s="9" t="n">
+        <v>400</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="C18" s="25" t="n">
+        <f aca="false">MAX(C17*IF(C17&lt;='Preise &amp; Pläne'!$C$6,'Preise &amp; Pläne'!$D$6,IF(C17&lt;='Preise &amp; Pläne'!$C$7,'Preise &amp; Pläne'!$D$7,'Preise &amp; Pläne'!$D$8)),'Preise &amp; Pläne'!$C$11,IF(C17&gt;'Preise &amp; Pläne'!$C$6,'Preise &amp; Pläne'!$C$6*'Preise &amp; Pläne'!$D$6,0),IF(C17&gt;'Preise &amp; Pläne'!$C$7,'Preise &amp; Pläne'!$C$7*'Preise &amp; Pläne'!$D$7,0))</f>
+        <v>26000</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B19" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="C19" s="21" t="n">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="C18" s="19" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="3" t="s">
-        <v>98</v>
+      <c r="C20" s="21" t="n">
+        <v>0.1</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="5" t="s">
-        <v>100</v>
-      </c>
-      <c r="C21" s="8" t="n">
-        <v>150</v>
+        <v>145</v>
+      </c>
+      <c r="C21" s="21" t="n">
+        <v>0.05</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="5" t="s">
-        <v>101</v>
-      </c>
-      <c r="C22" s="23" t="n">
-        <f aca="false">MAX(C21*IF(C21&lt;='Preise &amp; Pläne'!$C$6,'Preise &amp; Pläne'!$D$6,IF(C21&lt;='Preise &amp; Pläne'!$C$7,'Preise &amp; Pläne'!$D$7,'Preise &amp; Pläne'!$D$8)),'Preise &amp; Pläne'!$C$11)</f>
-        <v>9750</v>
+        <v>146</v>
+      </c>
+      <c r="C22" s="26" t="n">
+        <v>1.5</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="C23" s="19" t="n">
-        <v>0.85</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="5" t="s">
-        <v>105</v>
-      </c>
-      <c r="C24" s="24" t="n">
-        <v>3</v>
+        <v>147</v>
+      </c>
+      <c r="C23" s="10" t="n">
+        <v>6130</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="C25" s="9" t="n">
-        <v>6130</v>
+      <c r="B25" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="F25" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G25" s="7" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B26" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C26" s="22" t="n">
+        <f aca="false">$C$12*$C$16</f>
+        <v>9.21</v>
+      </c>
+      <c r="D26" s="22" t="n">
+        <f aca="false">$C$12*$C$16</f>
+        <v>9.21</v>
+      </c>
+      <c r="E26" s="22" t="n">
+        <f aca="false">$C$12*$C$16</f>
+        <v>9.21</v>
+      </c>
+      <c r="F26" s="22" t="n">
+        <f aca="false">$C$12*$C$16</f>
+        <v>9.21</v>
+      </c>
+      <c r="G26" s="22" t="n">
+        <f aca="false">$C$12*$C$16</f>
+        <v>9.21</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="C27" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="D27" s="7" t="s">
-        <v>109</v>
-      </c>
-      <c r="E27" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>112</v>
+      <c r="B27" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="C27" s="22" t="n">
+        <f aca="false">C26+C28</f>
+        <v>9.21</v>
+      </c>
+      <c r="D27" s="22" t="n">
+        <f aca="false">D26+D28</f>
+        <v>17.0385</v>
+      </c>
+      <c r="E27" s="22" t="n">
+        <f aca="false">E26+E28</f>
+        <v>23.692725</v>
+      </c>
+      <c r="F27" s="22" t="n">
+        <f aca="false">F26+F28</f>
+        <v>29.34881625</v>
+      </c>
+      <c r="G27" s="22" t="n">
+        <f aca="false">G26+G28</f>
+        <v>34.1564938125</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="5" t="s">
-        <v>113</v>
-      </c>
-      <c r="C28" s="20" t="n">
-        <f aca="false">$C$17*(1+$C$18)^0</f>
-        <v>18</v>
-      </c>
-      <c r="D28" s="20" t="n">
-        <f aca="false">$C$17*(1+$C$18)^1</f>
-        <v>21.6</v>
-      </c>
-      <c r="E28" s="20" t="n">
-        <f aca="false">$C$17*(1+$C$18)^2</f>
-        <v>25.92</v>
-      </c>
-      <c r="F28" s="20" t="n">
-        <f aca="false">$C$17*(1+$C$18)^3</f>
-        <v>31.104</v>
-      </c>
-      <c r="G28" s="20" t="n">
-        <f aca="false">$C$17*(1+$C$18)^4</f>
-        <v>37.3248</v>
+        <v>156</v>
+      </c>
+      <c r="C28" s="22" t="n">
+        <f aca="false">0</f>
+        <v>0</v>
+      </c>
+      <c r="D28" s="22" t="n">
+        <f aca="false">C27*$C$19</f>
+        <v>7.8285</v>
+      </c>
+      <c r="E28" s="22" t="n">
+        <f aca="false">D27*$C$19</f>
+        <v>14.482725</v>
+      </c>
+      <c r="F28" s="22" t="n">
+        <f aca="false">E27*$C$19</f>
+        <v>20.13881625</v>
+      </c>
+      <c r="G28" s="22" t="n">
+        <f aca="false">F27*$C$19</f>
+        <v>24.9464938125</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="5" t="s">
-        <v>114</v>
+        <v>157</v>
       </c>
       <c r="C29" s="20" t="n">
-        <f aca="false">C28+C30</f>
-        <v>18</v>
+        <f aca="false">C27*$C$17</f>
+        <v>3684</v>
       </c>
       <c r="D29" s="20" t="n">
-        <f aca="false">D28+D30</f>
-        <v>36.9</v>
+        <f aca="false">D27*$C$17</f>
+        <v>6815.4</v>
       </c>
       <c r="E29" s="20" t="n">
-        <f aca="false">E28+E30</f>
-        <v>57.285</v>
+        <f aca="false">E27*$C$17</f>
+        <v>9477.09</v>
       </c>
       <c r="F29" s="20" t="n">
-        <f aca="false">F28+F30</f>
-        <v>79.79625</v>
+        <f aca="false">F27*$C$17</f>
+        <v>11739.5265</v>
       </c>
       <c r="G29" s="20" t="n">
-        <f aca="false">G28+G30</f>
-        <v>105.1516125</v>
+        <f aca="false">G27*$C$17</f>
+        <v>13662.597525</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="5" t="s">
-        <v>115</v>
-      </c>
-      <c r="C30" s="20" t="n">
-        <f aca="false">0</f>
-        <v>0</v>
-      </c>
-      <c r="D30" s="20" t="n">
-        <f aca="false">C29*$C$23</f>
-        <v>15.3</v>
-      </c>
-      <c r="E30" s="20" t="n">
-        <f aca="false">D29*$C$23</f>
-        <v>31.365</v>
-      </c>
-      <c r="F30" s="20" t="n">
-        <f aca="false">E29*$C$23</f>
-        <v>48.69225</v>
-      </c>
-      <c r="G30" s="20" t="n">
-        <f aca="false">F29*$C$23</f>
-        <v>67.8268125</v>
+        <v>158</v>
+      </c>
+      <c r="C30" s="14" t="n">
+        <f aca="false">C26*$C$18</f>
+        <v>239460</v>
+      </c>
+      <c r="D30" s="14" t="n">
+        <f aca="false">D26*$C$18</f>
+        <v>239460</v>
+      </c>
+      <c r="E30" s="14" t="n">
+        <f aca="false">E26*$C$18</f>
+        <v>239460</v>
+      </c>
+      <c r="F30" s="14" t="n">
+        <f aca="false">F26*$C$18</f>
+        <v>239460</v>
+      </c>
+      <c r="G30" s="14" t="n">
+        <f aca="false">G26*$C$18</f>
+        <v>239460</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="5" t="s">
-        <v>116</v>
-      </c>
-      <c r="C31" s="18" t="n">
-        <f aca="false">C29*$C$21</f>
-        <v>2700</v>
-      </c>
-      <c r="D31" s="18" t="n">
-        <f aca="false">D29*$C$21</f>
-        <v>5535</v>
-      </c>
-      <c r="E31" s="18" t="n">
-        <f aca="false">E29*$C$21</f>
-        <v>8592.75</v>
-      </c>
-      <c r="F31" s="18" t="n">
-        <f aca="false">F29*$C$21</f>
-        <v>11969.4375</v>
-      </c>
-      <c r="G31" s="18" t="n">
-        <f aca="false">G29*$C$21</f>
-        <v>15772.741875</v>
+        <v>159</v>
+      </c>
+      <c r="C31" s="14" t="n">
+        <f aca="false">C28*$C$18</f>
+        <v>0</v>
+      </c>
+      <c r="D31" s="14" t="n">
+        <f aca="false">D28*$C$18</f>
+        <v>203541</v>
+      </c>
+      <c r="E31" s="14" t="n">
+        <f aca="false">E28*$C$18</f>
+        <v>376550.85</v>
+      </c>
+      <c r="F31" s="14" t="n">
+        <f aca="false">F28*$C$18</f>
+        <v>523609.2225</v>
+      </c>
+      <c r="G31" s="14" t="n">
+        <f aca="false">G28*$C$18</f>
+        <v>648608.839125</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="C32" s="14" t="n">
-        <f aca="false">C29*$C$22</f>
-        <v>175500</v>
-      </c>
-      <c r="D32" s="14" t="n">
-        <f aca="false">D29*$C$22</f>
-        <v>359775</v>
-      </c>
-      <c r="E32" s="14" t="n">
-        <f aca="false">E29*$C$22</f>
-        <v>558528.75</v>
-      </c>
-      <c r="F32" s="14" t="n">
-        <f aca="false">F29*$C$22</f>
-        <v>778013.4375</v>
-      </c>
-      <c r="G32" s="14" t="n">
-        <f aca="false">G29*$C$22</f>
-        <v>1025228.221875</v>
+        <v>160</v>
+      </c>
+      <c r="C32" s="15" t="n">
+        <f aca="false">C30+C31</f>
+        <v>239460</v>
+      </c>
+      <c r="D32" s="15" t="n">
+        <f aca="false">D30+D31</f>
+        <v>443001</v>
+      </c>
+      <c r="E32" s="15" t="n">
+        <f aca="false">E30+E31</f>
+        <v>616010.85</v>
+      </c>
+      <c r="F32" s="15" t="n">
+        <f aca="false">F30+F31</f>
+        <v>763069.2225</v>
+      </c>
+      <c r="G32" s="15" t="n">
+        <f aca="false">G30+G31</f>
+        <v>888068.839125</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="C33" s="13" t="n">
-        <f aca="false">-$C$10</f>
-        <v>-6000</v>
-      </c>
-      <c r="D33" s="13" t="n">
-        <f aca="false">-$C$10</f>
-        <v>-6000</v>
-      </c>
-      <c r="E33" s="13" t="n">
-        <f aca="false">-$C$10</f>
-        <v>-6000</v>
-      </c>
-      <c r="F33" s="13" t="n">
-        <f aca="false">-$C$10</f>
-        <v>-6000</v>
-      </c>
-      <c r="G33" s="13" t="n">
-        <f aca="false">-$C$10</f>
-        <v>-6000</v>
+        <v>161</v>
+      </c>
+      <c r="C33" s="14" t="n">
+        <f aca="false">-(C30*$C$20+C31*$C$21)</f>
+        <v>-23946</v>
+      </c>
+      <c r="D33" s="14" t="n">
+        <f aca="false">-(D30*$C$20+D31*$C$21)</f>
+        <v>-34123.05</v>
+      </c>
+      <c r="E33" s="14" t="n">
+        <f aca="false">-(E30*$C$20+E31*$C$21)</f>
+        <v>-42773.5425</v>
+      </c>
+      <c r="F33" s="14" t="n">
+        <f aca="false">-(F30*$C$20+F31*$C$21)</f>
+        <v>-50126.461125</v>
+      </c>
+      <c r="G33" s="14" t="n">
+        <f aca="false">-(G30*$C$20+G31*$C$21)</f>
+        <v>-56376.44195625</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="C34" s="13" t="n">
-        <f aca="false">-C31*$C$24</f>
-        <v>-8100</v>
-      </c>
-      <c r="D34" s="13" t="n">
-        <f aca="false">-D31*$C$24</f>
-        <v>-16605</v>
-      </c>
-      <c r="E34" s="13" t="n">
-        <f aca="false">-E31*$C$24</f>
-        <v>-25778.25</v>
-      </c>
-      <c r="F34" s="13" t="n">
-        <f aca="false">-F31*$C$24</f>
-        <v>-35908.3125</v>
-      </c>
-      <c r="G34" s="13" t="n">
-        <f aca="false">-G31*$C$24</f>
-        <v>-47318.225625</v>
+        <v>162</v>
+      </c>
+      <c r="C34" s="14" t="n">
+        <f aca="false">-C29*$C$22</f>
+        <v>-5526</v>
+      </c>
+      <c r="D34" s="14" t="n">
+        <f aca="false">-D29*$C$22</f>
+        <v>-10223.1</v>
+      </c>
+      <c r="E34" s="14" t="n">
+        <f aca="false">-E29*$C$22</f>
+        <v>-14215.635</v>
+      </c>
+      <c r="F34" s="14" t="n">
+        <f aca="false">-F29*$C$22</f>
+        <v>-17609.28975</v>
+      </c>
+      <c r="G34" s="14" t="n">
+        <f aca="false">-G29*$C$22</f>
+        <v>-20493.8962875</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="C35" s="13" t="n">
-        <f aca="false">-$C$25</f>
+        <v>163</v>
+      </c>
+      <c r="C35" s="14" t="n">
+        <f aca="false">-$C$23</f>
         <v>-6130</v>
       </c>
-      <c r="D35" s="13" t="n">
-        <f aca="false">-$C$25</f>
+      <c r="D35" s="14" t="n">
+        <f aca="false">-$C$23</f>
         <v>-6130</v>
       </c>
-      <c r="E35" s="13" t="n">
-        <f aca="false">-$C$25</f>
+      <c r="E35" s="14" t="n">
+        <f aca="false">-$C$23</f>
         <v>-6130</v>
       </c>
-      <c r="F35" s="13" t="n">
-        <f aca="false">-$C$25</f>
+      <c r="F35" s="14" t="n">
+        <f aca="false">-$C$23</f>
         <v>-6130</v>
       </c>
-      <c r="G35" s="13" t="n">
-        <f aca="false">-$C$25</f>
+      <c r="G35" s="14" t="n">
+        <f aca="false">-$C$23</f>
         <v>-6130</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="C36" s="14" t="n">
+        <v>164</v>
+      </c>
+      <c r="C36" s="15" t="n">
         <f aca="false">SUM(C32:C35)</f>
-        <v>155270</v>
-      </c>
-      <c r="D36" s="14" t="n">
+        <v>203858</v>
+      </c>
+      <c r="D36" s="15" t="n">
         <f aca="false">SUM(D32:D35)</f>
-        <v>331040</v>
-      </c>
-      <c r="E36" s="14" t="n">
+        <v>392524.85</v>
+      </c>
+      <c r="E36" s="15" t="n">
         <f aca="false">SUM(E32:E35)</f>
-        <v>520620.5</v>
-      </c>
-      <c r="F36" s="14" t="n">
+        <v>552891.6725</v>
+      </c>
+      <c r="F36" s="15" t="n">
         <f aca="false">SUM(F32:F35)</f>
-        <v>729975.125</v>
-      </c>
-      <c r="G36" s="14" t="n">
+        <v>689203.471625</v>
+      </c>
+      <c r="G36" s="15" t="n">
         <f aca="false">SUM(G32:G35)</f>
-        <v>965779.99625</v>
+        <v>805068.50088125</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="C37" s="25" t="n">
+        <v>165</v>
+      </c>
+      <c r="C37" s="27" t="n">
         <f aca="false">IF(C32&lt;&gt;0,C36/C32,0)</f>
-        <v>0.884729344729345</v>
-      </c>
-      <c r="D37" s="25" t="n">
+        <v>0.851323811910131</v>
+      </c>
+      <c r="D37" s="27" t="n">
         <f aca="false">IF(D32&lt;&gt;0,D36/D32,0)</f>
-        <v>0.920130637203808</v>
-      </c>
-      <c r="E37" s="25" t="n">
+        <v>0.886058609348512</v>
+      </c>
+      <c r="E37" s="27" t="n">
         <f aca="false">IF(E32&lt;&gt;0,E36/E32,0)</f>
-        <v>0.932128381931995</v>
-      </c>
-      <c r="F37" s="25" t="n">
+        <v>0.89753560753029</v>
+      </c>
+      <c r="F37" s="27" t="n">
         <f aca="false">IF(F32&lt;&gt;0,F36/F32,0)</f>
-        <v>0.938255163491312</v>
-      </c>
-      <c r="G37" s="25" t="n">
+        <v>0.90319914799735</v>
+      </c>
+      <c r="G37" s="27" t="n">
         <f aca="false">IF(G32&lt;&gt;0,G36/G32,0)</f>
-        <v>0.942014641855764</v>
+        <v>0.906538395913622</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="C39" s="14" t="n">
+        <v>166</v>
+      </c>
+      <c r="C39" s="15" t="n">
         <f aca="false">SUM(C32:G32)</f>
-        <v>2897045.409375</v>
+        <v>2949609.911625</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="5" t="s">
-        <v>146</v>
-      </c>
-      <c r="C40" s="13" t="n">
+        <v>167</v>
+      </c>
+      <c r="C40" s="14" t="n">
         <f aca="false">SUM(C33:G33)</f>
-        <v>-30000</v>
+        <v>-207345.49558125</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="C41" s="14" t="n">
+        <v>168</v>
+      </c>
+      <c r="C41" s="15" t="n">
         <f aca="false">SUM(C36:G36)</f>
-        <v>2702685.62125</v>
+        <v>2643546.49500625</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="2" t="s">
-        <v>147</v>
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -5043,6 +4922,503 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
+  <dimension ref="B2:G43"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="3" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="40"/>
+  </cols>
+  <sheetData>
+    <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="2" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="3" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B6" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="5" t="s">
+        <v>174</v>
+      </c>
+      <c r="C7" s="21" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="5" t="s">
+        <v>175</v>
+      </c>
+      <c r="C8" s="21" t="n">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="5" t="s">
+        <v>176</v>
+      </c>
+      <c r="C9" s="22" t="n">
+        <f aca="false">C6*C7*C8</f>
+        <v>4.5</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="C10" s="10" t="n">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="5" t="s">
+        <v>178</v>
+      </c>
+      <c r="C11" s="10" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="5" t="s">
+        <v>179</v>
+      </c>
+      <c r="C12" s="21" t="n">
+        <v>0.05</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="C13" s="22" t="n">
+        <f aca="false">IF(C11&gt;0,C10/C11*C12,0)</f>
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="5" t="s">
+        <v>181</v>
+      </c>
+      <c r="C14" s="9" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B15" s="5" t="s">
+        <v>182</v>
+      </c>
+      <c r="C15" s="21" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="5" t="s">
+        <v>183</v>
+      </c>
+      <c r="C16" s="22" t="n">
+        <f aca="false">C14*C15</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="5" t="s">
+        <v>184</v>
+      </c>
+      <c r="C17" s="23" t="n">
+        <f aca="false">C9+C13+C16</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="C18" s="21" t="n">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="5" t="s">
+        <v>141</v>
+      </c>
+      <c r="C21" s="9" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B22" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="C22" s="25" t="n">
+        <f aca="false">MAX(C21*IF(C21&lt;='Preise &amp; Pläne'!$C$6,'Preise &amp; Pläne'!$D$6,IF(C21&lt;='Preise &amp; Pläne'!$C$7,'Preise &amp; Pläne'!$D$7,'Preise &amp; Pläne'!$D$8)),'Preise &amp; Pläne'!$C$11,IF(C21&gt;'Preise &amp; Pläne'!$C$6,'Preise &amp; Pläne'!$C$6*'Preise &amp; Pläne'!$D$6,0),IF(C21&gt;'Preise &amp; Pläne'!$C$7,'Preise &amp; Pläne'!$C$7*'Preise &amp; Pläne'!$D$7,0))</f>
+        <v>9750</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B23" s="5" t="s">
+        <v>143</v>
+      </c>
+      <c r="C23" s="21" t="n">
+        <v>0.85</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="5" t="s">
+        <v>146</v>
+      </c>
+      <c r="C24" s="26" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="5" t="s">
+        <v>147</v>
+      </c>
+      <c r="C25" s="10" t="n">
+        <v>6130</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B27" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="F27" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="G27" s="7" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B28" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C28" s="22" t="n">
+        <f aca="false">$C$17*(1+$C$18)^0</f>
+        <v>18</v>
+      </c>
+      <c r="D28" s="22" t="n">
+        <f aca="false">$C$17*(1+$C$18)^1</f>
+        <v>21.6</v>
+      </c>
+      <c r="E28" s="22" t="n">
+        <f aca="false">$C$17*(1+$C$18)^2</f>
+        <v>25.92</v>
+      </c>
+      <c r="F28" s="22" t="n">
+        <f aca="false">$C$17*(1+$C$18)^3</f>
+        <v>31.104</v>
+      </c>
+      <c r="G28" s="22" t="n">
+        <f aca="false">$C$17*(1+$C$18)^4</f>
+        <v>37.3248</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="5" t="s">
+        <v>155</v>
+      </c>
+      <c r="C29" s="22" t="n">
+        <f aca="false">C28+C30</f>
+        <v>18</v>
+      </c>
+      <c r="D29" s="22" t="n">
+        <f aca="false">D28+D30</f>
+        <v>36.9</v>
+      </c>
+      <c r="E29" s="22" t="n">
+        <f aca="false">E28+E30</f>
+        <v>57.285</v>
+      </c>
+      <c r="F29" s="22" t="n">
+        <f aca="false">F28+F30</f>
+        <v>79.79625</v>
+      </c>
+      <c r="G29" s="22" t="n">
+        <f aca="false">G28+G30</f>
+        <v>105.1516125</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="C30" s="22" t="n">
+        <f aca="false">0</f>
+        <v>0</v>
+      </c>
+      <c r="D30" s="22" t="n">
+        <f aca="false">C29*$C$23</f>
+        <v>15.3</v>
+      </c>
+      <c r="E30" s="22" t="n">
+        <f aca="false">D29*$C$23</f>
+        <v>31.365</v>
+      </c>
+      <c r="F30" s="22" t="n">
+        <f aca="false">E29*$C$23</f>
+        <v>48.69225</v>
+      </c>
+      <c r="G30" s="22" t="n">
+        <f aca="false">F29*$C$23</f>
+        <v>67.8268125</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="5" t="s">
+        <v>157</v>
+      </c>
+      <c r="C31" s="20" t="n">
+        <f aca="false">C29*$C$21</f>
+        <v>2700</v>
+      </c>
+      <c r="D31" s="20" t="n">
+        <f aca="false">D29*$C$21</f>
+        <v>5535</v>
+      </c>
+      <c r="E31" s="20" t="n">
+        <f aca="false">E29*$C$21</f>
+        <v>8592.75</v>
+      </c>
+      <c r="F31" s="20" t="n">
+        <f aca="false">F29*$C$21</f>
+        <v>11969.4375</v>
+      </c>
+      <c r="G31" s="20" t="n">
+        <f aca="false">G29*$C$21</f>
+        <v>15772.741875</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C32" s="15" t="n">
+        <f aca="false">C29*$C$22</f>
+        <v>175500</v>
+      </c>
+      <c r="D32" s="15" t="n">
+        <f aca="false">D29*$C$22</f>
+        <v>359775</v>
+      </c>
+      <c r="E32" s="15" t="n">
+        <f aca="false">E29*$C$22</f>
+        <v>558528.75</v>
+      </c>
+      <c r="F32" s="15" t="n">
+        <f aca="false">F29*$C$22</f>
+        <v>778013.4375</v>
+      </c>
+      <c r="G32" s="15" t="n">
+        <f aca="false">G29*$C$22</f>
+        <v>1025228.221875</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="5" t="s">
+        <v>186</v>
+      </c>
+      <c r="C33" s="14" t="n">
+        <f aca="false">-$C$10</f>
+        <v>-6000</v>
+      </c>
+      <c r="D33" s="14" t="n">
+        <f aca="false">-$C$10</f>
+        <v>-6000</v>
+      </c>
+      <c r="E33" s="14" t="n">
+        <f aca="false">-$C$10</f>
+        <v>-6000</v>
+      </c>
+      <c r="F33" s="14" t="n">
+        <f aca="false">-$C$10</f>
+        <v>-6000</v>
+      </c>
+      <c r="G33" s="14" t="n">
+        <f aca="false">-$C$10</f>
+        <v>-6000</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="C34" s="14" t="n">
+        <f aca="false">-C31*$C$24</f>
+        <v>-8100</v>
+      </c>
+      <c r="D34" s="14" t="n">
+        <f aca="false">-D31*$C$24</f>
+        <v>-16605</v>
+      </c>
+      <c r="E34" s="14" t="n">
+        <f aca="false">-E31*$C$24</f>
+        <v>-25778.25</v>
+      </c>
+      <c r="F34" s="14" t="n">
+        <f aca="false">-F31*$C$24</f>
+        <v>-35908.3125</v>
+      </c>
+      <c r="G34" s="14" t="n">
+        <f aca="false">-G31*$C$24</f>
+        <v>-47318.225625</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B35" s="5" t="s">
+        <v>163</v>
+      </c>
+      <c r="C35" s="14" t="n">
+        <f aca="false">-$C$25</f>
+        <v>-6130</v>
+      </c>
+      <c r="D35" s="14" t="n">
+        <f aca="false">-$C$25</f>
+        <v>-6130</v>
+      </c>
+      <c r="E35" s="14" t="n">
+        <f aca="false">-$C$25</f>
+        <v>-6130</v>
+      </c>
+      <c r="F35" s="14" t="n">
+        <f aca="false">-$C$25</f>
+        <v>-6130</v>
+      </c>
+      <c r="G35" s="14" t="n">
+        <f aca="false">-$C$25</f>
+        <v>-6130</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B36" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="C36" s="15" t="n">
+        <f aca="false">SUM(C32:C35)</f>
+        <v>155270</v>
+      </c>
+      <c r="D36" s="15" t="n">
+        <f aca="false">SUM(D32:D35)</f>
+        <v>331040</v>
+      </c>
+      <c r="E36" s="15" t="n">
+        <f aca="false">SUM(E32:E35)</f>
+        <v>520620.5</v>
+      </c>
+      <c r="F36" s="15" t="n">
+        <f aca="false">SUM(F32:F35)</f>
+        <v>729975.125</v>
+      </c>
+      <c r="G36" s="15" t="n">
+        <f aca="false">SUM(G32:G35)</f>
+        <v>965779.99625</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B37" s="5" t="s">
+        <v>165</v>
+      </c>
+      <c r="C37" s="27" t="n">
+        <f aca="false">IF(C32&lt;&gt;0,C36/C32,0)</f>
+        <v>0.884729344729345</v>
+      </c>
+      <c r="D37" s="27" t="n">
+        <f aca="false">IF(D32&lt;&gt;0,D36/D32,0)</f>
+        <v>0.920130637203808</v>
+      </c>
+      <c r="E37" s="27" t="n">
+        <f aca="false">IF(E32&lt;&gt;0,E36/E32,0)</f>
+        <v>0.932128381931995</v>
+      </c>
+      <c r="F37" s="27" t="n">
+        <f aca="false">IF(F32&lt;&gt;0,F36/F32,0)</f>
+        <v>0.938255163491312</v>
+      </c>
+      <c r="G37" s="27" t="n">
+        <f aca="false">IF(G32&lt;&gt;0,G36/G32,0)</f>
+        <v>0.942014641855764</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B39" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="C39" s="15" t="n">
+        <f aca="false">SUM(C32:G32)</f>
+        <v>2897045.409375</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B40" s="5" t="s">
+        <v>187</v>
+      </c>
+      <c r="C40" s="14" t="n">
+        <f aca="false">SUM(C33:G33)</f>
+        <v>-30000</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="5" t="s">
+        <v>168</v>
+      </c>
+      <c r="C41" s="15" t="n">
+        <f aca="false">SUM(C36:G36)</f>
+        <v>2702685.62125</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B43" s="2" t="s">
+        <v>188</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
   <dimension ref="B2:H17"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
@@ -5054,337 +5430,337 @@
   <sheetData>
     <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>148</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
-        <v>149</v>
+        <v>190</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>150</v>
       </c>
-      <c r="C5" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>109</v>
-      </c>
       <c r="E5" s="7" t="s">
-        <v>110</v>
+        <v>151</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>111</v>
+        <v>152</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>112</v>
+        <v>153</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>151</v>
+        <v>192</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="s">
-        <v>152</v>
-      </c>
-      <c r="C6" s="23" t="n">
+        <v>193</v>
+      </c>
+      <c r="C6" s="25" t="n">
         <f aca="false">'Mit Anwalts-Funnel'!C32</f>
         <v>239460</v>
       </c>
-      <c r="D6" s="23" t="n">
+      <c r="D6" s="25" t="n">
         <f aca="false">'Mit Anwalts-Funnel'!D32</f>
         <v>443001</v>
       </c>
-      <c r="E6" s="23" t="n">
+      <c r="E6" s="25" t="n">
         <f aca="false">'Mit Anwalts-Funnel'!E32</f>
         <v>616010.85</v>
       </c>
-      <c r="F6" s="23" t="n">
+      <c r="F6" s="25" t="n">
         <f aca="false">'Mit Anwalts-Funnel'!F32</f>
         <v>763069.2225</v>
       </c>
-      <c r="G6" s="23" t="n">
+      <c r="G6" s="25" t="n">
         <f aca="false">'Mit Anwalts-Funnel'!G32</f>
         <v>888068.839125</v>
       </c>
-      <c r="H6" s="14" t="n">
+      <c r="H6" s="15" t="n">
         <f aca="false">SUM(C6:G6)</f>
         <v>2949609.911625</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="C7" s="23" t="n">
+        <v>194</v>
+      </c>
+      <c r="C7" s="25" t="n">
         <f aca="false">'Ohne Anwalt (Direkt)'!C32</f>
         <v>175500</v>
       </c>
-      <c r="D7" s="23" t="n">
+      <c r="D7" s="25" t="n">
         <f aca="false">'Ohne Anwalt (Direkt)'!D32</f>
         <v>359775</v>
       </c>
-      <c r="E7" s="23" t="n">
+      <c r="E7" s="25" t="n">
         <f aca="false">'Ohne Anwalt (Direkt)'!E32</f>
         <v>558528.75</v>
       </c>
-      <c r="F7" s="23" t="n">
+      <c r="F7" s="25" t="n">
         <f aca="false">'Ohne Anwalt (Direkt)'!F32</f>
         <v>778013.4375</v>
       </c>
-      <c r="G7" s="23" t="n">
+      <c r="G7" s="25" t="n">
         <f aca="false">'Ohne Anwalt (Direkt)'!G32</f>
         <v>1025228.221875</v>
       </c>
-      <c r="H7" s="14" t="n">
+      <c r="H7" s="15" t="n">
         <f aca="false">SUM(C7:G7)</f>
         <v>2897045.409375</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="C8" s="13" t="n">
+        <v>195</v>
+      </c>
+      <c r="C8" s="14" t="n">
         <f aca="false">C6+C7</f>
         <v>414960</v>
       </c>
-      <c r="D8" s="13" t="n">
+      <c r="D8" s="14" t="n">
         <f aca="false">D6+D7</f>
         <v>802776</v>
       </c>
-      <c r="E8" s="13" t="n">
+      <c r="E8" s="14" t="n">
         <f aca="false">E6+E7</f>
         <v>1174539.6</v>
       </c>
-      <c r="F8" s="13" t="n">
+      <c r="F8" s="14" t="n">
         <f aca="false">F6+F7</f>
         <v>1541082.66</v>
       </c>
-      <c r="G8" s="13" t="n">
+      <c r="G8" s="14" t="n">
         <f aca="false">G6+G7</f>
         <v>1913297.061</v>
       </c>
-      <c r="H8" s="14" t="n">
+      <c r="H8" s="15" t="n">
         <f aca="false">SUM(C8:G8)</f>
         <v>5846655.321</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="5" t="s">
-        <v>155</v>
-      </c>
-      <c r="C9" s="23" t="n">
+        <v>196</v>
+      </c>
+      <c r="C9" s="25" t="n">
         <f aca="false">'Mit Anwalts-Funnel'!C36</f>
         <v>203858</v>
       </c>
-      <c r="D9" s="23" t="n">
+      <c r="D9" s="25" t="n">
         <f aca="false">'Mit Anwalts-Funnel'!D36</f>
         <v>392524.85</v>
       </c>
-      <c r="E9" s="23" t="n">
+      <c r="E9" s="25" t="n">
         <f aca="false">'Mit Anwalts-Funnel'!E36</f>
         <v>552891.6725</v>
       </c>
-      <c r="F9" s="23" t="n">
+      <c r="F9" s="25" t="n">
         <f aca="false">'Mit Anwalts-Funnel'!F36</f>
         <v>689203.471625</v>
       </c>
-      <c r="G9" s="23" t="n">
+      <c r="G9" s="25" t="n">
         <f aca="false">'Mit Anwalts-Funnel'!G36</f>
         <v>805068.50088125</v>
       </c>
-      <c r="H9" s="14" t="n">
+      <c r="H9" s="15" t="n">
         <f aca="false">SUM(C9:G9)</f>
         <v>2643546.49500625</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="5" t="s">
-        <v>156</v>
-      </c>
-      <c r="C10" s="23" t="n">
+        <v>197</v>
+      </c>
+      <c r="C10" s="25" t="n">
         <f aca="false">'Ohne Anwalt (Direkt)'!C36</f>
         <v>155270</v>
       </c>
-      <c r="D10" s="23" t="n">
+      <c r="D10" s="25" t="n">
         <f aca="false">'Ohne Anwalt (Direkt)'!D36</f>
         <v>331040</v>
       </c>
-      <c r="E10" s="23" t="n">
+      <c r="E10" s="25" t="n">
         <f aca="false">'Ohne Anwalt (Direkt)'!E36</f>
         <v>520620.5</v>
       </c>
-      <c r="F10" s="23" t="n">
+      <c r="F10" s="25" t="n">
         <f aca="false">'Ohne Anwalt (Direkt)'!F36</f>
         <v>729975.125</v>
       </c>
-      <c r="G10" s="23" t="n">
+      <c r="G10" s="25" t="n">
         <f aca="false">'Ohne Anwalt (Direkt)'!G36</f>
         <v>965779.99625</v>
       </c>
-      <c r="H10" s="14" t="n">
+      <c r="H10" s="15" t="n">
         <f aca="false">SUM(C10:G10)</f>
         <v>2702685.62125</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="C11" s="13" t="n">
+        <v>198</v>
+      </c>
+      <c r="C11" s="14" t="n">
         <f aca="false">C9+C10+'Ohne Anwalt (Direkt)'!$C$25</f>
         <v>365258</v>
       </c>
-      <c r="D11" s="13" t="n">
+      <c r="D11" s="14" t="n">
         <f aca="false">D9+D10+'Ohne Anwalt (Direkt)'!$C$25</f>
         <v>729694.85</v>
       </c>
-      <c r="E11" s="13" t="n">
+      <c r="E11" s="14" t="n">
         <f aca="false">E9+E10+'Ohne Anwalt (Direkt)'!$C$25</f>
         <v>1079642.1725</v>
       </c>
-      <c r="F11" s="13" t="n">
+      <c r="F11" s="14" t="n">
         <f aca="false">F9+F10+'Ohne Anwalt (Direkt)'!$C$25</f>
         <v>1425308.596625</v>
       </c>
-      <c r="G11" s="13" t="n">
+      <c r="G11" s="14" t="n">
         <f aca="false">G9+G10+'Ohne Anwalt (Direkt)'!$C$25</f>
         <v>1776978.49713125</v>
       </c>
-      <c r="H11" s="14" t="n">
+      <c r="H11" s="15" t="n">
         <f aca="false">SUM(C11:G11)</f>
         <v>5376882.11625625</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="C12" s="26" t="n">
+        <v>199</v>
+      </c>
+      <c r="C12" s="28" t="n">
         <f aca="false">'Mit Anwalts-Funnel'!C27</f>
         <v>9.21</v>
       </c>
-      <c r="D12" s="26" t="n">
+      <c r="D12" s="28" t="n">
         <f aca="false">'Mit Anwalts-Funnel'!D27</f>
         <v>17.0385</v>
       </c>
-      <c r="E12" s="26" t="n">
+      <c r="E12" s="28" t="n">
         <f aca="false">'Mit Anwalts-Funnel'!E27</f>
         <v>23.692725</v>
       </c>
-      <c r="F12" s="26" t="n">
+      <c r="F12" s="28" t="n">
         <f aca="false">'Mit Anwalts-Funnel'!F27</f>
         <v>29.34881625</v>
       </c>
-      <c r="G12" s="26" t="n">
+      <c r="G12" s="28" t="n">
         <f aca="false">'Mit Anwalts-Funnel'!G27</f>
         <v>34.1564938125</v>
       </c>
-      <c r="H12" s="21" t="n">
+      <c r="H12" s="23" t="n">
         <f aca="false">G12</f>
         <v>34.1564938125</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="C13" s="26" t="n">
+        <v>200</v>
+      </c>
+      <c r="C13" s="28" t="n">
         <f aca="false">'Ohne Anwalt (Direkt)'!C29</f>
         <v>18</v>
       </c>
-      <c r="D13" s="26" t="n">
+      <c r="D13" s="28" t="n">
         <f aca="false">'Ohne Anwalt (Direkt)'!D29</f>
         <v>36.9</v>
       </c>
-      <c r="E13" s="26" t="n">
+      <c r="E13" s="28" t="n">
         <f aca="false">'Ohne Anwalt (Direkt)'!E29</f>
         <v>57.285</v>
       </c>
-      <c r="F13" s="26" t="n">
+      <c r="F13" s="28" t="n">
         <f aca="false">'Ohne Anwalt (Direkt)'!F29</f>
         <v>79.79625</v>
       </c>
-      <c r="G13" s="26" t="n">
+      <c r="G13" s="28" t="n">
         <f aca="false">'Ohne Anwalt (Direkt)'!G29</f>
         <v>105.1516125</v>
       </c>
-      <c r="H13" s="21" t="n">
+      <c r="H13" s="23" t="n">
         <f aca="false">G13</f>
         <v>105.1516125</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="5" t="s">
-        <v>160</v>
-      </c>
-      <c r="C14" s="13" t="n">
+        <v>201</v>
+      </c>
+      <c r="C14" s="14" t="n">
         <f aca="false">-'Mit Anwalts-Funnel'!C33</f>
         <v>23946</v>
       </c>
-      <c r="D14" s="13" t="n">
+      <c r="D14" s="14" t="n">
         <f aca="false">-'Mit Anwalts-Funnel'!D33</f>
         <v>34123.05</v>
       </c>
-      <c r="E14" s="13" t="n">
+      <c r="E14" s="14" t="n">
         <f aca="false">-'Mit Anwalts-Funnel'!E33</f>
         <v>42773.5425</v>
       </c>
-      <c r="F14" s="13" t="n">
+      <c r="F14" s="14" t="n">
         <f aca="false">-'Mit Anwalts-Funnel'!F33</f>
         <v>50126.461125</v>
       </c>
-      <c r="G14" s="13" t="n">
+      <c r="G14" s="14" t="n">
         <f aca="false">-'Mit Anwalts-Funnel'!G33</f>
         <v>56376.44195625</v>
       </c>
-      <c r="H14" s="14" t="n">
+      <c r="H14" s="15" t="n">
         <f aca="false">SUM(C14:G14)</f>
         <v>207345.49558125</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="C15" s="13" t="n">
+        <v>202</v>
+      </c>
+      <c r="C15" s="14" t="n">
         <f aca="false">-'Ohne Anwalt (Direkt)'!C33</f>
         <v>6000</v>
       </c>
-      <c r="D15" s="13" t="n">
+      <c r="D15" s="14" t="n">
         <f aca="false">-'Ohne Anwalt (Direkt)'!D33</f>
         <v>6000</v>
       </c>
-      <c r="E15" s="13" t="n">
+      <c r="E15" s="14" t="n">
         <f aca="false">-'Ohne Anwalt (Direkt)'!E33</f>
         <v>6000</v>
       </c>
-      <c r="F15" s="13" t="n">
+      <c r="F15" s="14" t="n">
         <f aca="false">-'Ohne Anwalt (Direkt)'!F33</f>
         <v>6000</v>
       </c>
-      <c r="G15" s="13" t="n">
+      <c r="G15" s="14" t="n">
         <f aca="false">-'Ohne Anwalt (Direkt)'!G33</f>
         <v>6000</v>
       </c>
-      <c r="H15" s="14" t="n">
+      <c r="H15" s="15" t="n">
         <f aca="false">SUM(C15:G15)</f>
         <v>30000</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="16" t="s">
-        <v>162</v>
-      </c>
-      <c r="C17" s="16"/>
-      <c r="D17" s="16"/>
-      <c r="E17" s="16"/>
-      <c r="F17" s="16"/>
-      <c r="G17" s="16"/>
-      <c r="H17" s="16"/>
+      <c r="B17" s="17" t="s">
+        <v>203</v>
+      </c>
+      <c r="C17" s="17"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="17"/>
+      <c r="G17" s="17"/>
+      <c r="H17" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5400,7 +5776,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
@@ -5424,4412 +5800,4412 @@
   <sheetData>
     <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>163</v>
+        <v>204</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
-        <v>164</v>
+        <v>205</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="7" t="s">
-        <v>165</v>
+        <v>206</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>166</v>
+        <v>207</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>167</v>
+        <v>208</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>168</v>
+        <v>209</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>169</v>
+        <v>210</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>170</v>
+        <v>211</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>171</v>
+        <v>212</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>172</v>
+        <v>213</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>173</v>
+        <v>214</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>174</v>
+        <v>215</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>175</v>
+        <v>216</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="4" t="s">
-        <v>176</v>
+        <v>217</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>177</v>
+        <v>218</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>178</v>
+        <v>219</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>177</v>
+        <v>218</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>179</v>
-      </c>
-      <c r="G6" s="27" t="s">
-        <v>180</v>
+        <v>220</v>
+      </c>
+      <c r="G6" s="29" t="s">
+        <v>221</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>181</v>
+        <v>222</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>182</v>
+        <v>223</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>184</v>
+        <v>225</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="4" t="s">
-        <v>176</v>
+        <v>217</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>177</v>
+        <v>218</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>178</v>
+        <v>219</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>177</v>
+        <v>218</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>185</v>
-      </c>
-      <c r="G7" s="27" t="s">
-        <v>186</v>
+        <v>226</v>
+      </c>
+      <c r="G7" s="29" t="s">
+        <v>227</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>181</v>
+        <v>222</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>187</v>
+        <v>228</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>188</v>
+        <v>229</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="4" t="s">
-        <v>176</v>
+        <v>217</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>177</v>
+        <v>218</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>178</v>
+        <v>219</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>177</v>
+        <v>218</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>189</v>
-      </c>
-      <c r="G8" s="27" t="s">
-        <v>190</v>
+        <v>230</v>
+      </c>
+      <c r="G8" s="29" t="s">
+        <v>231</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>192</v>
+        <v>233</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="4" t="s">
-        <v>176</v>
+        <v>217</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>177</v>
+        <v>218</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>178</v>
+        <v>219</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>194</v>
+        <v>235</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="G9" s="27" t="s">
-        <v>196</v>
+        <v>236</v>
+      </c>
+      <c r="G9" s="29" t="s">
+        <v>237</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>197</v>
+        <v>238</v>
       </c>
       <c r="J9" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="4" t="s">
-        <v>176</v>
+        <v>217</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>198</v>
+        <v>239</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>178</v>
+        <v>219</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>199</v>
+        <v>240</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>200</v>
-      </c>
-      <c r="G10" s="27" t="s">
-        <v>201</v>
+        <v>241</v>
+      </c>
+      <c r="G10" s="29" t="s">
+        <v>242</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>202</v>
+        <v>243</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>203</v>
+        <v>244</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>204</v>
+        <v>245</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="4" t="s">
-        <v>176</v>
+        <v>217</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>198</v>
+        <v>239</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>178</v>
+        <v>219</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>205</v>
+        <v>246</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>206</v>
-      </c>
-      <c r="G11" s="27" t="s">
-        <v>207</v>
+        <v>247</v>
+      </c>
+      <c r="G11" s="29" t="s">
+        <v>248</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>208</v>
+        <v>249</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="4" t="s">
-        <v>176</v>
+        <v>217</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>177</v>
+        <v>218</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>209</v>
+        <v>250</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>210</v>
+        <v>251</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="G12" s="27" t="s">
-        <v>212</v>
+        <v>252</v>
+      </c>
+      <c r="G12" s="29" t="s">
+        <v>253</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>202</v>
+        <v>243</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>213</v>
+        <v>254</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>214</v>
+        <v>255</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="4" t="s">
-        <v>176</v>
+        <v>217</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>198</v>
+        <v>239</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>209</v>
+        <v>250</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>215</v>
+        <v>256</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>216</v>
-      </c>
-      <c r="G13" s="27" t="s">
-        <v>217</v>
+        <v>257</v>
+      </c>
+      <c r="G13" s="29" t="s">
+        <v>258</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>202</v>
+        <v>243</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>218</v>
+        <v>259</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>219</v>
+        <v>260</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="4" t="s">
-        <v>176</v>
+        <v>217</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>198</v>
+        <v>239</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>209</v>
+        <v>250</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>215</v>
+        <v>256</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>220</v>
-      </c>
-      <c r="G14" s="27" t="s">
-        <v>221</v>
+        <v>261</v>
+      </c>
+      <c r="G14" s="29" t="s">
+        <v>262</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>181</v>
+        <v>222</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>222</v>
+        <v>263</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="4" t="s">
-        <v>176</v>
+        <v>217</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>223</v>
+        <v>264</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>224</v>
+        <v>265</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>225</v>
+        <v>266</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="G15" s="27" t="s">
-        <v>227</v>
+        <v>267</v>
+      </c>
+      <c r="G15" s="29" t="s">
+        <v>268</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>228</v>
+        <v>269</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>229</v>
+        <v>270</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="4" t="s">
-        <v>176</v>
+        <v>217</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>223</v>
+        <v>264</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>224</v>
+        <v>265</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>225</v>
+        <v>266</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>230</v>
-      </c>
-      <c r="G16" s="27" t="s">
-        <v>231</v>
+        <v>271</v>
+      </c>
+      <c r="G16" s="29" t="s">
+        <v>272</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>232</v>
+        <v>273</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="4" t="s">
-        <v>176</v>
+        <v>217</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>233</v>
+        <v>274</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>224</v>
+        <v>265</v>
       </c>
       <c r="E17" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="G17" s="29" t="s">
+        <v>277</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="L17" s="4" t="s">
         <v>234</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>235</v>
-      </c>
-      <c r="G17" s="27" t="s">
-        <v>236</v>
-      </c>
-      <c r="H17" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="K17" s="4" t="s">
-        <v>183</v>
-      </c>
-      <c r="L17" s="4" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="4" t="s">
-        <v>176</v>
+        <v>217</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>233</v>
+        <v>274</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>224</v>
+        <v>265</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>233</v>
+        <v>274</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>238</v>
-      </c>
-      <c r="G18" s="27" t="s">
-        <v>239</v>
+        <v>279</v>
+      </c>
+      <c r="G18" s="29" t="s">
+        <v>280</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>240</v>
+        <v>281</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="4" t="s">
-        <v>176</v>
+        <v>217</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>241</v>
+        <v>282</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>224</v>
+        <v>265</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>242</v>
+        <v>283</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="G19" s="27" t="s">
-        <v>244</v>
+        <v>284</v>
+      </c>
+      <c r="G19" s="29" t="s">
+        <v>285</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>245</v>
+        <v>286</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="4" t="s">
-        <v>176</v>
+        <v>217</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>241</v>
+        <v>282</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>224</v>
+        <v>265</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>241</v>
+        <v>282</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>246</v>
-      </c>
-      <c r="G20" s="27" t="s">
-        <v>247</v>
+        <v>287</v>
+      </c>
+      <c r="G20" s="29" t="s">
+        <v>288</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>181</v>
+        <v>222</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>248</v>
+        <v>289</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="4" t="s">
-        <v>176</v>
+        <v>217</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>249</v>
+        <v>290</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>224</v>
+        <v>265</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>250</v>
+        <v>291</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>251</v>
-      </c>
-      <c r="G21" s="27" t="s">
-        <v>252</v>
+        <v>292</v>
+      </c>
+      <c r="G21" s="29" t="s">
+        <v>293</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>253</v>
+        <v>294</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>254</v>
+        <v>295</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="4" t="s">
-        <v>176</v>
+        <v>217</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>177</v>
+        <v>218</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>255</v>
+        <v>296</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>177</v>
+        <v>218</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>256</v>
-      </c>
-      <c r="G22" s="27" t="s">
-        <v>257</v>
+        <v>297</v>
+      </c>
+      <c r="G22" s="29" t="s">
+        <v>298</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>181</v>
+        <v>222</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>258</v>
+        <v>299</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="4" t="s">
-        <v>176</v>
+        <v>217</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>259</v>
+        <v>300</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>260</v>
+        <v>301</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>261</v>
+        <v>302</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="G23" s="27" t="s">
-        <v>263</v>
+        <v>303</v>
+      </c>
+      <c r="G23" s="29" t="s">
+        <v>304</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>181</v>
+        <v>222</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>264</v>
+        <v>305</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L23" s="4" t="s">
-        <v>265</v>
+        <v>306</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="4" t="s">
-        <v>176</v>
+        <v>217</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>259</v>
+        <v>300</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>266</v>
+        <v>307</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>267</v>
+        <v>308</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="G24" s="27" t="s">
-        <v>269</v>
+        <v>309</v>
+      </c>
+      <c r="G24" s="29" t="s">
+        <v>310</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>181</v>
+        <v>222</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>270</v>
+        <v>311</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L24" s="4" t="s">
-        <v>271</v>
+        <v>312</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="4" t="s">
-        <v>176</v>
+        <v>217</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>259</v>
+        <v>300</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>266</v>
+        <v>307</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>259</v>
+        <v>300</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="G25" s="27" t="s">
-        <v>273</v>
+        <v>313</v>
+      </c>
+      <c r="G25" s="29" t="s">
+        <v>314</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>181</v>
+        <v>222</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>274</v>
+        <v>315</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L25" s="4" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="4" t="s">
-        <v>176</v>
+        <v>217</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>177</v>
+        <v>218</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>275</v>
+        <v>316</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>194</v>
+        <v>235</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="G26" s="27" t="s">
-        <v>277</v>
+        <v>317</v>
+      </c>
+      <c r="G26" s="29" t="s">
+        <v>318</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>278</v>
+        <v>319</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L26" s="4" t="s">
-        <v>279</v>
+        <v>320</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="4" t="s">
-        <v>176</v>
+        <v>217</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>177</v>
+        <v>218</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>275</v>
+        <v>316</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>177</v>
+        <v>218</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="G27" s="27" t="s">
-        <v>281</v>
+        <v>321</v>
+      </c>
+      <c r="G27" s="29" t="s">
+        <v>322</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>282</v>
+        <v>323</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L27" s="4" t="s">
-        <v>283</v>
+        <v>324</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="4" t="s">
-        <v>176</v>
+        <v>217</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>177</v>
+        <v>218</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>284</v>
+        <v>325</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>177</v>
+        <v>218</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>285</v>
-      </c>
-      <c r="G28" s="27" t="s">
-        <v>286</v>
+        <v>326</v>
+      </c>
+      <c r="G28" s="29" t="s">
+        <v>327</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>181</v>
+        <v>222</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>287</v>
+        <v>328</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K28" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L28" s="4" t="s">
-        <v>288</v>
+        <v>329</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="4" t="s">
-        <v>176</v>
+        <v>217</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>177</v>
+        <v>218</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>284</v>
+        <v>325</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>177</v>
+        <v>218</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>289</v>
-      </c>
-      <c r="G29" s="27" t="s">
-        <v>290</v>
+        <v>330</v>
+      </c>
+      <c r="G29" s="29" t="s">
+        <v>331</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>291</v>
+        <v>332</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L29" s="4" t="s">
-        <v>292</v>
+        <v>333</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="4" t="s">
-        <v>176</v>
+        <v>217</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>177</v>
+        <v>218</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>284</v>
+        <v>325</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>194</v>
+        <v>235</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>293</v>
-      </c>
-      <c r="G30" s="27" t="s">
-        <v>294</v>
+        <v>334</v>
+      </c>
+      <c r="G30" s="29" t="s">
+        <v>335</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>181</v>
+        <v>222</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>295</v>
+        <v>336</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L30" s="4" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="4" t="s">
-        <v>176</v>
+        <v>217</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>198</v>
+        <v>239</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>284</v>
+        <v>325</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>205</v>
+        <v>246</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>296</v>
-      </c>
-      <c r="G31" s="27" t="s">
-        <v>297</v>
+        <v>337</v>
+      </c>
+      <c r="G31" s="29" t="s">
+        <v>338</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>181</v>
+        <v>222</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>298</v>
+        <v>339</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L31" s="4" t="s">
-        <v>299</v>
+        <v>340</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="4" t="s">
-        <v>300</v>
+        <v>341</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>249</v>
+        <v>290</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>178</v>
+        <v>219</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>301</v>
+        <v>342</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>302</v>
-      </c>
-      <c r="G32" s="27" t="s">
-        <v>303</v>
+        <v>343</v>
+      </c>
+      <c r="G32" s="29" t="s">
+        <v>344</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>304</v>
+        <v>345</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K32" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L32" s="4" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="4" t="s">
-        <v>300</v>
+        <v>341</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>249</v>
+        <v>290</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>178</v>
+        <v>219</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>301</v>
+        <v>342</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>305</v>
-      </c>
-      <c r="G33" s="27" t="s">
-        <v>306</v>
+        <v>346</v>
+      </c>
+      <c r="G33" s="29" t="s">
+        <v>347</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>307</v>
+        <v>348</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L33" s="4" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="4" t="s">
-        <v>300</v>
+        <v>341</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>249</v>
+        <v>290</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>308</v>
+        <v>349</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>309</v>
+        <v>350</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>310</v>
+        <v>351</v>
       </c>
       <c r="G34" s="4"/>
       <c r="H34" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>311</v>
+        <v>352</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>312</v>
+        <v>353</v>
       </c>
       <c r="L34" s="4" t="s">
-        <v>313</v>
+        <v>354</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="4" t="s">
-        <v>300</v>
+        <v>341</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>249</v>
+        <v>290</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>255</v>
+        <v>296</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>301</v>
+        <v>342</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="G35" s="27" t="s">
-        <v>315</v>
+        <v>355</v>
+      </c>
+      <c r="G35" s="29" t="s">
+        <v>356</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>316</v>
+        <v>357</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L35" s="4" t="s">
-        <v>317</v>
+        <v>358</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="4" t="s">
-        <v>300</v>
+        <v>341</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>249</v>
+        <v>290</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>260</v>
+        <v>301</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>318</v>
+        <v>359</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>319</v>
-      </c>
-      <c r="G36" s="27" t="s">
-        <v>320</v>
+        <v>360</v>
+      </c>
+      <c r="G36" s="29" t="s">
+        <v>361</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>321</v>
+        <v>362</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>312</v>
+        <v>353</v>
       </c>
       <c r="L36" s="4" t="s">
-        <v>322</v>
+        <v>363</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="4" t="s">
-        <v>300</v>
+        <v>341</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>249</v>
+        <v>290</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>266</v>
+        <v>307</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>323</v>
+        <v>364</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>324</v>
-      </c>
-      <c r="G37" s="27" t="s">
-        <v>325</v>
+        <v>365</v>
+      </c>
+      <c r="G37" s="29" t="s">
+        <v>366</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>326</v>
+        <v>367</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L37" s="4" t="s">
-        <v>327</v>
+        <v>368</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="4" t="s">
-        <v>300</v>
+        <v>341</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>249</v>
+        <v>290</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>266</v>
+        <v>307</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>328</v>
+        <v>369</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>329</v>
-      </c>
-      <c r="G38" s="27" t="s">
-        <v>330</v>
+        <v>370</v>
+      </c>
+      <c r="G38" s="29" t="s">
+        <v>371</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>331</v>
+        <v>372</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L38" s="4" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="4" t="s">
-        <v>300</v>
+        <v>341</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>249</v>
+        <v>290</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>275</v>
+        <v>316</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>301</v>
+        <v>342</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="G39" s="27" t="s">
-        <v>333</v>
+        <v>373</v>
+      </c>
+      <c r="G39" s="29" t="s">
+        <v>374</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>334</v>
+        <v>375</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K39" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L39" s="4" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="4" t="s">
-        <v>300</v>
+        <v>341</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>249</v>
+        <v>290</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>275</v>
+        <v>316</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>301</v>
+        <v>342</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>335</v>
-      </c>
-      <c r="G40" s="27" t="s">
-        <v>336</v>
+        <v>376</v>
+      </c>
+      <c r="G40" s="29" t="s">
+        <v>377</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>337</v>
+        <v>378</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K40" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L40" s="4" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="4" t="s">
-        <v>300</v>
+        <v>341</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>249</v>
+        <v>290</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>284</v>
+        <v>325</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>301</v>
+        <v>342</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>338</v>
-      </c>
-      <c r="G41" s="27" t="s">
-        <v>339</v>
+        <v>379</v>
+      </c>
+      <c r="G41" s="29" t="s">
+        <v>380</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>340</v>
+        <v>381</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K41" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L41" s="4" t="s">
-        <v>341</v>
+        <v>382</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="4" t="s">
-        <v>300</v>
+        <v>341</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>249</v>
+        <v>290</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>284</v>
+        <v>325</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>301</v>
+        <v>342</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>342</v>
-      </c>
-      <c r="G42" s="27" t="s">
-        <v>343</v>
+        <v>383</v>
+      </c>
+      <c r="G42" s="29" t="s">
+        <v>384</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>344</v>
+        <v>385</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K42" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L42" s="4" t="s">
-        <v>345</v>
+        <v>386</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="4" t="s">
-        <v>300</v>
+        <v>341</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>249</v>
+        <v>290</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>346</v>
+        <v>387</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>347</v>
+        <v>388</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>348</v>
-      </c>
-      <c r="G43" s="27" t="s">
-        <v>349</v>
+        <v>389</v>
+      </c>
+      <c r="G43" s="29" t="s">
+        <v>390</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>181</v>
+        <v>222</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>350</v>
+        <v>391</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K43" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L43" s="4" t="s">
-        <v>351</v>
+        <v>392</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="4" t="s">
-        <v>352</v>
+        <v>393</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>241</v>
+        <v>282</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>178</v>
+        <v>219</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>353</v>
+        <v>394</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>354</v>
-      </c>
-      <c r="G44" s="27" t="s">
-        <v>355</v>
+        <v>395</v>
+      </c>
+      <c r="G44" s="29" t="s">
+        <v>396</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>181</v>
+        <v>222</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>356</v>
+        <v>397</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="K44" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L44" s="4" t="s">
-        <v>357</v>
+        <v>398</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="4" t="s">
-        <v>352</v>
+        <v>393</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>241</v>
+        <v>282</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>178</v>
+        <v>219</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>353</v>
+        <v>394</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>358</v>
-      </c>
-      <c r="G45" s="27" t="s">
-        <v>359</v>
+        <v>399</v>
+      </c>
+      <c r="G45" s="29" t="s">
+        <v>400</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>360</v>
+        <v>401</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L45" s="4" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="4" t="s">
-        <v>352</v>
+        <v>393</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>241</v>
+        <v>282</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>209</v>
+        <v>250</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>361</v>
+        <v>402</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>362</v>
-      </c>
-      <c r="G46" s="27" t="s">
-        <v>363</v>
+        <v>403</v>
+      </c>
+      <c r="G46" s="29" t="s">
+        <v>404</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>202</v>
+        <v>243</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>364</v>
+        <v>405</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="K46" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L46" s="4" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="4" t="s">
-        <v>352</v>
+        <v>393</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>241</v>
+        <v>282</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>308</v>
+        <v>349</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>365</v>
+        <v>406</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>366</v>
-      </c>
-      <c r="G47" s="27" t="s">
-        <v>367</v>
+        <v>407</v>
+      </c>
+      <c r="G47" s="29" t="s">
+        <v>408</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>368</v>
+        <v>409</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="K47" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L47" s="4" t="s">
-        <v>369</v>
+        <v>410</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="4" t="s">
-        <v>352</v>
+        <v>393</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>241</v>
+        <v>282</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>255</v>
+        <v>296</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>353</v>
+        <v>394</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>370</v>
-      </c>
-      <c r="G48" s="27" t="s">
-        <v>371</v>
+        <v>411</v>
+      </c>
+      <c r="G48" s="29" t="s">
+        <v>412</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>181</v>
+        <v>222</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>372</v>
+        <v>413</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="K48" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L48" s="4" t="s">
-        <v>373</v>
+        <v>414</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="4" t="s">
-        <v>352</v>
+        <v>393</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>241</v>
+        <v>282</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>255</v>
+        <v>296</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>353</v>
+        <v>394</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>374</v>
-      </c>
-      <c r="G49" s="27" t="s">
-        <v>375</v>
+        <v>415</v>
+      </c>
+      <c r="G49" s="29" t="s">
+        <v>416</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>181</v>
+        <v>222</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>376</v>
+        <v>417</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="K49" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L49" s="4" t="s">
-        <v>373</v>
+        <v>414</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="4" t="s">
-        <v>352</v>
+        <v>393</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>241</v>
+        <v>282</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>260</v>
+        <v>301</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>377</v>
+        <v>418</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>378</v>
-      </c>
-      <c r="G50" s="27" t="s">
-        <v>379</v>
+        <v>419</v>
+      </c>
+      <c r="G50" s="29" t="s">
+        <v>420</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I50" s="4" t="s">
-        <v>380</v>
+        <v>421</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="K50" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L50" s="4" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="4" t="s">
-        <v>352</v>
+        <v>393</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>241</v>
+        <v>282</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>266</v>
+        <v>307</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>381</v>
+        <v>422</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>382</v>
-      </c>
-      <c r="G51" s="27" t="s">
-        <v>383</v>
+        <v>423</v>
+      </c>
+      <c r="G51" s="29" t="s">
+        <v>424</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>384</v>
+        <v>425</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="K51" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L51" s="4" t="s">
-        <v>385</v>
+        <v>426</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="4" t="s">
-        <v>352</v>
+        <v>393</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>241</v>
+        <v>282</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>275</v>
+        <v>316</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>353</v>
+        <v>394</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>386</v>
-      </c>
-      <c r="G52" s="27" t="s">
-        <v>387</v>
+        <v>427</v>
+      </c>
+      <c r="G52" s="29" t="s">
+        <v>428</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>181</v>
+        <v>222</v>
       </c>
       <c r="I52" s="4" t="s">
-        <v>388</v>
+        <v>429</v>
       </c>
       <c r="J52" s="4" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="K52" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L52" s="4" t="s">
-        <v>373</v>
+        <v>414</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="4" t="s">
-        <v>352</v>
+        <v>393</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>241</v>
+        <v>282</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>275</v>
+        <v>316</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>389</v>
+        <v>430</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>390</v>
-      </c>
-      <c r="G53" s="27" t="s">
-        <v>391</v>
+        <v>431</v>
+      </c>
+      <c r="G53" s="29" t="s">
+        <v>432</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>181</v>
+        <v>222</v>
       </c>
       <c r="I53" s="4" t="s">
-        <v>392</v>
+        <v>433</v>
       </c>
       <c r="J53" s="4" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="K53" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L53" s="4" t="s">
-        <v>393</v>
+        <v>434</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="4" t="s">
-        <v>352</v>
+        <v>393</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>241</v>
+        <v>282</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>284</v>
+        <v>325</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>353</v>
+        <v>394</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>394</v>
-      </c>
-      <c r="G54" s="27" t="s">
-        <v>395</v>
+        <v>435</v>
+      </c>
+      <c r="G54" s="29" t="s">
+        <v>436</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>181</v>
+        <v>222</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>396</v>
+        <v>437</v>
       </c>
       <c r="J54" s="4" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="K54" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L54" s="4" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="4" t="s">
-        <v>352</v>
+        <v>393</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>241</v>
+        <v>282</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>346</v>
+        <v>387</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>397</v>
+        <v>438</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>398</v>
-      </c>
-      <c r="G55" s="27" t="s">
-        <v>399</v>
+        <v>439</v>
+      </c>
+      <c r="G55" s="29" t="s">
+        <v>440</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>400</v>
+        <v>441</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="K55" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L55" s="4" t="s">
-        <v>401</v>
+        <v>442</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="4" t="s">
-        <v>352</v>
+        <v>393</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>241</v>
+        <v>282</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>346</v>
+        <v>387</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>402</v>
+        <v>443</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>403</v>
-      </c>
-      <c r="G56" s="27" t="s">
-        <v>404</v>
+        <v>444</v>
+      </c>
+      <c r="G56" s="29" t="s">
+        <v>445</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>202</v>
+        <v>243</v>
       </c>
       <c r="I56" s="4" t="s">
-        <v>405</v>
+        <v>446</v>
       </c>
       <c r="J56" s="4" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="K56" s="4" t="s">
-        <v>312</v>
+        <v>353</v>
       </c>
       <c r="L56" s="4" t="s">
-        <v>406</v>
+        <v>447</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="4" t="s">
-        <v>352</v>
+        <v>393</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>241</v>
+        <v>282</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>407</v>
+        <v>448</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>408</v>
+        <v>449</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>409</v>
-      </c>
-      <c r="G57" s="27" t="s">
-        <v>410</v>
+        <v>450</v>
+      </c>
+      <c r="G57" s="29" t="s">
+        <v>451</v>
       </c>
       <c r="H57" s="4" t="s">
-        <v>181</v>
+        <v>222</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>411</v>
+        <v>452</v>
       </c>
       <c r="J57" s="4" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="K57" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L57" s="4" t="s">
-        <v>412</v>
+        <v>453</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="4" t="s">
-        <v>413</v>
+        <v>454</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>233</v>
+        <v>274</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>178</v>
+        <v>219</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>414</v>
+        <v>455</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>415</v>
-      </c>
-      <c r="G58" s="27" t="s">
-        <v>416</v>
+        <v>456</v>
+      </c>
+      <c r="G58" s="29" t="s">
+        <v>457</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I58" s="4" t="s">
-        <v>417</v>
+        <v>458</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="K58" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L58" s="4" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="4" t="s">
-        <v>413</v>
+        <v>454</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>233</v>
+        <v>274</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>178</v>
+        <v>219</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>414</v>
+        <v>455</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>418</v>
-      </c>
-      <c r="G59" s="27" t="s">
-        <v>419</v>
+        <v>459</v>
+      </c>
+      <c r="G59" s="29" t="s">
+        <v>460</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>181</v>
+        <v>222</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>420</v>
+        <v>461</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="K59" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L59" s="4" t="s">
-        <v>421</v>
+        <v>462</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B60" s="4" t="s">
-        <v>413</v>
+        <v>454</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>233</v>
+        <v>274</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>209</v>
+        <v>250</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>422</v>
+        <v>463</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>423</v>
-      </c>
-      <c r="G60" s="27" t="s">
-        <v>424</v>
+        <v>464</v>
+      </c>
+      <c r="G60" s="29" t="s">
+        <v>465</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>425</v>
+        <v>466</v>
       </c>
       <c r="J60" s="4" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="K60" s="4" t="s">
-        <v>312</v>
+        <v>353</v>
       </c>
       <c r="L60" s="4" t="s">
-        <v>426</v>
+        <v>467</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B61" s="4" t="s">
-        <v>413</v>
+        <v>454</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>233</v>
+        <v>274</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>308</v>
+        <v>349</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>427</v>
+        <v>468</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>428</v>
-      </c>
-      <c r="G61" s="27" t="s">
-        <v>429</v>
+        <v>469</v>
+      </c>
+      <c r="G61" s="29" t="s">
+        <v>470</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I61" s="4" t="s">
-        <v>430</v>
+        <v>471</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="K61" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L61" s="4" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B62" s="4" t="s">
-        <v>413</v>
+        <v>454</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>233</v>
+        <v>274</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>308</v>
+        <v>349</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>431</v>
+        <v>472</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>432</v>
-      </c>
-      <c r="G62" s="27" t="s">
-        <v>433</v>
+        <v>473</v>
+      </c>
+      <c r="G62" s="29" t="s">
+        <v>474</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I62" s="4" t="s">
-        <v>434</v>
+        <v>475</v>
       </c>
       <c r="J62" s="4" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="K62" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L62" s="4" t="s">
-        <v>435</v>
+        <v>476</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B63" s="4" t="s">
-        <v>413</v>
+        <v>454</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>233</v>
+        <v>274</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>255</v>
+        <v>296</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>414</v>
+        <v>455</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>436</v>
-      </c>
-      <c r="G63" s="27" t="s">
-        <v>437</v>
+        <v>477</v>
+      </c>
+      <c r="G63" s="29" t="s">
+        <v>478</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>181</v>
+        <v>222</v>
       </c>
       <c r="I63" s="4" t="s">
-        <v>438</v>
+        <v>479</v>
       </c>
       <c r="J63" s="4" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="K63" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L63" s="4" t="s">
-        <v>439</v>
+        <v>480</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B64" s="4" t="s">
-        <v>413</v>
+        <v>454</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>233</v>
+        <v>274</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>260</v>
+        <v>301</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>440</v>
+        <v>481</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>441</v>
-      </c>
-      <c r="G64" s="27" t="s">
-        <v>442</v>
+        <v>482</v>
+      </c>
+      <c r="G64" s="29" t="s">
+        <v>483</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>443</v>
+        <v>484</v>
       </c>
       <c r="J64" s="4" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="K64" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L64" s="4" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B65" s="4" t="s">
-        <v>413</v>
+        <v>454</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>233</v>
+        <v>274</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>266</v>
+        <v>307</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>444</v>
+        <v>485</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>445</v>
-      </c>
-      <c r="G65" s="27" t="s">
-        <v>446</v>
+        <v>486</v>
+      </c>
+      <c r="G65" s="29" t="s">
+        <v>487</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>447</v>
+        <v>488</v>
       </c>
       <c r="J65" s="4" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="K65" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L65" s="4" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B66" s="4" t="s">
-        <v>413</v>
+        <v>454</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>233</v>
+        <v>274</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>266</v>
+        <v>307</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>444</v>
+        <v>485</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>448</v>
-      </c>
-      <c r="G66" s="27" t="s">
-        <v>449</v>
+        <v>489</v>
+      </c>
+      <c r="G66" s="29" t="s">
+        <v>490</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>181</v>
+        <v>222</v>
       </c>
       <c r="I66" s="4" t="s">
-        <v>450</v>
+        <v>491</v>
       </c>
       <c r="J66" s="4" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="K66" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L66" s="4" t="s">
-        <v>451</v>
+        <v>492</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B67" s="4" t="s">
-        <v>413</v>
+        <v>454</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>233</v>
+        <v>274</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>275</v>
+        <v>316</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>414</v>
+        <v>455</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>452</v>
-      </c>
-      <c r="G67" s="27" t="s">
-        <v>453</v>
+        <v>493</v>
+      </c>
+      <c r="G67" s="29" t="s">
+        <v>494</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>181</v>
+        <v>222</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>454</v>
+        <v>495</v>
       </c>
       <c r="J67" s="4" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="K67" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L67" s="4" t="s">
-        <v>455</v>
+        <v>496</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B68" s="4" t="s">
-        <v>413</v>
+        <v>454</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>233</v>
+        <v>274</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>284</v>
+        <v>325</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>414</v>
+        <v>455</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>456</v>
-      </c>
-      <c r="G68" s="27" t="s">
-        <v>457</v>
+        <v>497</v>
+      </c>
+      <c r="G68" s="29" t="s">
+        <v>498</v>
       </c>
       <c r="H68" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I68" s="4" t="s">
-        <v>458</v>
+        <v>499</v>
       </c>
       <c r="J68" s="4" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="K68" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L68" s="4" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B69" s="4" t="s">
-        <v>413</v>
+        <v>454</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>233</v>
+        <v>274</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>284</v>
+        <v>325</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>414</v>
+        <v>455</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>459</v>
-      </c>
-      <c r="G69" s="27" t="s">
-        <v>460</v>
+        <v>500</v>
+      </c>
+      <c r="G69" s="29" t="s">
+        <v>501</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I69" s="4" t="s">
-        <v>461</v>
+        <v>502</v>
       </c>
       <c r="J69" s="4" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="K69" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L69" s="4" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B70" s="4" t="s">
-        <v>413</v>
+        <v>454</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>233</v>
+        <v>274</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>346</v>
+        <v>387</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>462</v>
+        <v>503</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>463</v>
-      </c>
-      <c r="G70" s="27" t="s">
-        <v>464</v>
+        <v>504</v>
+      </c>
+      <c r="G70" s="29" t="s">
+        <v>505</v>
       </c>
       <c r="H70" s="4" t="s">
-        <v>202</v>
+        <v>243</v>
       </c>
       <c r="I70" s="4" t="s">
-        <v>465</v>
+        <v>506</v>
       </c>
       <c r="J70" s="4" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="K70" s="4" t="s">
-        <v>312</v>
+        <v>353</v>
       </c>
       <c r="L70" s="4" t="s">
-        <v>466</v>
+        <v>507</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B71" s="4" t="s">
-        <v>413</v>
+        <v>454</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>233</v>
+        <v>274</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>346</v>
+        <v>387</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>467</v>
+        <v>508</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>468</v>
-      </c>
-      <c r="G71" s="27" t="s">
-        <v>469</v>
+        <v>509</v>
+      </c>
+      <c r="G71" s="29" t="s">
+        <v>510</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I71" s="4" t="s">
-        <v>470</v>
+        <v>511</v>
       </c>
       <c r="J71" s="4" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="K71" s="4" t="s">
-        <v>312</v>
+        <v>353</v>
       </c>
       <c r="L71" s="4" t="s">
-        <v>471</v>
+        <v>512</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B72" s="4" t="s">
-        <v>413</v>
+        <v>454</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>233</v>
+        <v>274</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>407</v>
+        <v>448</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>422</v>
+        <v>463</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>472</v>
-      </c>
-      <c r="G72" s="27" t="s">
-        <v>473</v>
+        <v>513</v>
+      </c>
+      <c r="G72" s="29" t="s">
+        <v>514</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I72" s="4" t="s">
-        <v>474</v>
+        <v>515</v>
       </c>
       <c r="J72" s="4" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="K72" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L72" s="4" t="s">
-        <v>475</v>
+        <v>516</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B73" s="4" t="s">
-        <v>476</v>
+        <v>517</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>177</v>
+        <v>218</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>178</v>
+        <v>219</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>194</v>
+        <v>235</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>477</v>
-      </c>
-      <c r="G73" s="27" t="s">
-        <v>478</v>
+        <v>518</v>
+      </c>
+      <c r="G73" s="29" t="s">
+        <v>519</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>181</v>
+        <v>222</v>
       </c>
       <c r="I73" s="4" t="s">
-        <v>479</v>
+        <v>520</v>
       </c>
       <c r="J73" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K73" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L73" s="4" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B74" s="4" t="s">
-        <v>476</v>
+        <v>517</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>177</v>
+        <v>218</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>308</v>
+        <v>349</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>480</v>
+        <v>521</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>481</v>
-      </c>
-      <c r="G74" s="27" t="s">
-        <v>482</v>
+        <v>522</v>
+      </c>
+      <c r="G74" s="29" t="s">
+        <v>523</v>
       </c>
       <c r="H74" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I74" s="4" t="s">
-        <v>483</v>
+        <v>524</v>
       </c>
       <c r="J74" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K74" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L74" s="4" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B75" s="4" t="s">
-        <v>476</v>
+        <v>517</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>177</v>
+        <v>218</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>308</v>
+        <v>349</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>480</v>
+        <v>521</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>484</v>
-      </c>
-      <c r="G75" s="27" t="s">
-        <v>485</v>
+        <v>525</v>
+      </c>
+      <c r="G75" s="29" t="s">
+        <v>526</v>
       </c>
       <c r="H75" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I75" s="4" t="s">
-        <v>486</v>
+        <v>527</v>
       </c>
       <c r="J75" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K75" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L75" s="4" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B76" s="4" t="s">
-        <v>476</v>
+        <v>517</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>177</v>
+        <v>218</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>260</v>
+        <v>301</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>487</v>
+        <v>528</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>488</v>
-      </c>
-      <c r="G76" s="27" t="s">
-        <v>489</v>
+        <v>529</v>
+      </c>
+      <c r="G76" s="29" t="s">
+        <v>530</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I76" s="4" t="s">
-        <v>490</v>
+        <v>531</v>
       </c>
       <c r="J76" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K76" s="4" t="s">
-        <v>312</v>
+        <v>353</v>
       </c>
       <c r="L76" s="4" t="s">
-        <v>491</v>
+        <v>532</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B77" s="4" t="s">
-        <v>476</v>
+        <v>517</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>259</v>
+        <v>300</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>266</v>
+        <v>307</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>492</v>
+        <v>533</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>493</v>
-      </c>
-      <c r="G77" s="27" t="s">
-        <v>494</v>
+        <v>534</v>
+      </c>
+      <c r="G77" s="29" t="s">
+        <v>535</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>181</v>
+        <v>222</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>495</v>
+        <v>536</v>
       </c>
       <c r="J77" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K77" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L77" s="4" t="s">
-        <v>496</v>
+        <v>537</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B78" s="4" t="s">
-        <v>476</v>
+        <v>517</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>177</v>
+        <v>218</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>275</v>
+        <v>316</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>497</v>
+        <v>538</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>498</v>
-      </c>
-      <c r="G78" s="27" t="s">
-        <v>499</v>
+        <v>539</v>
+      </c>
+      <c r="G78" s="29" t="s">
+        <v>540</v>
       </c>
       <c r="H78" s="4" t="s">
-        <v>181</v>
+        <v>222</v>
       </c>
       <c r="I78" s="4" t="s">
-        <v>500</v>
+        <v>541</v>
       </c>
       <c r="J78" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K78" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L78" s="4" t="s">
-        <v>501</v>
+        <v>542</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B79" s="4" t="s">
-        <v>476</v>
+        <v>517</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>177</v>
+        <v>218</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>284</v>
+        <v>325</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>177</v>
+        <v>218</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>502</v>
-      </c>
-      <c r="G79" s="27" t="s">
-        <v>503</v>
+        <v>543</v>
+      </c>
+      <c r="G79" s="29" t="s">
+        <v>544</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>181</v>
+        <v>222</v>
       </c>
       <c r="I79" s="4" t="s">
-        <v>504</v>
+        <v>545</v>
       </c>
       <c r="J79" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K79" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L79" s="4" t="s">
-        <v>505</v>
+        <v>546</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B80" s="4" t="s">
-        <v>476</v>
+        <v>517</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>177</v>
+        <v>218</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>346</v>
+        <v>387</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>506</v>
+        <v>547</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>507</v>
-      </c>
-      <c r="G80" s="27" t="s">
-        <v>508</v>
+        <v>548</v>
+      </c>
+      <c r="G80" s="29" t="s">
+        <v>549</v>
       </c>
       <c r="H80" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I80" s="4" t="s">
-        <v>509</v>
+        <v>550</v>
       </c>
       <c r="J80" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K80" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L80" s="4" t="s">
-        <v>510</v>
+        <v>551</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B81" s="4" t="s">
-        <v>511</v>
+        <v>552</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>177</v>
+        <v>218</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>178</v>
+        <v>219</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>194</v>
+        <v>235</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>512</v>
-      </c>
-      <c r="G81" s="27" t="s">
-        <v>513</v>
+        <v>553</v>
+      </c>
+      <c r="G81" s="29" t="s">
+        <v>554</v>
       </c>
       <c r="H81" s="4" t="s">
-        <v>181</v>
+        <v>222</v>
       </c>
       <c r="I81" s="4" t="s">
-        <v>514</v>
+        <v>555</v>
       </c>
       <c r="J81" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K81" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L81" s="4" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B82" s="4" t="s">
-        <v>511</v>
+        <v>552</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>177</v>
+        <v>218</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>308</v>
+        <v>349</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>515</v>
+        <v>556</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>516</v>
-      </c>
-      <c r="G82" s="27" t="s">
-        <v>517</v>
+        <v>557</v>
+      </c>
+      <c r="G82" s="29" t="s">
+        <v>558</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I82" s="4" t="s">
-        <v>518</v>
+        <v>559</v>
       </c>
       <c r="J82" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K82" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L82" s="4" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B83" s="4" t="s">
-        <v>511</v>
+        <v>552</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>177</v>
+        <v>218</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>308</v>
+        <v>349</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>515</v>
+        <v>556</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>519</v>
-      </c>
-      <c r="G83" s="27" t="s">
-        <v>520</v>
+        <v>560</v>
+      </c>
+      <c r="G83" s="29" t="s">
+        <v>561</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>181</v>
+        <v>222</v>
       </c>
       <c r="I83" s="4" t="s">
-        <v>521</v>
+        <v>562</v>
       </c>
       <c r="J83" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K83" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L83" s="4" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B84" s="4" t="s">
-        <v>511</v>
+        <v>552</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>177</v>
+        <v>218</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>275</v>
+        <v>316</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>522</v>
+        <v>563</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>523</v>
+        <v>564</v>
       </c>
       <c r="G84" s="4"/>
       <c r="H84" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I84" s="4" t="s">
-        <v>524</v>
+        <v>565</v>
       </c>
       <c r="J84" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K84" s="4" t="s">
-        <v>312</v>
+        <v>353</v>
       </c>
       <c r="L84" s="4" t="s">
-        <v>525</v>
+        <v>566</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B85" s="4" t="s">
-        <v>511</v>
+        <v>552</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>177</v>
+        <v>218</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>284</v>
+        <v>325</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>194</v>
+        <v>235</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>526</v>
-      </c>
-      <c r="G85" s="27" t="s">
-        <v>527</v>
+        <v>567</v>
+      </c>
+      <c r="G85" s="29" t="s">
+        <v>568</v>
       </c>
       <c r="H85" s="4" t="s">
-        <v>181</v>
+        <v>222</v>
       </c>
       <c r="I85" s="4" t="s">
-        <v>528</v>
+        <v>569</v>
       </c>
       <c r="J85" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K85" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L85" s="4" t="s">
-        <v>529</v>
+        <v>570</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B86" s="4" t="s">
-        <v>511</v>
+        <v>552</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>177</v>
+        <v>218</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>346</v>
+        <v>387</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>530</v>
+        <v>571</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>531</v>
-      </c>
-      <c r="G86" s="27" t="s">
-        <v>532</v>
+        <v>572</v>
+      </c>
+      <c r="G86" s="29" t="s">
+        <v>573</v>
       </c>
       <c r="H86" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I86" s="4" t="s">
-        <v>533</v>
+        <v>574</v>
       </c>
       <c r="J86" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K86" s="4" t="s">
-        <v>312</v>
+        <v>353</v>
       </c>
       <c r="L86" s="4" t="s">
-        <v>534</v>
+        <v>575</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B87" s="4" t="s">
-        <v>535</v>
+        <v>576</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>198</v>
+        <v>239</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>178</v>
+        <v>219</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>536</v>
+        <v>577</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>537</v>
-      </c>
-      <c r="G87" s="27" t="s">
-        <v>538</v>
+        <v>578</v>
+      </c>
+      <c r="G87" s="29" t="s">
+        <v>579</v>
       </c>
       <c r="H87" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I87" s="4" t="s">
-        <v>539</v>
+        <v>580</v>
       </c>
       <c r="J87" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K87" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L87" s="4" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B88" s="4" t="s">
-        <v>535</v>
+        <v>576</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>198</v>
+        <v>239</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>308</v>
+        <v>349</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>540</v>
+        <v>581</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>541</v>
+        <v>582</v>
       </c>
       <c r="G88" s="4"/>
       <c r="H88" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I88" s="4" t="s">
-        <v>542</v>
+        <v>583</v>
       </c>
       <c r="J88" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K88" s="4" t="s">
-        <v>312</v>
+        <v>353</v>
       </c>
       <c r="L88" s="4" t="s">
-        <v>543</v>
+        <v>584</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B89" s="4" t="s">
-        <v>535</v>
+        <v>576</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>198</v>
+        <v>239</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>260</v>
+        <v>301</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>544</v>
+        <v>585</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>545</v>
-      </c>
-      <c r="G89" s="27" t="s">
-        <v>546</v>
+        <v>586</v>
+      </c>
+      <c r="G89" s="29" t="s">
+        <v>587</v>
       </c>
       <c r="H89" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I89" s="4" t="s">
-        <v>547</v>
+        <v>588</v>
       </c>
       <c r="J89" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K89" s="4" t="s">
-        <v>312</v>
+        <v>353</v>
       </c>
       <c r="L89" s="4" t="s">
-        <v>548</v>
+        <v>589</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B90" s="4" t="s">
-        <v>535</v>
+        <v>576</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>198</v>
+        <v>239</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>275</v>
+        <v>316</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>549</v>
+        <v>590</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>550</v>
-      </c>
-      <c r="G90" s="27" t="s">
-        <v>551</v>
+        <v>591</v>
+      </c>
+      <c r="G90" s="29" t="s">
+        <v>592</v>
       </c>
       <c r="H90" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I90" s="4" t="s">
-        <v>552</v>
+        <v>593</v>
       </c>
       <c r="J90" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K90" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L90" s="4" t="s">
-        <v>553</v>
+        <v>594</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B91" s="4" t="s">
-        <v>535</v>
+        <v>576</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>198</v>
+        <v>239</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>346</v>
+        <v>387</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>554</v>
+        <v>595</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>555</v>
-      </c>
-      <c r="G91" s="27" t="s">
-        <v>556</v>
+        <v>596</v>
+      </c>
+      <c r="G91" s="29" t="s">
+        <v>597</v>
       </c>
       <c r="H91" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I91" s="4" t="s">
-        <v>557</v>
+        <v>598</v>
       </c>
       <c r="J91" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K91" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L91" s="4" t="s">
-        <v>558</v>
+        <v>599</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B92" s="4" t="s">
-        <v>535</v>
+        <v>576</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>198</v>
+        <v>239</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>346</v>
+        <v>387</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>559</v>
+        <v>600</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>531</v>
-      </c>
-      <c r="G92" s="27" t="s">
-        <v>560</v>
+        <v>572</v>
+      </c>
+      <c r="G92" s="29" t="s">
+        <v>601</v>
       </c>
       <c r="H92" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I92" s="4" t="s">
-        <v>561</v>
+        <v>602</v>
       </c>
       <c r="J92" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K92" s="4" t="s">
-        <v>312</v>
+        <v>353</v>
       </c>
       <c r="L92" s="4" t="s">
-        <v>562</v>
+        <v>603</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B93" s="4" t="s">
-        <v>563</v>
+        <v>604</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>233</v>
+        <v>274</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>178</v>
+        <v>219</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>564</v>
+        <v>605</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>178</v>
-      </c>
-      <c r="G93" s="27" t="s">
-        <v>565</v>
+        <v>219</v>
+      </c>
+      <c r="G93" s="29" t="s">
+        <v>606</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I93" s="4" t="s">
-        <v>566</v>
+        <v>607</v>
       </c>
       <c r="J93" s="4" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="K93" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L93" s="4" t="s">
-        <v>373</v>
+        <v>414</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B94" s="4" t="s">
-        <v>563</v>
+        <v>604</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>233</v>
+        <v>274</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>178</v>
+        <v>219</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>564</v>
+        <v>605</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>567</v>
-      </c>
-      <c r="G94" s="27" t="s">
-        <v>568</v>
+        <v>608</v>
+      </c>
+      <c r="G94" s="29" t="s">
+        <v>609</v>
       </c>
       <c r="H94" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I94" s="4" t="s">
-        <v>569</v>
+        <v>610</v>
       </c>
       <c r="J94" s="4" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="K94" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L94" s="4" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B95" s="4" t="s">
-        <v>563</v>
+        <v>604</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>233</v>
+        <v>274</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>209</v>
+        <v>250</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>570</v>
+        <v>611</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>571</v>
-      </c>
-      <c r="G95" s="27" t="s">
-        <v>572</v>
+        <v>612</v>
+      </c>
+      <c r="G95" s="29" t="s">
+        <v>613</v>
       </c>
       <c r="H95" s="4" t="s">
-        <v>202</v>
+        <v>243</v>
       </c>
       <c r="I95" s="4" t="s">
-        <v>573</v>
+        <v>614</v>
       </c>
       <c r="J95" s="4" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="K95" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L95" s="4" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B96" s="4" t="s">
-        <v>563</v>
+        <v>604</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>233</v>
+        <v>274</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>308</v>
+        <v>349</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>574</v>
+        <v>615</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>575</v>
-      </c>
-      <c r="G96" s="27" t="s">
-        <v>576</v>
+        <v>616</v>
+      </c>
+      <c r="G96" s="29" t="s">
+        <v>617</v>
       </c>
       <c r="H96" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I96" s="4" t="s">
-        <v>577</v>
+        <v>618</v>
       </c>
       <c r="J96" s="4" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="K96" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L96" s="4" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B97" s="4" t="s">
-        <v>563</v>
+        <v>604</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>233</v>
+        <v>274</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>260</v>
+        <v>301</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>578</v>
+        <v>619</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>579</v>
-      </c>
-      <c r="G97" s="27" t="s">
-        <v>580</v>
+        <v>620</v>
+      </c>
+      <c r="G97" s="29" t="s">
+        <v>621</v>
       </c>
       <c r="H97" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I97" s="4" t="s">
-        <v>581</v>
+        <v>622</v>
       </c>
       <c r="J97" s="4" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="K97" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L97" s="4" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B98" s="4" t="s">
-        <v>563</v>
+        <v>604</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>233</v>
+        <v>274</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>266</v>
+        <v>307</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>582</v>
+        <v>623</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>583</v>
-      </c>
-      <c r="G98" s="27" t="s">
-        <v>584</v>
+        <v>624</v>
+      </c>
+      <c r="G98" s="29" t="s">
+        <v>625</v>
       </c>
       <c r="H98" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I98" s="4" t="s">
-        <v>585</v>
+        <v>626</v>
       </c>
       <c r="J98" s="4" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="K98" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L98" s="4" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B99" s="4" t="s">
-        <v>563</v>
+        <v>604</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>233</v>
+        <v>274</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>275</v>
+        <v>316</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>564</v>
+        <v>605</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>586</v>
-      </c>
-      <c r="G99" s="27" t="s">
-        <v>587</v>
+        <v>627</v>
+      </c>
+      <c r="G99" s="29" t="s">
+        <v>628</v>
       </c>
       <c r="H99" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I99" s="4" t="s">
-        <v>588</v>
+        <v>629</v>
       </c>
       <c r="J99" s="4" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="K99" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L99" s="4" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B100" s="4" t="s">
-        <v>563</v>
+        <v>604</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>233</v>
+        <v>274</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>275</v>
+        <v>316</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>564</v>
+        <v>605</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>589</v>
-      </c>
-      <c r="G100" s="27" t="s">
-        <v>590</v>
+        <v>630</v>
+      </c>
+      <c r="G100" s="29" t="s">
+        <v>631</v>
       </c>
       <c r="H100" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I100" s="4" t="s">
-        <v>591</v>
+        <v>632</v>
       </c>
       <c r="J100" s="4" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="K100" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L100" s="4" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B101" s="4" t="s">
-        <v>563</v>
+        <v>604</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>233</v>
+        <v>274</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>284</v>
+        <v>325</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>564</v>
+        <v>605</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>592</v>
-      </c>
-      <c r="G101" s="27" t="s">
-        <v>593</v>
+        <v>633</v>
+      </c>
+      <c r="G101" s="29" t="s">
+        <v>634</v>
       </c>
       <c r="H101" s="4" t="s">
-        <v>181</v>
+        <v>222</v>
       </c>
       <c r="I101" s="4" t="s">
-        <v>594</v>
+        <v>635</v>
       </c>
       <c r="J101" s="4" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="K101" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L101" s="4" t="s">
-        <v>595</v>
+        <v>636</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B102" s="4" t="s">
-        <v>563</v>
+        <v>604</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>233</v>
+        <v>274</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>284</v>
+        <v>325</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>564</v>
+        <v>605</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>596</v>
-      </c>
-      <c r="G102" s="27" t="s">
-        <v>597</v>
+        <v>637</v>
+      </c>
+      <c r="G102" s="29" t="s">
+        <v>638</v>
       </c>
       <c r="H102" s="4" t="s">
-        <v>181</v>
+        <v>222</v>
       </c>
       <c r="I102" s="4" t="s">
-        <v>598</v>
+        <v>639</v>
       </c>
       <c r="J102" s="4" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="K102" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L102" s="4" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B103" s="4" t="s">
-        <v>563</v>
+        <v>604</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>233</v>
+        <v>274</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>346</v>
+        <v>387</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>599</v>
+        <v>640</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>600</v>
-      </c>
-      <c r="G103" s="27" t="s">
-        <v>601</v>
+        <v>641</v>
+      </c>
+      <c r="G103" s="29" t="s">
+        <v>642</v>
       </c>
       <c r="H103" s="4" t="s">
-        <v>181</v>
+        <v>222</v>
       </c>
       <c r="I103" s="4" t="s">
-        <v>602</v>
+        <v>643</v>
       </c>
       <c r="J103" s="4" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="K103" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L103" s="4" t="s">
-        <v>603</v>
+        <v>644</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B104" s="4" t="s">
-        <v>563</v>
+        <v>604</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>233</v>
+        <v>274</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>346</v>
+        <v>387</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>604</v>
+        <v>645</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>605</v>
-      </c>
-      <c r="G104" s="27" t="s">
-        <v>606</v>
+        <v>646</v>
+      </c>
+      <c r="G104" s="29" t="s">
+        <v>647</v>
       </c>
       <c r="H104" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I104" s="4" t="s">
-        <v>607</v>
+        <v>648</v>
       </c>
       <c r="J104" s="4" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="K104" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L104" s="4" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B105" s="4" t="s">
-        <v>563</v>
+        <v>604</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>233</v>
+        <v>274</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>407</v>
+        <v>448</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>570</v>
+        <v>611</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>608</v>
-      </c>
-      <c r="G105" s="27" t="s">
-        <v>609</v>
+        <v>649</v>
+      </c>
+      <c r="G105" s="29" t="s">
+        <v>650</v>
       </c>
       <c r="H105" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I105" s="4" t="s">
-        <v>610</v>
+        <v>651</v>
       </c>
       <c r="J105" s="4" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="K105" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L105" s="4" t="s">
-        <v>611</v>
+        <v>652</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B106" s="4" t="s">
-        <v>612</v>
+        <v>653</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>241</v>
+        <v>282</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>178</v>
+        <v>219</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>613</v>
+        <v>654</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>614</v>
-      </c>
-      <c r="G106" s="27" t="s">
-        <v>615</v>
+        <v>655</v>
+      </c>
+      <c r="G106" s="29" t="s">
+        <v>656</v>
       </c>
       <c r="H106" s="4" t="s">
-        <v>181</v>
+        <v>222</v>
       </c>
       <c r="I106" s="4" t="s">
-        <v>616</v>
+        <v>657</v>
       </c>
       <c r="J106" s="4" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="K106" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L106" s="4" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B107" s="4" t="s">
-        <v>612</v>
+        <v>653</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>241</v>
+        <v>282</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>209</v>
+        <v>250</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>617</v>
+        <v>658</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>618</v>
-      </c>
-      <c r="G107" s="27" t="s">
-        <v>619</v>
+        <v>659</v>
+      </c>
+      <c r="G107" s="29" t="s">
+        <v>660</v>
       </c>
       <c r="H107" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I107" s="4" t="s">
-        <v>620</v>
+        <v>661</v>
       </c>
       <c r="J107" s="4" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="K107" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L107" s="4" t="s">
-        <v>621</v>
+        <v>662</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B108" s="4" t="s">
-        <v>612</v>
+        <v>653</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>241</v>
+        <v>282</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>308</v>
+        <v>349</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>622</v>
+        <v>663</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>623</v>
-      </c>
-      <c r="G108" s="27" t="s">
-        <v>624</v>
+        <v>664</v>
+      </c>
+      <c r="G108" s="29" t="s">
+        <v>665</v>
       </c>
       <c r="H108" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I108" s="4" t="s">
-        <v>625</v>
+        <v>666</v>
       </c>
       <c r="J108" s="4" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="K108" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L108" s="4" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B109" s="4" t="s">
-        <v>612</v>
+        <v>653</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>241</v>
+        <v>282</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>255</v>
+        <v>296</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>613</v>
+        <v>654</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>626</v>
-      </c>
-      <c r="G109" s="27" t="s">
-        <v>627</v>
+        <v>667</v>
+      </c>
+      <c r="G109" s="29" t="s">
+        <v>668</v>
       </c>
       <c r="H109" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I109" s="4" t="s">
-        <v>628</v>
+        <v>669</v>
       </c>
       <c r="J109" s="4" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="K109" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L109" s="4" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B110" s="4" t="s">
-        <v>612</v>
+        <v>653</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>241</v>
+        <v>282</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>260</v>
+        <v>301</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>629</v>
+        <v>670</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>630</v>
-      </c>
-      <c r="G110" s="27" t="s">
-        <v>631</v>
+        <v>671</v>
+      </c>
+      <c r="G110" s="29" t="s">
+        <v>672</v>
       </c>
       <c r="H110" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I110" s="4" t="s">
-        <v>632</v>
+        <v>673</v>
       </c>
       <c r="J110" s="4" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="K110" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L110" s="4" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B111" s="4" t="s">
-        <v>612</v>
+        <v>653</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>241</v>
+        <v>282</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>266</v>
+        <v>307</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>613</v>
+        <v>654</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>633</v>
-      </c>
-      <c r="G111" s="27" t="s">
-        <v>634</v>
+        <v>674</v>
+      </c>
+      <c r="G111" s="29" t="s">
+        <v>675</v>
       </c>
       <c r="H111" s="4" t="s">
-        <v>181</v>
+        <v>222</v>
       </c>
       <c r="I111" s="4" t="s">
-        <v>635</v>
+        <v>676</v>
       </c>
       <c r="J111" s="4" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="K111" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L111" s="4" t="s">
-        <v>373</v>
+        <v>414</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B112" s="4" t="s">
-        <v>612</v>
+        <v>653</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>241</v>
+        <v>282</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>266</v>
+        <v>307</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>613</v>
+        <v>654</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>636</v>
-      </c>
-      <c r="G112" s="27" t="s">
-        <v>637</v>
+        <v>677</v>
+      </c>
+      <c r="G112" s="29" t="s">
+        <v>678</v>
       </c>
       <c r="H112" s="4" t="s">
-        <v>181</v>
+        <v>222</v>
       </c>
       <c r="I112" s="4" t="s">
-        <v>638</v>
+        <v>679</v>
       </c>
       <c r="J112" s="4" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="K112" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L112" s="4" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B113" s="4" t="s">
-        <v>612</v>
+        <v>653</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>241</v>
+        <v>282</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>275</v>
+        <v>316</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>613</v>
+        <v>654</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>639</v>
-      </c>
-      <c r="G113" s="27" t="s">
-        <v>640</v>
+        <v>680</v>
+      </c>
+      <c r="G113" s="29" t="s">
+        <v>681</v>
       </c>
       <c r="H113" s="4" t="s">
-        <v>181</v>
+        <v>222</v>
       </c>
       <c r="I113" s="4" t="s">
-        <v>641</v>
+        <v>682</v>
       </c>
       <c r="J113" s="4" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="K113" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L113" s="4" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B114" s="4" t="s">
-        <v>612</v>
+        <v>653</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>241</v>
+        <v>282</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>275</v>
+        <v>316</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>613</v>
+        <v>654</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>642</v>
-      </c>
-      <c r="G114" s="27" t="s">
-        <v>643</v>
+        <v>683</v>
+      </c>
+      <c r="G114" s="29" t="s">
+        <v>684</v>
       </c>
       <c r="H114" s="4" t="s">
-        <v>181</v>
+        <v>222</v>
       </c>
       <c r="I114" s="4" t="s">
-        <v>644</v>
+        <v>685</v>
       </c>
       <c r="J114" s="4" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="K114" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L114" s="4" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B115" s="4" t="s">
-        <v>612</v>
+        <v>653</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>241</v>
+        <v>282</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>284</v>
+        <v>325</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>613</v>
+        <v>654</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>645</v>
-      </c>
-      <c r="G115" s="27" t="s">
-        <v>646</v>
+        <v>686</v>
+      </c>
+      <c r="G115" s="29" t="s">
+        <v>687</v>
       </c>
       <c r="H115" s="4" t="s">
-        <v>181</v>
+        <v>222</v>
       </c>
       <c r="I115" s="4" t="s">
-        <v>647</v>
+        <v>688</v>
       </c>
       <c r="J115" s="4" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="K115" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L115" s="4" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B116" s="4" t="s">
-        <v>612</v>
+        <v>653</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>241</v>
+        <v>282</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>346</v>
+        <v>387</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>648</v>
+        <v>689</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>649</v>
-      </c>
-      <c r="G116" s="27" t="s">
-        <v>650</v>
+        <v>690</v>
+      </c>
+      <c r="G116" s="29" t="s">
+        <v>691</v>
       </c>
       <c r="H116" s="4" t="s">
-        <v>181</v>
+        <v>222</v>
       </c>
       <c r="I116" s="4" t="s">
-        <v>651</v>
+        <v>692</v>
       </c>
       <c r="J116" s="4" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="K116" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L116" s="4" t="s">
-        <v>373</v>
+        <v>414</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B117" s="4" t="s">
-        <v>612</v>
+        <v>653</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>241</v>
+        <v>282</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>346</v>
+        <v>387</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>652</v>
+        <v>693</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>653</v>
-      </c>
-      <c r="G117" s="27" t="s">
-        <v>654</v>
+        <v>694</v>
+      </c>
+      <c r="G117" s="29" t="s">
+        <v>695</v>
       </c>
       <c r="H117" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I117" s="4" t="s">
-        <v>655</v>
+        <v>696</v>
       </c>
       <c r="J117" s="4" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="K117" s="4" t="s">
-        <v>312</v>
+        <v>353</v>
       </c>
       <c r="L117" s="4" t="s">
-        <v>656</v>
+        <v>697</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B118" s="4" t="s">
-        <v>657</v>
+        <v>698</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>198</v>
+        <v>239</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>178</v>
+        <v>219</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>536</v>
+        <v>577</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>658</v>
-      </c>
-      <c r="G118" s="27" t="s">
-        <v>659</v>
+        <v>699</v>
+      </c>
+      <c r="G118" s="29" t="s">
+        <v>700</v>
       </c>
       <c r="H118" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I118" s="4" t="s">
-        <v>660</v>
+        <v>701</v>
       </c>
       <c r="J118" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K118" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L118" s="4" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B119" s="4" t="s">
-        <v>657</v>
+        <v>698</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>249</v>
+        <v>290</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>224</v>
+        <v>265</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>661</v>
+        <v>702</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>662</v>
-      </c>
-      <c r="G119" s="27" t="s">
-        <v>663</v>
+        <v>703</v>
+      </c>
+      <c r="G119" s="29" t="s">
+        <v>704</v>
       </c>
       <c r="H119" s="4" t="s">
-        <v>181</v>
+        <v>222</v>
       </c>
       <c r="I119" s="4" t="s">
-        <v>664</v>
+        <v>705</v>
       </c>
       <c r="J119" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K119" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L119" s="4" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B120" s="4" t="s">
-        <v>657</v>
+        <v>698</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>198</v>
+        <v>239</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>308</v>
+        <v>349</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>665</v>
+        <v>706</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>666</v>
+        <v>707</v>
       </c>
       <c r="G120" s="4"/>
       <c r="H120" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I120" s="4" t="s">
-        <v>667</v>
+        <v>708</v>
       </c>
       <c r="J120" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K120" s="4" t="s">
-        <v>312</v>
+        <v>353</v>
       </c>
       <c r="L120" s="4" t="s">
-        <v>668</v>
+        <v>709</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B121" s="4" t="s">
-        <v>657</v>
+        <v>698</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>198</v>
+        <v>239</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>260</v>
+        <v>301</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>669</v>
+        <v>710</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>669</v>
-      </c>
-      <c r="G121" s="27" t="s">
-        <v>670</v>
+        <v>710</v>
+      </c>
+      <c r="G121" s="29" t="s">
+        <v>711</v>
       </c>
       <c r="H121" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I121" s="4" t="s">
-        <v>671</v>
+        <v>712</v>
       </c>
       <c r="J121" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K121" s="4" t="s">
-        <v>312</v>
+        <v>353</v>
       </c>
       <c r="L121" s="4" t="s">
-        <v>672</v>
+        <v>713</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B122" s="4" t="s">
-        <v>657</v>
+        <v>698</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>198</v>
+        <v>239</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>346</v>
+        <v>387</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>673</v>
+        <v>714</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>674</v>
-      </c>
-      <c r="G122" s="27" t="s">
-        <v>675</v>
+        <v>715</v>
+      </c>
+      <c r="G122" s="29" t="s">
+        <v>716</v>
       </c>
       <c r="H122" s="4" t="s">
-        <v>181</v>
+        <v>222</v>
       </c>
       <c r="I122" s="4" t="s">
-        <v>676</v>
+        <v>717</v>
       </c>
       <c r="J122" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K122" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L122" s="4" t="s">
-        <v>677</v>
+        <v>718</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B123" s="4" t="s">
-        <v>678</v>
+        <v>719</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>177</v>
+        <v>218</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>178</v>
+        <v>219</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>194</v>
+        <v>235</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>679</v>
-      </c>
-      <c r="G123" s="27" t="s">
-        <v>680</v>
+        <v>720</v>
+      </c>
+      <c r="G123" s="29" t="s">
+        <v>721</v>
       </c>
       <c r="H123" s="4" t="s">
-        <v>181</v>
+        <v>222</v>
       </c>
       <c r="I123" s="4" t="s">
-        <v>681</v>
+        <v>722</v>
       </c>
       <c r="J123" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K123" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L123" s="4" t="s">
-        <v>682</v>
+        <v>723</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B124" s="4" t="s">
-        <v>678</v>
+        <v>719</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>177</v>
+        <v>218</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>308</v>
+        <v>349</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>683</v>
+        <v>724</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>684</v>
-      </c>
-      <c r="G124" s="27" t="s">
-        <v>685</v>
+        <v>725</v>
+      </c>
+      <c r="G124" s="29" t="s">
+        <v>726</v>
       </c>
       <c r="H124" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I124" s="4" t="s">
-        <v>686</v>
+        <v>727</v>
       </c>
       <c r="J124" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K124" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L124" s="4" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B125" s="4" t="s">
-        <v>678</v>
+        <v>719</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>177</v>
+        <v>218</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>284</v>
+        <v>325</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>177</v>
+        <v>218</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>687</v>
-      </c>
-      <c r="G125" s="27" t="s">
-        <v>688</v>
+        <v>728</v>
+      </c>
+      <c r="G125" s="29" t="s">
+        <v>729</v>
       </c>
       <c r="H125" s="4" t="s">
-        <v>181</v>
+        <v>222</v>
       </c>
       <c r="I125" s="4" t="s">
-        <v>689</v>
+        <v>730</v>
       </c>
       <c r="J125" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K125" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L125" s="4" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B126" s="4" t="s">
-        <v>690</v>
+        <v>731</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>177</v>
+        <v>218</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>178</v>
+        <v>219</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>194</v>
+        <v>235</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>691</v>
-      </c>
-      <c r="G126" s="27" t="s">
-        <v>692</v>
+        <v>732</v>
+      </c>
+      <c r="G126" s="29" t="s">
+        <v>733</v>
       </c>
       <c r="H126" s="4" t="s">
-        <v>181</v>
+        <v>222</v>
       </c>
       <c r="I126" s="4" t="s">
-        <v>693</v>
+        <v>734</v>
       </c>
       <c r="J126" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K126" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L126" s="4" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B127" s="4" t="s">
-        <v>690</v>
+        <v>731</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>177</v>
+        <v>218</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>308</v>
+        <v>349</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>694</v>
+        <v>735</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>695</v>
-      </c>
-      <c r="G127" s="27" t="s">
-        <v>696</v>
+        <v>736</v>
+      </c>
+      <c r="G127" s="29" t="s">
+        <v>737</v>
       </c>
       <c r="H127" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I127" s="4" t="s">
-        <v>697</v>
+        <v>738</v>
       </c>
       <c r="J127" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K127" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L127" s="4" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B128" s="4" t="s">
-        <v>698</v>
+        <v>739</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>198</v>
+        <v>239</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>178</v>
+        <v>219</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>536</v>
+        <v>577</v>
       </c>
       <c r="F128" s="4" t="s">
-        <v>699</v>
-      </c>
-      <c r="G128" s="27" t="s">
-        <v>700</v>
+        <v>740</v>
+      </c>
+      <c r="G128" s="29" t="s">
+        <v>741</v>
       </c>
       <c r="H128" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I128" s="4" t="s">
-        <v>701</v>
+        <v>742</v>
       </c>
       <c r="J128" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K128" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L128" s="4" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B129" s="4" t="s">
-        <v>698</v>
+        <v>739</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>249</v>
+        <v>290</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>224</v>
+        <v>265</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>249</v>
+        <v>290</v>
       </c>
       <c r="F129" s="4" t="s">
-        <v>702</v>
-      </c>
-      <c r="G129" s="27" t="s">
-        <v>703</v>
+        <v>743</v>
+      </c>
+      <c r="G129" s="29" t="s">
+        <v>744</v>
       </c>
       <c r="H129" s="4" t="s">
-        <v>181</v>
+        <v>222</v>
       </c>
       <c r="I129" s="4" t="s">
-        <v>704</v>
+        <v>745</v>
       </c>
       <c r="J129" s="4" t="s">
-        <v>51</v>
+        <v>89</v>
       </c>
       <c r="K129" s="4" t="s">
-        <v>183</v>
+        <v>224</v>
       </c>
       <c r="L129" s="4" t="s">
-        <v>193</v>
+        <v>234</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B130" s="4" t="s">
-        <v>698</v>
+        <v>739</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>198</v>
+        <v>239</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>308</v>
+        <v>349</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>705</v>
+        <v>746</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>706</v>
+        <v>747</v>
       </c>
       <c r="G130" s="4"/>
       <c r="H130" s="4" t="s">
-        <v>191</v>
+        <v>232</v>
       </c>
       <c r="I130" s="4" t="s">
-        <v>707</v>
+        <v>748</v>
       </c>
       <c r="J130" s="4" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="K130" s="4" t="s">
-        <v>312</v>
+        <v>353</v>
       </c>
       <c r="L130" s="4" t="s">
-        <v>668</v>
+        <v>709</v>
       </c>
     </row>
   </sheetData>

--- a/docs/RALK_Preise_Plaene_Vertrieb.xlsx
+++ b/docs/RALK_Preise_Plaene_Vertrieb.xlsx
@@ -42,7 +42,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Obergrenze der Klasse (Mitarbeiterzahl). Quelle: dein Preismodell.</t>
+          <t xml:space="preserve">Obergrenze der Klasse (Mitarbeiterzahl).</t>
         </r>
       </text>
     </comment>
@@ -54,7 +54,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Obergrenze der Klasse (Mitarbeiterzahl). Quelle: dein Preismodell.</t>
+          <t xml:space="preserve">Obergrenze der Klasse (Mitarbeiterzahl).</t>
         </r>
       </text>
     </comment>
@@ -66,11 +66,35 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
+          <t xml:space="preserve">Obergrenze der Klasse (Mitarbeiterzahl).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C9" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Obergrenze der Klasse (Mitarbeiterzahl).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C10" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
           <t xml:space="preserve">Obergrenze der Klasse (Mitarbeiterzahl). Letzte Klasse = unbegrenzt.</t>
         </r>
       </text>
     </comment>
-    <comment ref="C11" authorId="0">
+    <comment ref="C13" authorId="0">
       <text>
         <r>
           <rPr>
@@ -82,7 +106,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C12" authorId="0">
+    <comment ref="C14" authorId="0">
       <text>
         <r>
           <rPr>
@@ -94,7 +118,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C13" authorId="0">
+    <comment ref="C15" authorId="0">
       <text>
         <r>
           <rPr>
@@ -106,7 +130,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C23" authorId="0">
+    <comment ref="C26" authorId="0">
       <text>
         <r>
           <rPr>
@@ -126,7 +150,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Quelle: RALK_Preismodell, Blatt „Preise &amp; ARR“.</t>
+          <t xml:space="preserve">Preisstaffel Okt. 2026 (feinere Stufen nach Marktvergleich; 45 $ für Großorganisationen wie mit Achapa vereinbart).</t>
         </r>
       </text>
     </comment>
@@ -138,7 +162,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Quelle: RALK_Preismodell, Blatt „Preise &amp; ARR“.</t>
+          <t xml:space="preserve">Preisstaffel Okt. 2026 (feinere Stufen nach Marktvergleich; 45 $ für Großorganisationen wie mit Achapa vereinbart).</t>
         </r>
       </text>
     </comment>
@@ -150,7 +174,31 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Quelle: RALK_Preismodell, Blatt „Preise &amp; ARR“.</t>
+          <t xml:space="preserve">Preisstaffel Okt. 2026 (feinere Stufen nach Marktvergleich; 45 $ für Großorganisationen wie mit Achapa vereinbart).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D9" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Preisstaffel Okt. 2026 (feinere Stufen nach Marktvergleich; 45 $ für Großorganisationen wie mit Achapa vereinbart).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D10" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Preisstaffel Okt. 2026 (feinere Stufen nach Marktvergleich; 45 $ für Großorganisationen wie mit Achapa vereinbart).</t>
         </r>
       </text>
     </comment>
@@ -479,7 +527,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1618" uniqueCount="749">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="753">
   <si>
     <t xml:space="preserve">RALK – Preise, Pläne &amp; Vertriebsmodell</t>
   </si>
@@ -547,7 +595,7 @@
     <t xml:space="preserve">Preise</t>
   </si>
   <si>
-    <t xml:space="preserve">Aus deiner Datei „RALK_Preismodell_DE_ohne_Setup-Fee.xlsx“ (Blatt „Preise &amp; ARR“): ≤4.000 MA 65 $, 4.001–7.999 MA 50 $, ≥8.000 MA 45 $, Mindest-Jahreslizenz 5.000 $, keine Setup-Fee.</t>
+    <t xml:space="preserve">Neue Staffel (Okt. 2026, nach Marktvergleich): bis 500 MA 65 $, 501–2.000 60 $, 2.001–5.000 55 $, 5.001–10.000 50 $, über 10.000 45 $. Mindest-Jahreslizenz 5.000 $, keine Setup-Fee. Vorher (RALK_Preismodell): ≤4.000 65 $, 4.001–7.999 50 $, ≥8.000 45 $.</t>
   </si>
   <si>
     <t xml:space="preserve">Funnel-Zahlen</t>
@@ -691,7 +739,7 @@
     <t xml:space="preserve">Preise &amp; Pläne – Jahreslizenz pro Mitarbeiter</t>
   </si>
   <si>
-    <t xml:space="preserve">Fester Satz pro Mitarbeiter, abhängig von der Unternehmensgröße. Gilt für alle Mitarbeitenden des Kunden. Netto, USD, keine Einrichtungsgebühr.</t>
+    <t xml:space="preserve">Fester Satz pro Mitarbeiter je Größenklasse (Mengenstaffel wie KnowBe4/Atlassian). Gilt für alle Mitarbeitenden des Kunden. Netto, USD, keine Einrichtungsgebühr, keine Einzelrabatte.</t>
   </si>
   <si>
     <t xml:space="preserve">Größenklasse</t>
@@ -703,19 +751,28 @@
     <t xml:space="preserve">USD / MA / Jahr</t>
   </si>
   <si>
-    <t xml:space="preserve">Beispiel-Satz in €</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Klein &amp; mittel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Groß</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sehr groß / Verbände</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ab 4.001 bzw. ab 8.000 Mitarbeitende</t>
+    <t xml:space="preserve">in €</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lizenz an der Obergrenze</t>
+  </si>
+  <si>
+    <t xml:space="preserve">bis 500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">501 – 2.000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.001 – 5.000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.001 – 10.000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">über 10.000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">–</t>
   </si>
   <si>
     <t xml:space="preserve">Mindest-Jahreslizenz (USD)</t>
@@ -811,22 +868,25 @@
     <t xml:space="preserve">typischer Mittelkunde</t>
   </si>
   <si>
+    <t xml:space="preserve">Klassengrenze</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Übergangsregel: wie 500 MA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Übergangsregel: wie 2.000 MA</t>
+  </si>
+  <si>
     <t xml:space="preserve">z. B. große Bank</t>
   </si>
   <si>
-    <t xml:space="preserve">Klassengrenze</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Übergangsregel: wie 4.000 MA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ab hier normaler 50-$-Satz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Übergangsregel: wie 7.999 MA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ab hier normaler 45-$-Satz</t>
+    <t xml:space="preserve">Übergangsregel: wie 5.000 MA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">z. B. Kenya Revenue Authority</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Übergangsregel: wie 10.000 MA</t>
   </si>
   <si>
     <t xml:space="preserve">Verband</t>
@@ -835,10 +895,10 @@
     <t xml:space="preserve">z. B. Law Society of Kenya</t>
   </si>
   <si>
-    <t xml:space="preserve">Übergangsregel (wie bei Atlassian-Stufen): Wer in eine günstigere Klasse rutscht, zahlt nie weniger als die größte Organisation der Klasse darunter. 4.001–5.200 MA zahlen also 260.000 $ (wie 4.000 MA), 8.000–8.888 MA zahlen 399.950 $ (wie 7.999 MA). Danach gilt der normale Satz. So gibt es keinen Preissprung nach unten.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Feste Preisliste wie Google Workspace / Microsoft 365: gleicher Preis für alle, Mengenrabatt steckt in den Klassen, keine Einzelrabatte, keine Verhandlung.</t>
+    <t xml:space="preserve">Übergangsregel (wie bei Atlassian-Stufen): Wer in eine günstigere Klasse rutscht, zahlt nie weniger als die größte Organisation der Klasse darunter (Spalte „Lizenz an der Obergrenze“). Beispiel: 501–541 MA zahlen 32.500 $ wie 500 MA, danach gilt 60 $. So gibt es keinen Preissprung nach unten.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Feste Preisliste: gleicher Preis für alle, Mengenrabatt steckt in den Klassen (wie KnowBe4/Atlassian), keine Einzelrabatte, keine Verhandlung.</t>
   </si>
   <si>
     <t xml:space="preserve">Leistungsumfang (in allen Klassen gleich)</t>
@@ -862,7 +922,7 @@
     <t xml:space="preserve">• E-Mail-Support</t>
   </si>
   <si>
-    <t xml:space="preserve">• Ab 4.001 MA zusätzlich: fester Ansprechpartner für die Einführung</t>
+    <t xml:space="preserve">• Ab 2.001 MA zusätzlich: fester Ansprechpartner für die Einführung</t>
   </si>
   <si>
     <t xml:space="preserve">Mit Anwalts-Funnel – Kunden über Partner-Anwälte</t>
@@ -2953,16 +3013,16 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="168" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
@@ -3663,11 +3723,11 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:G58"/>
+  <dimension ref="B2:G61"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="38"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="40"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="3" style="0" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="40"/>
   </cols>
@@ -3682,7 +3742,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="7" t="s">
         <v>71</v>
       </c>
@@ -3695,635 +3755,652 @@
       <c r="E5" s="7" t="s">
         <v>74</v>
       </c>
+      <c r="F5" s="7" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C6" s="9" t="n">
-        <v>4000</v>
+        <v>500</v>
       </c>
       <c r="D6" s="10" t="n">
         <v>65</v>
       </c>
       <c r="E6" s="11" t="n">
-        <f aca="false">D6*$C$12</f>
+        <f aca="false">D6*$C$14</f>
         <v>59.8</v>
+      </c>
+      <c r="F6" s="12" t="n">
+        <f aca="false">C6*D6</f>
+        <v>32500</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>7999</v>
+        <v>2000</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E7" s="11" t="n">
-        <f aca="false">D7*$C$12</f>
-        <v>46</v>
+        <f aca="false">D7*$C$14</f>
+        <v>55.2</v>
+      </c>
+      <c r="F7" s="12" t="n">
+        <f aca="false">C7*D7</f>
+        <v>120000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="5" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C8" s="9" t="n">
+        <v>5000</v>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>55</v>
+      </c>
+      <c r="E8" s="11" t="n">
+        <f aca="false">D8*$C$14</f>
+        <v>50.6</v>
+      </c>
+      <c r="F8" s="12" t="n">
+        <f aca="false">C8*D8</f>
+        <v>275000</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B9" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="E9" s="11" t="n">
+        <f aca="false">D9*$C$14</f>
+        <v>46</v>
+      </c>
+      <c r="F9" s="12" t="n">
+        <f aca="false">C9*D9</f>
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C10" s="9" t="n">
         <v>999999999</v>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D10" s="10" t="n">
         <v>45</v>
       </c>
-      <c r="E8" s="11" t="n">
-        <f aca="false">D8*$C$12</f>
+      <c r="E10" s="11" t="n">
+        <f aca="false">D10*$C$14</f>
         <v>41.4</v>
       </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="2" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B11" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="C11" s="10" t="n">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="C12" s="12" t="n">
-        <v>0.92</v>
+      <c r="F10" s="12" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="5" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C13" s="10" t="n">
-        <v>0</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="5" t="s">
-        <v>82</v>
-      </c>
-      <c r="C14" s="5" t="s">
         <v>83</v>
+      </c>
+      <c r="C14" s="13" t="n">
+        <v>0.92</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B16" s="5" t="s">
         <v>85</v>
       </c>
+      <c r="C16" s="5" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="3" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="C18" s="13" t="s">
+      <c r="C17" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-    </row>
-    <row r="19" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="3" t="s">
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B20" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="C19" s="13" t="s">
+    </row>
+    <row r="21" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B21" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-    </row>
-    <row r="20" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="3" t="s">
+      <c r="C21" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="C20" s="13" t="s">
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+    </row>
+    <row r="22" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="D20" s="13"/>
-      <c r="E20" s="13"/>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-    </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B22" s="3" t="s">
+      <c r="C22" s="14" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B23" s="5" t="s">
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
+    </row>
+    <row r="23" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B23" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C23" s="9" t="n">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B24" s="5" t="s">
+      <c r="C23" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="C24" s="14" t="n">
-        <f aca="false">IF(C23&lt;=$C$6,$D$6,IF(C23&lt;=$C$7,$D$7,$D$8))</f>
-        <v>65</v>
-      </c>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="14"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="5" t="s">
+      <c r="B25" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="C25" s="14" t="n">
-        <f aca="false">C23*C24</f>
-        <v>26000</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="C26" s="15" t="n">
-        <f aca="false">MAX(C25,$C$11,IF(C23&gt;$C$6,$C$6*$D$6,0),IF(C23&gt;$C$7,$C$7*$D$7,0))</f>
-        <v>26000</v>
+      <c r="C26" s="9" t="n">
+        <v>400</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="C27" s="11" t="n">
-        <f aca="false">C26*$C$12</f>
-        <v>23920</v>
+      <c r="C27" s="12" t="n">
+        <f aca="false">IF(C26&lt;=$C$6,$D$6,IF(C26&lt;=$C$7,$D$7,IF(C26&lt;=$C$8,$D$8,IF(C26&lt;=$C$9,$D$9,$D$10))))</f>
+        <v>65</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C28" s="16" t="n">
-        <f aca="false">IF(C23&gt;0,C26/C23,0)</f>
+      <c r="C28" s="12" t="n">
+        <f aca="false">C26*C27</f>
+        <v>26000</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B29" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="C29" s="15" t="n">
+        <f aca="false">MAX(C26*IF(C26&lt;=$C$6,$D$6,IF(C26&lt;=$C$7,$D$7,IF(C26&lt;=$C$8,$D$8,IF(C26&lt;=$C$9,$D$9,$D$10)))),$C$13,IF(C26&gt;$C$6,$C$6*$D$6,0),IF(C26&gt;$C$7,$C$7*$D$7,0),IF(C26&gt;$C$8,$C$8*$D$8,0),IF(C26&gt;$C$9,$C$9*$D$9,0))</f>
+        <v>26000</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B30" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="C30" s="11" t="n">
+        <f aca="false">C29*$C$14</f>
+        <v>23920</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="C31" s="16" t="n">
+        <f aca="false">IF(C26&gt;0,C29/C26,0)</f>
         <v>65</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="3" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="C31" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="D31" s="7" t="s">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="E31" s="7" t="s">
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B34" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="F31" s="7" t="s">
+      <c r="C34" s="7" t="s">
         <v>105</v>
       </c>
-      <c r="G31" s="7" t="s">
+      <c r="D34" s="7" t="s">
         <v>106</v>
       </c>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="9" t="n">
-        <v>10</v>
-      </c>
-      <c r="C32" s="14" t="n">
-        <f aca="false">IF(B32&lt;=$C$6,$D$6,IF(B32&lt;=$C$7,$D$7,$D$8))</f>
-        <v>65</v>
-      </c>
-      <c r="D32" s="14" t="n">
-        <f aca="false">MAX(B32*C32,$C$11,IF(B32&gt;$C$6,$C$6*$D$6,0),IF(B32&gt;$C$7,$C$7*$D$7,0))</f>
-        <v>5000</v>
-      </c>
-      <c r="E32" s="11" t="n">
-        <f aca="false">D32*$C$12</f>
-        <v>4600</v>
-      </c>
-      <c r="F32" s="16" t="n">
-        <f aca="false">IF(B32&gt;0,D32/B32,0)</f>
-        <v>500</v>
-      </c>
-      <c r="G32" s="2" t="s">
+      <c r="E34" s="7" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="9" t="n">
-        <v>50</v>
-      </c>
-      <c r="C33" s="14" t="n">
-        <f aca="false">IF(B33&lt;=$C$6,$D$6,IF(B33&lt;=$C$7,$D$7,$D$8))</f>
-        <v>65</v>
-      </c>
-      <c r="D33" s="14" t="n">
-        <f aca="false">MAX(B33*C33,$C$11,IF(B33&gt;$C$6,$C$6*$D$6,0),IF(B33&gt;$C$7,$C$7*$D$7,0))</f>
-        <v>5000</v>
-      </c>
-      <c r="E33" s="11" t="n">
-        <f aca="false">D33*$C$12</f>
-        <v>4600</v>
-      </c>
-      <c r="F33" s="16" t="n">
-        <f aca="false">IF(B33&gt;0,D33/B33,0)</f>
-        <v>100</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="9" t="n">
-        <v>77</v>
-      </c>
-      <c r="C34" s="14" t="n">
-        <f aca="false">IF(B34&lt;=$C$6,$D$6,IF(B34&lt;=$C$7,$D$7,$D$8))</f>
-        <v>65</v>
-      </c>
-      <c r="D34" s="14" t="n">
-        <f aca="false">MAX(B34*C34,$C$11,IF(B34&gt;$C$6,$C$6*$D$6,0),IF(B34&gt;$C$7,$C$7*$D$7,0))</f>
-        <v>5005</v>
-      </c>
-      <c r="E34" s="11" t="n">
-        <f aca="false">D34*$C$12</f>
-        <v>4604.6</v>
-      </c>
-      <c r="F34" s="16" t="n">
-        <f aca="false">IF(B34&gt;0,D34/B34,0)</f>
-        <v>65</v>
-      </c>
-      <c r="G34" s="2" t="s">
+      <c r="F34" s="7" t="s">
         <v>108</v>
+      </c>
+      <c r="G34" s="7" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="9" t="n">
-        <v>100</v>
-      </c>
-      <c r="C35" s="14" t="n">
-        <f aca="false">IF(B35&lt;=$C$6,$D$6,IF(B35&lt;=$C$7,$D$7,$D$8))</f>
+        <v>10</v>
+      </c>
+      <c r="C35" s="12" t="n">
+        <f aca="false">IF(B35&lt;=$C$6,$D$6,IF(B35&lt;=$C$7,$D$7,IF(B35&lt;=$C$8,$D$8,IF(B35&lt;=$C$9,$D$9,$D$10))))</f>
         <v>65</v>
       </c>
-      <c r="D35" s="14" t="n">
-        <f aca="false">MAX(B35*C35,$C$11,IF(B35&gt;$C$6,$C$6*$D$6,0),IF(B35&gt;$C$7,$C$7*$D$7,0))</f>
-        <v>6500</v>
+      <c r="D35" s="12" t="n">
+        <f aca="false">MAX(B35*IF(B35&lt;=$C$6,$D$6,IF(B35&lt;=$C$7,$D$7,IF(B35&lt;=$C$8,$D$8,IF(B35&lt;=$C$9,$D$9,$D$10)))),$C$13,IF(B35&gt;$C$6,$C$6*$D$6,0),IF(B35&gt;$C$7,$C$7*$D$7,0),IF(B35&gt;$C$8,$C$8*$D$8,0),IF(B35&gt;$C$9,$C$9*$D$9,0))</f>
+        <v>5000</v>
       </c>
       <c r="E35" s="11" t="n">
-        <f aca="false">D35*$C$12</f>
-        <v>5980</v>
+        <f aca="false">D35*$C$14</f>
+        <v>4600</v>
       </c>
       <c r="F35" s="16" t="n">
         <f aca="false">IF(B35&gt;0,D35/B35,0)</f>
-        <v>65</v>
-      </c>
-      <c r="G35" s="2"/>
+        <v>500</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="9" t="n">
-        <v>400</v>
-      </c>
-      <c r="C36" s="14" t="n">
-        <f aca="false">IF(B36&lt;=$C$6,$D$6,IF(B36&lt;=$C$7,$D$7,$D$8))</f>
+        <v>50</v>
+      </c>
+      <c r="C36" s="12" t="n">
+        <f aca="false">IF(B36&lt;=$C$6,$D$6,IF(B36&lt;=$C$7,$D$7,IF(B36&lt;=$C$8,$D$8,IF(B36&lt;=$C$9,$D$9,$D$10))))</f>
         <v>65</v>
       </c>
-      <c r="D36" s="14" t="n">
-        <f aca="false">MAX(B36*C36,$C$11,IF(B36&gt;$C$6,$C$6*$D$6,0),IF(B36&gt;$C$7,$C$7*$D$7,0))</f>
-        <v>26000</v>
+      <c r="D36" s="12" t="n">
+        <f aca="false">MAX(B36*IF(B36&lt;=$C$6,$D$6,IF(B36&lt;=$C$7,$D$7,IF(B36&lt;=$C$8,$D$8,IF(B36&lt;=$C$9,$D$9,$D$10)))),$C$13,IF(B36&gt;$C$6,$C$6*$D$6,0),IF(B36&gt;$C$7,$C$7*$D$7,0),IF(B36&gt;$C$8,$C$8*$D$8,0),IF(B36&gt;$C$9,$C$9*$D$9,0))</f>
+        <v>5000</v>
       </c>
       <c r="E36" s="11" t="n">
-        <f aca="false">D36*$C$12</f>
-        <v>23920</v>
+        <f aca="false">D36*$C$14</f>
+        <v>4600</v>
       </c>
       <c r="F36" s="16" t="n">
         <f aca="false">IF(B36&gt;0,D36/B36,0)</f>
-        <v>65</v>
+        <v>100</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="C37" s="14" t="n">
-        <f aca="false">IF(B37&lt;=$C$6,$D$6,IF(B37&lt;=$C$7,$D$7,$D$8))</f>
+        <v>77</v>
+      </c>
+      <c r="C37" s="12" t="n">
+        <f aca="false">IF(B37&lt;=$C$6,$D$6,IF(B37&lt;=$C$7,$D$7,IF(B37&lt;=$C$8,$D$8,IF(B37&lt;=$C$9,$D$9,$D$10))))</f>
         <v>65</v>
       </c>
-      <c r="D37" s="14" t="n">
-        <f aca="false">MAX(B37*C37,$C$11,IF(B37&gt;$C$6,$C$6*$D$6,0),IF(B37&gt;$C$7,$C$7*$D$7,0))</f>
-        <v>65000</v>
+      <c r="D37" s="12" t="n">
+        <f aca="false">MAX(B37*IF(B37&lt;=$C$6,$D$6,IF(B37&lt;=$C$7,$D$7,IF(B37&lt;=$C$8,$D$8,IF(B37&lt;=$C$9,$D$9,$D$10)))),$C$13,IF(B37&gt;$C$6,$C$6*$D$6,0),IF(B37&gt;$C$7,$C$7*$D$7,0),IF(B37&gt;$C$8,$C$8*$D$8,0),IF(B37&gt;$C$9,$C$9*$D$9,0))</f>
+        <v>5005</v>
       </c>
       <c r="E37" s="11" t="n">
-        <f aca="false">D37*$C$12</f>
-        <v>59800</v>
+        <f aca="false">D37*$C$14</f>
+        <v>4604.6</v>
       </c>
       <c r="F37" s="16" t="n">
         <f aca="false">IF(B37&gt;0,D37/B37,0)</f>
         <v>65</v>
       </c>
-      <c r="G37" s="2"/>
+      <c r="G37" s="2" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="9" t="n">
-        <v>3000</v>
-      </c>
-      <c r="C38" s="14" t="n">
-        <f aca="false">IF(B38&lt;=$C$6,$D$6,IF(B38&lt;=$C$7,$D$7,$D$8))</f>
+        <v>100</v>
+      </c>
+      <c r="C38" s="12" t="n">
+        <f aca="false">IF(B38&lt;=$C$6,$D$6,IF(B38&lt;=$C$7,$D$7,IF(B38&lt;=$C$8,$D$8,IF(B38&lt;=$C$9,$D$9,$D$10))))</f>
         <v>65</v>
       </c>
-      <c r="D38" s="14" t="n">
-        <f aca="false">MAX(B38*C38,$C$11,IF(B38&gt;$C$6,$C$6*$D$6,0),IF(B38&gt;$C$7,$C$7*$D$7,0))</f>
-        <v>195000</v>
+      <c r="D38" s="12" t="n">
+        <f aca="false">MAX(B38*IF(B38&lt;=$C$6,$D$6,IF(B38&lt;=$C$7,$D$7,IF(B38&lt;=$C$8,$D$8,IF(B38&lt;=$C$9,$D$9,$D$10)))),$C$13,IF(B38&gt;$C$6,$C$6*$D$6,0),IF(B38&gt;$C$7,$C$7*$D$7,0),IF(B38&gt;$C$8,$C$8*$D$8,0),IF(B38&gt;$C$9,$C$9*$D$9,0))</f>
+        <v>6500</v>
       </c>
       <c r="E38" s="11" t="n">
-        <f aca="false">D38*$C$12</f>
-        <v>179400</v>
+        <f aca="false">D38*$C$14</f>
+        <v>5980</v>
       </c>
       <c r="F38" s="16" t="n">
         <f aca="false">IF(B38&gt;0,D38/B38,0)</f>
         <v>65</v>
       </c>
-      <c r="G38" s="2" t="s">
-        <v>110</v>
-      </c>
+      <c r="G38" s="2"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="9" t="n">
-        <v>4000</v>
-      </c>
-      <c r="C39" s="14" t="n">
-        <f aca="false">IF(B39&lt;=$C$6,$D$6,IF(B39&lt;=$C$7,$D$7,$D$8))</f>
+        <v>400</v>
+      </c>
+      <c r="C39" s="12" t="n">
+        <f aca="false">IF(B39&lt;=$C$6,$D$6,IF(B39&lt;=$C$7,$D$7,IF(B39&lt;=$C$8,$D$8,IF(B39&lt;=$C$9,$D$9,$D$10))))</f>
         <v>65</v>
       </c>
-      <c r="D39" s="14" t="n">
-        <f aca="false">MAX(B39*C39,$C$11,IF(B39&gt;$C$6,$C$6*$D$6,0),IF(B39&gt;$C$7,$C$7*$D$7,0))</f>
-        <v>260000</v>
+      <c r="D39" s="12" t="n">
+        <f aca="false">MAX(B39*IF(B39&lt;=$C$6,$D$6,IF(B39&lt;=$C$7,$D$7,IF(B39&lt;=$C$8,$D$8,IF(B39&lt;=$C$9,$D$9,$D$10)))),$C$13,IF(B39&gt;$C$6,$C$6*$D$6,0),IF(B39&gt;$C$7,$C$7*$D$7,0),IF(B39&gt;$C$8,$C$8*$D$8,0),IF(B39&gt;$C$9,$C$9*$D$9,0))</f>
+        <v>26000</v>
       </c>
       <c r="E39" s="11" t="n">
-        <f aca="false">D39*$C$12</f>
-        <v>239200</v>
+        <f aca="false">D39*$C$14</f>
+        <v>23920</v>
       </c>
       <c r="F39" s="16" t="n">
         <f aca="false">IF(B39&gt;0,D39/B39,0)</f>
         <v>65</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="9" t="n">
-        <v>4001</v>
-      </c>
-      <c r="C40" s="14" t="n">
-        <f aca="false">IF(B40&lt;=$C$6,$D$6,IF(B40&lt;=$C$7,$D$7,$D$8))</f>
-        <v>50</v>
-      </c>
-      <c r="D40" s="14" t="n">
-        <f aca="false">MAX(B40*C40,$C$11,IF(B40&gt;$C$6,$C$6*$D$6,0),IF(B40&gt;$C$7,$C$7*$D$7,0))</f>
-        <v>260000</v>
+        <v>500</v>
+      </c>
+      <c r="C40" s="12" t="n">
+        <f aca="false">IF(B40&lt;=$C$6,$D$6,IF(B40&lt;=$C$7,$D$7,IF(B40&lt;=$C$8,$D$8,IF(B40&lt;=$C$9,$D$9,$D$10))))</f>
+        <v>65</v>
+      </c>
+      <c r="D40" s="12" t="n">
+        <f aca="false">MAX(B40*IF(B40&lt;=$C$6,$D$6,IF(B40&lt;=$C$7,$D$7,IF(B40&lt;=$C$8,$D$8,IF(B40&lt;=$C$9,$D$9,$D$10)))),$C$13,IF(B40&gt;$C$6,$C$6*$D$6,0),IF(B40&gt;$C$7,$C$7*$D$7,0),IF(B40&gt;$C$8,$C$8*$D$8,0),IF(B40&gt;$C$9,$C$9*$D$9,0))</f>
+        <v>32500</v>
       </c>
       <c r="E40" s="11" t="n">
-        <f aca="false">D40*$C$12</f>
-        <v>239200</v>
+        <f aca="false">D40*$C$14</f>
+        <v>29900</v>
       </c>
       <c r="F40" s="16" t="n">
         <f aca="false">IF(B40&gt;0,D40/B40,0)</f>
-        <v>64.9837540614846</v>
+        <v>65</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="9" t="n">
-        <v>5200</v>
-      </c>
-      <c r="C41" s="14" t="n">
-        <f aca="false">IF(B41&lt;=$C$6,$D$6,IF(B41&lt;=$C$7,$D$7,$D$8))</f>
-        <v>50</v>
-      </c>
-      <c r="D41" s="14" t="n">
-        <f aca="false">MAX(B41*C41,$C$11,IF(B41&gt;$C$6,$C$6*$D$6,0),IF(B41&gt;$C$7,$C$7*$D$7,0))</f>
-        <v>260000</v>
+        <v>501</v>
+      </c>
+      <c r="C41" s="12" t="n">
+        <f aca="false">IF(B41&lt;=$C$6,$D$6,IF(B41&lt;=$C$7,$D$7,IF(B41&lt;=$C$8,$D$8,IF(B41&lt;=$C$9,$D$9,$D$10))))</f>
+        <v>60</v>
+      </c>
+      <c r="D41" s="12" t="n">
+        <f aca="false">MAX(B41*IF(B41&lt;=$C$6,$D$6,IF(B41&lt;=$C$7,$D$7,IF(B41&lt;=$C$8,$D$8,IF(B41&lt;=$C$9,$D$9,$D$10)))),$C$13,IF(B41&gt;$C$6,$C$6*$D$6,0),IF(B41&gt;$C$7,$C$7*$D$7,0),IF(B41&gt;$C$8,$C$8*$D$8,0),IF(B41&gt;$C$9,$C$9*$D$9,0))</f>
+        <v>32500</v>
       </c>
       <c r="E41" s="11" t="n">
-        <f aca="false">D41*$C$12</f>
-        <v>239200</v>
+        <f aca="false">D41*$C$14</f>
+        <v>29900</v>
       </c>
       <c r="F41" s="16" t="n">
         <f aca="false">IF(B41&gt;0,D41/B41,0)</f>
-        <v>50</v>
+        <v>64.8702594810379</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="9" t="n">
-        <v>7999</v>
-      </c>
-      <c r="C42" s="14" t="n">
-        <f aca="false">IF(B42&lt;=$C$6,$D$6,IF(B42&lt;=$C$7,$D$7,$D$8))</f>
-        <v>50</v>
-      </c>
-      <c r="D42" s="14" t="n">
-        <f aca="false">MAX(B42*C42,$C$11,IF(B42&gt;$C$6,$C$6*$D$6,0),IF(B42&gt;$C$7,$C$7*$D$7,0))</f>
-        <v>399950</v>
+        <v>1000</v>
+      </c>
+      <c r="C42" s="12" t="n">
+        <f aca="false">IF(B42&lt;=$C$6,$D$6,IF(B42&lt;=$C$7,$D$7,IF(B42&lt;=$C$8,$D$8,IF(B42&lt;=$C$9,$D$9,$D$10))))</f>
+        <v>60</v>
+      </c>
+      <c r="D42" s="12" t="n">
+        <f aca="false">MAX(B42*IF(B42&lt;=$C$6,$D$6,IF(B42&lt;=$C$7,$D$7,IF(B42&lt;=$C$8,$D$8,IF(B42&lt;=$C$9,$D$9,$D$10)))),$C$13,IF(B42&gt;$C$6,$C$6*$D$6,0),IF(B42&gt;$C$7,$C$7*$D$7,0),IF(B42&gt;$C$8,$C$8*$D$8,0),IF(B42&gt;$C$9,$C$9*$D$9,0))</f>
+        <v>60000</v>
       </c>
       <c r="E42" s="11" t="n">
-        <f aca="false">D42*$C$12</f>
-        <v>367954</v>
+        <f aca="false">D42*$C$14</f>
+        <v>55200</v>
       </c>
       <c r="F42" s="16" t="n">
         <f aca="false">IF(B42&gt;0,D42/B42,0)</f>
-        <v>50</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>111</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="G42" s="2"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="9" t="n">
-        <v>8000</v>
-      </c>
-      <c r="C43" s="14" t="n">
-        <f aca="false">IF(B43&lt;=$C$6,$D$6,IF(B43&lt;=$C$7,$D$7,$D$8))</f>
-        <v>45</v>
-      </c>
-      <c r="D43" s="14" t="n">
-        <f aca="false">MAX(B43*C43,$C$11,IF(B43&gt;$C$6,$C$6*$D$6,0),IF(B43&gt;$C$7,$C$7*$D$7,0))</f>
-        <v>399950</v>
+        <v>2001</v>
+      </c>
+      <c r="C43" s="12" t="n">
+        <f aca="false">IF(B43&lt;=$C$6,$D$6,IF(B43&lt;=$C$7,$D$7,IF(B43&lt;=$C$8,$D$8,IF(B43&lt;=$C$9,$D$9,$D$10))))</f>
+        <v>55</v>
+      </c>
+      <c r="D43" s="12" t="n">
+        <f aca="false">MAX(B43*IF(B43&lt;=$C$6,$D$6,IF(B43&lt;=$C$7,$D$7,IF(B43&lt;=$C$8,$D$8,IF(B43&lt;=$C$9,$D$9,$D$10)))),$C$13,IF(B43&gt;$C$6,$C$6*$D$6,0),IF(B43&gt;$C$7,$C$7*$D$7,0),IF(B43&gt;$C$8,$C$8*$D$8,0),IF(B43&gt;$C$9,$C$9*$D$9,0))</f>
+        <v>120000</v>
       </c>
       <c r="E43" s="11" t="n">
-        <f aca="false">D43*$C$12</f>
-        <v>367954</v>
+        <f aca="false">D43*$C$14</f>
+        <v>110400</v>
       </c>
       <c r="F43" s="16" t="n">
         <f aca="false">IF(B43&gt;0,D43/B43,0)</f>
-        <v>49.99375</v>
+        <v>59.9700149925038</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="9" t="n">
-        <v>8889</v>
-      </c>
-      <c r="C44" s="14" t="n">
-        <f aca="false">IF(B44&lt;=$C$6,$D$6,IF(B44&lt;=$C$7,$D$7,$D$8))</f>
-        <v>45</v>
-      </c>
-      <c r="D44" s="14" t="n">
-        <f aca="false">MAX(B44*C44,$C$11,IF(B44&gt;$C$6,$C$6*$D$6,0),IF(B44&gt;$C$7,$C$7*$D$7,0))</f>
-        <v>400005</v>
+        <v>3000</v>
+      </c>
+      <c r="C44" s="12" t="n">
+        <f aca="false">IF(B44&lt;=$C$6,$D$6,IF(B44&lt;=$C$7,$D$7,IF(B44&lt;=$C$8,$D$8,IF(B44&lt;=$C$9,$D$9,$D$10))))</f>
+        <v>55</v>
+      </c>
+      <c r="D44" s="12" t="n">
+        <f aca="false">MAX(B44*IF(B44&lt;=$C$6,$D$6,IF(B44&lt;=$C$7,$D$7,IF(B44&lt;=$C$8,$D$8,IF(B44&lt;=$C$9,$D$9,$D$10)))),$C$13,IF(B44&gt;$C$6,$C$6*$D$6,0),IF(B44&gt;$C$7,$C$7*$D$7,0),IF(B44&gt;$C$8,$C$8*$D$8,0),IF(B44&gt;$C$9,$C$9*$D$9,0))</f>
+        <v>165000</v>
       </c>
       <c r="E44" s="11" t="n">
-        <f aca="false">D44*$C$12</f>
-        <v>368004.6</v>
+        <f aca="false">D44*$C$14</f>
+        <v>151800</v>
       </c>
       <c r="F44" s="16" t="n">
         <f aca="false">IF(B44&gt;0,D44/B44,0)</f>
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="9" t="n">
-        <v>15000</v>
-      </c>
-      <c r="C45" s="14" t="n">
-        <f aca="false">IF(B45&lt;=$C$6,$D$6,IF(B45&lt;=$C$7,$D$7,$D$8))</f>
-        <v>45</v>
-      </c>
-      <c r="D45" s="14" t="n">
-        <f aca="false">MAX(B45*C45,$C$11,IF(B45&gt;$C$6,$C$6*$D$6,0),IF(B45&gt;$C$7,$C$7*$D$7,0))</f>
-        <v>675000</v>
+        <v>5001</v>
+      </c>
+      <c r="C45" s="12" t="n">
+        <f aca="false">IF(B45&lt;=$C$6,$D$6,IF(B45&lt;=$C$7,$D$7,IF(B45&lt;=$C$8,$D$8,IF(B45&lt;=$C$9,$D$9,$D$10))))</f>
+        <v>50</v>
+      </c>
+      <c r="D45" s="12" t="n">
+        <f aca="false">MAX(B45*IF(B45&lt;=$C$6,$D$6,IF(B45&lt;=$C$7,$D$7,IF(B45&lt;=$C$8,$D$8,IF(B45&lt;=$C$9,$D$9,$D$10)))),$C$13,IF(B45&gt;$C$6,$C$6*$D$6,0),IF(B45&gt;$C$7,$C$7*$D$7,0),IF(B45&gt;$C$8,$C$8*$D$8,0),IF(B45&gt;$C$9,$C$9*$D$9,0))</f>
+        <v>275000</v>
       </c>
       <c r="E45" s="11" t="n">
-        <f aca="false">D45*$C$12</f>
-        <v>621000</v>
+        <f aca="false">D45*$C$14</f>
+        <v>253000</v>
       </c>
       <c r="F45" s="16" t="n">
         <f aca="false">IF(B45&gt;0,D45/B45,0)</f>
-        <v>45</v>
+        <v>54.9890021995601</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="9" t="n">
-        <v>30000</v>
-      </c>
-      <c r="C46" s="14" t="n">
-        <f aca="false">IF(B46&lt;=$C$6,$D$6,IF(B46&lt;=$C$7,$D$7,$D$8))</f>
-        <v>45</v>
-      </c>
-      <c r="D46" s="14" t="n">
-        <f aca="false">MAX(B46*C46,$C$11,IF(B46&gt;$C$6,$C$6*$D$6,0),IF(B46&gt;$C$7,$C$7*$D$7,0))</f>
-        <v>1350000</v>
+        <v>8000</v>
+      </c>
+      <c r="C46" s="12" t="n">
+        <f aca="false">IF(B46&lt;=$C$6,$D$6,IF(B46&lt;=$C$7,$D$7,IF(B46&lt;=$C$8,$D$8,IF(B46&lt;=$C$9,$D$9,$D$10))))</f>
+        <v>50</v>
+      </c>
+      <c r="D46" s="12" t="n">
+        <f aca="false">MAX(B46*IF(B46&lt;=$C$6,$D$6,IF(B46&lt;=$C$7,$D$7,IF(B46&lt;=$C$8,$D$8,IF(B46&lt;=$C$9,$D$9,$D$10)))),$C$13,IF(B46&gt;$C$6,$C$6*$D$6,0),IF(B46&gt;$C$7,$C$7*$D$7,0),IF(B46&gt;$C$8,$C$8*$D$8,0),IF(B46&gt;$C$9,$C$9*$D$9,0))</f>
+        <v>400000</v>
       </c>
       <c r="E46" s="11" t="n">
-        <f aca="false">D46*$C$12</f>
-        <v>1242000</v>
+        <f aca="false">D46*$C$14</f>
+        <v>368000</v>
       </c>
       <c r="F46" s="16" t="n">
         <f aca="false">IF(B46&gt;0,D46/B46,0)</f>
+        <v>50</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B47" s="9" t="n">
+        <v>10001</v>
+      </c>
+      <c r="C47" s="12" t="n">
+        <f aca="false">IF(B47&lt;=$C$6,$D$6,IF(B47&lt;=$C$7,$D$7,IF(B47&lt;=$C$8,$D$8,IF(B47&lt;=$C$9,$D$9,$D$10))))</f>
         <v>45</v>
       </c>
-      <c r="G46" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B48" s="17" t="s">
-        <v>118</v>
-      </c>
-      <c r="C48" s="17"/>
-      <c r="D48" s="17"/>
-      <c r="E48" s="17"/>
-      <c r="F48" s="17"/>
-      <c r="G48" s="17"/>
-    </row>
-    <row r="49" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B49" s="18" t="s">
+      <c r="D47" s="12" t="n">
+        <f aca="false">MAX(B47*IF(B47&lt;=$C$6,$D$6,IF(B47&lt;=$C$7,$D$7,IF(B47&lt;=$C$8,$D$8,IF(B47&lt;=$C$9,$D$9,$D$10)))),$C$13,IF(B47&gt;$C$6,$C$6*$D$6,0),IF(B47&gt;$C$7,$C$7*$D$7,0),IF(B47&gt;$C$8,$C$8*$D$8,0),IF(B47&gt;$C$9,$C$9*$D$9,0))</f>
+        <v>500000</v>
+      </c>
+      <c r="E47" s="11" t="n">
+        <f aca="false">D47*$C$14</f>
+        <v>460000</v>
+      </c>
+      <c r="F47" s="16" t="n">
+        <f aca="false">IF(B47&gt;0,D47/B47,0)</f>
+        <v>49.99500049995</v>
+      </c>
+      <c r="G47" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C49" s="18"/>
-      <c r="D49" s="18"/>
-      <c r="E49" s="18"/>
-      <c r="F49" s="18"/>
-      <c r="G49" s="18"/>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B51" s="3" t="s">
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B48" s="9" t="n">
+        <v>15000</v>
+      </c>
+      <c r="C48" s="12" t="n">
+        <f aca="false">IF(B48&lt;=$C$6,$D$6,IF(B48&lt;=$C$7,$D$7,IF(B48&lt;=$C$8,$D$8,IF(B48&lt;=$C$9,$D$9,$D$10))))</f>
+        <v>45</v>
+      </c>
+      <c r="D48" s="12" t="n">
+        <f aca="false">MAX(B48*IF(B48&lt;=$C$6,$D$6,IF(B48&lt;=$C$7,$D$7,IF(B48&lt;=$C$8,$D$8,IF(B48&lt;=$C$9,$D$9,$D$10)))),$C$13,IF(B48&gt;$C$6,$C$6*$D$6,0),IF(B48&gt;$C$7,$C$7*$D$7,0),IF(B48&gt;$C$8,$C$8*$D$8,0),IF(B48&gt;$C$9,$C$9*$D$9,0))</f>
+        <v>675000</v>
+      </c>
+      <c r="E48" s="11" t="n">
+        <f aca="false">D48*$C$14</f>
+        <v>621000</v>
+      </c>
+      <c r="F48" s="16" t="n">
+        <f aca="false">IF(B48&gt;0,D48/B48,0)</f>
+        <v>45</v>
+      </c>
+      <c r="G48" s="2" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B52" s="19" t="s">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B49" s="9" t="n">
+        <v>30000</v>
+      </c>
+      <c r="C49" s="12" t="n">
+        <f aca="false">IF(B49&lt;=$C$6,$D$6,IF(B49&lt;=$C$7,$D$7,IF(B49&lt;=$C$8,$D$8,IF(B49&lt;=$C$9,$D$9,$D$10))))</f>
+        <v>45</v>
+      </c>
+      <c r="D49" s="12" t="n">
+        <f aca="false">MAX(B49*IF(B49&lt;=$C$6,$D$6,IF(B49&lt;=$C$7,$D$7,IF(B49&lt;=$C$8,$D$8,IF(B49&lt;=$C$9,$D$9,$D$10)))),$C$13,IF(B49&gt;$C$6,$C$6*$D$6,0),IF(B49&gt;$C$7,$C$7*$D$7,0),IF(B49&gt;$C$8,$C$8*$D$8,0),IF(B49&gt;$C$9,$C$9*$D$9,0))</f>
+        <v>1350000</v>
+      </c>
+      <c r="E49" s="11" t="n">
+        <f aca="false">D49*$C$14</f>
+        <v>1242000</v>
+      </c>
+      <c r="F49" s="16" t="n">
+        <f aca="false">IF(B49&gt;0,D49/B49,0)</f>
+        <v>45</v>
+      </c>
+      <c r="G49" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C52" s="19"/>
-      <c r="D52" s="19"/>
-      <c r="E52" s="19"/>
-      <c r="F52" s="19"/>
-      <c r="G52" s="19"/>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B53" s="19" t="s">
+    </row>
+    <row r="51" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B51" s="17" t="s">
         <v>122</v>
       </c>
-      <c r="C53" s="19"/>
-      <c r="D53" s="19"/>
-      <c r="E53" s="19"/>
-      <c r="F53" s="19"/>
-      <c r="G53" s="19"/>
+      <c r="C51" s="17"/>
+      <c r="D51" s="17"/>
+      <c r="E51" s="17"/>
+      <c r="F51" s="17"/>
+      <c r="G51" s="17"/>
+    </row>
+    <row r="52" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B52" s="18" t="s">
+        <v>123</v>
+      </c>
+      <c r="C52" s="18"/>
+      <c r="D52" s="18"/>
+      <c r="E52" s="18"/>
+      <c r="F52" s="18"/>
+      <c r="G52" s="18"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B54" s="19" t="s">
-        <v>123</v>
-      </c>
-      <c r="C54" s="19"/>
-      <c r="D54" s="19"/>
-      <c r="E54" s="19"/>
-      <c r="F54" s="19"/>
-      <c r="G54" s="19"/>
+      <c r="B54" s="3" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="19" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C55" s="19"/>
       <c r="D55" s="19"/>
@@ -4333,7 +4410,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="19" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C56" s="19"/>
       <c r="D56" s="19"/>
@@ -4343,7 +4420,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="19" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C57" s="19"/>
       <c r="D57" s="19"/>
@@ -4353,7 +4430,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="19" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C58" s="19"/>
       <c r="D58" s="19"/>
@@ -4361,20 +4438,50 @@
       <c r="F58" s="19"/>
       <c r="G58" s="19"/>
     </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B59" s="19" t="s">
+        <v>129</v>
+      </c>
+      <c r="C59" s="19"/>
+      <c r="D59" s="19"/>
+      <c r="E59" s="19"/>
+      <c r="F59" s="19"/>
+      <c r="G59" s="19"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B60" s="19" t="s">
+        <v>130</v>
+      </c>
+      <c r="C60" s="19"/>
+      <c r="D60" s="19"/>
+      <c r="E60" s="19"/>
+      <c r="F60" s="19"/>
+      <c r="G60" s="19"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B61" s="19" t="s">
+        <v>131</v>
+      </c>
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="19"/>
+      <c r="G61" s="19"/>
+    </row>
   </sheetData>
   <mergeCells count="12">
-    <mergeCell ref="C18:G18"/>
-    <mergeCell ref="C19:G19"/>
-    <mergeCell ref="C20:G20"/>
-    <mergeCell ref="B48:G48"/>
-    <mergeCell ref="B49:G49"/>
+    <mergeCell ref="C21:G21"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="C23:G23"/>
+    <mergeCell ref="B51:G51"/>
     <mergeCell ref="B52:G52"/>
-    <mergeCell ref="B53:G53"/>
-    <mergeCell ref="B54:G54"/>
     <mergeCell ref="B55:G55"/>
     <mergeCell ref="B56:G56"/>
     <mergeCell ref="B57:G57"/>
     <mergeCell ref="B58:G58"/>
+    <mergeCell ref="B59:G59"/>
+    <mergeCell ref="B60:G60"/>
+    <mergeCell ref="B61:G61"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4403,22 +4510,22 @@
   <sheetData>
     <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="3" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C6" s="9" t="n">
         <v>313</v>
@@ -4426,7 +4533,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="C7" s="9" t="n">
         <v>6</v>
@@ -4434,7 +4541,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="5" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C8" s="20" t="n">
         <f aca="false">C6-C7</f>
@@ -4443,7 +4550,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="5" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="C9" s="21" t="n">
         <v>0.1</v>
@@ -4451,7 +4558,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="5" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C10" s="22" t="n">
         <f aca="false">C8*C9</f>
@@ -4460,7 +4567,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="5" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="C11" s="21" t="n">
         <v>0.3</v>
@@ -4468,7 +4575,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="5" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C12" s="23" t="n">
         <f aca="false">C10*C11</f>
@@ -4477,7 +4584,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="5" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="C13" s="9" t="n">
         <v>18</v>
@@ -4485,12 +4592,12 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="5" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="C16" s="24" t="n">
         <v>1</v>
@@ -4498,7 +4605,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="5" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C17" s="9" t="n">
         <v>400</v>
@@ -4506,16 +4613,16 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="5" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C18" s="25" t="n">
-        <f aca="false">MAX(C17*IF(C17&lt;='Preise &amp; Pläne'!$C$6,'Preise &amp; Pläne'!$D$6,IF(C17&lt;='Preise &amp; Pläne'!$C$7,'Preise &amp; Pläne'!$D$7,'Preise &amp; Pläne'!$D$8)),'Preise &amp; Pläne'!$C$11,IF(C17&gt;'Preise &amp; Pläne'!$C$6,'Preise &amp; Pläne'!$C$6*'Preise &amp; Pläne'!$D$6,0),IF(C17&gt;'Preise &amp; Pläne'!$C$7,'Preise &amp; Pläne'!$C$7*'Preise &amp; Pläne'!$D$7,0))</f>
+        <f aca="false">MAX(C17*IF(C17&lt;='Preise &amp; Pläne'!$C$6,'Preise &amp; Pläne'!$D$6,IF(C17&lt;='Preise &amp; Pläne'!$C$7,'Preise &amp; Pläne'!$D$7,IF(C17&lt;='Preise &amp; Pläne'!$C$8,'Preise &amp; Pläne'!$D$8,IF(C17&lt;='Preise &amp; Pläne'!$C$9,'Preise &amp; Pläne'!$D$9,'Preise &amp; Pläne'!$D$10)))),'Preise &amp; Pläne'!$C$13,IF(C17&gt;'Preise &amp; Pläne'!$C$6,'Preise &amp; Pläne'!$C$6*'Preise &amp; Pläne'!$D$6,0),IF(C17&gt;'Preise &amp; Pläne'!$C$7,'Preise &amp; Pläne'!$C$7*'Preise &amp; Pläne'!$D$7,0),IF(C17&gt;'Preise &amp; Pläne'!$C$8,'Preise &amp; Pläne'!$C$8*'Preise &amp; Pläne'!$D$8,0),IF(C17&gt;'Preise &amp; Pläne'!$C$9,'Preise &amp; Pläne'!$C$9*'Preise &amp; Pläne'!$D$9,0))</f>
         <v>26000</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="5" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C19" s="21" t="n">
         <v>0.85</v>
@@ -4523,7 +4630,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="5" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C20" s="21" t="n">
         <v>0.1</v>
@@ -4531,7 +4638,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="5" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C21" s="21" t="n">
         <v>0.05</v>
@@ -4539,7 +4646,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="5" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C22" s="26" t="n">
         <v>1.5</v>
@@ -4547,7 +4654,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="5" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C23" s="10" t="n">
         <v>6130</v>
@@ -4555,27 +4662,27 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="7" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="F25" s="7" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="G25" s="7" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="5" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="C26" s="22" t="n">
         <f aca="false">$C$12*$C$16</f>
@@ -4600,7 +4707,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="5" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C27" s="22" t="n">
         <f aca="false">C26+C28</f>
@@ -4625,7 +4732,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="5" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C28" s="22" t="n">
         <f aca="false">0</f>
@@ -4650,7 +4757,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="5" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C29" s="20" t="n">
         <f aca="false">C27*$C$17</f>
@@ -4675,57 +4782,57 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="5" t="s">
-        <v>158</v>
-      </c>
-      <c r="C30" s="14" t="n">
+        <v>162</v>
+      </c>
+      <c r="C30" s="12" t="n">
         <f aca="false">C26*$C$18</f>
         <v>239460</v>
       </c>
-      <c r="D30" s="14" t="n">
+      <c r="D30" s="12" t="n">
         <f aca="false">D26*$C$18</f>
         <v>239460</v>
       </c>
-      <c r="E30" s="14" t="n">
+      <c r="E30" s="12" t="n">
         <f aca="false">E26*$C$18</f>
         <v>239460</v>
       </c>
-      <c r="F30" s="14" t="n">
+      <c r="F30" s="12" t="n">
         <f aca="false">F26*$C$18</f>
         <v>239460</v>
       </c>
-      <c r="G30" s="14" t="n">
+      <c r="G30" s="12" t="n">
         <f aca="false">G26*$C$18</f>
         <v>239460</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="5" t="s">
-        <v>159</v>
-      </c>
-      <c r="C31" s="14" t="n">
+        <v>163</v>
+      </c>
+      <c r="C31" s="12" t="n">
         <f aca="false">C28*$C$18</f>
         <v>0</v>
       </c>
-      <c r="D31" s="14" t="n">
+      <c r="D31" s="12" t="n">
         <f aca="false">D28*$C$18</f>
         <v>203541</v>
       </c>
-      <c r="E31" s="14" t="n">
+      <c r="E31" s="12" t="n">
         <f aca="false">E28*$C$18</f>
         <v>376550.85</v>
       </c>
-      <c r="F31" s="14" t="n">
+      <c r="F31" s="12" t="n">
         <f aca="false">F28*$C$18</f>
         <v>523609.2225</v>
       </c>
-      <c r="G31" s="14" t="n">
+      <c r="G31" s="12" t="n">
         <f aca="false">G28*$C$18</f>
         <v>648608.839125</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C32" s="15" t="n">
         <f aca="false">C30+C31</f>
@@ -4750,82 +4857,82 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="5" t="s">
-        <v>161</v>
-      </c>
-      <c r="C33" s="14" t="n">
+        <v>165</v>
+      </c>
+      <c r="C33" s="12" t="n">
         <f aca="false">-(C30*$C$20+C31*$C$21)</f>
         <v>-23946</v>
       </c>
-      <c r="D33" s="14" t="n">
+      <c r="D33" s="12" t="n">
         <f aca="false">-(D30*$C$20+D31*$C$21)</f>
         <v>-34123.05</v>
       </c>
-      <c r="E33" s="14" t="n">
+      <c r="E33" s="12" t="n">
         <f aca="false">-(E30*$C$20+E31*$C$21)</f>
         <v>-42773.5425</v>
       </c>
-      <c r="F33" s="14" t="n">
+      <c r="F33" s="12" t="n">
         <f aca="false">-(F30*$C$20+F31*$C$21)</f>
         <v>-50126.461125</v>
       </c>
-      <c r="G33" s="14" t="n">
+      <c r="G33" s="12" t="n">
         <f aca="false">-(G30*$C$20+G31*$C$21)</f>
         <v>-56376.44195625</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="C34" s="14" t="n">
+        <v>166</v>
+      </c>
+      <c r="C34" s="12" t="n">
         <f aca="false">-C29*$C$22</f>
         <v>-5526</v>
       </c>
-      <c r="D34" s="14" t="n">
+      <c r="D34" s="12" t="n">
         <f aca="false">-D29*$C$22</f>
         <v>-10223.1</v>
       </c>
-      <c r="E34" s="14" t="n">
+      <c r="E34" s="12" t="n">
         <f aca="false">-E29*$C$22</f>
         <v>-14215.635</v>
       </c>
-      <c r="F34" s="14" t="n">
+      <c r="F34" s="12" t="n">
         <f aca="false">-F29*$C$22</f>
         <v>-17609.28975</v>
       </c>
-      <c r="G34" s="14" t="n">
+      <c r="G34" s="12" t="n">
         <f aca="false">-G29*$C$22</f>
         <v>-20493.8962875</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="C35" s="14" t="n">
+        <v>167</v>
+      </c>
+      <c r="C35" s="12" t="n">
         <f aca="false">-$C$23</f>
         <v>-6130</v>
       </c>
-      <c r="D35" s="14" t="n">
+      <c r="D35" s="12" t="n">
         <f aca="false">-$C$23</f>
         <v>-6130</v>
       </c>
-      <c r="E35" s="14" t="n">
+      <c r="E35" s="12" t="n">
         <f aca="false">-$C$23</f>
         <v>-6130</v>
       </c>
-      <c r="F35" s="14" t="n">
+      <c r="F35" s="12" t="n">
         <f aca="false">-$C$23</f>
         <v>-6130</v>
       </c>
-      <c r="G35" s="14" t="n">
+      <c r="G35" s="12" t="n">
         <f aca="false">-$C$23</f>
         <v>-6130</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="3" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C36" s="15" t="n">
         <f aca="false">SUM(C32:C35)</f>
@@ -4850,7 +4957,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="5" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C37" s="27" t="n">
         <f aca="false">IF(C32&lt;&gt;0,C36/C32,0)</f>
@@ -4875,7 +4982,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="5" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C39" s="15" t="n">
         <f aca="false">SUM(C32:G32)</f>
@@ -4884,16 +4991,16 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="5" t="s">
-        <v>167</v>
-      </c>
-      <c r="C40" s="14" t="n">
+        <v>171</v>
+      </c>
+      <c r="C40" s="12" t="n">
         <f aca="false">SUM(C33:G33)</f>
         <v>-207345.49558125</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="5" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C41" s="15" t="n">
         <f aca="false">SUM(C36:G36)</f>
@@ -4902,7 +5009,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="2" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -4933,22 +5040,22 @@
   <sheetData>
     <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="3" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="C6" s="9" t="n">
         <v>600</v>
@@ -4956,7 +5063,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C7" s="21" t="n">
         <v>0.05</v>
@@ -4964,7 +5071,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="5" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="C8" s="21" t="n">
         <v>0.15</v>
@@ -4972,7 +5079,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="5" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C9" s="22" t="n">
         <f aca="false">C6*C7*C8</f>
@@ -4981,7 +5088,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="5" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="C10" s="10" t="n">
         <v>6000</v>
@@ -4989,7 +5096,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="5" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C11" s="10" t="n">
         <v>40</v>
@@ -4997,7 +5104,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="5" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="C12" s="21" t="n">
         <v>0.05</v>
@@ -5005,7 +5112,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="5" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C13" s="22" t="n">
         <f aca="false">IF(C11&gt;0,C10/C11*C12,0)</f>
@@ -5014,7 +5121,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="5" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="C14" s="9" t="n">
         <v>60</v>
@@ -5022,7 +5129,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="5" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="C15" s="21" t="n">
         <v>0.1</v>
@@ -5030,7 +5137,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="5" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="C16" s="22" t="n">
         <f aca="false">C14*C15</f>
@@ -5039,7 +5146,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="5" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="C17" s="23" t="n">
         <f aca="false">C9+C13+C16</f>
@@ -5048,7 +5155,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="5" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C18" s="21" t="n">
         <v>0.2</v>
@@ -5056,12 +5163,12 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="5" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C21" s="9" t="n">
         <v>150</v>
@@ -5069,16 +5176,16 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="5" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="C22" s="25" t="n">
-        <f aca="false">MAX(C21*IF(C21&lt;='Preise &amp; Pläne'!$C$6,'Preise &amp; Pläne'!$D$6,IF(C21&lt;='Preise &amp; Pläne'!$C$7,'Preise &amp; Pläne'!$D$7,'Preise &amp; Pläne'!$D$8)),'Preise &amp; Pläne'!$C$11,IF(C21&gt;'Preise &amp; Pläne'!$C$6,'Preise &amp; Pläne'!$C$6*'Preise &amp; Pläne'!$D$6,0),IF(C21&gt;'Preise &amp; Pläne'!$C$7,'Preise &amp; Pläne'!$C$7*'Preise &amp; Pläne'!$D$7,0))</f>
+        <f aca="false">MAX(C21*IF(C21&lt;='Preise &amp; Pläne'!$C$6,'Preise &amp; Pläne'!$D$6,IF(C21&lt;='Preise &amp; Pläne'!$C$7,'Preise &amp; Pläne'!$D$7,IF(C21&lt;='Preise &amp; Pläne'!$C$8,'Preise &amp; Pläne'!$D$8,IF(C21&lt;='Preise &amp; Pläne'!$C$9,'Preise &amp; Pläne'!$D$9,'Preise &amp; Pläne'!$D$10)))),'Preise &amp; Pläne'!$C$13,IF(C21&gt;'Preise &amp; Pläne'!$C$6,'Preise &amp; Pläne'!$C$6*'Preise &amp; Pläne'!$D$6,0),IF(C21&gt;'Preise &amp; Pläne'!$C$7,'Preise &amp; Pläne'!$C$7*'Preise &amp; Pläne'!$D$7,0),IF(C21&gt;'Preise &amp; Pläne'!$C$8,'Preise &amp; Pläne'!$C$8*'Preise &amp; Pläne'!$D$8,0),IF(C21&gt;'Preise &amp; Pläne'!$C$9,'Preise &amp; Pläne'!$C$9*'Preise &amp; Pläne'!$D$9,0))</f>
         <v>9750</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="5" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C23" s="21" t="n">
         <v>0.85</v>
@@ -5086,7 +5193,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="5" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C24" s="26" t="n">
         <v>3</v>
@@ -5094,7 +5201,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="5" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C25" s="10" t="n">
         <v>6130</v>
@@ -5102,27 +5209,27 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="7" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="D27" s="7" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E27" s="7" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="F27" s="7" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="G27" s="7" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="5" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="C28" s="22" t="n">
         <f aca="false">$C$17*(1+$C$18)^0</f>
@@ -5147,7 +5254,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="5" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C29" s="22" t="n">
         <f aca="false">C28+C30</f>
@@ -5172,7 +5279,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="5" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C30" s="22" t="n">
         <f aca="false">0</f>
@@ -5197,7 +5304,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="5" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C31" s="20" t="n">
         <f aca="false">C29*$C$21</f>
@@ -5222,7 +5329,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="3" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="C32" s="15" t="n">
         <f aca="false">C29*$C$22</f>
@@ -5247,82 +5354,82 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="5" t="s">
-        <v>186</v>
-      </c>
-      <c r="C33" s="14" t="n">
+        <v>190</v>
+      </c>
+      <c r="C33" s="12" t="n">
         <f aca="false">-$C$10</f>
         <v>-6000</v>
       </c>
-      <c r="D33" s="14" t="n">
+      <c r="D33" s="12" t="n">
         <f aca="false">-$C$10</f>
         <v>-6000</v>
       </c>
-      <c r="E33" s="14" t="n">
+      <c r="E33" s="12" t="n">
         <f aca="false">-$C$10</f>
         <v>-6000</v>
       </c>
-      <c r="F33" s="14" t="n">
+      <c r="F33" s="12" t="n">
         <f aca="false">-$C$10</f>
         <v>-6000</v>
       </c>
-      <c r="G33" s="14" t="n">
+      <c r="G33" s="12" t="n">
         <f aca="false">-$C$10</f>
         <v>-6000</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="5" t="s">
-        <v>162</v>
-      </c>
-      <c r="C34" s="14" t="n">
+        <v>166</v>
+      </c>
+      <c r="C34" s="12" t="n">
         <f aca="false">-C31*$C$24</f>
         <v>-8100</v>
       </c>
-      <c r="D34" s="14" t="n">
+      <c r="D34" s="12" t="n">
         <f aca="false">-D31*$C$24</f>
         <v>-16605</v>
       </c>
-      <c r="E34" s="14" t="n">
+      <c r="E34" s="12" t="n">
         <f aca="false">-E31*$C$24</f>
         <v>-25778.25</v>
       </c>
-      <c r="F34" s="14" t="n">
+      <c r="F34" s="12" t="n">
         <f aca="false">-F31*$C$24</f>
         <v>-35908.3125</v>
       </c>
-      <c r="G34" s="14" t="n">
+      <c r="G34" s="12" t="n">
         <f aca="false">-G31*$C$24</f>
         <v>-47318.225625</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="5" t="s">
-        <v>163</v>
-      </c>
-      <c r="C35" s="14" t="n">
+        <v>167</v>
+      </c>
+      <c r="C35" s="12" t="n">
         <f aca="false">-$C$25</f>
         <v>-6130</v>
       </c>
-      <c r="D35" s="14" t="n">
+      <c r="D35" s="12" t="n">
         <f aca="false">-$C$25</f>
         <v>-6130</v>
       </c>
-      <c r="E35" s="14" t="n">
+      <c r="E35" s="12" t="n">
         <f aca="false">-$C$25</f>
         <v>-6130</v>
       </c>
-      <c r="F35" s="14" t="n">
+      <c r="F35" s="12" t="n">
         <f aca="false">-$C$25</f>
         <v>-6130</v>
       </c>
-      <c r="G35" s="14" t="n">
+      <c r="G35" s="12" t="n">
         <f aca="false">-$C$25</f>
         <v>-6130</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="3" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="C36" s="15" t="n">
         <f aca="false">SUM(C32:C35)</f>
@@ -5347,7 +5454,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="5" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C37" s="27" t="n">
         <f aca="false">IF(C32&lt;&gt;0,C36/C32,0)</f>
@@ -5372,7 +5479,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="5" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C39" s="15" t="n">
         <f aca="false">SUM(C32:G32)</f>
@@ -5381,16 +5488,16 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="5" t="s">
-        <v>187</v>
-      </c>
-      <c r="C40" s="14" t="n">
+        <v>191</v>
+      </c>
+      <c r="C40" s="12" t="n">
         <f aca="false">SUM(C33:G33)</f>
         <v>-30000</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="5" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="C41" s="15" t="n">
         <f aca="false">SUM(C36:G36)</f>
@@ -5399,7 +5506,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="2" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
     </row>
   </sheetData>
@@ -5430,40 +5537,40 @@
   <sheetData>
     <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="7" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="C6" s="25" t="n">
         <f aca="false">'Mit Anwalts-Funnel'!C32</f>
@@ -5492,7 +5599,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C7" s="25" t="n">
         <f aca="false">'Ohne Anwalt (Direkt)'!C32</f>
@@ -5521,25 +5628,25 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="C8" s="14" t="n">
+        <v>199</v>
+      </c>
+      <c r="C8" s="12" t="n">
         <f aca="false">C6+C7</f>
         <v>414960</v>
       </c>
-      <c r="D8" s="14" t="n">
+      <c r="D8" s="12" t="n">
         <f aca="false">D6+D7</f>
         <v>802776</v>
       </c>
-      <c r="E8" s="14" t="n">
+      <c r="E8" s="12" t="n">
         <f aca="false">E6+E7</f>
         <v>1174539.6</v>
       </c>
-      <c r="F8" s="14" t="n">
+      <c r="F8" s="12" t="n">
         <f aca="false">F6+F7</f>
         <v>1541082.66</v>
       </c>
-      <c r="G8" s="14" t="n">
+      <c r="G8" s="12" t="n">
         <f aca="false">G6+G7</f>
         <v>1913297.061</v>
       </c>
@@ -5550,7 +5657,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="5" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="C9" s="25" t="n">
         <f aca="false">'Mit Anwalts-Funnel'!C36</f>
@@ -5579,7 +5686,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="5" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="C10" s="25" t="n">
         <f aca="false">'Ohne Anwalt (Direkt)'!C36</f>
@@ -5608,25 +5715,25 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="C11" s="14" t="n">
+        <v>202</v>
+      </c>
+      <c r="C11" s="12" t="n">
         <f aca="false">C9+C10+'Ohne Anwalt (Direkt)'!$C$25</f>
         <v>365258</v>
       </c>
-      <c r="D11" s="14" t="n">
+      <c r="D11" s="12" t="n">
         <f aca="false">D9+D10+'Ohne Anwalt (Direkt)'!$C$25</f>
         <v>729694.85</v>
       </c>
-      <c r="E11" s="14" t="n">
+      <c r="E11" s="12" t="n">
         <f aca="false">E9+E10+'Ohne Anwalt (Direkt)'!$C$25</f>
         <v>1079642.1725</v>
       </c>
-      <c r="F11" s="14" t="n">
+      <c r="F11" s="12" t="n">
         <f aca="false">F9+F10+'Ohne Anwalt (Direkt)'!$C$25</f>
         <v>1425308.596625</v>
       </c>
-      <c r="G11" s="14" t="n">
+      <c r="G11" s="12" t="n">
         <f aca="false">G9+G10+'Ohne Anwalt (Direkt)'!$C$25</f>
         <v>1776978.49713125</v>
       </c>
@@ -5637,7 +5744,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="5" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="C12" s="28" t="n">
         <f aca="false">'Mit Anwalts-Funnel'!C27</f>
@@ -5666,7 +5773,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="5" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C13" s="28" t="n">
         <f aca="false">'Ohne Anwalt (Direkt)'!C29</f>
@@ -5695,25 +5802,25 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="5" t="s">
-        <v>201</v>
-      </c>
-      <c r="C14" s="14" t="n">
+        <v>205</v>
+      </c>
+      <c r="C14" s="12" t="n">
         <f aca="false">-'Mit Anwalts-Funnel'!C33</f>
         <v>23946</v>
       </c>
-      <c r="D14" s="14" t="n">
+      <c r="D14" s="12" t="n">
         <f aca="false">-'Mit Anwalts-Funnel'!D33</f>
         <v>34123.05</v>
       </c>
-      <c r="E14" s="14" t="n">
+      <c r="E14" s="12" t="n">
         <f aca="false">-'Mit Anwalts-Funnel'!E33</f>
         <v>42773.5425</v>
       </c>
-      <c r="F14" s="14" t="n">
+      <c r="F14" s="12" t="n">
         <f aca="false">-'Mit Anwalts-Funnel'!F33</f>
         <v>50126.461125</v>
       </c>
-      <c r="G14" s="14" t="n">
+      <c r="G14" s="12" t="n">
         <f aca="false">-'Mit Anwalts-Funnel'!G33</f>
         <v>56376.44195625</v>
       </c>
@@ -5724,25 +5831,25 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="5" t="s">
-        <v>202</v>
-      </c>
-      <c r="C15" s="14" t="n">
+        <v>206</v>
+      </c>
+      <c r="C15" s="12" t="n">
         <f aca="false">-'Ohne Anwalt (Direkt)'!C33</f>
         <v>6000</v>
       </c>
-      <c r="D15" s="14" t="n">
+      <c r="D15" s="12" t="n">
         <f aca="false">-'Ohne Anwalt (Direkt)'!D33</f>
         <v>6000</v>
       </c>
-      <c r="E15" s="14" t="n">
+      <c r="E15" s="12" t="n">
         <f aca="false">-'Ohne Anwalt (Direkt)'!E33</f>
         <v>6000</v>
       </c>
-      <c r="F15" s="14" t="n">
+      <c r="F15" s="12" t="n">
         <f aca="false">-'Ohne Anwalt (Direkt)'!F33</f>
         <v>6000</v>
       </c>
-      <c r="G15" s="14" t="n">
+      <c r="G15" s="12" t="n">
         <f aca="false">-'Ohne Anwalt (Direkt)'!G33</f>
         <v>6000</v>
       </c>
@@ -5753,7 +5860,7 @@
     </row>
     <row r="17" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="17" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="C17" s="17"/>
       <c r="D17" s="17"/>
@@ -5800,4412 +5907,4412 @@
   <sheetData>
     <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="7" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="H5" s="7" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="I5" s="7" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="J5" s="7" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="L5" s="7" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="4" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="G6" s="29" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="4" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="F7" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="G7" s="29" t="s">
+        <v>231</v>
+      </c>
+      <c r="H7" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="G7" s="29" t="s">
-        <v>227</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>222</v>
-      </c>
       <c r="I7" s="4" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="J7" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="4" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="E8" s="4" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="G8" s="29" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="J8" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="4" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="F9" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="G9" s="29" t="s">
+        <v>241</v>
+      </c>
+      <c r="H9" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="G9" s="29" t="s">
-        <v>237</v>
-      </c>
-      <c r="H9" s="4" t="s">
-        <v>232</v>
-      </c>
       <c r="I9" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="L9" s="4" t="s">
         <v>238</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>224</v>
-      </c>
-      <c r="L9" s="4" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="4" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D10" s="4" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="G10" s="29" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="H10" s="4" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="J10" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="4" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="G11" s="29" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="H11" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="J11" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="4" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="G12" s="29" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="H12" s="4" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="J12" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L12" s="4" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="4" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="G13" s="29" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="H13" s="4" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="J13" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L13" s="4" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="4" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="G14" s="29" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="J14" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="4" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="G15" s="29" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="H15" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="J15" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K15" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L15" s="4" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="4" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="G16" s="29" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K16" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L16" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="4" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="G17" s="29" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="J17" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K17" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L17" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="4" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="G18" s="29" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="H18" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="J18" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K18" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L18" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="4" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="G19" s="29" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="H19" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="J19" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K19" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L19" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="4" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="G20" s="29" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="H20" s="4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="I20" s="4" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="J20" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="4" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="G21" s="29" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="J21" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K21" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L21" s="4" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="4" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="G22" s="29" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="H22" s="4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="J22" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="4" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="G23" s="29" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="J23" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K23" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L23" s="4" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="4" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="G24" s="29" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="J24" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K24" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L24" s="4" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="4" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="G25" s="29" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="J25" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L25" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="4" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="G26" s="29" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="J26" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K26" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L26" s="4" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="4" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="G27" s="29" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="H27" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="J27" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K27" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L27" s="4" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="4" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="G28" s="29" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="H28" s="4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="J28" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K28" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L28" s="4" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="4" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="G29" s="29" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="H29" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="J29" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K29" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L29" s="4" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="4" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="G30" s="29" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="H30" s="4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="J30" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L30" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="4" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="G31" s="29" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="J31" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K31" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L31" s="4" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="4" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="G32" s="29" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="H32" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I32" s="4" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="J32" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K32" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L32" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="4" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="G33" s="29" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="H33" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="J33" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K33" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L33" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="4" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="G34" s="4"/>
       <c r="H34" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="J34" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K34" s="4" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="L34" s="4" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="4" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="G35" s="29" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="H35" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="J35" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K35" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L35" s="4" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="4" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="G36" s="29" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="H36" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="J36" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K36" s="4" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="L36" s="4" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="4" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="G37" s="29" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="J37" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K37" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L37" s="4" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="4" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="G38" s="29" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="J38" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K38" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L38" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="4" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="G39" s="29" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="J39" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K39" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L39" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="4" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="G40" s="29" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="J40" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K40" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L40" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="4" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="G41" s="29" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="H41" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="J41" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K41" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L41" s="4" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="4" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="G42" s="29" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="H42" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="J42" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K42" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L42" s="4" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="4" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="G43" s="29" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="H43" s="4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="J43" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K43" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L43" s="4" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="G44" s="29" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="H44" s="4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="I44" s="4" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="J44" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K44" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L44" s="4" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="G45" s="29" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="H45" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I45" s="4" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="J45" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K45" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L45" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="G46" s="29" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="H46" s="4" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="J46" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K46" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L46" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="G47" s="29" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="H47" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="J47" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K47" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L47" s="4" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="G48" s="29" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="H48" s="4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="J48" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K48" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L48" s="4" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="G49" s="29" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="H49" s="4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="J49" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K49" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L49" s="4" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="G50" s="29" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="H50" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I50" s="4" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="J50" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K50" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L50" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="G51" s="29" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="H51" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="J51" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K51" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L51" s="4" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="G52" s="29" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="H52" s="4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="I52" s="4" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="J52" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K52" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L52" s="4" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="G53" s="29" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="H53" s="4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="I53" s="4" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="J53" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K53" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L53" s="4" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="G54" s="29" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="H54" s="4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="J54" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K54" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L54" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="G55" s="29" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="H55" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="J55" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K55" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L55" s="4" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="G56" s="29" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="H56" s="4" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="I56" s="4" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="J56" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K56" s="4" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="L56" s="4" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="4" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="G57" s="29" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="H57" s="4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="J57" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K57" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L57" s="4" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="4" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="G58" s="29" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="H58" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I58" s="4" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="J58" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K58" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L58" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="4" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="G59" s="29" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="H59" s="4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="J59" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K59" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L59" s="4" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B60" s="4" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="G60" s="29" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="H60" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="J60" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K60" s="4" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="L60" s="4" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B61" s="4" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="G61" s="29" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="H61" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I61" s="4" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="J61" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K61" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L61" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B62" s="4" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="G62" s="29" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="H62" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I62" s="4" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="J62" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K62" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L62" s="4" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B63" s="4" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="G63" s="29" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="H63" s="4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="I63" s="4" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="J63" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K63" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L63" s="4" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B64" s="4" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="G64" s="29" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="H64" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="J64" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K64" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L64" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B65" s="4" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="G65" s="29" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="H65" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="J65" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K65" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L65" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B66" s="4" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="G66" s="29" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="H66" s="4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="I66" s="4" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="J66" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K66" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L66" s="4" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B67" s="4" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="G67" s="29" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="H67" s="4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="I67" s="4" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="J67" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K67" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L67" s="4" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B68" s="4" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="G68" s="29" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="H68" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I68" s="4" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="J68" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K68" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L68" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B69" s="4" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="G69" s="29" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="H69" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I69" s="4" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="J69" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K69" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L69" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B70" s="4" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="G70" s="29" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="H70" s="4" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="I70" s="4" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="J70" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K70" s="4" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="L70" s="4" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B71" s="4" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="G71" s="29" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="H71" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I71" s="4" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="J71" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K71" s="4" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="L71" s="4" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B72" s="4" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="G72" s="29" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="H72" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I72" s="4" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="J72" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K72" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L72" s="4" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B73" s="4" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="G73" s="29" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="H73" s="4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="I73" s="4" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="J73" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K73" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L73" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B74" s="4" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="G74" s="29" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="H74" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I74" s="4" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="J74" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K74" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L74" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B75" s="4" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="G75" s="29" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="H75" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I75" s="4" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="J75" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K75" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L75" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B76" s="4" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="G76" s="29" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="H76" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I76" s="4" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="J76" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K76" s="4" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="L76" s="4" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B77" s="4" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="G77" s="29" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="H77" s="4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="I77" s="4" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="J77" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K77" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L77" s="4" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B78" s="4" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="G78" s="29" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="H78" s="4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="I78" s="4" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="J78" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K78" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L78" s="4" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B79" s="4" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="G79" s="29" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="H79" s="4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="I79" s="4" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="J79" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K79" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L79" s="4" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B80" s="4" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="G80" s="29" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="H80" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I80" s="4" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="J80" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K80" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L80" s="4" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B81" s="4" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="G81" s="29" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="H81" s="4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="I81" s="4" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="J81" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K81" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L81" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B82" s="4" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="G82" s="29" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="H82" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I82" s="4" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="J82" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K82" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L82" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B83" s="4" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="G83" s="29" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="H83" s="4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="I83" s="4" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="J83" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K83" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L83" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B84" s="4" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="G84" s="4"/>
       <c r="H84" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I84" s="4" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="J84" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K84" s="4" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="L84" s="4" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B85" s="4" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="G85" s="29" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="H85" s="4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="I85" s="4" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="J85" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K85" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L85" s="4" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B86" s="4" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
       <c r="G86" s="29" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="H86" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I86" s="4" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="J86" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K86" s="4" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="L86" s="4" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B87" s="4" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="C87" s="4" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
       <c r="G87" s="29" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="H87" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I87" s="4" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
       <c r="J87" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K87" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L87" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B88" s="4" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
       <c r="G88" s="4"/>
       <c r="H88" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I88" s="4" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="J88" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K88" s="4" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="L88" s="4" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B89" s="4" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
       <c r="G89" s="29" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="H89" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I89" s="4" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="J89" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K89" s="4" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="L89" s="4" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B90" s="4" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="G90" s="29" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="H90" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I90" s="4" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="J90" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K90" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L90" s="4" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B91" s="4" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="G91" s="29" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="H91" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I91" s="4" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="J91" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K91" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L91" s="4" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B92" s="4" t="s">
+        <v>580</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="D92" s="4" t="s">
+        <v>391</v>
+      </c>
+      <c r="E92" s="4" t="s">
+        <v>604</v>
+      </c>
+      <c r="F92" s="4" t="s">
         <v>576</v>
       </c>
-      <c r="C92" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="D92" s="4" t="s">
-        <v>387</v>
-      </c>
-      <c r="E92" s="4" t="s">
-        <v>600</v>
-      </c>
-      <c r="F92" s="4" t="s">
-        <v>572</v>
-      </c>
       <c r="G92" s="29" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="H92" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I92" s="4" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="J92" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K92" s="4" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="L92" s="4" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B93" s="4" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="G93" s="29" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="H93" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I93" s="4" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="J93" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K93" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L93" s="4" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B94" s="4" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="G94" s="29" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="H94" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I94" s="4" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="J94" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K94" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L94" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B95" s="4" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="G95" s="29" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="H95" s="4" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="I95" s="4" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="J95" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K95" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L95" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B96" s="4" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="G96" s="29" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="H96" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I96" s="4" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="J96" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K96" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L96" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B97" s="4" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="G97" s="29" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="H97" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I97" s="4" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="J97" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K97" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L97" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B98" s="4" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="E98" s="4" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="F98" s="4" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="G98" s="29" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="H98" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I98" s="4" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="J98" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K98" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L98" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B99" s="4" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="G99" s="29" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="H99" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I99" s="4" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="J99" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K99" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L99" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B100" s="4" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="G100" s="29" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="H100" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I100" s="4" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="J100" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K100" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L100" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B101" s="4" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="G101" s="29" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
       <c r="H101" s="4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="I101" s="4" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="J101" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K101" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L101" s="4" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B102" s="4" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="G102" s="29" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="H102" s="4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="I102" s="4" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="J102" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K102" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L102" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B103" s="4" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="G103" s="29" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="H103" s="4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="I103" s="4" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="J103" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K103" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L103" s="4" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B104" s="4" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="G104" s="29" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="H104" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I104" s="4" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
       <c r="J104" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K104" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L104" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B105" s="4" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="G105" s="29" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="H105" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I105" s="4" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="J105" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K105" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L105" s="4" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B106" s="4" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="G106" s="29" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="H106" s="4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="I106" s="4" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="J106" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K106" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L106" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B107" s="4" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
       <c r="G107" s="29" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="H107" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I107" s="4" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
       <c r="J107" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K107" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L107" s="4" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B108" s="4" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="G108" s="29" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="H108" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I108" s="4" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="J108" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K108" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L108" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B109" s="4" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="G109" s="29" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="H109" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I109" s="4" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="J109" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K109" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L109" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B110" s="4" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="G110" s="29" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="H110" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I110" s="4" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="J110" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K110" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L110" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B111" s="4" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
       <c r="G111" s="29" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
       <c r="H111" s="4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="I111" s="4" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="J111" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K111" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L111" s="4" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B112" s="4" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="G112" s="29" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="H112" s="4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="I112" s="4" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="J112" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K112" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L112" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B113" s="4" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="G113" s="29" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="H113" s="4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="I113" s="4" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="J113" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K113" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L113" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B114" s="4" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="G114" s="29" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="H114" s="4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="I114" s="4" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="J114" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K114" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L114" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B115" s="4" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="G115" s="29" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="H115" s="4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="I115" s="4" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="J115" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K115" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L115" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B116" s="4" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="G116" s="29" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="H116" s="4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="I116" s="4" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="J116" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K116" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L116" s="4" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B117" s="4" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="G117" s="29" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="H117" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I117" s="4" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="J117" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K117" s="4" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="L117" s="4" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B118" s="4" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="G118" s="29" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="H118" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I118" s="4" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="J118" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K118" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L118" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B119" s="4" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="G119" s="29" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="H119" s="4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="I119" s="4" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="J119" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K119" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L119" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B120" s="4" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="G120" s="4"/>
       <c r="H120" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I120" s="4" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="J120" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K120" s="4" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="L120" s="4" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B121" s="4" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="G121" s="29" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="H121" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I121" s="4" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="J121" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K121" s="4" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="L121" s="4" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B122" s="4" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="G122" s="29" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="H122" s="4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="I122" s="4" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="J122" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K122" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L122" s="4" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B123" s="4" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="C123" s="4" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="G123" s="29" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="H123" s="4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="I123" s="4" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="J123" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K123" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L123" s="4" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B124" s="4" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="G124" s="29" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="H124" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I124" s="4" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="J124" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K124" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L124" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B125" s="4" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="G125" s="29" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="H125" s="4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="I125" s="4" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="J125" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K125" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L125" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B126" s="4" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="C126" s="4" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="G126" s="29" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="H126" s="4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="I126" s="4" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="J126" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K126" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L126" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B127" s="4" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
       <c r="G127" s="29" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
       <c r="H127" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I127" s="4" t="s">
-        <v>738</v>
+        <v>742</v>
       </c>
       <c r="J127" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K127" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L127" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B128" s="4" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="C128" s="4" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="F128" s="4" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="G128" s="29" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="H128" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I128" s="4" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="J128" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K128" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L128" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B129" s="4" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F129" s="4" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="G129" s="29" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
       <c r="H129" s="4" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="I129" s="4" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="J129" s="4" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="K129" s="4" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L129" s="4" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B130" s="4" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="G130" s="4"/>
       <c r="H130" s="4" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="I130" s="4" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="J130" s="4" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="K130" s="4" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="L130" s="4" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
     </row>
   </sheetData>

--- a/docs/RALK_Preise_Plaene_Vertrieb.xlsx
+++ b/docs/RALK_Preise_Plaene_Vertrieb.xlsx
@@ -66,11 +66,11 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Obergrenze der Klasse (Mitarbeiterzahl).</t>
+          <t xml:space="preserve">Obergrenze der Klasse (Mitarbeiterzahl). Letzte Klasse = unbegrenzt.</t>
         </r>
       </text>
     </comment>
-    <comment ref="C9" authorId="0">
+    <comment ref="C11" authorId="0">
       <text>
         <r>
           <rPr>
@@ -78,11 +78,11 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Obergrenze der Klasse (Mitarbeiterzahl).</t>
+          <t xml:space="preserve">Quelle: RALK_Preismodell, „Mindest-Jahreslizenz (Floor)“.</t>
         </r>
       </text>
     </comment>
-    <comment ref="C10" authorId="0">
+    <comment ref="C12" authorId="0">
       <text>
         <r>
           <rPr>
@@ -90,7 +90,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Obergrenze der Klasse (Mitarbeiterzahl). Letzte Klasse = unbegrenzt.</t>
+          <t xml:space="preserve">Quelle: RALK_Preismodell, Blatt „Annahmen“. Bei Bedarf aktualisieren.</t>
         </r>
       </text>
     </comment>
@@ -102,35 +102,11 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Quelle: RALK_Preismodell, „Mindest-Jahreslizenz (Floor)“.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C14" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Quelle: RALK_Preismodell, Blatt „Annahmen“. Bei Bedarf aktualisieren.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C15" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
           <t xml:space="preserve">Gestrichen (früher 15 %, mind. 2.500 €).</t>
         </r>
       </text>
     </comment>
-    <comment ref="C26" authorId="0">
+    <comment ref="C24" authorId="0">
       <text>
         <r>
           <rPr>
@@ -150,7 +126,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Preisstaffel Okt. 2026 (feinere Stufen nach Marktvergleich; 45 $ für Großorganisationen wie mit Achapa vereinbart).</t>
+          <t xml:space="preserve">Preisstaffel Okt. 2026 (3 Stufen, Grenzen nach Marktvergleich; 45 $ für Großorganisationen wie mit Achapa vereinbart).</t>
         </r>
       </text>
     </comment>
@@ -162,7 +138,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Preisstaffel Okt. 2026 (feinere Stufen nach Marktvergleich; 45 $ für Großorganisationen wie mit Achapa vereinbart).</t>
+          <t xml:space="preserve">Preisstaffel Okt. 2026 (3 Stufen, Grenzen nach Marktvergleich; 45 $ für Großorganisationen wie mit Achapa vereinbart).</t>
         </r>
       </text>
     </comment>
@@ -174,31 +150,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Preisstaffel Okt. 2026 (feinere Stufen nach Marktvergleich; 45 $ für Großorganisationen wie mit Achapa vereinbart).</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D9" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Preisstaffel Okt. 2026 (feinere Stufen nach Marktvergleich; 45 $ für Großorganisationen wie mit Achapa vereinbart).</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="D10" authorId="0">
-      <text>
-        <r>
-          <rPr>
-            <sz val="10"/>
-            <rFont val="Arial"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">Preisstaffel Okt. 2026 (feinere Stufen nach Marktvergleich; 45 $ für Großorganisationen wie mit Achapa vereinbart).</t>
+          <t xml:space="preserve">Preisstaffel Okt. 2026 (3 Stufen, Grenzen nach Marktvergleich; 45 $ für Großorganisationen wie mit Achapa vereinbart).</t>
         </r>
       </text>
     </comment>
@@ -527,7 +479,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1621" uniqueCount="753">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1620" uniqueCount="751">
   <si>
     <t xml:space="preserve">RALK – Preise, Pläne &amp; Vertriebsmodell</t>
   </si>
@@ -595,7 +547,7 @@
     <t xml:space="preserve">Preise</t>
   </si>
   <si>
-    <t xml:space="preserve">Neue Staffel (Okt. 2026, nach Marktvergleich): bis 500 MA 65 $, 501–2.000 60 $, 2.001–5.000 55 $, 5.001–10.000 50 $, über 10.000 45 $. Mindest-Jahreslizenz 5.000 $, keine Setup-Fee. Vorher (RALK_Preismodell): ≤4.000 65 $, 4.001–7.999 50 $, ≥8.000 45 $.</t>
+    <t xml:space="preserve">Neue Staffel (Okt. 2026, nach Marktvergleich): bis 1.000 MA 65 $, 1.001–10.000 MA 55 $, über 10.000 MA 45 $. Mindest-Jahreslizenz 5.000 $, keine Setup-Fee. Vorher (RALK_Preismodell): ≤4.000 65 $, 4.001–7.999 50 $, ≥8.000 45 $.</t>
   </si>
   <si>
     <t xml:space="preserve">Funnel-Zahlen</t>
@@ -757,16 +709,10 @@
     <t xml:space="preserve">Lizenz an der Obergrenze</t>
   </si>
   <si>
-    <t xml:space="preserve">bis 500</t>
-  </si>
-  <si>
-    <t xml:space="preserve">501 – 2.000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.001 – 5.000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.001 – 10.000</t>
+    <t xml:space="preserve">bis 1.000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.001 – 10.000</t>
   </si>
   <si>
     <t xml:space="preserve">über 10.000</t>
@@ -871,31 +817,31 @@
     <t xml:space="preserve">Klassengrenze</t>
   </si>
   <si>
-    <t xml:space="preserve">Übergangsregel: wie 500 MA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Übergangsregel: wie 2.000 MA</t>
+    <t xml:space="preserve">Übergangsregel: wie 1.000 MA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ab hier normaler 55-$-Satz</t>
   </si>
   <si>
     <t xml:space="preserve">z. B. große Bank</t>
   </si>
   <si>
-    <t xml:space="preserve">Übergangsregel: wie 5.000 MA</t>
-  </si>
-  <si>
     <t xml:space="preserve">z. B. Kenya Revenue Authority</t>
   </si>
   <si>
     <t xml:space="preserve">Übergangsregel: wie 10.000 MA</t>
   </si>
   <si>
+    <t xml:space="preserve">ab hier normaler 45-$-Satz</t>
+  </si>
+  <si>
     <t xml:space="preserve">Verband</t>
   </si>
   <si>
     <t xml:space="preserve">z. B. Law Society of Kenya</t>
   </si>
   <si>
-    <t xml:space="preserve">Übergangsregel (wie bei Atlassian-Stufen): Wer in eine günstigere Klasse rutscht, zahlt nie weniger als die größte Organisation der Klasse darunter (Spalte „Lizenz an der Obergrenze“). Beispiel: 501–541 MA zahlen 32.500 $ wie 500 MA, danach gilt 60 $. So gibt es keinen Preissprung nach unten.</t>
+    <t xml:space="preserve">Übergangsregel (wie bei Atlassian-Stufen): Wer in eine günstigere Klasse rutscht, zahlt nie weniger als die größte Organisation der Klasse darunter (Spalte „Lizenz an der Obergrenze“). Beispiel: 1.001–1.181 MA zahlen 65.000 $ wie 1.000 MA, danach gilt 55 $; 10.001–12.222 MA zahlen 550.000 $ wie 10.000 MA, danach 45 $. So gibt es keinen Preissprung nach unten.</t>
   </si>
   <si>
     <t xml:space="preserve">Feste Preisliste: gleicher Preis für alle, Mengenrabatt steckt in den Klassen (wie KnowBe4/Atlassian), keine Einzelrabatte, keine Verhandlung.</t>
@@ -922,7 +868,7 @@
     <t xml:space="preserve">• E-Mail-Support</t>
   </si>
   <si>
-    <t xml:space="preserve">• Ab 2.001 MA zusätzlich: fester Ansprechpartner für die Einführung</t>
+    <t xml:space="preserve">• Ab 1.001 MA zusätzlich: fester Ansprechpartner für die Einführung</t>
   </si>
   <si>
     <t xml:space="preserve">Mit Anwalts-Funnel – Kunden über Partner-Anwälte</t>
@@ -3723,7 +3669,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:G61"/>
+  <dimension ref="B2:G59"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
@@ -3764,18 +3710,18 @@
         <v>76</v>
       </c>
       <c r="C6" s="9" t="n">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="D6" s="10" t="n">
         <v>65</v>
       </c>
       <c r="E6" s="11" t="n">
-        <f aca="false">D6*$C$14</f>
+        <f aca="false">D6*$C$12</f>
         <v>59.8</v>
       </c>
       <c r="F6" s="12" t="n">
         <f aca="false">C6*D6</f>
-        <v>32500</v>
+        <v>65000</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3783,18 +3729,18 @@
         <v>77</v>
       </c>
       <c r="C7" s="9" t="n">
-        <v>2000</v>
+        <v>10000</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="E7" s="11" t="n">
-        <f aca="false">D7*$C$14</f>
-        <v>55.2</v>
+        <f aca="false">D7*$C$12</f>
+        <v>50.6</v>
       </c>
       <c r="F7" s="12" t="n">
         <f aca="false">C7*D7</f>
-        <v>120000</v>
+        <v>550000</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3802,55 +3748,33 @@
         <v>78</v>
       </c>
       <c r="C8" s="9" t="n">
+        <v>999999999</v>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>45</v>
+      </c>
+      <c r="E8" s="11" t="n">
+        <f aca="false">D8*$C$12</f>
+        <v>41.4</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B11" s="5" t="s">
+        <v>80</v>
+      </c>
+      <c r="C11" s="10" t="n">
         <v>5000</v>
       </c>
-      <c r="D8" s="10" t="n">
-        <v>55</v>
-      </c>
-      <c r="E8" s="11" t="n">
-        <f aca="false">D8*$C$14</f>
-        <v>50.6</v>
-      </c>
-      <c r="F8" s="12" t="n">
-        <f aca="false">C8*D8</f>
-        <v>275000</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B9" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="C9" s="9" t="n">
-        <v>10000</v>
-      </c>
-      <c r="D9" s="10" t="n">
-        <v>50</v>
-      </c>
-      <c r="E9" s="11" t="n">
-        <f aca="false">D9*$C$14</f>
-        <v>46</v>
-      </c>
-      <c r="F9" s="12" t="n">
-        <f aca="false">C9*D9</f>
-        <v>500000</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="5" t="s">
-        <v>80</v>
-      </c>
-      <c r="C10" s="9" t="n">
-        <v>999999999</v>
-      </c>
-      <c r="D10" s="10" t="n">
-        <v>45</v>
-      </c>
-      <c r="E10" s="11" t="n">
-        <f aca="false">D10*$C$14</f>
-        <v>41.4</v>
-      </c>
-      <c r="F10" s="12" t="s">
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="5" t="s">
         <v>81</v>
+      </c>
+      <c r="C12" s="13" t="n">
+        <v>0.92</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3858,278 +3782,310 @@
         <v>82</v>
       </c>
       <c r="C13" s="10" t="n">
-        <v>5000</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C14" s="13" t="n">
-        <v>0.92</v>
+      <c r="C14" s="5" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="C15" s="10" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C15" s="5" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="5" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B18" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="C17" s="5" t="s">
+    </row>
+    <row r="19" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B19" s="3" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C19" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="14"/>
+    </row>
+    <row r="20" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B20" s="3" t="s">
-        <v>89</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="C20" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
     </row>
     <row r="21" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B21" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C21" s="14" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="D21" s="14"/>
       <c r="E21" s="14"/>
       <c r="F21" s="14"/>
       <c r="G21" s="14"/>
     </row>
-    <row r="22" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="C22" s="14" t="s">
-        <v>93</v>
-      </c>
-      <c r="D22" s="14"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14"/>
-      <c r="G22" s="14"/>
-    </row>
-    <row r="23" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C23" s="14" t="s">
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="D23" s="14"/>
-      <c r="E23" s="14"/>
-      <c r="F23" s="14"/>
-      <c r="G23" s="14"/>
+      <c r="C24" s="9" t="n">
+        <v>400</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="5" t="s">
         <v>96</v>
+      </c>
+      <c r="C25" s="12" t="n">
+        <f aca="false">IF(C24&lt;=$C$6,$D$6,IF(C24&lt;=$C$7,$D$7,$D$8))</f>
+        <v>65</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="C26" s="9" t="n">
-        <v>400</v>
+      <c r="C26" s="12" t="n">
+        <f aca="false">C24*C25</f>
+        <v>26000</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="C27" s="12" t="n">
-        <f aca="false">IF(C26&lt;=$C$6,$D$6,IF(C26&lt;=$C$7,$D$7,IF(C26&lt;=$C$8,$D$8,IF(C26&lt;=$C$9,$D$9,$D$10))))</f>
-        <v>65</v>
+      <c r="C27" s="15" t="n">
+        <f aca="false">MAX(C24*IF(C24&lt;=$C$6,$D$6,IF(C24&lt;=$C$7,$D$7,$D$8)),$C$11,IF(C24&gt;$C$6,$C$6*$D$6,0),IF(C24&gt;$C$7,$C$7*$D$7,0))</f>
+        <v>26000</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="C28" s="12" t="n">
-        <f aca="false">C26*C27</f>
-        <v>26000</v>
+      <c r="C28" s="11" t="n">
+        <f aca="false">C27*$C$12</f>
+        <v>23920</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="C29" s="15" t="n">
-        <f aca="false">MAX(C26*IF(C26&lt;=$C$6,$D$6,IF(C26&lt;=$C$7,$D$7,IF(C26&lt;=$C$8,$D$8,IF(C26&lt;=$C$9,$D$9,$D$10)))),$C$13,IF(C26&gt;$C$6,$C$6*$D$6,0),IF(C26&gt;$C$7,$C$7*$D$7,0),IF(C26&gt;$C$8,$C$8*$D$8,0),IF(C26&gt;$C$9,$C$9*$D$9,0))</f>
-        <v>26000</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="5" t="s">
+      <c r="C29" s="16" t="n">
+        <f aca="false">IF(C24&gt;0,C27/C24,0)</f>
+        <v>65</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B31" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="C30" s="11" t="n">
-        <f aca="false">C29*$C$14</f>
-        <v>23920</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="5" t="s">
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B32" s="7" t="s">
         <v>102</v>
       </c>
-      <c r="C31" s="16" t="n">
-        <f aca="false">IF(C26&gt;0,C29/C26,0)</f>
+      <c r="C32" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="E32" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="G32" s="7" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B33" s="9" t="n">
+        <v>10</v>
+      </c>
+      <c r="C33" s="12" t="n">
+        <f aca="false">IF(B33&lt;=$C$6,$D$6,IF(B33&lt;=$C$7,$D$7,$D$8))</f>
         <v>65</v>
       </c>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="3" t="s">
-        <v>103</v>
+      <c r="D33" s="12" t="n">
+        <f aca="false">MAX(B33*IF(B33&lt;=$C$6,$D$6,IF(B33&lt;=$C$7,$D$7,$D$8)),$C$11,IF(B33&gt;$C$6,$C$6*$D$6,0),IF(B33&gt;$C$7,$C$7*$D$7,0))</f>
+        <v>5000</v>
+      </c>
+      <c r="E33" s="11" t="n">
+        <f aca="false">D33*$C$12</f>
+        <v>4600</v>
+      </c>
+      <c r="F33" s="16" t="n">
+        <f aca="false">IF(B33&gt;0,D33/B33,0)</f>
+        <v>500</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="7" t="s">
-        <v>104</v>
-      </c>
-      <c r="C34" s="7" t="s">
-        <v>105</v>
-      </c>
-      <c r="D34" s="7" t="s">
-        <v>106</v>
-      </c>
-      <c r="E34" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="F34" s="7" t="s">
+      <c r="B34" s="9" t="n">
+        <v>50</v>
+      </c>
+      <c r="C34" s="12" t="n">
+        <f aca="false">IF(B34&lt;=$C$6,$D$6,IF(B34&lt;=$C$7,$D$7,$D$8))</f>
+        <v>65</v>
+      </c>
+      <c r="D34" s="12" t="n">
+        <f aca="false">MAX(B34*IF(B34&lt;=$C$6,$D$6,IF(B34&lt;=$C$7,$D$7,$D$8)),$C$11,IF(B34&gt;$C$6,$C$6*$D$6,0),IF(B34&gt;$C$7,$C$7*$D$7,0))</f>
+        <v>5000</v>
+      </c>
+      <c r="E34" s="11" t="n">
+        <f aca="false">D34*$C$12</f>
+        <v>4600</v>
+      </c>
+      <c r="F34" s="16" t="n">
+        <f aca="false">IF(B34&gt;0,D34/B34,0)</f>
+        <v>100</v>
+      </c>
+      <c r="G34" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="G34" s="7" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="9" t="n">
-        <v>10</v>
+        <v>77</v>
       </c>
       <c r="C35" s="12" t="n">
-        <f aca="false">IF(B35&lt;=$C$6,$D$6,IF(B35&lt;=$C$7,$D$7,IF(B35&lt;=$C$8,$D$8,IF(B35&lt;=$C$9,$D$9,$D$10))))</f>
+        <f aca="false">IF(B35&lt;=$C$6,$D$6,IF(B35&lt;=$C$7,$D$7,$D$8))</f>
         <v>65</v>
       </c>
       <c r="D35" s="12" t="n">
-        <f aca="false">MAX(B35*IF(B35&lt;=$C$6,$D$6,IF(B35&lt;=$C$7,$D$7,IF(B35&lt;=$C$8,$D$8,IF(B35&lt;=$C$9,$D$9,$D$10)))),$C$13,IF(B35&gt;$C$6,$C$6*$D$6,0),IF(B35&gt;$C$7,$C$7*$D$7,0),IF(B35&gt;$C$8,$C$8*$D$8,0),IF(B35&gt;$C$9,$C$9*$D$9,0))</f>
-        <v>5000</v>
+        <f aca="false">MAX(B35*IF(B35&lt;=$C$6,$D$6,IF(B35&lt;=$C$7,$D$7,$D$8)),$C$11,IF(B35&gt;$C$6,$C$6*$D$6,0),IF(B35&gt;$C$7,$C$7*$D$7,0))</f>
+        <v>5005</v>
       </c>
       <c r="E35" s="11" t="n">
-        <f aca="false">D35*$C$14</f>
-        <v>4600</v>
+        <f aca="false">D35*$C$12</f>
+        <v>4604.6</v>
       </c>
       <c r="F35" s="16" t="n">
         <f aca="false">IF(B35&gt;0,D35/B35,0)</f>
-        <v>500</v>
+        <v>65</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="9" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="C36" s="12" t="n">
-        <f aca="false">IF(B36&lt;=$C$6,$D$6,IF(B36&lt;=$C$7,$D$7,IF(B36&lt;=$C$8,$D$8,IF(B36&lt;=$C$9,$D$9,$D$10))))</f>
+        <f aca="false">IF(B36&lt;=$C$6,$D$6,IF(B36&lt;=$C$7,$D$7,$D$8))</f>
         <v>65</v>
       </c>
       <c r="D36" s="12" t="n">
-        <f aca="false">MAX(B36*IF(B36&lt;=$C$6,$D$6,IF(B36&lt;=$C$7,$D$7,IF(B36&lt;=$C$8,$D$8,IF(B36&lt;=$C$9,$D$9,$D$10)))),$C$13,IF(B36&gt;$C$6,$C$6*$D$6,0),IF(B36&gt;$C$7,$C$7*$D$7,0),IF(B36&gt;$C$8,$C$8*$D$8,0),IF(B36&gt;$C$9,$C$9*$D$9,0))</f>
-        <v>5000</v>
+        <f aca="false">MAX(B36*IF(B36&lt;=$C$6,$D$6,IF(B36&lt;=$C$7,$D$7,$D$8)),$C$11,IF(B36&gt;$C$6,$C$6*$D$6,0),IF(B36&gt;$C$7,$C$7*$D$7,0))</f>
+        <v>6500</v>
       </c>
       <c r="E36" s="11" t="n">
-        <f aca="false">D36*$C$14</f>
-        <v>4600</v>
+        <f aca="false">D36*$C$12</f>
+        <v>5980</v>
       </c>
       <c r="F36" s="16" t="n">
         <f aca="false">IF(B36&gt;0,D36/B36,0)</f>
-        <v>100</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>110</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="G36" s="2"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="9" t="n">
-        <v>77</v>
+        <v>400</v>
       </c>
       <c r="C37" s="12" t="n">
-        <f aca="false">IF(B37&lt;=$C$6,$D$6,IF(B37&lt;=$C$7,$D$7,IF(B37&lt;=$C$8,$D$8,IF(B37&lt;=$C$9,$D$9,$D$10))))</f>
+        <f aca="false">IF(B37&lt;=$C$6,$D$6,IF(B37&lt;=$C$7,$D$7,$D$8))</f>
         <v>65</v>
       </c>
       <c r="D37" s="12" t="n">
-        <f aca="false">MAX(B37*IF(B37&lt;=$C$6,$D$6,IF(B37&lt;=$C$7,$D$7,IF(B37&lt;=$C$8,$D$8,IF(B37&lt;=$C$9,$D$9,$D$10)))),$C$13,IF(B37&gt;$C$6,$C$6*$D$6,0),IF(B37&gt;$C$7,$C$7*$D$7,0),IF(B37&gt;$C$8,$C$8*$D$8,0),IF(B37&gt;$C$9,$C$9*$D$9,0))</f>
-        <v>5005</v>
+        <f aca="false">MAX(B37*IF(B37&lt;=$C$6,$D$6,IF(B37&lt;=$C$7,$D$7,$D$8)),$C$11,IF(B37&gt;$C$6,$C$6*$D$6,0),IF(B37&gt;$C$7,$C$7*$D$7,0))</f>
+        <v>26000</v>
       </c>
       <c r="E37" s="11" t="n">
-        <f aca="false">D37*$C$14</f>
-        <v>4604.6</v>
+        <f aca="false">D37*$C$12</f>
+        <v>23920</v>
       </c>
       <c r="F37" s="16" t="n">
         <f aca="false">IF(B37&gt;0,D37/B37,0)</f>
         <v>65</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="9" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="C38" s="12" t="n">
-        <f aca="false">IF(B38&lt;=$C$6,$D$6,IF(B38&lt;=$C$7,$D$7,IF(B38&lt;=$C$8,$D$8,IF(B38&lt;=$C$9,$D$9,$D$10))))</f>
+        <f aca="false">IF(B38&lt;=$C$6,$D$6,IF(B38&lt;=$C$7,$D$7,$D$8))</f>
         <v>65</v>
       </c>
       <c r="D38" s="12" t="n">
-        <f aca="false">MAX(B38*IF(B38&lt;=$C$6,$D$6,IF(B38&lt;=$C$7,$D$7,IF(B38&lt;=$C$8,$D$8,IF(B38&lt;=$C$9,$D$9,$D$10)))),$C$13,IF(B38&gt;$C$6,$C$6*$D$6,0),IF(B38&gt;$C$7,$C$7*$D$7,0),IF(B38&gt;$C$8,$C$8*$D$8,0),IF(B38&gt;$C$9,$C$9*$D$9,0))</f>
-        <v>6500</v>
+        <f aca="false">MAX(B38*IF(B38&lt;=$C$6,$D$6,IF(B38&lt;=$C$7,$D$7,$D$8)),$C$11,IF(B38&gt;$C$6,$C$6*$D$6,0),IF(B38&gt;$C$7,$C$7*$D$7,0))</f>
+        <v>65000</v>
       </c>
       <c r="E38" s="11" t="n">
-        <f aca="false">D38*$C$14</f>
-        <v>5980</v>
+        <f aca="false">D38*$C$12</f>
+        <v>59800</v>
       </c>
       <c r="F38" s="16" t="n">
         <f aca="false">IF(B38&gt;0,D38/B38,0)</f>
         <v>65</v>
       </c>
-      <c r="G38" s="2"/>
+      <c r="G38" s="2" t="s">
+        <v>111</v>
+      </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="9" t="n">
-        <v>400</v>
+        <v>1001</v>
       </c>
       <c r="C39" s="12" t="n">
-        <f aca="false">IF(B39&lt;=$C$6,$D$6,IF(B39&lt;=$C$7,$D$7,IF(B39&lt;=$C$8,$D$8,IF(B39&lt;=$C$9,$D$9,$D$10))))</f>
-        <v>65</v>
+        <f aca="false">IF(B39&lt;=$C$6,$D$6,IF(B39&lt;=$C$7,$D$7,$D$8))</f>
+        <v>55</v>
       </c>
       <c r="D39" s="12" t="n">
-        <f aca="false">MAX(B39*IF(B39&lt;=$C$6,$D$6,IF(B39&lt;=$C$7,$D$7,IF(B39&lt;=$C$8,$D$8,IF(B39&lt;=$C$9,$D$9,$D$10)))),$C$13,IF(B39&gt;$C$6,$C$6*$D$6,0),IF(B39&gt;$C$7,$C$7*$D$7,0),IF(B39&gt;$C$8,$C$8*$D$8,0),IF(B39&gt;$C$9,$C$9*$D$9,0))</f>
-        <v>26000</v>
+        <f aca="false">MAX(B39*IF(B39&lt;=$C$6,$D$6,IF(B39&lt;=$C$7,$D$7,$D$8)),$C$11,IF(B39&gt;$C$6,$C$6*$D$6,0),IF(B39&gt;$C$7,$C$7*$D$7,0))</f>
+        <v>65000</v>
       </c>
       <c r="E39" s="11" t="n">
-        <f aca="false">D39*$C$14</f>
-        <v>23920</v>
+        <f aca="false">D39*$C$12</f>
+        <v>59800</v>
       </c>
       <c r="F39" s="16" t="n">
         <f aca="false">IF(B39&gt;0,D39/B39,0)</f>
-        <v>65</v>
+        <v>64.9350649350649</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>112</v>
@@ -4137,23 +4093,23 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="9" t="n">
-        <v>500</v>
+        <v>1182</v>
       </c>
       <c r="C40" s="12" t="n">
-        <f aca="false">IF(B40&lt;=$C$6,$D$6,IF(B40&lt;=$C$7,$D$7,IF(B40&lt;=$C$8,$D$8,IF(B40&lt;=$C$9,$D$9,$D$10))))</f>
-        <v>65</v>
+        <f aca="false">IF(B40&lt;=$C$6,$D$6,IF(B40&lt;=$C$7,$D$7,$D$8))</f>
+        <v>55</v>
       </c>
       <c r="D40" s="12" t="n">
-        <f aca="false">MAX(B40*IF(B40&lt;=$C$6,$D$6,IF(B40&lt;=$C$7,$D$7,IF(B40&lt;=$C$8,$D$8,IF(B40&lt;=$C$9,$D$9,$D$10)))),$C$13,IF(B40&gt;$C$6,$C$6*$D$6,0),IF(B40&gt;$C$7,$C$7*$D$7,0),IF(B40&gt;$C$8,$C$8*$D$8,0),IF(B40&gt;$C$9,$C$9*$D$9,0))</f>
-        <v>32500</v>
+        <f aca="false">MAX(B40*IF(B40&lt;=$C$6,$D$6,IF(B40&lt;=$C$7,$D$7,$D$8)),$C$11,IF(B40&gt;$C$6,$C$6*$D$6,0),IF(B40&gt;$C$7,$C$7*$D$7,0))</f>
+        <v>65010</v>
       </c>
       <c r="E40" s="11" t="n">
-        <f aca="false">D40*$C$14</f>
-        <v>29900</v>
+        <f aca="false">D40*$C$12</f>
+        <v>59809.2</v>
       </c>
       <c r="F40" s="16" t="n">
         <f aca="false">IF(B40&gt;0,D40/B40,0)</f>
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>113</v>
@@ -4161,23 +4117,23 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="9" t="n">
-        <v>501</v>
+        <v>3000</v>
       </c>
       <c r="C41" s="12" t="n">
-        <f aca="false">IF(B41&lt;=$C$6,$D$6,IF(B41&lt;=$C$7,$D$7,IF(B41&lt;=$C$8,$D$8,IF(B41&lt;=$C$9,$D$9,$D$10))))</f>
-        <v>60</v>
+        <f aca="false">IF(B41&lt;=$C$6,$D$6,IF(B41&lt;=$C$7,$D$7,$D$8))</f>
+        <v>55</v>
       </c>
       <c r="D41" s="12" t="n">
-        <f aca="false">MAX(B41*IF(B41&lt;=$C$6,$D$6,IF(B41&lt;=$C$7,$D$7,IF(B41&lt;=$C$8,$D$8,IF(B41&lt;=$C$9,$D$9,$D$10)))),$C$13,IF(B41&gt;$C$6,$C$6*$D$6,0),IF(B41&gt;$C$7,$C$7*$D$7,0),IF(B41&gt;$C$8,$C$8*$D$8,0),IF(B41&gt;$C$9,$C$9*$D$9,0))</f>
-        <v>32500</v>
+        <f aca="false">MAX(B41*IF(B41&lt;=$C$6,$D$6,IF(B41&lt;=$C$7,$D$7,$D$8)),$C$11,IF(B41&gt;$C$6,$C$6*$D$6,0),IF(B41&gt;$C$7,$C$7*$D$7,0))</f>
+        <v>165000</v>
       </c>
       <c r="E41" s="11" t="n">
-        <f aca="false">D41*$C$14</f>
-        <v>29900</v>
+        <f aca="false">D41*$C$12</f>
+        <v>151800</v>
       </c>
       <c r="F41" s="16" t="n">
         <f aca="false">IF(B41&gt;0,D41/B41,0)</f>
-        <v>64.8702594810379</v>
+        <v>55</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>114</v>
@@ -4185,69 +4141,71 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="9" t="n">
-        <v>1000</v>
+        <v>8000</v>
       </c>
       <c r="C42" s="12" t="n">
-        <f aca="false">IF(B42&lt;=$C$6,$D$6,IF(B42&lt;=$C$7,$D$7,IF(B42&lt;=$C$8,$D$8,IF(B42&lt;=$C$9,$D$9,$D$10))))</f>
-        <v>60</v>
+        <f aca="false">IF(B42&lt;=$C$6,$D$6,IF(B42&lt;=$C$7,$D$7,$D$8))</f>
+        <v>55</v>
       </c>
       <c r="D42" s="12" t="n">
-        <f aca="false">MAX(B42*IF(B42&lt;=$C$6,$D$6,IF(B42&lt;=$C$7,$D$7,IF(B42&lt;=$C$8,$D$8,IF(B42&lt;=$C$9,$D$9,$D$10)))),$C$13,IF(B42&gt;$C$6,$C$6*$D$6,0),IF(B42&gt;$C$7,$C$7*$D$7,0),IF(B42&gt;$C$8,$C$8*$D$8,0),IF(B42&gt;$C$9,$C$9*$D$9,0))</f>
-        <v>60000</v>
+        <f aca="false">MAX(B42*IF(B42&lt;=$C$6,$D$6,IF(B42&lt;=$C$7,$D$7,$D$8)),$C$11,IF(B42&gt;$C$6,$C$6*$D$6,0),IF(B42&gt;$C$7,$C$7*$D$7,0))</f>
+        <v>440000</v>
       </c>
       <c r="E42" s="11" t="n">
-        <f aca="false">D42*$C$14</f>
-        <v>55200</v>
+        <f aca="false">D42*$C$12</f>
+        <v>404800</v>
       </c>
       <c r="F42" s="16" t="n">
         <f aca="false">IF(B42&gt;0,D42/B42,0)</f>
-        <v>60</v>
-      </c>
-      <c r="G42" s="2"/>
+        <v>55</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="9" t="n">
-        <v>2001</v>
+        <v>10000</v>
       </c>
       <c r="C43" s="12" t="n">
-        <f aca="false">IF(B43&lt;=$C$6,$D$6,IF(B43&lt;=$C$7,$D$7,IF(B43&lt;=$C$8,$D$8,IF(B43&lt;=$C$9,$D$9,$D$10))))</f>
+        <f aca="false">IF(B43&lt;=$C$6,$D$6,IF(B43&lt;=$C$7,$D$7,$D$8))</f>
         <v>55</v>
       </c>
       <c r="D43" s="12" t="n">
-        <f aca="false">MAX(B43*IF(B43&lt;=$C$6,$D$6,IF(B43&lt;=$C$7,$D$7,IF(B43&lt;=$C$8,$D$8,IF(B43&lt;=$C$9,$D$9,$D$10)))),$C$13,IF(B43&gt;$C$6,$C$6*$D$6,0),IF(B43&gt;$C$7,$C$7*$D$7,0),IF(B43&gt;$C$8,$C$8*$D$8,0),IF(B43&gt;$C$9,$C$9*$D$9,0))</f>
-        <v>120000</v>
+        <f aca="false">MAX(B43*IF(B43&lt;=$C$6,$D$6,IF(B43&lt;=$C$7,$D$7,$D$8)),$C$11,IF(B43&gt;$C$6,$C$6*$D$6,0),IF(B43&gt;$C$7,$C$7*$D$7,0))</f>
+        <v>550000</v>
       </c>
       <c r="E43" s="11" t="n">
-        <f aca="false">D43*$C$14</f>
-        <v>110400</v>
+        <f aca="false">D43*$C$12</f>
+        <v>506000</v>
       </c>
       <c r="F43" s="16" t="n">
         <f aca="false">IF(B43&gt;0,D43/B43,0)</f>
-        <v>59.9700149925038</v>
+        <v>55</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="9" t="n">
-        <v>3000</v>
+        <v>10001</v>
       </c>
       <c r="C44" s="12" t="n">
-        <f aca="false">IF(B44&lt;=$C$6,$D$6,IF(B44&lt;=$C$7,$D$7,IF(B44&lt;=$C$8,$D$8,IF(B44&lt;=$C$9,$D$9,$D$10))))</f>
-        <v>55</v>
+        <f aca="false">IF(B44&lt;=$C$6,$D$6,IF(B44&lt;=$C$7,$D$7,$D$8))</f>
+        <v>45</v>
       </c>
       <c r="D44" s="12" t="n">
-        <f aca="false">MAX(B44*IF(B44&lt;=$C$6,$D$6,IF(B44&lt;=$C$7,$D$7,IF(B44&lt;=$C$8,$D$8,IF(B44&lt;=$C$9,$D$9,$D$10)))),$C$13,IF(B44&gt;$C$6,$C$6*$D$6,0),IF(B44&gt;$C$7,$C$7*$D$7,0),IF(B44&gt;$C$8,$C$8*$D$8,0),IF(B44&gt;$C$9,$C$9*$D$9,0))</f>
-        <v>165000</v>
+        <f aca="false">MAX(B44*IF(B44&lt;=$C$6,$D$6,IF(B44&lt;=$C$7,$D$7,$D$8)),$C$11,IF(B44&gt;$C$6,$C$6*$D$6,0),IF(B44&gt;$C$7,$C$7*$D$7,0))</f>
+        <v>550000</v>
       </c>
       <c r="E44" s="11" t="n">
-        <f aca="false">D44*$C$14</f>
-        <v>151800</v>
+        <f aca="false">D44*$C$12</f>
+        <v>506000</v>
       </c>
       <c r="F44" s="16" t="n">
         <f aca="false">IF(B44&gt;0,D44/B44,0)</f>
-        <v>55</v>
+        <v>54.994500549945</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>116</v>
@@ -4255,23 +4213,23 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="9" t="n">
-        <v>5001</v>
+        <v>12223</v>
       </c>
       <c r="C45" s="12" t="n">
-        <f aca="false">IF(B45&lt;=$C$6,$D$6,IF(B45&lt;=$C$7,$D$7,IF(B45&lt;=$C$8,$D$8,IF(B45&lt;=$C$9,$D$9,$D$10))))</f>
-        <v>50</v>
+        <f aca="false">IF(B45&lt;=$C$6,$D$6,IF(B45&lt;=$C$7,$D$7,$D$8))</f>
+        <v>45</v>
       </c>
       <c r="D45" s="12" t="n">
-        <f aca="false">MAX(B45*IF(B45&lt;=$C$6,$D$6,IF(B45&lt;=$C$7,$D$7,IF(B45&lt;=$C$8,$D$8,IF(B45&lt;=$C$9,$D$9,$D$10)))),$C$13,IF(B45&gt;$C$6,$C$6*$D$6,0),IF(B45&gt;$C$7,$C$7*$D$7,0),IF(B45&gt;$C$8,$C$8*$D$8,0),IF(B45&gt;$C$9,$C$9*$D$9,0))</f>
-        <v>275000</v>
+        <f aca="false">MAX(B45*IF(B45&lt;=$C$6,$D$6,IF(B45&lt;=$C$7,$D$7,$D$8)),$C$11,IF(B45&gt;$C$6,$C$6*$D$6,0),IF(B45&gt;$C$7,$C$7*$D$7,0))</f>
+        <v>550035</v>
       </c>
       <c r="E45" s="11" t="n">
-        <f aca="false">D45*$C$14</f>
-        <v>253000</v>
+        <f aca="false">D45*$C$12</f>
+        <v>506032.2</v>
       </c>
       <c r="F45" s="16" t="n">
         <f aca="false">IF(B45&gt;0,D45/B45,0)</f>
-        <v>54.9890021995601</v>
+        <v>45</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>117</v>
@@ -4279,23 +4237,23 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="9" t="n">
-        <v>8000</v>
+        <v>15000</v>
       </c>
       <c r="C46" s="12" t="n">
-        <f aca="false">IF(B46&lt;=$C$6,$D$6,IF(B46&lt;=$C$7,$D$7,IF(B46&lt;=$C$8,$D$8,IF(B46&lt;=$C$9,$D$9,$D$10))))</f>
-        <v>50</v>
+        <f aca="false">IF(B46&lt;=$C$6,$D$6,IF(B46&lt;=$C$7,$D$7,$D$8))</f>
+        <v>45</v>
       </c>
       <c r="D46" s="12" t="n">
-        <f aca="false">MAX(B46*IF(B46&lt;=$C$6,$D$6,IF(B46&lt;=$C$7,$D$7,IF(B46&lt;=$C$8,$D$8,IF(B46&lt;=$C$9,$D$9,$D$10)))),$C$13,IF(B46&gt;$C$6,$C$6*$D$6,0),IF(B46&gt;$C$7,$C$7*$D$7,0),IF(B46&gt;$C$8,$C$8*$D$8,0),IF(B46&gt;$C$9,$C$9*$D$9,0))</f>
-        <v>400000</v>
+        <f aca="false">MAX(B46*IF(B46&lt;=$C$6,$D$6,IF(B46&lt;=$C$7,$D$7,$D$8)),$C$11,IF(B46&gt;$C$6,$C$6*$D$6,0),IF(B46&gt;$C$7,$C$7*$D$7,0))</f>
+        <v>675000</v>
       </c>
       <c r="E46" s="11" t="n">
-        <f aca="false">D46*$C$14</f>
-        <v>368000</v>
+        <f aca="false">D46*$C$12</f>
+        <v>621000</v>
       </c>
       <c r="F46" s="16" t="n">
         <f aca="false">IF(B46&gt;0,D46/B46,0)</f>
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>118</v>
@@ -4303,100 +4261,72 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="9" t="n">
-        <v>10001</v>
+        <v>30000</v>
       </c>
       <c r="C47" s="12" t="n">
-        <f aca="false">IF(B47&lt;=$C$6,$D$6,IF(B47&lt;=$C$7,$D$7,IF(B47&lt;=$C$8,$D$8,IF(B47&lt;=$C$9,$D$9,$D$10))))</f>
+        <f aca="false">IF(B47&lt;=$C$6,$D$6,IF(B47&lt;=$C$7,$D$7,$D$8))</f>
         <v>45</v>
       </c>
       <c r="D47" s="12" t="n">
-        <f aca="false">MAX(B47*IF(B47&lt;=$C$6,$D$6,IF(B47&lt;=$C$7,$D$7,IF(B47&lt;=$C$8,$D$8,IF(B47&lt;=$C$9,$D$9,$D$10)))),$C$13,IF(B47&gt;$C$6,$C$6*$D$6,0),IF(B47&gt;$C$7,$C$7*$D$7,0),IF(B47&gt;$C$8,$C$8*$D$8,0),IF(B47&gt;$C$9,$C$9*$D$9,0))</f>
-        <v>500000</v>
+        <f aca="false">MAX(B47*IF(B47&lt;=$C$6,$D$6,IF(B47&lt;=$C$7,$D$7,$D$8)),$C$11,IF(B47&gt;$C$6,$C$6*$D$6,0),IF(B47&gt;$C$7,$C$7*$D$7,0))</f>
+        <v>1350000</v>
       </c>
       <c r="E47" s="11" t="n">
-        <f aca="false">D47*$C$14</f>
-        <v>460000</v>
+        <f aca="false">D47*$C$12</f>
+        <v>1242000</v>
       </c>
       <c r="F47" s="16" t="n">
         <f aca="false">IF(B47&gt;0,D47/B47,0)</f>
-        <v>49.99500049995</v>
+        <v>45</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="9" t="n">
-        <v>15000</v>
-      </c>
-      <c r="C48" s="12" t="n">
-        <f aca="false">IF(B48&lt;=$C$6,$D$6,IF(B48&lt;=$C$7,$D$7,IF(B48&lt;=$C$8,$D$8,IF(B48&lt;=$C$9,$D$9,$D$10))))</f>
-        <v>45</v>
-      </c>
-      <c r="D48" s="12" t="n">
-        <f aca="false">MAX(B48*IF(B48&lt;=$C$6,$D$6,IF(B48&lt;=$C$7,$D$7,IF(B48&lt;=$C$8,$D$8,IF(B48&lt;=$C$9,$D$9,$D$10)))),$C$13,IF(B48&gt;$C$6,$C$6*$D$6,0),IF(B48&gt;$C$7,$C$7*$D$7,0),IF(B48&gt;$C$8,$C$8*$D$8,0),IF(B48&gt;$C$9,$C$9*$D$9,0))</f>
-        <v>675000</v>
-      </c>
-      <c r="E48" s="11" t="n">
-        <f aca="false">D48*$C$14</f>
-        <v>621000</v>
-      </c>
-      <c r="F48" s="16" t="n">
-        <f aca="false">IF(B48&gt;0,D48/B48,0)</f>
-        <v>45</v>
-      </c>
-      <c r="G48" s="2" t="s">
+    <row r="49" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B49" s="17" t="s">
         <v>120</v>
       </c>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B49" s="9" t="n">
-        <v>30000</v>
-      </c>
-      <c r="C49" s="12" t="n">
-        <f aca="false">IF(B49&lt;=$C$6,$D$6,IF(B49&lt;=$C$7,$D$7,IF(B49&lt;=$C$8,$D$8,IF(B49&lt;=$C$9,$D$9,$D$10))))</f>
-        <v>45</v>
-      </c>
-      <c r="D49" s="12" t="n">
-        <f aca="false">MAX(B49*IF(B49&lt;=$C$6,$D$6,IF(B49&lt;=$C$7,$D$7,IF(B49&lt;=$C$8,$D$8,IF(B49&lt;=$C$9,$D$9,$D$10)))),$C$13,IF(B49&gt;$C$6,$C$6*$D$6,0),IF(B49&gt;$C$7,$C$7*$D$7,0),IF(B49&gt;$C$8,$C$8*$D$8,0),IF(B49&gt;$C$9,$C$9*$D$9,0))</f>
-        <v>1350000</v>
-      </c>
-      <c r="E49" s="11" t="n">
-        <f aca="false">D49*$C$14</f>
-        <v>1242000</v>
-      </c>
-      <c r="F49" s="16" t="n">
-        <f aca="false">IF(B49&gt;0,D49/B49,0)</f>
-        <v>45</v>
-      </c>
-      <c r="G49" s="2" t="s">
+      <c r="C49" s="17"/>
+      <c r="D49" s="17"/>
+      <c r="E49" s="17"/>
+      <c r="F49" s="17"/>
+      <c r="G49" s="17"/>
+    </row>
+    <row r="50" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B50" s="18" t="s">
         <v>121</v>
       </c>
-    </row>
-    <row r="51" customFormat="false" ht="43.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B51" s="17" t="s">
+      <c r="C50" s="18"/>
+      <c r="D50" s="18"/>
+      <c r="E50" s="18"/>
+      <c r="F50" s="18"/>
+      <c r="G50" s="18"/>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B52" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C51" s="17"/>
-      <c r="D51" s="17"/>
-      <c r="E51" s="17"/>
-      <c r="F51" s="17"/>
-      <c r="G51" s="17"/>
-    </row>
-    <row r="52" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B52" s="18" t="s">
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B53" s="19" t="s">
         <v>123</v>
       </c>
-      <c r="C52" s="18"/>
-      <c r="D52" s="18"/>
-      <c r="E52" s="18"/>
-      <c r="F52" s="18"/>
-      <c r="G52" s="18"/>
+      <c r="C53" s="19"/>
+      <c r="D53" s="19"/>
+      <c r="E53" s="19"/>
+      <c r="F53" s="19"/>
+      <c r="G53" s="19"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B54" s="3" t="s">
+      <c r="B54" s="19" t="s">
         <v>124</v>
       </c>
+      <c r="C54" s="19"/>
+      <c r="D54" s="19"/>
+      <c r="E54" s="19"/>
+      <c r="F54" s="19"/>
+      <c r="G54" s="19"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="19" t="s">
@@ -4448,40 +4378,20 @@
       <c r="F59" s="19"/>
       <c r="G59" s="19"/>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B60" s="19" t="s">
-        <v>130</v>
-      </c>
-      <c r="C60" s="19"/>
-      <c r="D60" s="19"/>
-      <c r="E60" s="19"/>
-      <c r="F60" s="19"/>
-      <c r="G60" s="19"/>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B61" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="C61" s="19"/>
-      <c r="D61" s="19"/>
-      <c r="E61" s="19"/>
-      <c r="F61" s="19"/>
-      <c r="G61" s="19"/>
-    </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="C19:G19"/>
+    <mergeCell ref="C20:G20"/>
     <mergeCell ref="C21:G21"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="C23:G23"/>
-    <mergeCell ref="B51:G51"/>
-    <mergeCell ref="B52:G52"/>
+    <mergeCell ref="B49:G49"/>
+    <mergeCell ref="B50:G50"/>
+    <mergeCell ref="B53:G53"/>
+    <mergeCell ref="B54:G54"/>
     <mergeCell ref="B55:G55"/>
     <mergeCell ref="B56:G56"/>
     <mergeCell ref="B57:G57"/>
     <mergeCell ref="B58:G58"/>
     <mergeCell ref="B59:G59"/>
-    <mergeCell ref="B60:G60"/>
-    <mergeCell ref="B61:G61"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -4510,22 +4420,22 @@
   <sheetData>
     <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="3" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="C6" s="9" t="n">
         <v>313</v>
@@ -4533,7 +4443,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="C7" s="9" t="n">
         <v>6</v>
@@ -4541,7 +4451,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="5" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C8" s="20" t="n">
         <f aca="false">C6-C7</f>
@@ -4550,7 +4460,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="5" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C9" s="21" t="n">
         <v>0.1</v>
@@ -4558,7 +4468,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="5" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C10" s="22" t="n">
         <f aca="false">C8*C9</f>
@@ -4567,7 +4477,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="5" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="C11" s="21" t="n">
         <v>0.3</v>
@@ -4575,7 +4485,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="5" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C12" s="23" t="n">
         <f aca="false">C10*C11</f>
@@ -4584,7 +4494,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="5" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="C13" s="9" t="n">
         <v>18</v>
@@ -4592,12 +4502,12 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="5" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="C16" s="24" t="n">
         <v>1</v>
@@ -4605,7 +4515,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="5" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C17" s="9" t="n">
         <v>400</v>
@@ -4613,16 +4523,16 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="5" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C18" s="25" t="n">
-        <f aca="false">MAX(C17*IF(C17&lt;='Preise &amp; Pläne'!$C$6,'Preise &amp; Pläne'!$D$6,IF(C17&lt;='Preise &amp; Pläne'!$C$7,'Preise &amp; Pläne'!$D$7,IF(C17&lt;='Preise &amp; Pläne'!$C$8,'Preise &amp; Pläne'!$D$8,IF(C17&lt;='Preise &amp; Pläne'!$C$9,'Preise &amp; Pläne'!$D$9,'Preise &amp; Pläne'!$D$10)))),'Preise &amp; Pläne'!$C$13,IF(C17&gt;'Preise &amp; Pläne'!$C$6,'Preise &amp; Pläne'!$C$6*'Preise &amp; Pläne'!$D$6,0),IF(C17&gt;'Preise &amp; Pläne'!$C$7,'Preise &amp; Pläne'!$C$7*'Preise &amp; Pläne'!$D$7,0),IF(C17&gt;'Preise &amp; Pläne'!$C$8,'Preise &amp; Pläne'!$C$8*'Preise &amp; Pläne'!$D$8,0),IF(C17&gt;'Preise &amp; Pläne'!$C$9,'Preise &amp; Pläne'!$C$9*'Preise &amp; Pläne'!$D$9,0))</f>
+        <f aca="false">MAX(C17*IF(C17&lt;='Preise &amp; Pläne'!$C$6,'Preise &amp; Pläne'!$D$6,IF(C17&lt;='Preise &amp; Pläne'!$C$7,'Preise &amp; Pläne'!$D$7,'Preise &amp; Pläne'!$D$8)),'Preise &amp; Pläne'!$C$11,IF(C17&gt;'Preise &amp; Pläne'!$C$6,'Preise &amp; Pläne'!$C$6*'Preise &amp; Pläne'!$D$6,0),IF(C17&gt;'Preise &amp; Pläne'!$C$7,'Preise &amp; Pläne'!$C$7*'Preise &amp; Pläne'!$D$7,0))</f>
         <v>26000</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C19" s="21" t="n">
         <v>0.85</v>
@@ -4630,7 +4540,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="5" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C20" s="21" t="n">
         <v>0.1</v>
@@ -4638,7 +4548,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="5" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C21" s="21" t="n">
         <v>0.05</v>
@@ -4646,7 +4556,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="5" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C22" s="26" t="n">
         <v>1.5</v>
@@ -4654,7 +4564,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C23" s="10" t="n">
         <v>6130</v>
@@ -4662,27 +4572,27 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="D25" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="C25" s="7" t="s">
+      <c r="E25" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="D25" s="7" t="s">
+      <c r="F25" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="E25" s="7" t="s">
+      <c r="G25" s="7" t="s">
         <v>155</v>
-      </c>
-      <c r="F25" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="G25" s="7" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="5" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C26" s="22" t="n">
         <f aca="false">$C$12*$C$16</f>
@@ -4707,7 +4617,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="5" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C27" s="22" t="n">
         <f aca="false">C26+C28</f>
@@ -4732,7 +4642,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="5" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C28" s="22" t="n">
         <f aca="false">0</f>
@@ -4757,7 +4667,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C29" s="20" t="n">
         <f aca="false">C27*$C$17</f>
@@ -4782,7 +4692,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="5" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C30" s="12" t="n">
         <f aca="false">C26*$C$18</f>
@@ -4807,7 +4717,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="5" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="C31" s="12" t="n">
         <f aca="false">C28*$C$18</f>
@@ -4832,7 +4742,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C32" s="15" t="n">
         <f aca="false">C30+C31</f>
@@ -4857,7 +4767,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="5" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C33" s="12" t="n">
         <f aca="false">-(C30*$C$20+C31*$C$21)</f>
@@ -4882,7 +4792,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="5" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C34" s="12" t="n">
         <f aca="false">-C29*$C$22</f>
@@ -4907,7 +4817,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="5" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C35" s="12" t="n">
         <f aca="false">-$C$23</f>
@@ -4932,7 +4842,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C36" s="15" t="n">
         <f aca="false">SUM(C32:C35)</f>
@@ -4957,7 +4867,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="5" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C37" s="27" t="n">
         <f aca="false">IF(C32&lt;&gt;0,C36/C32,0)</f>
@@ -4982,7 +4892,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C39" s="15" t="n">
         <f aca="false">SUM(C32:G32)</f>
@@ -4991,7 +4901,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="5" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C40" s="12" t="n">
         <f aca="false">SUM(C33:G33)</f>
@@ -5000,7 +4910,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="5" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C41" s="15" t="n">
         <f aca="false">SUM(C36:G36)</f>
@@ -5009,7 +4919,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="2" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
   </sheetData>
@@ -5040,22 +4950,22 @@
   <sheetData>
     <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C6" s="9" t="n">
         <v>600</v>
@@ -5063,7 +4973,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C7" s="21" t="n">
         <v>0.05</v>
@@ -5071,7 +4981,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="5" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="C8" s="21" t="n">
         <v>0.15</v>
@@ -5079,7 +4989,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="5" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C9" s="22" t="n">
         <f aca="false">C6*C7*C8</f>
@@ -5088,7 +4998,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="5" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C10" s="10" t="n">
         <v>6000</v>
@@ -5096,7 +5006,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="5" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C11" s="10" t="n">
         <v>40</v>
@@ -5104,7 +5014,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="5" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C12" s="21" t="n">
         <v>0.05</v>
@@ -5112,7 +5022,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="5" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C13" s="22" t="n">
         <f aca="false">IF(C11&gt;0,C10/C11*C12,0)</f>
@@ -5121,7 +5031,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="5" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C14" s="9" t="n">
         <v>60</v>
@@ -5129,7 +5039,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="5" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C15" s="21" t="n">
         <v>0.1</v>
@@ -5137,7 +5047,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="5" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="C16" s="22" t="n">
         <f aca="false">C14*C15</f>
@@ -5146,7 +5056,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="5" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C17" s="23" t="n">
         <f aca="false">C9+C13+C16</f>
@@ -5155,7 +5065,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="5" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="C18" s="21" t="n">
         <v>0.2</v>
@@ -5163,12 +5073,12 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="5" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C21" s="9" t="n">
         <v>150</v>
@@ -5176,16 +5086,16 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="5" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C22" s="25" t="n">
-        <f aca="false">MAX(C21*IF(C21&lt;='Preise &amp; Pläne'!$C$6,'Preise &amp; Pläne'!$D$6,IF(C21&lt;='Preise &amp; Pläne'!$C$7,'Preise &amp; Pläne'!$D$7,IF(C21&lt;='Preise &amp; Pläne'!$C$8,'Preise &amp; Pläne'!$D$8,IF(C21&lt;='Preise &amp; Pläne'!$C$9,'Preise &amp; Pläne'!$D$9,'Preise &amp; Pläne'!$D$10)))),'Preise &amp; Pläne'!$C$13,IF(C21&gt;'Preise &amp; Pläne'!$C$6,'Preise &amp; Pläne'!$C$6*'Preise &amp; Pläne'!$D$6,0),IF(C21&gt;'Preise &amp; Pläne'!$C$7,'Preise &amp; Pläne'!$C$7*'Preise &amp; Pläne'!$D$7,0),IF(C21&gt;'Preise &amp; Pläne'!$C$8,'Preise &amp; Pläne'!$C$8*'Preise &amp; Pläne'!$D$8,0),IF(C21&gt;'Preise &amp; Pläne'!$C$9,'Preise &amp; Pläne'!$C$9*'Preise &amp; Pläne'!$D$9,0))</f>
+        <f aca="false">MAX(C21*IF(C21&lt;='Preise &amp; Pläne'!$C$6,'Preise &amp; Pläne'!$D$6,IF(C21&lt;='Preise &amp; Pläne'!$C$7,'Preise &amp; Pläne'!$D$7,'Preise &amp; Pläne'!$D$8)),'Preise &amp; Pläne'!$C$11,IF(C21&gt;'Preise &amp; Pläne'!$C$6,'Preise &amp; Pläne'!$C$6*'Preise &amp; Pläne'!$D$6,0),IF(C21&gt;'Preise &amp; Pläne'!$C$7,'Preise &amp; Pläne'!$C$7*'Preise &amp; Pläne'!$D$7,0))</f>
         <v>9750</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="5" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="C23" s="21" t="n">
         <v>0.85</v>
@@ -5193,7 +5103,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="5" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C24" s="26" t="n">
         <v>3</v>
@@ -5201,7 +5111,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="5" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C25" s="10" t="n">
         <v>6130</v>
@@ -5209,27 +5119,27 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="D27" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="C27" s="7" t="s">
+      <c r="E27" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="D27" s="7" t="s">
+      <c r="F27" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="E27" s="7" t="s">
+      <c r="G27" s="7" t="s">
         <v>155</v>
-      </c>
-      <c r="F27" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="G27" s="7" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="5" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C28" s="22" t="n">
         <f aca="false">$C$17*(1+$C$18)^0</f>
@@ -5254,7 +5164,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="5" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="C29" s="22" t="n">
         <f aca="false">C28+C30</f>
@@ -5279,7 +5189,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="5" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C30" s="22" t="n">
         <f aca="false">0</f>
@@ -5304,7 +5214,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="5" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C31" s="20" t="n">
         <f aca="false">C29*$C$21</f>
@@ -5329,7 +5239,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C32" s="15" t="n">
         <f aca="false">C29*$C$22</f>
@@ -5354,7 +5264,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="5" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C33" s="12" t="n">
         <f aca="false">-$C$10</f>
@@ -5379,7 +5289,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="5" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C34" s="12" t="n">
         <f aca="false">-C31*$C$24</f>
@@ -5404,7 +5314,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="5" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C35" s="12" t="n">
         <f aca="false">-$C$25</f>
@@ -5429,7 +5339,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C36" s="15" t="n">
         <f aca="false">SUM(C32:C35)</f>
@@ -5454,7 +5364,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="5" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C37" s="27" t="n">
         <f aca="false">IF(C32&lt;&gt;0,C36/C32,0)</f>
@@ -5479,7 +5389,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="5" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C39" s="15" t="n">
         <f aca="false">SUM(C32:G32)</f>
@@ -5488,7 +5398,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="5" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="C40" s="12" t="n">
         <f aca="false">SUM(C33:G33)</f>
@@ -5497,7 +5407,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="5" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C41" s="15" t="n">
         <f aca="false">SUM(C36:G36)</f>
@@ -5506,7 +5416,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
     </row>
   </sheetData>
@@ -5537,40 +5447,40 @@
   <sheetData>
     <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="7" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="C5" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="E5" s="7" t="s">
         <v>153</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="F5" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="G5" s="7" t="s">
         <v>155</v>
       </c>
-      <c r="F5" s="7" t="s">
-        <v>156</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>157</v>
-      </c>
       <c r="H5" s="7" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="5" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C6" s="25" t="n">
         <f aca="false">'Mit Anwalts-Funnel'!C32</f>
@@ -5599,7 +5509,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C7" s="25" t="n">
         <f aca="false">'Ohne Anwalt (Direkt)'!C32</f>
@@ -5628,7 +5538,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="3" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C8" s="12" t="n">
         <f aca="false">C6+C7</f>
@@ -5657,7 +5567,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="5" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C9" s="25" t="n">
         <f aca="false">'Mit Anwalts-Funnel'!C36</f>
@@ -5686,7 +5596,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="5" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C10" s="25" t="n">
         <f aca="false">'Ohne Anwalt (Direkt)'!C36</f>
@@ -5715,7 +5625,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C11" s="12" t="n">
         <f aca="false">C9+C10+'Ohne Anwalt (Direkt)'!$C$25</f>
@@ -5744,7 +5654,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="5" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C12" s="28" t="n">
         <f aca="false">'Mit Anwalts-Funnel'!C27</f>
@@ -5773,7 +5683,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="5" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C13" s="28" t="n">
         <f aca="false">'Ohne Anwalt (Direkt)'!C29</f>
@@ -5802,7 +5712,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="5" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C14" s="12" t="n">
         <f aca="false">-'Mit Anwalts-Funnel'!C33</f>
@@ -5831,7 +5741,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="5" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C15" s="12" t="n">
         <f aca="false">-'Ohne Anwalt (Direkt)'!C33</f>
@@ -5860,7 +5770,7 @@
     </row>
     <row r="17" customFormat="false" ht="48" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B17" s="17" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="C17" s="17"/>
       <c r="D17" s="17"/>
@@ -5907,4412 +5817,4412 @@
   <sheetData>
     <row r="2" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="1" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B3" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>210</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="E5" s="7" t="s">
         <v>211</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="F5" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="G5" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="F5" s="7" t="s">
+      <c r="H5" s="7" t="s">
         <v>214</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="I5" s="7" t="s">
         <v>215</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="J5" s="7" t="s">
         <v>216</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="K5" s="7" t="s">
         <v>217</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="L5" s="7" t="s">
         <v>218</v>
-      </c>
-      <c r="K5" s="7" t="s">
-        <v>219</v>
-      </c>
-      <c r="L5" s="7" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="E6" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="F6" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="G6" s="29" t="s">
         <v>223</v>
       </c>
-      <c r="E6" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="F6" s="4" t="s">
+      <c r="H6" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="G6" s="29" t="s">
+      <c r="I6" s="4" t="s">
         <v>225</v>
       </c>
-      <c r="H6" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="I6" s="4" t="s">
+      <c r="J6" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L6" s="4" t="s">
         <v>227</v>
-      </c>
-      <c r="J6" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="K6" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L6" s="4" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="D7" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>223</v>
-      </c>
       <c r="E7" s="4" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F7" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="G7" s="29" t="s">
+        <v>229</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="I7" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="G7" s="29" t="s">
+      <c r="J7" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K7" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L7" s="4" t="s">
         <v>231</v>
-      </c>
-      <c r="H7" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="I7" s="4" t="s">
-        <v>232</v>
-      </c>
-      <c r="J7" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="K7" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L7" s="4" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>223</v>
-      </c>
       <c r="E8" s="4" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F8" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="G8" s="29" t="s">
+        <v>233</v>
+      </c>
+      <c r="H8" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="G8" s="29" t="s">
+      <c r="I8" s="4" t="s">
         <v>235</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="J8" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L8" s="4" t="s">
         <v>236</v>
-      </c>
-      <c r="I8" s="4" t="s">
-        <v>237</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L8" s="4" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B9" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="C9" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>223</v>
-      </c>
       <c r="E9" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="G9" s="29" t="s">
         <v>239</v>
       </c>
-      <c r="F9" s="4" t="s">
+      <c r="H9" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I9" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="G9" s="29" t="s">
-        <v>241</v>
-      </c>
-      <c r="H9" s="4" t="s">
+      <c r="J9" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K9" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L9" s="4" t="s">
         <v>236</v>
-      </c>
-      <c r="I9" s="4" t="s">
-        <v>242</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="K9" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L9" s="4" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="D10" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="E10" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>243</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="E10" s="4" t="s">
+      <c r="G10" s="29" t="s">
         <v>244</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="H10" s="4" t="s">
         <v>245</v>
       </c>
-      <c r="G10" s="29" t="s">
+      <c r="I10" s="4" t="s">
         <v>246</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="J10" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L10" s="4" t="s">
         <v>247</v>
-      </c>
-      <c r="I10" s="4" t="s">
-        <v>248</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="K10" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L10" s="4" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B11" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="D11" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="C11" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>223</v>
-      </c>
       <c r="E11" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="G11" s="29" t="s">
         <v>250</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="H11" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I11" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="G11" s="29" t="s">
-        <v>252</v>
-      </c>
-      <c r="H11" s="4" t="s">
+      <c r="J11" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L11" s="4" t="s">
         <v>236</v>
-      </c>
-      <c r="I11" s="4" t="s">
-        <v>253</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L11" s="4" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B12" s="4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D12" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="F12" s="4" t="s">
         <v>254</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="G12" s="29" t="s">
         <v>255</v>
       </c>
-      <c r="F12" s="4" t="s">
+      <c r="H12" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="I12" s="4" t="s">
         <v>256</v>
       </c>
-      <c r="G12" s="29" t="s">
+      <c r="J12" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L12" s="4" t="s">
         <v>257</v>
-      </c>
-      <c r="H12" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="I12" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="K12" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L12" s="4" t="s">
-        <v>259</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E13" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="G13" s="29" t="s">
         <v>260</v>
       </c>
-      <c r="F13" s="4" t="s">
+      <c r="H13" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="I13" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="G13" s="29" t="s">
+      <c r="J13" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L13" s="4" t="s">
         <v>262</v>
-      </c>
-      <c r="H13" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="I13" s="4" t="s">
-        <v>263</v>
-      </c>
-      <c r="J13" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="K13" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L13" s="4" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="F14" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="G14" s="29" t="s">
+        <v>264</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="I14" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="G14" s="29" t="s">
-        <v>266</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="I14" s="4" t="s">
-        <v>267</v>
-      </c>
       <c r="J14" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="K14" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L14" s="4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B15" s="4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C15" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="E15" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="F15" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="G15" s="29" t="s">
         <v>270</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="H15" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I15" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="G15" s="29" t="s">
+      <c r="J15" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L15" s="4" t="s">
         <v>272</v>
-      </c>
-      <c r="H15" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="I15" s="4" t="s">
-        <v>273</v>
-      </c>
-      <c r="J15" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="K15" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L15" s="4" t="s">
-        <v>274</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B16" s="4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C16" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="E16" s="4" t="s">
         <v>268</v>
       </c>
-      <c r="D16" s="4" t="s">
-        <v>269</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>270</v>
-      </c>
       <c r="F16" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="G16" s="29" t="s">
+        <v>274</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I16" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="G16" s="29" t="s">
-        <v>276</v>
-      </c>
-      <c r="H16" s="4" t="s">
+      <c r="J16" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L16" s="4" t="s">
         <v>236</v>
-      </c>
-      <c r="I16" s="4" t="s">
-        <v>277</v>
-      </c>
-      <c r="J16" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="K16" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L16" s="4" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C17" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="F17" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="D17" s="4" t="s">
-        <v>269</v>
-      </c>
-      <c r="E17" s="4" t="s">
+      <c r="G17" s="29" t="s">
         <v>279</v>
       </c>
-      <c r="F17" s="4" t="s">
+      <c r="H17" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I17" s="4" t="s">
         <v>280</v>
       </c>
-      <c r="G17" s="29" t="s">
-        <v>281</v>
-      </c>
-      <c r="H17" s="4" t="s">
+      <c r="J17" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L17" s="4" t="s">
         <v>236</v>
-      </c>
-      <c r="I17" s="4" t="s">
-        <v>282</v>
-      </c>
-      <c r="J17" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="K17" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L17" s="4" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B18" s="4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="F18" s="4" t="s">
+        <v>281</v>
+      </c>
+      <c r="G18" s="29" t="s">
+        <v>282</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I18" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="G18" s="29" t="s">
-        <v>284</v>
-      </c>
-      <c r="H18" s="4" t="s">
+      <c r="J18" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L18" s="4" t="s">
         <v>236</v>
-      </c>
-      <c r="I18" s="4" t="s">
-        <v>285</v>
-      </c>
-      <c r="J18" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="K18" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L18" s="4" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B19" s="4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C19" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="F19" s="4" t="s">
         <v>286</v>
       </c>
-      <c r="D19" s="4" t="s">
-        <v>269</v>
-      </c>
-      <c r="E19" s="4" t="s">
+      <c r="G19" s="29" t="s">
         <v>287</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="H19" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I19" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="G19" s="29" t="s">
-        <v>289</v>
-      </c>
-      <c r="H19" s="4" t="s">
+      <c r="J19" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L19" s="4" t="s">
         <v>236</v>
-      </c>
-      <c r="I19" s="4" t="s">
-        <v>290</v>
-      </c>
-      <c r="J19" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="K19" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L19" s="4" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="F20" s="4" t="s">
+        <v>289</v>
+      </c>
+      <c r="G20" s="29" t="s">
+        <v>290</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="I20" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="G20" s="29" t="s">
-        <v>292</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="I20" s="4" t="s">
-        <v>293</v>
-      </c>
       <c r="J20" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="K20" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L20" s="4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C21" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>293</v>
+      </c>
+      <c r="F21" s="4" t="s">
         <v>294</v>
       </c>
-      <c r="D21" s="4" t="s">
-        <v>269</v>
-      </c>
-      <c r="E21" s="4" t="s">
+      <c r="G21" s="29" t="s">
         <v>295</v>
       </c>
-      <c r="F21" s="4" t="s">
+      <c r="H21" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I21" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="G21" s="29" t="s">
+      <c r="J21" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K21" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L21" s="4" t="s">
         <v>297</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="I21" s="4" t="s">
-        <v>298</v>
-      </c>
-      <c r="J21" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="K21" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L21" s="4" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B22" s="4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D22" s="4" t="s">
+        <v>298</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="G22" s="29" t="s">
         <v>300</v>
       </c>
-      <c r="E22" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="F22" s="4" t="s">
+      <c r="H22" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="I22" s="4" t="s">
         <v>301</v>
       </c>
-      <c r="G22" s="29" t="s">
-        <v>302</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="I22" s="4" t="s">
-        <v>303</v>
-      </c>
       <c r="J22" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="K22" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L22" s="4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C23" s="4" t="s">
+        <v>302</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>303</v>
+      </c>
+      <c r="E23" s="4" t="s">
         <v>304</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="F23" s="4" t="s">
         <v>305</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="G23" s="29" t="s">
         <v>306</v>
       </c>
-      <c r="F23" s="4" t="s">
+      <c r="H23" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="I23" s="4" t="s">
         <v>307</v>
       </c>
-      <c r="G23" s="29" t="s">
+      <c r="J23" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K23" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L23" s="4" t="s">
         <v>308</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="I23" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="J23" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="K23" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L23" s="4" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B24" s="4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D24" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>310</v>
+      </c>
+      <c r="F24" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="G24" s="29" t="s">
         <v>312</v>
       </c>
-      <c r="F24" s="4" t="s">
+      <c r="H24" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="I24" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="G24" s="29" t="s">
+      <c r="J24" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K24" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L24" s="4" t="s">
         <v>314</v>
-      </c>
-      <c r="H24" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="I24" s="4" t="s">
-        <v>315</v>
-      </c>
-      <c r="J24" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="K24" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L24" s="4" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B25" s="4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="F25" s="4" t="s">
+        <v>315</v>
+      </c>
+      <c r="G25" s="29" t="s">
+        <v>316</v>
+      </c>
+      <c r="H25" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="I25" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="G25" s="29" t="s">
-        <v>318</v>
-      </c>
-      <c r="H25" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="I25" s="4" t="s">
-        <v>319</v>
-      </c>
       <c r="J25" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="K25" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L25" s="4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B26" s="4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D26" s="4" t="s">
+        <v>318</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>319</v>
+      </c>
+      <c r="G26" s="29" t="s">
         <v>320</v>
       </c>
-      <c r="E26" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="F26" s="4" t="s">
+      <c r="H26" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I26" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="G26" s="29" t="s">
+      <c r="J26" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K26" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L26" s="4" t="s">
         <v>322</v>
-      </c>
-      <c r="H26" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="I26" s="4" t="s">
-        <v>323</v>
-      </c>
-      <c r="J26" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="K26" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L26" s="4" t="s">
-        <v>324</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B27" s="4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F27" s="4" t="s">
+        <v>323</v>
+      </c>
+      <c r="G27" s="29" t="s">
+        <v>324</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I27" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="G27" s="29" t="s">
+      <c r="J27" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K27" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L27" s="4" t="s">
         <v>326</v>
-      </c>
-      <c r="H27" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="I27" s="4" t="s">
-        <v>327</v>
-      </c>
-      <c r="J27" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="K27" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L27" s="4" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B28" s="4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D28" s="4" t="s">
+        <v>327</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>328</v>
+      </c>
+      <c r="G28" s="29" t="s">
         <v>329</v>
       </c>
-      <c r="E28" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="F28" s="4" t="s">
+      <c r="H28" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="I28" s="4" t="s">
         <v>330</v>
       </c>
-      <c r="G28" s="29" t="s">
+      <c r="J28" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K28" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L28" s="4" t="s">
         <v>331</v>
-      </c>
-      <c r="H28" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="I28" s="4" t="s">
-        <v>332</v>
-      </c>
-      <c r="J28" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="K28" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L28" s="4" t="s">
-        <v>333</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B29" s="4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F29" s="4" t="s">
+        <v>332</v>
+      </c>
+      <c r="G29" s="29" t="s">
+        <v>333</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I29" s="4" t="s">
         <v>334</v>
       </c>
-      <c r="G29" s="29" t="s">
+      <c r="J29" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K29" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L29" s="4" t="s">
         <v>335</v>
-      </c>
-      <c r="H29" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="I29" s="4" t="s">
-        <v>336</v>
-      </c>
-      <c r="J29" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="K29" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L29" s="4" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B30" s="4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F30" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="G30" s="29" t="s">
+        <v>337</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="I30" s="4" t="s">
         <v>338</v>
       </c>
-      <c r="G30" s="29" t="s">
-        <v>339</v>
-      </c>
-      <c r="H30" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="I30" s="4" t="s">
-        <v>340</v>
-      </c>
       <c r="J30" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="K30" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L30" s="4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B31" s="4" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="F31" s="4" t="s">
+        <v>339</v>
+      </c>
+      <c r="G31" s="29" t="s">
+        <v>340</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="I31" s="4" t="s">
         <v>341</v>
       </c>
-      <c r="G31" s="29" t="s">
+      <c r="J31" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K31" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L31" s="4" t="s">
         <v>342</v>
-      </c>
-      <c r="H31" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="I31" s="4" t="s">
-        <v>343</v>
-      </c>
-      <c r="J31" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="K31" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L31" s="4" t="s">
-        <v>344</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B32" s="4" t="s">
+        <v>343</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>292</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="F32" s="4" t="s">
         <v>345</v>
       </c>
-      <c r="C32" s="4" t="s">
-        <v>294</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="E32" s="4" t="s">
+      <c r="G32" s="29" t="s">
         <v>346</v>
       </c>
-      <c r="F32" s="4" t="s">
+      <c r="H32" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I32" s="4" t="s">
         <v>347</v>
       </c>
-      <c r="G32" s="29" t="s">
-        <v>348</v>
-      </c>
-      <c r="H32" s="4" t="s">
+      <c r="J32" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K32" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L32" s="4" t="s">
         <v>236</v>
-      </c>
-      <c r="I32" s="4" t="s">
-        <v>349</v>
-      </c>
-      <c r="J32" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="K32" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L32" s="4" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B33" s="4" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="F33" s="4" t="s">
+        <v>348</v>
+      </c>
+      <c r="G33" s="29" t="s">
+        <v>349</v>
+      </c>
+      <c r="H33" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I33" s="4" t="s">
         <v>350</v>
       </c>
-      <c r="G33" s="29" t="s">
-        <v>351</v>
-      </c>
-      <c r="H33" s="4" t="s">
+      <c r="J33" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K33" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L33" s="4" t="s">
         <v>236</v>
-      </c>
-      <c r="I33" s="4" t="s">
-        <v>352</v>
-      </c>
-      <c r="J33" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="K33" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L33" s="4" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B34" s="4" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D34" s="4" t="s">
+        <v>351</v>
+      </c>
+      <c r="E34" s="4" t="s">
+        <v>352</v>
+      </c>
+      <c r="F34" s="4" t="s">
         <v>353</v>
-      </c>
-      <c r="E34" s="4" t="s">
-        <v>354</v>
-      </c>
-      <c r="F34" s="4" t="s">
-        <v>355</v>
       </c>
       <c r="G34" s="4"/>
       <c r="H34" s="4" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="I34" s="4" t="s">
+        <v>354</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K34" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="L34" s="4" t="s">
         <v>356</v>
-      </c>
-      <c r="J34" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="K34" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="L34" s="4" t="s">
-        <v>358</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B35" s="4" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="F35" s="4" t="s">
+        <v>357</v>
+      </c>
+      <c r="G35" s="29" t="s">
+        <v>358</v>
+      </c>
+      <c r="H35" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I35" s="4" t="s">
         <v>359</v>
       </c>
-      <c r="G35" s="29" t="s">
+      <c r="J35" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K35" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L35" s="4" t="s">
         <v>360</v>
-      </c>
-      <c r="H35" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="I35" s="4" t="s">
-        <v>361</v>
-      </c>
-      <c r="J35" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="K35" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L35" s="4" t="s">
-        <v>362</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B36" s="4" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E36" s="4" t="s">
+        <v>361</v>
+      </c>
+      <c r="F36" s="4" t="s">
+        <v>362</v>
+      </c>
+      <c r="G36" s="29" t="s">
         <v>363</v>
       </c>
-      <c r="F36" s="4" t="s">
+      <c r="H36" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I36" s="4" t="s">
         <v>364</v>
       </c>
-      <c r="G36" s="29" t="s">
+      <c r="J36" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K36" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="L36" s="4" t="s">
         <v>365</v>
-      </c>
-      <c r="H36" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="I36" s="4" t="s">
-        <v>366</v>
-      </c>
-      <c r="J36" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="K36" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="L36" s="4" t="s">
-        <v>367</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B37" s="4" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E37" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>367</v>
+      </c>
+      <c r="G37" s="29" t="s">
         <v>368</v>
       </c>
-      <c r="F37" s="4" t="s">
+      <c r="H37" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I37" s="4" t="s">
         <v>369</v>
       </c>
-      <c r="G37" s="29" t="s">
+      <c r="J37" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K37" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L37" s="4" t="s">
         <v>370</v>
-      </c>
-      <c r="H37" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="I37" s="4" t="s">
-        <v>371</v>
-      </c>
-      <c r="J37" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="K37" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L37" s="4" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B38" s="4" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E38" s="4" t="s">
+        <v>371</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>372</v>
+      </c>
+      <c r="G38" s="29" t="s">
         <v>373</v>
       </c>
-      <c r="F38" s="4" t="s">
+      <c r="H38" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I38" s="4" t="s">
         <v>374</v>
       </c>
-      <c r="G38" s="29" t="s">
-        <v>375</v>
-      </c>
-      <c r="H38" s="4" t="s">
+      <c r="J38" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K38" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L38" s="4" t="s">
         <v>236</v>
-      </c>
-      <c r="I38" s="4" t="s">
-        <v>376</v>
-      </c>
-      <c r="J38" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="K38" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L38" s="4" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="4" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="F39" s="4" t="s">
+        <v>375</v>
+      </c>
+      <c r="G39" s="29" t="s">
+        <v>376</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I39" s="4" t="s">
         <v>377</v>
       </c>
-      <c r="G39" s="29" t="s">
-        <v>378</v>
-      </c>
-      <c r="H39" s="4" t="s">
+      <c r="J39" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K39" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L39" s="4" t="s">
         <v>236</v>
-      </c>
-      <c r="I39" s="4" t="s">
-        <v>379</v>
-      </c>
-      <c r="J39" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="K39" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L39" s="4" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="4" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="F40" s="4" t="s">
+        <v>378</v>
+      </c>
+      <c r="G40" s="29" t="s">
+        <v>379</v>
+      </c>
+      <c r="H40" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I40" s="4" t="s">
         <v>380</v>
       </c>
-      <c r="G40" s="29" t="s">
-        <v>381</v>
-      </c>
-      <c r="H40" s="4" t="s">
+      <c r="J40" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K40" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L40" s="4" t="s">
         <v>236</v>
-      </c>
-      <c r="I40" s="4" t="s">
-        <v>382</v>
-      </c>
-      <c r="J40" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="K40" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L40" s="4" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="4" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="F41" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="G41" s="29" t="s">
+        <v>382</v>
+      </c>
+      <c r="H41" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I41" s="4" t="s">
         <v>383</v>
       </c>
-      <c r="G41" s="29" t="s">
+      <c r="J41" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K41" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L41" s="4" t="s">
         <v>384</v>
-      </c>
-      <c r="H41" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="I41" s="4" t="s">
-        <v>385</v>
-      </c>
-      <c r="J41" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="K41" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L41" s="4" t="s">
-        <v>386</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="4" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="F42" s="4" t="s">
+        <v>385</v>
+      </c>
+      <c r="G42" s="29" t="s">
+        <v>386</v>
+      </c>
+      <c r="H42" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I42" s="4" t="s">
         <v>387</v>
       </c>
-      <c r="G42" s="29" t="s">
+      <c r="J42" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K42" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L42" s="4" t="s">
         <v>388</v>
-      </c>
-      <c r="H42" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="I42" s="4" t="s">
-        <v>389</v>
-      </c>
-      <c r="J42" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="K42" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L42" s="4" t="s">
-        <v>390</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="4" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D43" s="4" t="s">
+        <v>389</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>390</v>
+      </c>
+      <c r="F43" s="4" t="s">
         <v>391</v>
       </c>
-      <c r="E43" s="4" t="s">
+      <c r="G43" s="29" t="s">
         <v>392</v>
       </c>
-      <c r="F43" s="4" t="s">
+      <c r="H43" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="I43" s="4" t="s">
         <v>393</v>
       </c>
-      <c r="G43" s="29" t="s">
+      <c r="J43" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K43" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L43" s="4" t="s">
         <v>394</v>
-      </c>
-      <c r="H43" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="I43" s="4" t="s">
-        <v>395</v>
-      </c>
-      <c r="J43" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="K43" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L43" s="4" t="s">
-        <v>396</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B44" s="4" t="s">
+        <v>395</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="D44" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="E44" s="4" t="s">
+        <v>396</v>
+      </c>
+      <c r="F44" s="4" t="s">
         <v>397</v>
       </c>
-      <c r="C44" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="E44" s="4" t="s">
+      <c r="G44" s="29" t="s">
         <v>398</v>
       </c>
-      <c r="F44" s="4" t="s">
+      <c r="H44" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="I44" s="4" t="s">
         <v>399</v>
       </c>
-      <c r="G44" s="29" t="s">
+      <c r="J44" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="K44" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L44" s="4" t="s">
         <v>400</v>
-      </c>
-      <c r="H44" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="I44" s="4" t="s">
-        <v>401</v>
-      </c>
-      <c r="J44" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="K44" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L44" s="4" t="s">
-        <v>402</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B45" s="4" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F45" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="G45" s="29" t="s">
+        <v>402</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I45" s="4" t="s">
         <v>403</v>
       </c>
-      <c r="G45" s="29" t="s">
-        <v>404</v>
-      </c>
-      <c r="H45" s="4" t="s">
+      <c r="J45" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="K45" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L45" s="4" t="s">
         <v>236</v>
-      </c>
-      <c r="I45" s="4" t="s">
-        <v>405</v>
-      </c>
-      <c r="J45" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="K45" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L45" s="4" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B46" s="4" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E46" s="4" t="s">
+        <v>404</v>
+      </c>
+      <c r="F46" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="G46" s="29" t="s">
         <v>406</v>
       </c>
-      <c r="F46" s="4" t="s">
+      <c r="H46" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="I46" s="4" t="s">
         <v>407</v>
       </c>
-      <c r="G46" s="29" t="s">
-        <v>408</v>
-      </c>
-      <c r="H46" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="I46" s="4" t="s">
-        <v>409</v>
-      </c>
       <c r="J46" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="K46" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L46" s="4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B47" s="4" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E47" s="4" t="s">
+        <v>408</v>
+      </c>
+      <c r="F47" s="4" t="s">
+        <v>409</v>
+      </c>
+      <c r="G47" s="29" t="s">
         <v>410</v>
       </c>
-      <c r="F47" s="4" t="s">
+      <c r="H47" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I47" s="4" t="s">
         <v>411</v>
       </c>
-      <c r="G47" s="29" t="s">
+      <c r="J47" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="K47" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L47" s="4" t="s">
         <v>412</v>
-      </c>
-      <c r="H47" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="I47" s="4" t="s">
-        <v>413</v>
-      </c>
-      <c r="J47" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="K47" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L47" s="4" t="s">
-        <v>414</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B48" s="4" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E48" s="4" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F48" s="4" t="s">
+        <v>413</v>
+      </c>
+      <c r="G48" s="29" t="s">
+        <v>414</v>
+      </c>
+      <c r="H48" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="I48" s="4" t="s">
         <v>415</v>
       </c>
-      <c r="G48" s="29" t="s">
+      <c r="J48" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="K48" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L48" s="4" t="s">
         <v>416</v>
-      </c>
-      <c r="H48" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="I48" s="4" t="s">
-        <v>417</v>
-      </c>
-      <c r="J48" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="K48" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L48" s="4" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B49" s="4" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F49" s="4" t="s">
+        <v>417</v>
+      </c>
+      <c r="G49" s="29" t="s">
+        <v>418</v>
+      </c>
+      <c r="H49" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="I49" s="4" t="s">
         <v>419</v>
       </c>
-      <c r="G49" s="29" t="s">
-        <v>420</v>
-      </c>
-      <c r="H49" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="I49" s="4" t="s">
-        <v>421</v>
-      </c>
       <c r="J49" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="K49" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L49" s="4" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B50" s="4" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E50" s="4" t="s">
+        <v>420</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>421</v>
+      </c>
+      <c r="G50" s="29" t="s">
         <v>422</v>
       </c>
-      <c r="F50" s="4" t="s">
+      <c r="H50" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I50" s="4" t="s">
         <v>423</v>
       </c>
-      <c r="G50" s="29" t="s">
-        <v>424</v>
-      </c>
-      <c r="H50" s="4" t="s">
+      <c r="J50" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="K50" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L50" s="4" t="s">
         <v>236</v>
-      </c>
-      <c r="I50" s="4" t="s">
-        <v>425</v>
-      </c>
-      <c r="J50" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="K50" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L50" s="4" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B51" s="4" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E51" s="4" t="s">
+        <v>424</v>
+      </c>
+      <c r="F51" s="4" t="s">
+        <v>425</v>
+      </c>
+      <c r="G51" s="29" t="s">
         <v>426</v>
       </c>
-      <c r="F51" s="4" t="s">
+      <c r="H51" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I51" s="4" t="s">
         <v>427</v>
       </c>
-      <c r="G51" s="29" t="s">
+      <c r="J51" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="K51" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L51" s="4" t="s">
         <v>428</v>
-      </c>
-      <c r="H51" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="I51" s="4" t="s">
-        <v>429</v>
-      </c>
-      <c r="J51" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="K51" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L51" s="4" t="s">
-        <v>430</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B52" s="4" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F52" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="G52" s="29" t="s">
+        <v>430</v>
+      </c>
+      <c r="H52" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="I52" s="4" t="s">
         <v>431</v>
       </c>
-      <c r="G52" s="29" t="s">
-        <v>432</v>
-      </c>
-      <c r="H52" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="I52" s="4" t="s">
-        <v>433</v>
-      </c>
       <c r="J52" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="K52" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L52" s="4" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B53" s="4" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E53" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="F53" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="G53" s="29" t="s">
         <v>434</v>
       </c>
-      <c r="F53" s="4" t="s">
+      <c r="H53" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="I53" s="4" t="s">
         <v>435</v>
       </c>
-      <c r="G53" s="29" t="s">
+      <c r="J53" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="K53" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L53" s="4" t="s">
         <v>436</v>
-      </c>
-      <c r="H53" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="I53" s="4" t="s">
-        <v>437</v>
-      </c>
-      <c r="J53" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="K53" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L53" s="4" t="s">
-        <v>438</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B54" s="4" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F54" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="G54" s="29" t="s">
+        <v>438</v>
+      </c>
+      <c r="H54" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="I54" s="4" t="s">
         <v>439</v>
       </c>
-      <c r="G54" s="29" t="s">
-        <v>440</v>
-      </c>
-      <c r="H54" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="I54" s="4" t="s">
-        <v>441</v>
-      </c>
       <c r="J54" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="K54" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L54" s="4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B55" s="4" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E55" s="4" t="s">
+        <v>440</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="G55" s="29" t="s">
         <v>442</v>
       </c>
-      <c r="F55" s="4" t="s">
+      <c r="H55" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I55" s="4" t="s">
         <v>443</v>
       </c>
-      <c r="G55" s="29" t="s">
+      <c r="J55" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="K55" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L55" s="4" t="s">
         <v>444</v>
-      </c>
-      <c r="H55" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="I55" s="4" t="s">
-        <v>445</v>
-      </c>
-      <c r="J55" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="K55" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L55" s="4" t="s">
-        <v>446</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B56" s="4" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E56" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="F56" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="G56" s="29" t="s">
         <v>447</v>
       </c>
-      <c r="F56" s="4" t="s">
+      <c r="H56" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="I56" s="4" t="s">
         <v>448</v>
       </c>
-      <c r="G56" s="29" t="s">
+      <c r="J56" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="K56" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="L56" s="4" t="s">
         <v>449</v>
-      </c>
-      <c r="H56" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="I56" s="4" t="s">
-        <v>450</v>
-      </c>
-      <c r="J56" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="K56" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="L56" s="4" t="s">
-        <v>451</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B57" s="4" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D57" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>451</v>
+      </c>
+      <c r="F57" s="4" t="s">
         <v>452</v>
       </c>
-      <c r="E57" s="4" t="s">
+      <c r="G57" s="29" t="s">
         <v>453</v>
       </c>
-      <c r="F57" s="4" t="s">
+      <c r="H57" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="I57" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="G57" s="29" t="s">
+      <c r="J57" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="K57" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L57" s="4" t="s">
         <v>455</v>
-      </c>
-      <c r="H57" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="I57" s="4" t="s">
-        <v>456</v>
-      </c>
-      <c r="J57" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="K57" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L57" s="4" t="s">
-        <v>457</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B58" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="E58" s="4" t="s">
+        <v>457</v>
+      </c>
+      <c r="F58" s="4" t="s">
         <v>458</v>
       </c>
-      <c r="C58" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="D58" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="E58" s="4" t="s">
+      <c r="G58" s="29" t="s">
         <v>459</v>
       </c>
-      <c r="F58" s="4" t="s">
+      <c r="H58" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I58" s="4" t="s">
         <v>460</v>
       </c>
-      <c r="G58" s="29" t="s">
-        <v>461</v>
-      </c>
-      <c r="H58" s="4" t="s">
+      <c r="J58" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="K58" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L58" s="4" t="s">
         <v>236</v>
-      </c>
-      <c r="I58" s="4" t="s">
-        <v>462</v>
-      </c>
-      <c r="J58" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="K58" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L58" s="4" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B59" s="4" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="F59" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="G59" s="29" t="s">
+        <v>462</v>
+      </c>
+      <c r="H59" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="I59" s="4" t="s">
         <v>463</v>
       </c>
-      <c r="G59" s="29" t="s">
+      <c r="J59" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="K59" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L59" s="4" t="s">
         <v>464</v>
-      </c>
-      <c r="H59" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="I59" s="4" t="s">
-        <v>465</v>
-      </c>
-      <c r="J59" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="K59" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L59" s="4" t="s">
-        <v>466</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B60" s="4" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E60" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="F60" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="G60" s="29" t="s">
         <v>467</v>
       </c>
-      <c r="F60" s="4" t="s">
+      <c r="H60" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I60" s="4" t="s">
         <v>468</v>
       </c>
-      <c r="G60" s="29" t="s">
+      <c r="J60" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="K60" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="L60" s="4" t="s">
         <v>469</v>
-      </c>
-      <c r="H60" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="I60" s="4" t="s">
-        <v>470</v>
-      </c>
-      <c r="J60" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="K60" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="L60" s="4" t="s">
-        <v>471</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B61" s="4" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E61" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="F61" s="4" t="s">
+        <v>471</v>
+      </c>
+      <c r="G61" s="29" t="s">
         <v>472</v>
       </c>
-      <c r="F61" s="4" t="s">
+      <c r="H61" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I61" s="4" t="s">
         <v>473</v>
       </c>
-      <c r="G61" s="29" t="s">
-        <v>474</v>
-      </c>
-      <c r="H61" s="4" t="s">
+      <c r="J61" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="K61" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L61" s="4" t="s">
         <v>236</v>
-      </c>
-      <c r="I61" s="4" t="s">
-        <v>475</v>
-      </c>
-      <c r="J61" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="K61" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L61" s="4" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B62" s="4" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E62" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="F62" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="G62" s="29" t="s">
         <v>476</v>
       </c>
-      <c r="F62" s="4" t="s">
+      <c r="H62" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I62" s="4" t="s">
         <v>477</v>
       </c>
-      <c r="G62" s="29" t="s">
+      <c r="J62" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="K62" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L62" s="4" t="s">
         <v>478</v>
-      </c>
-      <c r="H62" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="I62" s="4" t="s">
-        <v>479</v>
-      </c>
-      <c r="J62" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="K62" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L62" s="4" t="s">
-        <v>480</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="64.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B63" s="4" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="F63" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="G63" s="29" t="s">
+        <v>480</v>
+      </c>
+      <c r="H63" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="I63" s="4" t="s">
         <v>481</v>
       </c>
-      <c r="G63" s="29" t="s">
+      <c r="J63" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="K63" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L63" s="4" t="s">
         <v>482</v>
-      </c>
-      <c r="H63" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="I63" s="4" t="s">
-        <v>483</v>
-      </c>
-      <c r="J63" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="K63" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L63" s="4" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B64" s="4" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E64" s="4" t="s">
+        <v>483</v>
+      </c>
+      <c r="F64" s="4" t="s">
+        <v>484</v>
+      </c>
+      <c r="G64" s="29" t="s">
         <v>485</v>
       </c>
-      <c r="F64" s="4" t="s">
+      <c r="H64" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I64" s="4" t="s">
         <v>486</v>
       </c>
-      <c r="G64" s="29" t="s">
-        <v>487</v>
-      </c>
-      <c r="H64" s="4" t="s">
+      <c r="J64" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="K64" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L64" s="4" t="s">
         <v>236</v>
-      </c>
-      <c r="I64" s="4" t="s">
-        <v>488</v>
-      </c>
-      <c r="J64" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="K64" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L64" s="4" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B65" s="4" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E65" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="F65" s="4" t="s">
+        <v>488</v>
+      </c>
+      <c r="G65" s="29" t="s">
         <v>489</v>
       </c>
-      <c r="F65" s="4" t="s">
+      <c r="H65" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I65" s="4" t="s">
         <v>490</v>
       </c>
-      <c r="G65" s="29" t="s">
-        <v>491</v>
-      </c>
-      <c r="H65" s="4" t="s">
+      <c r="J65" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="K65" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L65" s="4" t="s">
         <v>236</v>
-      </c>
-      <c r="I65" s="4" t="s">
-        <v>492</v>
-      </c>
-      <c r="J65" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="K65" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L65" s="4" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B66" s="4" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="F66" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="G66" s="29" t="s">
+        <v>492</v>
+      </c>
+      <c r="H66" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="I66" s="4" t="s">
         <v>493</v>
       </c>
-      <c r="G66" s="29" t="s">
+      <c r="J66" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="K66" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L66" s="4" t="s">
         <v>494</v>
-      </c>
-      <c r="H66" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="I66" s="4" t="s">
-        <v>495</v>
-      </c>
-      <c r="J66" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="K66" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L66" s="4" t="s">
-        <v>496</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B67" s="4" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="F67" s="4" t="s">
+        <v>495</v>
+      </c>
+      <c r="G67" s="29" t="s">
+        <v>496</v>
+      </c>
+      <c r="H67" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="I67" s="4" t="s">
         <v>497</v>
       </c>
-      <c r="G67" s="29" t="s">
+      <c r="J67" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="K67" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L67" s="4" t="s">
         <v>498</v>
-      </c>
-      <c r="H67" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="I67" s="4" t="s">
-        <v>499</v>
-      </c>
-      <c r="J67" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="K67" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L67" s="4" t="s">
-        <v>500</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B68" s="4" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="F68" s="4" t="s">
+        <v>499</v>
+      </c>
+      <c r="G68" s="29" t="s">
+        <v>500</v>
+      </c>
+      <c r="H68" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I68" s="4" t="s">
         <v>501</v>
       </c>
-      <c r="G68" s="29" t="s">
-        <v>502</v>
-      </c>
-      <c r="H68" s="4" t="s">
+      <c r="J68" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="K68" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L68" s="4" t="s">
         <v>236</v>
-      </c>
-      <c r="I68" s="4" t="s">
-        <v>503</v>
-      </c>
-      <c r="J68" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="K68" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L68" s="4" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B69" s="4" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="F69" s="4" t="s">
+        <v>502</v>
+      </c>
+      <c r="G69" s="29" t="s">
+        <v>503</v>
+      </c>
+      <c r="H69" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I69" s="4" t="s">
         <v>504</v>
       </c>
-      <c r="G69" s="29" t="s">
-        <v>505</v>
-      </c>
-      <c r="H69" s="4" t="s">
+      <c r="J69" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="K69" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L69" s="4" t="s">
         <v>236</v>
-      </c>
-      <c r="I69" s="4" t="s">
-        <v>506</v>
-      </c>
-      <c r="J69" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="K69" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L69" s="4" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B70" s="4" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E70" s="4" t="s">
+        <v>505</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>506</v>
+      </c>
+      <c r="G70" s="29" t="s">
         <v>507</v>
       </c>
-      <c r="F70" s="4" t="s">
+      <c r="H70" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="I70" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="G70" s="29" t="s">
+      <c r="J70" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="K70" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="L70" s="4" t="s">
         <v>509</v>
-      </c>
-      <c r="H70" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="I70" s="4" t="s">
-        <v>510</v>
-      </c>
-      <c r="J70" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="K70" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="L70" s="4" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B71" s="4" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E71" s="4" t="s">
+        <v>510</v>
+      </c>
+      <c r="F71" s="4" t="s">
+        <v>511</v>
+      </c>
+      <c r="G71" s="29" t="s">
         <v>512</v>
       </c>
-      <c r="F71" s="4" t="s">
+      <c r="H71" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I71" s="4" t="s">
         <v>513</v>
       </c>
-      <c r="G71" s="29" t="s">
+      <c r="J71" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="K71" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="L71" s="4" t="s">
         <v>514</v>
-      </c>
-      <c r="H71" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="I71" s="4" t="s">
-        <v>515</v>
-      </c>
-      <c r="J71" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="K71" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="L71" s="4" t="s">
-        <v>516</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B72" s="4" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="F72" s="4" t="s">
+        <v>515</v>
+      </c>
+      <c r="G72" s="29" t="s">
+        <v>516</v>
+      </c>
+      <c r="H72" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I72" s="4" t="s">
         <v>517</v>
       </c>
-      <c r="G72" s="29" t="s">
+      <c r="J72" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="K72" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L72" s="4" t="s">
         <v>518</v>
-      </c>
-      <c r="H72" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="I72" s="4" t="s">
-        <v>519</v>
-      </c>
-      <c r="J72" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="K72" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L72" s="4" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B73" s="4" t="s">
+        <v>519</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="E73" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="F73" s="4" t="s">
+        <v>520</v>
+      </c>
+      <c r="G73" s="29" t="s">
         <v>521</v>
       </c>
-      <c r="C73" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="D73" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="E73" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="F73" s="4" t="s">
+      <c r="H73" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="I73" s="4" t="s">
         <v>522</v>
       </c>
-      <c r="G73" s="29" t="s">
-        <v>523</v>
-      </c>
-      <c r="H73" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="I73" s="4" t="s">
-        <v>524</v>
-      </c>
       <c r="J73" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="K73" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L73" s="4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B74" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E74" s="4" t="s">
+        <v>523</v>
+      </c>
+      <c r="F74" s="4" t="s">
+        <v>524</v>
+      </c>
+      <c r="G74" s="29" t="s">
         <v>525</v>
       </c>
-      <c r="F74" s="4" t="s">
+      <c r="H74" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I74" s="4" t="s">
         <v>526</v>
       </c>
-      <c r="G74" s="29" t="s">
-        <v>527</v>
-      </c>
-      <c r="H74" s="4" t="s">
+      <c r="J74" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K74" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L74" s="4" t="s">
         <v>236</v>
-      </c>
-      <c r="I74" s="4" t="s">
-        <v>528</v>
-      </c>
-      <c r="J74" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="K74" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L74" s="4" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B75" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="F75" s="4" t="s">
+        <v>527</v>
+      </c>
+      <c r="G75" s="29" t="s">
+        <v>528</v>
+      </c>
+      <c r="H75" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I75" s="4" t="s">
         <v>529</v>
       </c>
-      <c r="G75" s="29" t="s">
-        <v>530</v>
-      </c>
-      <c r="H75" s="4" t="s">
+      <c r="J75" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K75" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L75" s="4" t="s">
         <v>236</v>
-      </c>
-      <c r="I75" s="4" t="s">
-        <v>531</v>
-      </c>
-      <c r="J75" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="K75" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L75" s="4" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B76" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E76" s="4" t="s">
+        <v>530</v>
+      </c>
+      <c r="F76" s="4" t="s">
+        <v>531</v>
+      </c>
+      <c r="G76" s="29" t="s">
         <v>532</v>
       </c>
-      <c r="F76" s="4" t="s">
+      <c r="H76" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I76" s="4" t="s">
         <v>533</v>
       </c>
-      <c r="G76" s="29" t="s">
+      <c r="J76" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K76" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="L76" s="4" t="s">
         <v>534</v>
-      </c>
-      <c r="H76" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="I76" s="4" t="s">
-        <v>535</v>
-      </c>
-      <c r="J76" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="K76" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="L76" s="4" t="s">
-        <v>536</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B77" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E77" s="4" t="s">
+        <v>535</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>536</v>
+      </c>
+      <c r="G77" s="29" t="s">
         <v>537</v>
       </c>
-      <c r="F77" s="4" t="s">
+      <c r="H77" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="I77" s="4" t="s">
         <v>538</v>
       </c>
-      <c r="G77" s="29" t="s">
+      <c r="J77" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K77" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L77" s="4" t="s">
         <v>539</v>
-      </c>
-      <c r="H77" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="I77" s="4" t="s">
-        <v>540</v>
-      </c>
-      <c r="J77" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="K77" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L77" s="4" t="s">
-        <v>541</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B78" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E78" s="4" t="s">
+        <v>540</v>
+      </c>
+      <c r="F78" s="4" t="s">
+        <v>541</v>
+      </c>
+      <c r="G78" s="29" t="s">
         <v>542</v>
       </c>
-      <c r="F78" s="4" t="s">
+      <c r="H78" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="I78" s="4" t="s">
         <v>543</v>
       </c>
-      <c r="G78" s="29" t="s">
+      <c r="J78" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K78" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L78" s="4" t="s">
         <v>544</v>
-      </c>
-      <c r="H78" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="I78" s="4" t="s">
-        <v>545</v>
-      </c>
-      <c r="J78" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="K78" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L78" s="4" t="s">
-        <v>546</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B79" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F79" s="4" t="s">
+        <v>545</v>
+      </c>
+      <c r="G79" s="29" t="s">
+        <v>546</v>
+      </c>
+      <c r="H79" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="I79" s="4" t="s">
         <v>547</v>
       </c>
-      <c r="G79" s="29" t="s">
+      <c r="J79" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K79" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L79" s="4" t="s">
         <v>548</v>
-      </c>
-      <c r="H79" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="I79" s="4" t="s">
-        <v>549</v>
-      </c>
-      <c r="J79" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="K79" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L79" s="4" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B80" s="4" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E80" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>550</v>
+      </c>
+      <c r="G80" s="29" t="s">
         <v>551</v>
       </c>
-      <c r="F80" s="4" t="s">
+      <c r="H80" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I80" s="4" t="s">
         <v>552</v>
       </c>
-      <c r="G80" s="29" t="s">
+      <c r="J80" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K80" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L80" s="4" t="s">
         <v>553</v>
-      </c>
-      <c r="H80" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="I80" s="4" t="s">
-        <v>554</v>
-      </c>
-      <c r="J80" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="K80" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L80" s="4" t="s">
-        <v>555</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B81" s="4" t="s">
+        <v>554</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="E81" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="F81" s="4" t="s">
+        <v>555</v>
+      </c>
+      <c r="G81" s="29" t="s">
         <v>556</v>
       </c>
-      <c r="C81" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="D81" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="E81" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="F81" s="4" t="s">
+      <c r="H81" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="I81" s="4" t="s">
         <v>557</v>
       </c>
-      <c r="G81" s="29" t="s">
-        <v>558</v>
-      </c>
-      <c r="H81" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="I81" s="4" t="s">
-        <v>559</v>
-      </c>
       <c r="J81" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="K81" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L81" s="4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B82" s="4" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E82" s="4" t="s">
+        <v>558</v>
+      </c>
+      <c r="F82" s="4" t="s">
+        <v>559</v>
+      </c>
+      <c r="G82" s="29" t="s">
         <v>560</v>
       </c>
-      <c r="F82" s="4" t="s">
+      <c r="H82" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I82" s="4" t="s">
         <v>561</v>
       </c>
-      <c r="G82" s="29" t="s">
-        <v>562</v>
-      </c>
-      <c r="H82" s="4" t="s">
+      <c r="J82" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K82" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L82" s="4" t="s">
         <v>236</v>
-      </c>
-      <c r="I82" s="4" t="s">
-        <v>563</v>
-      </c>
-      <c r="J82" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="K82" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L82" s="4" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B83" s="4" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="F83" s="4" t="s">
+        <v>562</v>
+      </c>
+      <c r="G83" s="29" t="s">
+        <v>563</v>
+      </c>
+      <c r="H83" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="I83" s="4" t="s">
         <v>564</v>
       </c>
-      <c r="G83" s="29" t="s">
-        <v>565</v>
-      </c>
-      <c r="H83" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="I83" s="4" t="s">
-        <v>566</v>
-      </c>
       <c r="J83" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="K83" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L83" s="4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B84" s="4" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="G84" s="4"/>
       <c r="H84" s="4" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="I84" s="4" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="J84" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="K84" s="4" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="L84" s="4" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B85" s="4" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="F85" s="4" t="s">
+        <v>569</v>
+      </c>
+      <c r="G85" s="29" t="s">
+        <v>570</v>
+      </c>
+      <c r="H85" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="I85" s="4" t="s">
         <v>571</v>
       </c>
-      <c r="G85" s="29" t="s">
+      <c r="J85" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K85" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L85" s="4" t="s">
         <v>572</v>
-      </c>
-      <c r="H85" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="I85" s="4" t="s">
-        <v>573</v>
-      </c>
-      <c r="J85" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="K85" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L85" s="4" t="s">
-        <v>574</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B86" s="4" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="C86" s="4" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E86" s="4" t="s">
+        <v>573</v>
+      </c>
+      <c r="F86" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="G86" s="29" t="s">
         <v>575</v>
       </c>
-      <c r="F86" s="4" t="s">
+      <c r="H86" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I86" s="4" t="s">
         <v>576</v>
       </c>
-      <c r="G86" s="29" t="s">
+      <c r="J86" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K86" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="L86" s="4" t="s">
         <v>577</v>
-      </c>
-      <c r="H86" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="I86" s="4" t="s">
-        <v>578</v>
-      </c>
-      <c r="J86" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="K86" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="L86" s="4" t="s">
-        <v>579</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B87" s="4" t="s">
+        <v>578</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="D87" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="E87" s="4" t="s">
+        <v>579</v>
+      </c>
+      <c r="F87" s="4" t="s">
         <v>580</v>
       </c>
-      <c r="C87" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="D87" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="E87" s="4" t="s">
+      <c r="G87" s="29" t="s">
         <v>581</v>
       </c>
-      <c r="F87" s="4" t="s">
+      <c r="H87" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I87" s="4" t="s">
         <v>582</v>
       </c>
-      <c r="G87" s="29" t="s">
-        <v>583</v>
-      </c>
-      <c r="H87" s="4" t="s">
+      <c r="J87" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K87" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L87" s="4" t="s">
         <v>236</v>
-      </c>
-      <c r="I87" s="4" t="s">
-        <v>584</v>
-      </c>
-      <c r="J87" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="K87" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L87" s="4" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B88" s="4" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="G88" s="4"/>
       <c r="H88" s="4" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="I88" s="4" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="J88" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="K88" s="4" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="L88" s="4" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B89" s="4" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E89" s="4" t="s">
+        <v>587</v>
+      </c>
+      <c r="F89" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="G89" s="29" t="s">
         <v>589</v>
       </c>
-      <c r="F89" s="4" t="s">
+      <c r="H89" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I89" s="4" t="s">
         <v>590</v>
       </c>
-      <c r="G89" s="29" t="s">
+      <c r="J89" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K89" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="L89" s="4" t="s">
         <v>591</v>
-      </c>
-      <c r="H89" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="I89" s="4" t="s">
-        <v>592</v>
-      </c>
-      <c r="J89" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="K89" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="L89" s="4" t="s">
-        <v>593</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B90" s="4" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E90" s="4" t="s">
+        <v>592</v>
+      </c>
+      <c r="F90" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="G90" s="29" t="s">
         <v>594</v>
       </c>
-      <c r="F90" s="4" t="s">
+      <c r="H90" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I90" s="4" t="s">
         <v>595</v>
       </c>
-      <c r="G90" s="29" t="s">
+      <c r="J90" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K90" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L90" s="4" t="s">
         <v>596</v>
-      </c>
-      <c r="H90" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="I90" s="4" t="s">
-        <v>597</v>
-      </c>
-      <c r="J90" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="K90" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L90" s="4" t="s">
-        <v>598</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B91" s="4" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E91" s="4" t="s">
+        <v>597</v>
+      </c>
+      <c r="F91" s="4" t="s">
+        <v>598</v>
+      </c>
+      <c r="G91" s="29" t="s">
         <v>599</v>
       </c>
-      <c r="F91" s="4" t="s">
+      <c r="H91" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I91" s="4" t="s">
         <v>600</v>
       </c>
-      <c r="G91" s="29" t="s">
+      <c r="J91" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K91" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L91" s="4" t="s">
         <v>601</v>
-      </c>
-      <c r="H91" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="I91" s="4" t="s">
-        <v>602</v>
-      </c>
-      <c r="J91" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="K91" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L91" s="4" t="s">
-        <v>603</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B92" s="4" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E92" s="4" t="s">
+        <v>602</v>
+      </c>
+      <c r="F92" s="4" t="s">
+        <v>574</v>
+      </c>
+      <c r="G92" s="29" t="s">
+        <v>603</v>
+      </c>
+      <c r="H92" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I92" s="4" t="s">
         <v>604</v>
       </c>
-      <c r="F92" s="4" t="s">
-        <v>576</v>
-      </c>
-      <c r="G92" s="29" t="s">
+      <c r="J92" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K92" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="L92" s="4" t="s">
         <v>605</v>
-      </c>
-      <c r="H92" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="I92" s="4" t="s">
-        <v>606</v>
-      </c>
-      <c r="J92" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="K92" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="L92" s="4" t="s">
-        <v>607</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B93" s="4" t="s">
+        <v>606</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>276</v>
+      </c>
+      <c r="D93" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="E93" s="4" t="s">
+        <v>607</v>
+      </c>
+      <c r="F93" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="G93" s="29" t="s">
         <v>608</v>
       </c>
-      <c r="C93" s="4" t="s">
-        <v>278</v>
-      </c>
-      <c r="D93" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="E93" s="4" t="s">
+      <c r="H93" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I93" s="4" t="s">
         <v>609</v>
       </c>
-      <c r="F93" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="G93" s="29" t="s">
-        <v>610</v>
-      </c>
-      <c r="H93" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="I93" s="4" t="s">
-        <v>611</v>
-      </c>
       <c r="J93" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="K93" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L93" s="4" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B94" s="4" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="F94" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="G94" s="29" t="s">
+        <v>611</v>
+      </c>
+      <c r="H94" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I94" s="4" t="s">
         <v>612</v>
       </c>
-      <c r="G94" s="29" t="s">
-        <v>613</v>
-      </c>
-      <c r="H94" s="4" t="s">
+      <c r="J94" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="K94" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L94" s="4" t="s">
         <v>236</v>
-      </c>
-      <c r="I94" s="4" t="s">
-        <v>614</v>
-      </c>
-      <c r="J94" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="K94" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L94" s="4" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B95" s="4" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E95" s="4" t="s">
+        <v>613</v>
+      </c>
+      <c r="F95" s="4" t="s">
+        <v>614</v>
+      </c>
+      <c r="G95" s="29" t="s">
         <v>615</v>
       </c>
-      <c r="F95" s="4" t="s">
+      <c r="H95" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="I95" s="4" t="s">
         <v>616</v>
       </c>
-      <c r="G95" s="29" t="s">
-        <v>617</v>
-      </c>
-      <c r="H95" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="I95" s="4" t="s">
-        <v>618</v>
-      </c>
       <c r="J95" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="K95" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L95" s="4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B96" s="4" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C96" s="4" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E96" s="4" t="s">
+        <v>617</v>
+      </c>
+      <c r="F96" s="4" t="s">
+        <v>618</v>
+      </c>
+      <c r="G96" s="29" t="s">
         <v>619</v>
       </c>
-      <c r="F96" s="4" t="s">
+      <c r="H96" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I96" s="4" t="s">
         <v>620</v>
       </c>
-      <c r="G96" s="29" t="s">
-        <v>621</v>
-      </c>
-      <c r="H96" s="4" t="s">
+      <c r="J96" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="K96" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L96" s="4" t="s">
         <v>236</v>
-      </c>
-      <c r="I96" s="4" t="s">
-        <v>622</v>
-      </c>
-      <c r="J96" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="K96" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L96" s="4" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B97" s="4" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C97" s="4" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E97" s="4" t="s">
+        <v>621</v>
+      </c>
+      <c r="F97" s="4" t="s">
+        <v>622</v>
+      </c>
+      <c r="G97" s="29" t="s">
         <v>623</v>
       </c>
-      <c r="F97" s="4" t="s">
+      <c r="H97" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I97" s="4" t="s">
         <v>624</v>
       </c>
-      <c r="G97" s="29" t="s">
-        <v>625</v>
-      </c>
-      <c r="H97" s="4" t="s">
+      <c r="J97" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="K97" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L97" s="4" t="s">
         <v>236</v>
-      </c>
-      <c r="I97" s="4" t="s">
-        <v>626</v>
-      </c>
-      <c r="J97" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="K97" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L97" s="4" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B98" s="4" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D98" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E98" s="4" t="s">
+        <v>625</v>
+      </c>
+      <c r="F98" s="4" t="s">
+        <v>626</v>
+      </c>
+      <c r="G98" s="29" t="s">
         <v>627</v>
       </c>
-      <c r="F98" s="4" t="s">
+      <c r="H98" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I98" s="4" t="s">
         <v>628</v>
       </c>
-      <c r="G98" s="29" t="s">
-        <v>629</v>
-      </c>
-      <c r="H98" s="4" t="s">
+      <c r="J98" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="K98" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L98" s="4" t="s">
         <v>236</v>
-      </c>
-      <c r="I98" s="4" t="s">
-        <v>630</v>
-      </c>
-      <c r="J98" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="K98" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L98" s="4" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B99" s="4" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="F99" s="4" t="s">
+        <v>629</v>
+      </c>
+      <c r="G99" s="29" t="s">
+        <v>630</v>
+      </c>
+      <c r="H99" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I99" s="4" t="s">
         <v>631</v>
       </c>
-      <c r="G99" s="29" t="s">
-        <v>632</v>
-      </c>
-      <c r="H99" s="4" t="s">
+      <c r="J99" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="K99" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L99" s="4" t="s">
         <v>236</v>
-      </c>
-      <c r="I99" s="4" t="s">
-        <v>633</v>
-      </c>
-      <c r="J99" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="K99" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L99" s="4" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B100" s="4" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="F100" s="4" t="s">
+        <v>632</v>
+      </c>
+      <c r="G100" s="29" t="s">
+        <v>633</v>
+      </c>
+      <c r="H100" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I100" s="4" t="s">
         <v>634</v>
       </c>
-      <c r="G100" s="29" t="s">
-        <v>635</v>
-      </c>
-      <c r="H100" s="4" t="s">
+      <c r="J100" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="K100" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L100" s="4" t="s">
         <v>236</v>
-      </c>
-      <c r="I100" s="4" t="s">
-        <v>636</v>
-      </c>
-      <c r="J100" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="K100" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L100" s="4" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B101" s="4" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="F101" s="4" t="s">
+        <v>635</v>
+      </c>
+      <c r="G101" s="29" t="s">
+        <v>636</v>
+      </c>
+      <c r="H101" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="I101" s="4" t="s">
         <v>637</v>
       </c>
-      <c r="G101" s="29" t="s">
+      <c r="J101" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="K101" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L101" s="4" t="s">
         <v>638</v>
-      </c>
-      <c r="H101" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="I101" s="4" t="s">
-        <v>639</v>
-      </c>
-      <c r="J101" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="K101" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L101" s="4" t="s">
-        <v>640</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B102" s="4" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C102" s="4" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="F102" s="4" t="s">
+        <v>639</v>
+      </c>
+      <c r="G102" s="29" t="s">
+        <v>640</v>
+      </c>
+      <c r="H102" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="I102" s="4" t="s">
         <v>641</v>
       </c>
-      <c r="G102" s="29" t="s">
-        <v>642</v>
-      </c>
-      <c r="H102" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="I102" s="4" t="s">
-        <v>643</v>
-      </c>
       <c r="J102" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="K102" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L102" s="4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B103" s="4" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C103" s="4" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E103" s="4" t="s">
+        <v>642</v>
+      </c>
+      <c r="F103" s="4" t="s">
+        <v>643</v>
+      </c>
+      <c r="G103" s="29" t="s">
         <v>644</v>
       </c>
-      <c r="F103" s="4" t="s">
+      <c r="H103" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="I103" s="4" t="s">
         <v>645</v>
       </c>
-      <c r="G103" s="29" t="s">
+      <c r="J103" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="K103" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L103" s="4" t="s">
         <v>646</v>
-      </c>
-      <c r="H103" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="I103" s="4" t="s">
-        <v>647</v>
-      </c>
-      <c r="J103" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="K103" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L103" s="4" t="s">
-        <v>648</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B104" s="4" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E104" s="4" t="s">
+        <v>647</v>
+      </c>
+      <c r="F104" s="4" t="s">
+        <v>648</v>
+      </c>
+      <c r="G104" s="29" t="s">
         <v>649</v>
       </c>
-      <c r="F104" s="4" t="s">
+      <c r="H104" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I104" s="4" t="s">
         <v>650</v>
       </c>
-      <c r="G104" s="29" t="s">
-        <v>651</v>
-      </c>
-      <c r="H104" s="4" t="s">
+      <c r="J104" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="K104" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L104" s="4" t="s">
         <v>236</v>
-      </c>
-      <c r="I104" s="4" t="s">
-        <v>652</v>
-      </c>
-      <c r="J104" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="K104" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L104" s="4" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B105" s="4" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C105" s="4" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="F105" s="4" t="s">
+        <v>651</v>
+      </c>
+      <c r="G105" s="29" t="s">
+        <v>652</v>
+      </c>
+      <c r="H105" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I105" s="4" t="s">
         <v>653</v>
       </c>
-      <c r="G105" s="29" t="s">
+      <c r="J105" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="K105" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L105" s="4" t="s">
         <v>654</v>
-      </c>
-      <c r="H105" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="I105" s="4" t="s">
-        <v>655</v>
-      </c>
-      <c r="J105" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="K105" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L105" s="4" t="s">
-        <v>656</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B106" s="4" t="s">
+        <v>655</v>
+      </c>
+      <c r="C106" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="D106" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="E106" s="4" t="s">
+        <v>656</v>
+      </c>
+      <c r="F106" s="4" t="s">
         <v>657</v>
       </c>
-      <c r="C106" s="4" t="s">
-        <v>286</v>
-      </c>
-      <c r="D106" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="E106" s="4" t="s">
+      <c r="G106" s="29" t="s">
         <v>658</v>
       </c>
-      <c r="F106" s="4" t="s">
+      <c r="H106" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="I106" s="4" t="s">
         <v>659</v>
       </c>
-      <c r="G106" s="29" t="s">
-        <v>660</v>
-      </c>
-      <c r="H106" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="I106" s="4" t="s">
-        <v>661</v>
-      </c>
       <c r="J106" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="K106" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L106" s="4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B107" s="4" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E107" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="F107" s="4" t="s">
+        <v>661</v>
+      </c>
+      <c r="G107" s="29" t="s">
         <v>662</v>
       </c>
-      <c r="F107" s="4" t="s">
+      <c r="H107" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I107" s="4" t="s">
         <v>663</v>
       </c>
-      <c r="G107" s="29" t="s">
+      <c r="J107" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="K107" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L107" s="4" t="s">
         <v>664</v>
-      </c>
-      <c r="H107" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="I107" s="4" t="s">
-        <v>665</v>
-      </c>
-      <c r="J107" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="K107" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L107" s="4" t="s">
-        <v>666</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B108" s="4" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E108" s="4" t="s">
+        <v>665</v>
+      </c>
+      <c r="F108" s="4" t="s">
+        <v>666</v>
+      </c>
+      <c r="G108" s="29" t="s">
         <v>667</v>
       </c>
-      <c r="F108" s="4" t="s">
+      <c r="H108" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I108" s="4" t="s">
         <v>668</v>
       </c>
-      <c r="G108" s="29" t="s">
-        <v>669</v>
-      </c>
-      <c r="H108" s="4" t="s">
+      <c r="J108" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="K108" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L108" s="4" t="s">
         <v>236</v>
-      </c>
-      <c r="I108" s="4" t="s">
-        <v>670</v>
-      </c>
-      <c r="J108" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="K108" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L108" s="4" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B109" s="4" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="F109" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="G109" s="29" t="s">
+        <v>670</v>
+      </c>
+      <c r="H109" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I109" s="4" t="s">
         <v>671</v>
       </c>
-      <c r="G109" s="29" t="s">
-        <v>672</v>
-      </c>
-      <c r="H109" s="4" t="s">
+      <c r="J109" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="K109" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L109" s="4" t="s">
         <v>236</v>
-      </c>
-      <c r="I109" s="4" t="s">
-        <v>673</v>
-      </c>
-      <c r="J109" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="K109" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L109" s="4" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B110" s="4" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E110" s="4" t="s">
+        <v>672</v>
+      </c>
+      <c r="F110" s="4" t="s">
+        <v>673</v>
+      </c>
+      <c r="G110" s="29" t="s">
         <v>674</v>
       </c>
-      <c r="F110" s="4" t="s">
+      <c r="H110" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I110" s="4" t="s">
         <v>675</v>
       </c>
-      <c r="G110" s="29" t="s">
-        <v>676</v>
-      </c>
-      <c r="H110" s="4" t="s">
+      <c r="J110" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="K110" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L110" s="4" t="s">
         <v>236</v>
-      </c>
-      <c r="I110" s="4" t="s">
-        <v>677</v>
-      </c>
-      <c r="J110" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="K110" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L110" s="4" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B111" s="4" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="F111" s="4" t="s">
+        <v>676</v>
+      </c>
+      <c r="G111" s="29" t="s">
+        <v>677</v>
+      </c>
+      <c r="H111" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="I111" s="4" t="s">
         <v>678</v>
       </c>
-      <c r="G111" s="29" t="s">
-        <v>679</v>
-      </c>
-      <c r="H111" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="I111" s="4" t="s">
-        <v>680</v>
-      </c>
       <c r="J111" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="K111" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L111" s="4" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B112" s="4" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C112" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="F112" s="4" t="s">
+        <v>679</v>
+      </c>
+      <c r="G112" s="29" t="s">
+        <v>680</v>
+      </c>
+      <c r="H112" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="I112" s="4" t="s">
         <v>681</v>
       </c>
-      <c r="G112" s="29" t="s">
-        <v>682</v>
-      </c>
-      <c r="H112" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="I112" s="4" t="s">
-        <v>683</v>
-      </c>
       <c r="J112" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="K112" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L112" s="4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B113" s="4" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C113" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="F113" s="4" t="s">
+        <v>682</v>
+      </c>
+      <c r="G113" s="29" t="s">
+        <v>683</v>
+      </c>
+      <c r="H113" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="I113" s="4" t="s">
         <v>684</v>
       </c>
-      <c r="G113" s="29" t="s">
-        <v>685</v>
-      </c>
-      <c r="H113" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="I113" s="4" t="s">
-        <v>686</v>
-      </c>
       <c r="J113" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="K113" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L113" s="4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B114" s="4" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C114" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="F114" s="4" t="s">
+        <v>685</v>
+      </c>
+      <c r="G114" s="29" t="s">
+        <v>686</v>
+      </c>
+      <c r="H114" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="I114" s="4" t="s">
         <v>687</v>
       </c>
-      <c r="G114" s="29" t="s">
-        <v>688</v>
-      </c>
-      <c r="H114" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="I114" s="4" t="s">
-        <v>689</v>
-      </c>
       <c r="J114" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="K114" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L114" s="4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B115" s="4" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="F115" s="4" t="s">
+        <v>688</v>
+      </c>
+      <c r="G115" s="29" t="s">
+        <v>689</v>
+      </c>
+      <c r="H115" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="I115" s="4" t="s">
         <v>690</v>
       </c>
-      <c r="G115" s="29" t="s">
-        <v>691</v>
-      </c>
-      <c r="H115" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="I115" s="4" t="s">
-        <v>692</v>
-      </c>
       <c r="J115" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="K115" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L115" s="4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B116" s="4" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C116" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E116" s="4" t="s">
+        <v>691</v>
+      </c>
+      <c r="F116" s="4" t="s">
+        <v>692</v>
+      </c>
+      <c r="G116" s="29" t="s">
         <v>693</v>
       </c>
-      <c r="F116" s="4" t="s">
+      <c r="H116" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="I116" s="4" t="s">
         <v>694</v>
       </c>
-      <c r="G116" s="29" t="s">
-        <v>695</v>
-      </c>
-      <c r="H116" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="I116" s="4" t="s">
-        <v>696</v>
-      </c>
       <c r="J116" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="K116" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L116" s="4" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B117" s="4" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E117" s="4" t="s">
+        <v>695</v>
+      </c>
+      <c r="F117" s="4" t="s">
+        <v>696</v>
+      </c>
+      <c r="G117" s="29" t="s">
         <v>697</v>
       </c>
-      <c r="F117" s="4" t="s">
+      <c r="H117" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I117" s="4" t="s">
         <v>698</v>
       </c>
-      <c r="G117" s="29" t="s">
+      <c r="J117" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="K117" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="L117" s="4" t="s">
         <v>699</v>
-      </c>
-      <c r="H117" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="I117" s="4" t="s">
-        <v>700</v>
-      </c>
-      <c r="J117" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="K117" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="L117" s="4" t="s">
-        <v>701</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B118" s="4" t="s">
+        <v>700</v>
+      </c>
+      <c r="C118" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="D118" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="E118" s="4" t="s">
+        <v>579</v>
+      </c>
+      <c r="F118" s="4" t="s">
+        <v>701</v>
+      </c>
+      <c r="G118" s="29" t="s">
         <v>702</v>
       </c>
-      <c r="C118" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="D118" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="E118" s="4" t="s">
-        <v>581</v>
-      </c>
-      <c r="F118" s="4" t="s">
+      <c r="H118" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I118" s="4" t="s">
         <v>703</v>
       </c>
-      <c r="G118" s="29" t="s">
-        <v>704</v>
-      </c>
-      <c r="H118" s="4" t="s">
+      <c r="J118" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K118" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L118" s="4" t="s">
         <v>236</v>
-      </c>
-      <c r="I118" s="4" t="s">
-        <v>705</v>
-      </c>
-      <c r="J118" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="K118" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L118" s="4" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B119" s="4" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="E119" s="4" t="s">
+        <v>704</v>
+      </c>
+      <c r="F119" s="4" t="s">
+        <v>705</v>
+      </c>
+      <c r="G119" s="29" t="s">
         <v>706</v>
       </c>
-      <c r="F119" s="4" t="s">
+      <c r="H119" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="I119" s="4" t="s">
         <v>707</v>
       </c>
-      <c r="G119" s="29" t="s">
-        <v>708</v>
-      </c>
-      <c r="H119" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="I119" s="4" t="s">
-        <v>709</v>
-      </c>
       <c r="J119" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="K119" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L119" s="4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B120" s="4" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="G120" s="4"/>
       <c r="H120" s="4" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="I120" s="4" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="J120" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="K120" s="4" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="L120" s="4" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B121" s="4" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="E121" s="4" t="s">
+        <v>712</v>
+      </c>
+      <c r="F121" s="4" t="s">
+        <v>712</v>
+      </c>
+      <c r="G121" s="29" t="s">
+        <v>713</v>
+      </c>
+      <c r="H121" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I121" s="4" t="s">
         <v>714</v>
       </c>
-      <c r="F121" s="4" t="s">
-        <v>714</v>
-      </c>
-      <c r="G121" s="29" t="s">
+      <c r="J121" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K121" s="4" t="s">
+        <v>355</v>
+      </c>
+      <c r="L121" s="4" t="s">
         <v>715</v>
-      </c>
-      <c r="H121" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="I121" s="4" t="s">
-        <v>716</v>
-      </c>
-      <c r="J121" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="K121" s="4" t="s">
-        <v>357</v>
-      </c>
-      <c r="L121" s="4" t="s">
-        <v>717</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="52.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B122" s="4" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="E122" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="F122" s="4" t="s">
+        <v>717</v>
+      </c>
+      <c r="G122" s="29" t="s">
         <v>718</v>
       </c>
-      <c r="F122" s="4" t="s">
+      <c r="H122" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="I122" s="4" t="s">
         <v>719</v>
       </c>
-      <c r="G122" s="29" t="s">
+      <c r="J122" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K122" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L122" s="4" t="s">
         <v>720</v>
-      </c>
-      <c r="H122" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="I122" s="4" t="s">
-        <v>721</v>
-      </c>
-      <c r="J122" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="K122" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L122" s="4" t="s">
-        <v>722</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B123" s="4" t="s">
+        <v>721</v>
+      </c>
+      <c r="C123" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="D123" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="E123" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="F123" s="4" t="s">
+        <v>722</v>
+      </c>
+      <c r="G123" s="29" t="s">
         <v>723</v>
       </c>
-      <c r="C123" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="D123" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="E123" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="F123" s="4" t="s">
+      <c r="H123" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="I123" s="4" t="s">
         <v>724</v>
       </c>
-      <c r="G123" s="29" t="s">
+      <c r="J123" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K123" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L123" s="4" t="s">
         <v>725</v>
-      </c>
-      <c r="H123" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="I123" s="4" t="s">
-        <v>726</v>
-      </c>
-      <c r="J123" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="K123" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L123" s="4" t="s">
-        <v>727</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B124" s="4" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="C124" s="4" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E124" s="4" t="s">
+        <v>726</v>
+      </c>
+      <c r="F124" s="4" t="s">
+        <v>727</v>
+      </c>
+      <c r="G124" s="29" t="s">
         <v>728</v>
       </c>
-      <c r="F124" s="4" t="s">
+      <c r="H124" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I124" s="4" t="s">
         <v>729</v>
       </c>
-      <c r="G124" s="29" t="s">
-        <v>730</v>
-      </c>
-      <c r="H124" s="4" t="s">
+      <c r="J124" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K124" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L124" s="4" t="s">
         <v>236</v>
-      </c>
-      <c r="I124" s="4" t="s">
-        <v>731</v>
-      </c>
-      <c r="J124" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="K124" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L124" s="4" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B125" s="4" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F125" s="4" t="s">
+        <v>730</v>
+      </c>
+      <c r="G125" s="29" t="s">
+        <v>731</v>
+      </c>
+      <c r="H125" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="I125" s="4" t="s">
         <v>732</v>
       </c>
-      <c r="G125" s="29" t="s">
-        <v>733</v>
-      </c>
-      <c r="H125" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="I125" s="4" t="s">
-        <v>734</v>
-      </c>
       <c r="J125" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="K125" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L125" s="4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B126" s="4" t="s">
+        <v>733</v>
+      </c>
+      <c r="C126" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="D126" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="E126" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="F126" s="4" t="s">
+        <v>734</v>
+      </c>
+      <c r="G126" s="29" t="s">
         <v>735</v>
       </c>
-      <c r="C126" s="4" t="s">
-        <v>222</v>
-      </c>
-      <c r="D126" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="E126" s="4" t="s">
-        <v>239</v>
-      </c>
-      <c r="F126" s="4" t="s">
+      <c r="H126" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="I126" s="4" t="s">
         <v>736</v>
       </c>
-      <c r="G126" s="29" t="s">
-        <v>737</v>
-      </c>
-      <c r="H126" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="I126" s="4" t="s">
-        <v>738</v>
-      </c>
       <c r="J126" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="K126" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L126" s="4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B127" s="4" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="C127" s="4" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E127" s="4" t="s">
+        <v>737</v>
+      </c>
+      <c r="F127" s="4" t="s">
+        <v>738</v>
+      </c>
+      <c r="G127" s="29" t="s">
         <v>739</v>
       </c>
-      <c r="F127" s="4" t="s">
+      <c r="H127" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I127" s="4" t="s">
         <v>740</v>
       </c>
-      <c r="G127" s="29" t="s">
-        <v>741</v>
-      </c>
-      <c r="H127" s="4" t="s">
+      <c r="J127" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K127" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L127" s="4" t="s">
         <v>236</v>
-      </c>
-      <c r="I127" s="4" t="s">
-        <v>742</v>
-      </c>
-      <c r="J127" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="K127" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L127" s="4" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B128" s="4" t="s">
+        <v>741</v>
+      </c>
+      <c r="C128" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="D128" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="E128" s="4" t="s">
+        <v>579</v>
+      </c>
+      <c r="F128" s="4" t="s">
+        <v>742</v>
+      </c>
+      <c r="G128" s="29" t="s">
         <v>743</v>
       </c>
-      <c r="C128" s="4" t="s">
-        <v>243</v>
-      </c>
-      <c r="D128" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="E128" s="4" t="s">
-        <v>581</v>
-      </c>
-      <c r="F128" s="4" t="s">
+      <c r="H128" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="I128" s="4" t="s">
         <v>744</v>
       </c>
-      <c r="G128" s="29" t="s">
-        <v>745</v>
-      </c>
-      <c r="H128" s="4" t="s">
+      <c r="J128" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="K128" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="L128" s="4" t="s">
         <v>236</v>
-      </c>
-      <c r="I128" s="4" t="s">
-        <v>746</v>
-      </c>
-      <c r="J128" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="K128" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="L128" s="4" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B129" s="4" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="C129" s="4" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="F129" s="4" t="s">
+        <v>745</v>
+      </c>
+      <c r="G129" s="29" t="s">
+        <v>746</v>
+      </c>
+      <c r="H129" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="I129" s="4" t="s">
         <v>747</v>
       </c>
-      <c r="G129" s="29" t="s">
-        <v>748</v>
-      </c>
-      <c r="H129" s="4" t="s">
-        <v>226</v>
-      </c>
-      <c r="I129" s="4" t="s">
-        <v>749</v>
-      </c>
       <c r="J129" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="K129" s="4" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="L129" s="4" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B130" s="4" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="C130" s="4" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="G130" s="4"/>
       <c r="H130" s="4" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="I130" s="4" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="J130" s="4" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="K130" s="4" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="L130" s="4" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
     </row>
   </sheetData>

--- a/docs/RALK_Preise_Plaene_Vertrieb.xlsx
+++ b/docs/RALK_Preise_Plaene_Vertrieb.xlsx
@@ -880,7 +880,7 @@
           <t>So liest du die Datei</t>
         </is>
       </c>
-      <c r="C5" s="35" t="n"/>
+      <c r="C5" s="59" t="n"/>
     </row>
     <row r="6" ht="15" customHeight="1" s="31">
       <c r="B6" s="36" t="inlineStr">
@@ -888,7 +888,7 @@
           <t>Gelbe Zellen, blaue Schrift</t>
         </is>
       </c>
-      <c r="C6" s="35" t="inlineStr">
+      <c r="C6" s="59" t="inlineStr">
         <is>
           <t>Eingaben/Annahmen – diese Zahlen darfst du ändern, alles andere rechnet sich neu.</t>
         </is>
@@ -900,7 +900,7 @@
           <t>Schwarze Schrift</t>
         </is>
       </c>
-      <c r="C7" s="35" t="inlineStr">
+      <c r="C7" s="59" t="inlineStr">
         <is>
           <t>Formeln – nicht überschreiben.</t>
         </is>
@@ -912,7 +912,7 @@
           <t>Grüne Schrift</t>
         </is>
       </c>
-      <c r="C8" s="35" t="inlineStr">
+      <c r="C8" s="59" t="inlineStr">
         <is>
           <t>Wert kommt aus einem anderen Blatt (meist „Preise &amp; Pläne“).</t>
         </is>
@@ -920,7 +920,7 @@
     </row>
     <row r="9" ht="15" customHeight="1" s="31">
       <c r="B9" s="34" t="n"/>
-      <c r="C9" s="35" t="n"/>
+      <c r="C9" s="59" t="n"/>
     </row>
     <row r="10" ht="15" customHeight="1" s="31">
       <c r="B10" s="34" t="inlineStr">
@@ -928,7 +928,7 @@
           <t>Blätter</t>
         </is>
       </c>
-      <c r="C10" s="35" t="n"/>
+      <c r="C10" s="59" t="n"/>
     </row>
     <row r="11" ht="26.85" customHeight="1" s="31">
       <c r="B11" s="36" t="inlineStr">
@@ -936,7 +936,7 @@
           <t>Preise &amp; Pläne</t>
         </is>
       </c>
-      <c r="C11" s="35" t="inlineStr">
+      <c r="C11" s="59" t="inlineStr">
         <is>
           <t>Preisstaffel, Mindestlizenz, Quellensteuer-Hinweis (DE/EN/FR), Preisrechner, Beispiele, Leistungsumfang.</t>
         </is>
@@ -948,7 +948,7 @@
           <t>Mit Anwalts-Funnel</t>
         </is>
       </c>
-      <c r="C12" s="35" t="inlineStr">
+      <c r="C12" s="59" t="inlineStr">
         <is>
           <t>5-Jahres-Rechnung, wenn Kunden über Partner-Anwälte kommen (Provision 10 % / 5 %).</t>
         </is>
@@ -960,7 +960,7 @@
           <t>Ohne Anwalt (Direkt)</t>
         </is>
       </c>
-      <c r="C13" s="35" t="inlineStr">
+      <c r="C13" s="59" t="inlineStr">
         <is>
           <t>5-Jahres-Rechnung, wenn du Kunden selbst gewinnst (Register-Ansprache, Anzeigen, Quick-Check) – ohne Provision, aber mit Werbekosten.</t>
         </is>
@@ -972,7 +972,7 @@
           <t>Vergleich</t>
         </is>
       </c>
-      <c r="C14" s="35" t="inlineStr">
+      <c r="C14" s="59" t="inlineStr">
         <is>
           <t>Beide Wege nebeneinander und kombiniert.</t>
         </is>
@@ -984,7 +984,7 @@
           <t>Zielkunden – Register</t>
         </is>
       </c>
-      <c r="C15" s="35" t="inlineStr">
+      <c r="C15" s="59" t="inlineStr">
         <is>
           <t>Öffentliche Seiten/Listen von Aufsichtsbehörden, Verbänden und Kammern, auf denen deine Zielkunden stehen – Grundlage für Kontaktlisten.</t>
         </is>
@@ -992,7 +992,7 @@
     </row>
     <row r="16" ht="15" customHeight="1" s="31">
       <c r="B16" s="34" t="n"/>
-      <c r="C16" s="35" t="n"/>
+      <c r="C16" s="59" t="n"/>
     </row>
     <row r="17" ht="15" customHeight="1" s="31">
       <c r="B17" s="34" t="inlineStr">
@@ -1000,7 +1000,7 @@
           <t>Quellen</t>
         </is>
       </c>
-      <c r="C17" s="35" t="n"/>
+      <c r="C17" s="59" t="n"/>
     </row>
     <row r="18" ht="39.55" customHeight="1" s="31">
       <c r="B18" s="36" t="inlineStr">
@@ -1008,7 +1008,7 @@
           <t>Preise</t>
         </is>
       </c>
-      <c r="C18" s="35" t="inlineStr">
+      <c r="C18" s="59" t="inlineStr">
         <is>
           <t>Neue Staffel (Okt. 2026, nach Marktvergleich): bis 1.000 MA 65 $, 1.001–10.000 MA 55 $, über 10.000 MA 45 $. Mindest-Jahreslizenz 5.000 $, keine Setup-Fee. Vorher (RALK_Preismodell): ≤4.000 65 $, 4.001–7.999 50 $, ≥8.000 45 $.</t>
         </is>
@@ -1020,7 +1020,7 @@
           <t>Funnel-Zahlen</t>
         </is>
       </c>
-      <c r="C19" s="35" t="inlineStr">
+      <c r="C19" s="59" t="inlineStr">
         <is>
           <t>Aus derselben Datei (Blätter „Anwalts-Funnel“, „Realistisch“, „Kosten &amp; Marge“): 313 kontaktierte Kanzleien, 6 Bounces, 10 % Antwortquote, 30 % Konversion, 85 % Verlängerung, Provision 10 %/5 %, Fixkosten 5.640,12 €/Jahr.</t>
         </is>
@@ -1032,7 +1032,7 @@
           <t>Korrekturen ggü. alter Datei</t>
         </is>
       </c>
-      <c r="C20" s="35" t="inlineStr">
+      <c r="C20" s="59" t="inlineStr">
         <is>
           <t>1) Antworten = Zugestellt × Antwortquote (alte Datei zeigte −1.878). 2) Einheitlich USD statt €/$ gemischt; € nur über den Wechselkurs. 3) Kein Ø-Preis von 35 € mehr – jeder Vertrag wird mit der echten Staffel gerechnet.</t>
         </is>
@@ -1044,7 +1044,7 @@
           <t>Preisstaffel</t>
         </is>
       </c>
-      <c r="C21" s="35" t="inlineStr">
+      <c r="C21" s="59" t="inlineStr">
         <is>
           <t>Der Satz gilt für alle Mitarbeitenden des Kunden. Übergangsregel: Wer in eine günstigere Klasse rutscht, zahlt nie weniger als die größte Organisation der Klasse darunter – kein Preissprung nach unten.</t>
         </is>
@@ -1056,7 +1056,7 @@
           <t>Preispolitik</t>
         </is>
       </c>
-      <c r="C22" s="35" t="inlineStr">
+      <c r="C22" s="59" t="inlineStr">
         <is>
           <t>Feste, veröffentlichte Preisliste wie bei Google Workspace, Microsoft 365, Atlassian und KnowBe4: gleicher Preis für alle, Mengenrabatt steckt in den Klassen, keine Einzelrabatte. Siehe Blatt „Marktvergleich“.</t>
         </is>
@@ -1134,132 +1134,132 @@
       </c>
     </row>
     <row r="6" ht="45.75" customHeight="1" s="31">
-      <c r="B6" s="35" t="inlineStr">
+      <c r="B6" s="59" t="inlineStr">
         <is>
           <t>Google Workspace</t>
         </is>
       </c>
-      <c r="C6" s="35" t="inlineStr">
+      <c r="C6" s="59" t="inlineStr">
         <is>
           <t>Pläne nach Funktionsumfang, gleicher Preis pro Nutzer für alle; Jahresvertrag günstiger als monatlich; Enterprise auf Anfrage</t>
         </is>
       </c>
-      <c r="D6" s="35" t="inlineStr">
+      <c r="D6" s="59" t="inlineStr">
         <is>
           <t>ca. 84–264 $ (7–22 $/Monat)</t>
         </is>
       </c>
-      <c r="E6" s="35" t="inlineStr">
+      <c r="E6" s="59" t="inlineStr">
         <is>
           <t>Ein öffentlicher Preis für alle, keine Verhandlung</t>
         </is>
       </c>
     </row>
     <row r="7" ht="45.75" customHeight="1" s="31">
-      <c r="B7" s="35" t="inlineStr">
+      <c r="B7" s="59" t="inlineStr">
         <is>
           <t>Microsoft 365</t>
         </is>
       </c>
-      <c r="C7" s="35" t="inlineStr">
+      <c r="C7" s="59" t="inlineStr">
         <is>
           <t>Business-Pläne für kleinere Firmen, Enterprise-Pläne (E3/E5) für große; Preis pro Nutzer, Jahresbindung</t>
         </is>
       </c>
-      <c r="D7" s="35" t="inlineStr">
+      <c r="D7" s="59" t="inlineStr">
         <is>
           <t>ca. 84–720 $ (7–60 $/Monat)</t>
         </is>
       </c>
-      <c r="E7" s="35" t="inlineStr">
+      <c r="E7" s="59" t="inlineStr">
         <is>
           <t>Feste Preisliste; Preiserhöhungen mit Vorankündigung</t>
         </is>
       </c>
     </row>
     <row r="8" ht="45.75" customHeight="1" s="31">
-      <c r="B8" s="35" t="inlineStr">
+      <c r="B8" s="59" t="inlineStr">
         <is>
           <t>Atlassian (Jira)</t>
         </is>
       </c>
-      <c r="C8" s="35" t="inlineStr">
+      <c r="C8" s="59" t="inlineStr">
         <is>
           <t>Jahresabos in festen Nutzerstufen; jede Nutzerzahl innerhalb einer Stufe zahlt gleich viel</t>
         </is>
       </c>
-      <c r="D8" s="35" t="inlineStr">
+      <c r="D8" s="59" t="inlineStr">
         <is>
           <t>stufenabhängig</t>
         </is>
       </c>
-      <c r="E8" s="35" t="inlineStr">
+      <c r="E8" s="59" t="inlineStr">
         <is>
           <t>Übergangsregel an den Klassengrenzen statt Preissprung</t>
         </is>
       </c>
     </row>
     <row r="9" ht="45.75" customHeight="1" s="31">
-      <c r="B9" s="35" t="inlineStr">
+      <c r="B9" s="59" t="inlineStr">
         <is>
           <t>KnowBe4 (Security-Awareness)</t>
         </is>
       </c>
-      <c r="C9" s="35" t="inlineStr">
+      <c r="C9" s="59" t="inlineStr">
         <is>
           <t>Staffelpreis pro Platz nach Mengenband, günstiger bei längerer Laufzeit; ab 1.001 Plätzen Angebot</t>
         </is>
       </c>
-      <c r="D9" s="35" t="inlineStr">
+      <c r="D9" s="59" t="inlineStr">
         <is>
           <t>ca. 20–45 $ (Liste, 3-Jahres-Vertrag)</t>
         </is>
       </c>
-      <c r="E9" s="35" t="inlineStr">
+      <c r="E9" s="59" t="inlineStr">
         <is>
           <t>Mengenrabatt über Größenklassen</t>
         </is>
       </c>
     </row>
     <row r="10" ht="45.75" customHeight="1" s="31">
-      <c r="B10" s="35" t="inlineStr">
+      <c r="B10" s="59" t="inlineStr">
         <is>
           <t>AML-/Compliance-E-Learning (UK u. a.)</t>
         </is>
       </c>
-      <c r="C10" s="35" t="inlineStr">
+      <c r="C10" s="59" t="inlineStr">
         <is>
           <t>Pro Kurs oder pro Nutzer, Mengenstaffel; große Anbieter (NAVEX, LRN, Thomson Reuters) nur auf Anfrage</t>
         </is>
       </c>
-      <c r="D10" s="35" t="inlineStr">
+      <c r="D10" s="59" t="inlineStr">
         <is>
           <t>ca. 8–13 $ pro Kurs bzw. 60–200 $ pro Plattform-Nutzer</t>
         </is>
       </c>
-      <c r="E10" s="35" t="inlineStr">
-        <is>
-          <t>RALK liegt mit 45–65 $ im Mittelfeld – für alle 13 Module</t>
+      <c r="E10" s="59" t="inlineStr">
+        <is>
+          <t>RALK liegt mit 45–65 $ im Mittelfeld – für alle 9 Module</t>
         </is>
       </c>
     </row>
     <row r="11" ht="45.75" customHeight="1" s="31">
-      <c r="B11" s="35" t="inlineStr">
+      <c r="B11" s="59" t="inlineStr">
         <is>
           <t>Klassische Präsenzschulung (dein Modell)</t>
         </is>
       </c>
-      <c r="C11" s="35" t="inlineStr">
+      <c r="C11" s="59" t="inlineStr">
         <is>
           <t>Einmalig pro Person</t>
         </is>
       </c>
-      <c r="D11" s="35" t="inlineStr">
+      <c r="D11" s="59" t="inlineStr">
         <is>
           <t>ca. 462 $ für 5 Tage</t>
         </is>
       </c>
-      <c r="E11" s="35" t="inlineStr">
+      <c r="E11" s="59" t="inlineStr">
         <is>
           <t>RALK: dauerhaft, nachweisbar, Bruchteil der Kosten</t>
         </is>
@@ -2044,7 +2044,7 @@
       </c>
     </row>
     <row r="49" ht="43.5" customHeight="1" s="31">
-      <c r="B49" s="35" t="inlineStr">
+      <c r="B49" s="59" t="inlineStr">
         <is>
           <t>Übergangsregel (wie bei Atlassian-Stufen): Wer in eine günstigere Klasse rutscht, zahlt nie weniger als die größte Organisation der Klasse darunter (Spalte „Lizenz an der Obergrenze“). Beispiel: 1.001–1.181 MA zahlen 65.000 $ wie 1.000 MA, danach gilt 55 $; 10.001–12.222 MA zahlen 550.000 $ wie 10.000 MA, danach 45 $. So gibt es keinen Preissprung nach unten.</t>
         </is>
@@ -2067,7 +2067,7 @@
     <row r="53" ht="15" customHeight="1" s="31">
       <c r="B53" s="36" t="inlineStr">
         <is>
-          <t>• Alle 13 Module (Sanktionen, AML/KYC, UBO, PEP, Monitoring/STR, Krypto, Betrug, Korruption, Datenschutz, Cyber, KI, Governance, Whistleblowing)</t>
+          <t>• Alle 9 Module (Betrug, Korruption, Sanktionen &amp; Embargo, AML/CFT mit KYC &amp; PEP, Datenschutz, Cybersicherheit, KI &amp; Finanzkriminalität, Krypto &amp; virtuelle Assets, Whistleblower-Schutz)</t>
         </is>
       </c>
     </row>
@@ -3701,7 +3701,7 @@
       </c>
     </row>
     <row r="17" ht="48" customHeight="1" s="31">
-      <c r="B17" s="35" t="inlineStr">
+      <c r="B17" s="59" t="inlineStr">
         <is>
           <t>Lies es so: Anwälte bringen größere Kunden und kosten Provision; der Direktweg kostet Werbebudget und Zeit. Beides zusammen ist am stärksten. Der größte Hebel bleiben Verbände/Behörden (z. B. Law Society of Kenya, 30.000 × 45 $) – die stehen als Einzelfälle in deiner alten Datei.</t>
         </is>
@@ -3812,7105 +3812,7105 @@
       </c>
     </row>
     <row r="6" ht="39.55" customHeight="1" s="31">
-      <c r="B6" s="35" t="inlineStr">
+      <c r="B6" s="59" t="inlineStr">
         <is>
           <t>Regional</t>
         </is>
       </c>
-      <c r="C6" s="35" t="inlineStr">
+      <c r="C6" s="59" t="inlineStr">
         <is>
           <t>BCEAO</t>
         </is>
       </c>
-      <c r="D6" s="35" t="inlineStr">
+      <c r="D6" s="59" t="inlineStr">
         <is>
           <t>Banks</t>
         </is>
       </c>
-      <c r="E6" s="35" t="inlineStr">
+      <c r="E6" s="59" t="inlineStr">
         <is>
           <t>BCEAO</t>
         </is>
       </c>
-      <c r="F6" s="35" t="inlineStr">
+      <c r="F6" s="59" t="inlineStr">
         <is>
           <t>Liste des établissements de crédit agréés dans l'UMOA au 31 décembre 2025</t>
         </is>
       </c>
-      <c r="G6" s="58" t="inlineStr">
+      <c r="G6" s="60" t="inlineStr">
         <is>
           <t>https://www.bceao.int/sites/default/files/2026-04/LISTE%20DES%20%C3%89TABLISSEMENTS%20DE%20CR%C3%89DIT%20AGR%C3%89%C3%89S%20DANS%20L'UMOA%20au%2031%20d%C3%A9cembre%202025.pdf</t>
         </is>
       </c>
-      <c r="H6" s="35" t="inlineStr">
+      <c r="H6" s="59" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="I6" s="35" t="inlineStr">
+      <c r="I6" s="59" t="inlineStr">
         <is>
           <t>161 credit institutions (136 banks + 25 financial institutions) by country with licence codes; CI 33, Senegal 33, Mali 17, Togo 17</t>
         </is>
       </c>
-      <c r="J6" s="35" t="inlineStr">
+      <c r="J6" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K6" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L6" s="35" t="inlineStr">
+      <c r="K6" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L6" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox). Published April 2026. No contact details.</t>
         </is>
       </c>
     </row>
     <row r="7" ht="52.2" customHeight="1" s="31">
-      <c r="B7" s="35" t="inlineStr">
+      <c r="B7" s="59" t="inlineStr">
         <is>
           <t>Regional</t>
         </is>
       </c>
-      <c r="C7" s="35" t="inlineStr">
+      <c r="C7" s="59" t="inlineStr">
         <is>
           <t>BCEAO</t>
         </is>
       </c>
-      <c r="D7" s="35" t="inlineStr">
+      <c r="D7" s="59" t="inlineStr">
         <is>
           <t>Banks</t>
         </is>
       </c>
-      <c r="E7" s="35" t="inlineStr">
+      <c r="E7" s="59" t="inlineStr">
         <is>
           <t>BCEAO</t>
         </is>
       </c>
-      <c r="F7" s="35" t="inlineStr">
+      <c r="F7" s="59" t="inlineStr">
         <is>
           <t>Annuaire des banques, établissements financiers à caractère bancaire et compagnies financières de l'UMOA 2024 (mars 2026)</t>
         </is>
       </c>
-      <c r="G7" s="58" t="inlineStr">
+      <c r="G7" s="60" t="inlineStr">
         <is>
           <t>https://www.bceao.int/sites/default/files/2026-04/Annuaire-des-Banques-etablissements-financiers-a-caractere-bancaire-et-compagnies-financieres-de-l-UMOA-2024_mars_2026.pdf</t>
         </is>
       </c>
-      <c r="H7" s="35" t="inlineStr">
+      <c r="H7" s="59" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="I7" s="35" t="inlineStr">
+      <c r="I7" s="59" t="inlineStr">
         <is>
           <t>Directory of all UMOA banks with addresses, phone, management, shareholders, branch counts</t>
         </is>
       </c>
-      <c r="J7" s="35" t="inlineStr">
+      <c r="J7" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K7" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L7" s="35" t="inlineStr">
+      <c r="K7" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L7" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox). Best source for contact details/CEO names.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="26.85" customHeight="1" s="31">
-      <c r="B8" s="35" t="inlineStr">
+      <c r="B8" s="59" t="inlineStr">
         <is>
           <t>Regional</t>
         </is>
       </c>
-      <c r="C8" s="35" t="inlineStr">
+      <c r="C8" s="59" t="inlineStr">
         <is>
           <t>BCEAO</t>
         </is>
       </c>
-      <c r="D8" s="35" t="inlineStr">
+      <c r="D8" s="59" t="inlineStr">
         <is>
           <t>Banks</t>
         </is>
       </c>
-      <c r="E8" s="35" t="inlineStr">
+      <c r="E8" s="59" t="inlineStr">
         <is>
           <t>BCEAO</t>
         </is>
       </c>
-      <c r="F8" s="35" t="inlineStr">
+      <c r="F8" s="59" t="inlineStr">
         <is>
           <t>Paysage bancaire de l'UMOA</t>
         </is>
       </c>
-      <c r="G8" s="58" t="inlineStr">
+      <c r="G8" s="60" t="inlineStr">
         <is>
           <t>https://www.bceao.int/fr/content/paysage-bancaire</t>
         </is>
       </c>
-      <c r="H8" s="35" t="inlineStr">
+      <c r="H8" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I8" s="35" t="inlineStr">
+      <c r="I8" s="59" t="inlineStr">
         <is>
           <t>Country-by-country banking landscape</t>
         </is>
       </c>
-      <c r="J8" s="35" t="inlineStr">
+      <c r="J8" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K8" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L8" s="35" t="inlineStr">
+      <c r="K8" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L8" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox).</t>
         </is>
       </c>
     </row>
     <row r="9" ht="26.85" customHeight="1" s="31">
-      <c r="B9" s="35" t="inlineStr">
+      <c r="B9" s="59" t="inlineStr">
         <is>
           <t>Regional</t>
         </is>
       </c>
-      <c r="C9" s="35" t="inlineStr">
+      <c r="C9" s="59" t="inlineStr">
         <is>
           <t>BCEAO</t>
         </is>
       </c>
-      <c r="D9" s="35" t="inlineStr">
+      <c r="D9" s="59" t="inlineStr">
         <is>
           <t>Banks</t>
         </is>
       </c>
-      <c r="E9" s="35" t="inlineStr">
+      <c r="E9" s="59" t="inlineStr">
         <is>
           <t>Commission Bancaire de l'UMOA</t>
         </is>
       </c>
-      <c r="F9" s="35" t="inlineStr">
+      <c r="F9" s="59" t="inlineStr">
         <is>
           <t>Établissements assujettis au contrôle de la Commission Bancaire de l'UMOA</t>
         </is>
       </c>
-      <c r="G9" s="58" t="inlineStr">
+      <c r="G9" s="60" t="inlineStr">
         <is>
           <t>https://cb-umoa.org/en/institutions-regulated-wamu-banking-commission</t>
         </is>
       </c>
-      <c r="H9" s="35" t="inlineStr">
+      <c r="H9" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I9" s="35" t="inlineStr">
+      <c r="I9" s="59" t="inlineStr">
         <is>
           <t>Hub with per-country PDF lists (banks, FIs, EMEs, EPs) for all 8 UMOA states</t>
         </is>
       </c>
-      <c r="J9" s="35" t="inlineStr">
+      <c r="J9" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K9" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L9" s="35" t="inlineStr">
+      <c r="K9" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L9" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox).</t>
         </is>
       </c>
     </row>
     <row r="10" ht="52.2" customHeight="1" s="31">
-      <c r="B10" s="35" t="inlineStr">
+      <c r="B10" s="59" t="inlineStr">
         <is>
           <t>Regional</t>
         </is>
       </c>
-      <c r="C10" s="35" t="inlineStr">
+      <c r="C10" s="59" t="inlineStr">
         <is>
           <t>COBAC/BEAC</t>
         </is>
       </c>
-      <c r="D10" s="35" t="inlineStr">
+      <c r="D10" s="59" t="inlineStr">
         <is>
           <t>Banks</t>
         </is>
       </c>
-      <c r="E10" s="35" t="inlineStr">
+      <c r="E10" s="59" t="inlineStr">
         <is>
           <t>COBAC (Commission Bancaire de l'Afrique Centrale)</t>
         </is>
       </c>
-      <c r="F10" s="35" t="inlineStr">
+      <c r="F10" s="59" t="inlineStr">
         <is>
           <t>COBAC - Assujettis (annuaire des établissements)</t>
         </is>
       </c>
-      <c r="G10" s="58" t="inlineStr">
+      <c r="G10" s="60" t="inlineStr">
         <is>
           <t>http://www.sgcobac.org/jcms/ess_7505/en/organes-faitiers?opLetterSearch=true&amp;directoryLetter=B&amp;memberId=&amp;directory_start=20&amp;directory_pageSize=50</t>
         </is>
       </c>
-      <c r="H10" s="35" t="inlineStr">
+      <c r="H10" s="59" t="inlineStr">
         <is>
           <t>Search tool</t>
         </is>
       </c>
-      <c r="I10" s="35" t="inlineStr">
+      <c r="I10" s="59" t="inlineStr">
         <is>
           <t>A-Z directory of supervised credit institutions in CEMAC (Cameroon, Gabon, Congo...) with per-bank pages</t>
         </is>
       </c>
-      <c r="J10" s="35" t="inlineStr">
+      <c r="J10" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K10" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L10" s="35" t="inlineStr">
+      <c r="K10" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L10" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox). Last consolidated list seen is 30 Sept 2020; HTTP only.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="26.85" customHeight="1" s="31">
-      <c r="B11" s="35" t="inlineStr">
+      <c r="B11" s="59" t="inlineStr">
         <is>
           <t>Regional</t>
         </is>
       </c>
-      <c r="C11" s="35" t="inlineStr">
+      <c r="C11" s="59" t="inlineStr">
         <is>
           <t>COBAC/BEAC</t>
         </is>
       </c>
-      <c r="D11" s="35" t="inlineStr">
+      <c r="D11" s="59" t="inlineStr">
         <is>
           <t>Banks</t>
         </is>
       </c>
-      <c r="E11" s="35" t="inlineStr">
+      <c r="E11" s="59" t="inlineStr">
         <is>
           <t>BEAC</t>
         </is>
       </c>
-      <c r="F11" s="35" t="inlineStr">
+      <c r="F11" s="59" t="inlineStr">
         <is>
           <t>Lexique des Banques de la CEMAC</t>
         </is>
       </c>
-      <c r="G11" s="58" t="inlineStr">
+      <c r="G11" s="60" t="inlineStr">
         <is>
           <t>https://www.beac.int/supervision-bancaire/lexique-banques-de-cemac/</t>
         </is>
       </c>
-      <c r="H11" s="35" t="inlineStr">
+      <c r="H11" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I11" s="35" t="inlineStr">
+      <c r="I11" s="59" t="inlineStr">
         <is>
           <t>Glossary/list of CEMAC banks by country</t>
         </is>
       </c>
-      <c r="J11" s="35" t="inlineStr">
+      <c r="J11" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K11" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L11" s="35" t="inlineStr">
+      <c r="K11" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L11" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox).</t>
         </is>
       </c>
     </row>
     <row r="12" ht="39.55" customHeight="1" s="31">
-      <c r="B12" s="35" t="inlineStr">
+      <c r="B12" s="59" t="inlineStr">
         <is>
           <t>Regional</t>
         </is>
       </c>
-      <c r="C12" s="35" t="inlineStr">
+      <c r="C12" s="59" t="inlineStr">
         <is>
           <t>BCEAO</t>
         </is>
       </c>
-      <c r="D12" s="35" t="inlineStr">
+      <c r="D12" s="59" t="inlineStr">
         <is>
           <t>Capital markets</t>
         </is>
       </c>
-      <c r="E12" s="35" t="inlineStr">
+      <c r="E12" s="59" t="inlineStr">
         <is>
           <t>AMF-UMOA (Autorité des Marchés Financiers de l'UMOA)</t>
         </is>
       </c>
-      <c r="F12" s="35" t="inlineStr">
+      <c r="F12" s="59" t="inlineStr">
         <is>
           <t>Liste des intervenants agréés du Marché Financier Régional de l'UMOA</t>
         </is>
       </c>
-      <c r="G12" s="58" t="inlineStr">
+      <c r="G12" s="60" t="inlineStr">
         <is>
           <t>https://www.amf-umoa.org/accueil/intervenant</t>
         </is>
       </c>
-      <c r="H12" s="35" t="inlineStr">
+      <c r="H12" s="59" t="inlineStr">
         <is>
           <t>Search tool</t>
         </is>
       </c>
-      <c r="I12" s="35" t="inlineStr">
+      <c r="I12" s="59" t="inlineStr">
         <is>
           <t>SGIs (~36 brokers), SGOs (asset managers), custodians, business introducers; filterable by type/country with status</t>
         </is>
       </c>
-      <c r="J12" s="35" t="inlineStr">
+      <c r="J12" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K12" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L12" s="35" t="inlineStr">
+      <c r="K12" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L12" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox). 394 professional cards renewed for 2026.</t>
         </is>
       </c>
     </row>
     <row r="13" ht="39.55" customHeight="1" s="31">
-      <c r="B13" s="35" t="inlineStr">
+      <c r="B13" s="59" t="inlineStr">
         <is>
           <t>Regional</t>
         </is>
       </c>
-      <c r="C13" s="35" t="inlineStr">
+      <c r="C13" s="59" t="inlineStr">
         <is>
           <t>COBAC/BEAC</t>
         </is>
       </c>
-      <c r="D13" s="35" t="inlineStr">
+      <c r="D13" s="59" t="inlineStr">
         <is>
           <t>Capital markets</t>
         </is>
       </c>
-      <c r="E13" s="35" t="inlineStr">
+      <c r="E13" s="59" t="inlineStr">
         <is>
           <t>COSUMAF</t>
         </is>
       </c>
-      <c r="F13" s="35" t="inlineStr">
+      <c r="F13" s="59" t="inlineStr">
         <is>
           <t>Intermédiaires - COSUMAF</t>
         </is>
       </c>
-      <c r="G13" s="58" t="inlineStr">
+      <c r="G13" s="60" t="inlineStr">
         <is>
           <t>https://cosumaf.org/liste-intermediaires?category=cif</t>
         </is>
       </c>
-      <c r="H13" s="35" t="inlineStr">
+      <c r="H13" s="59" t="inlineStr">
         <is>
           <t>Search tool</t>
         </is>
       </c>
-      <c r="I13" s="35" t="inlineStr">
+      <c r="I13" s="59" t="inlineStr">
         <is>
           <t>Licensed brokers (sociétés de bourse ~26), asset managers (~16), advisers, custodians in CEMAC; approval no. and managers</t>
         </is>
       </c>
-      <c r="J13" s="35" t="inlineStr">
+      <c r="J13" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K13" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L13" s="35" t="inlineStr">
+      <c r="K13" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L13" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox). English: cosumaf.org/intermediaries-list</t>
         </is>
       </c>
     </row>
     <row r="14" ht="26.85" customHeight="1" s="31">
-      <c r="B14" s="35" t="inlineStr">
+      <c r="B14" s="59" t="inlineStr">
         <is>
           <t>Regional</t>
         </is>
       </c>
-      <c r="C14" s="35" t="inlineStr">
+      <c r="C14" s="59" t="inlineStr">
         <is>
           <t>COBAC/BEAC</t>
         </is>
       </c>
-      <c r="D14" s="35" t="inlineStr">
+      <c r="D14" s="59" t="inlineStr">
         <is>
           <t>Capital markets</t>
         </is>
       </c>
-      <c r="E14" s="35" t="inlineStr">
+      <c r="E14" s="59" t="inlineStr">
         <is>
           <t>COSUMAF</t>
         </is>
       </c>
-      <c r="F14" s="35" t="inlineStr">
+      <c r="F14" s="59" t="inlineStr">
         <is>
           <t>L'ESSENTIEL 2e semestre 2025</t>
         </is>
       </c>
-      <c r="G14" s="58" t="inlineStr">
+      <c r="G14" s="60" t="inlineStr">
         <is>
           <t>https://cosumaf.org/files/documents/01KQRSJ4VRDZJ12Q805HTX1QYE.pdf</t>
         </is>
       </c>
-      <c r="H14" s="35" t="inlineStr">
+      <c r="H14" s="59" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="I14" s="35" t="inlineStr">
+      <c r="I14" s="59" t="inlineStr">
         <is>
           <t>List of approved market actors as at 31 Dec 2025</t>
         </is>
       </c>
-      <c r="J14" s="35" t="inlineStr">
+      <c r="J14" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K14" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L14" s="35" t="inlineStr">
+      <c r="K14" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L14" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox).</t>
         </is>
       </c>
     </row>
     <row r="15" ht="64.90000000000001" customHeight="1" s="31">
-      <c r="B15" s="35" t="inlineStr">
+      <c r="B15" s="59" t="inlineStr">
         <is>
           <t>Regional</t>
         </is>
       </c>
-      <c r="C15" s="35" t="inlineStr">
+      <c r="C15" s="59" t="inlineStr">
         <is>
           <t>FATF</t>
         </is>
       </c>
-      <c r="D15" s="35" t="inlineStr">
+      <c r="D15" s="59" t="inlineStr">
         <is>
           <t>FATF/regional</t>
         </is>
       </c>
-      <c r="E15" s="35" t="inlineStr">
+      <c r="E15" s="59" t="inlineStr">
         <is>
           <t>Financial Action Task Force</t>
         </is>
       </c>
-      <c r="F15" s="35" t="inlineStr">
+      <c r="F15" s="59" t="inlineStr">
         <is>
           <t>Jurisdictions under Increased Monitoring - 19 June 2026</t>
         </is>
       </c>
-      <c r="G15" s="58" t="inlineStr">
+      <c r="G15" s="60" t="inlineStr">
         <is>
           <t>https://www.fatf-gafi.org/en/publications/High-risk-and-other-monitored-jurisdictions/increased-monitoring-june-2026.html</t>
         </is>
       </c>
-      <c r="H15" s="35" t="inlineStr">
+      <c r="H15" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I15" s="35" t="inlineStr">
+      <c r="I15" s="59" t="inlineStr">
         <is>
           <t>Grey list (22 jurisdictions) incl. Cameroon, Côte d'Ivoire, DR Congo, Kenya; DRC &amp; CI judged to have substantially completed action plans (on-site visit due)</t>
         </is>
       </c>
-      <c r="J15" s="35" t="inlineStr">
+      <c r="J15" s="59" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="K15" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L15" s="35" t="inlineStr">
+      <c r="K15" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L15" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox). October 2026 plenary update may supersede; also see black-and-grey-lists hub.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="26.85" customHeight="1" s="31">
-      <c r="B16" s="35" t="inlineStr">
+      <c r="B16" s="59" t="inlineStr">
         <is>
           <t>Regional</t>
         </is>
       </c>
-      <c r="C16" s="35" t="inlineStr">
+      <c r="C16" s="59" t="inlineStr">
         <is>
           <t>FATF</t>
         </is>
       </c>
-      <c r="D16" s="35" t="inlineStr">
+      <c r="D16" s="59" t="inlineStr">
         <is>
           <t>FATF/regional</t>
         </is>
       </c>
-      <c r="E16" s="35" t="inlineStr">
+      <c r="E16" s="59" t="inlineStr">
         <is>
           <t>Financial Action Task Force</t>
         </is>
       </c>
-      <c r="F16" s="35" t="inlineStr">
+      <c r="F16" s="59" t="inlineStr">
         <is>
           <t>"Black and grey" lists (hub)</t>
         </is>
       </c>
-      <c r="G16" s="58" t="inlineStr">
+      <c r="G16" s="60" t="inlineStr">
         <is>
           <t>https://www.fatf-gafi.org/en/countries/black-and-grey-lists.html</t>
         </is>
       </c>
-      <c r="H16" s="35" t="inlineStr">
+      <c r="H16" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I16" s="35" t="inlineStr">
+      <c r="I16" s="59" t="inlineStr">
         <is>
           <t>Hub page always linking to the current grey and black lists</t>
         </is>
       </c>
-      <c r="J16" s="35" t="inlineStr">
+      <c r="J16" s="59" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="K16" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L16" s="35" t="inlineStr">
+      <c r="K16" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L16" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox).</t>
         </is>
       </c>
     </row>
     <row r="17" ht="39.55" customHeight="1" s="31">
-      <c r="B17" s="35" t="inlineStr">
+      <c r="B17" s="59" t="inlineStr">
         <is>
           <t>Regional</t>
         </is>
       </c>
-      <c r="C17" s="35" t="inlineStr">
+      <c r="C17" s="59" t="inlineStr">
         <is>
           <t>GIABA</t>
         </is>
       </c>
-      <c r="D17" s="35" t="inlineStr">
+      <c r="D17" s="59" t="inlineStr">
         <is>
           <t>FATF/regional</t>
         </is>
       </c>
-      <c r="E17" s="35" t="inlineStr">
+      <c r="E17" s="59" t="inlineStr">
         <is>
           <t>GIABA (Inter-Governmental Action Group against Money Laundering in West Africa)</t>
         </is>
       </c>
-      <c r="F17" s="35" t="inlineStr">
+      <c r="F17" s="59" t="inlineStr">
         <is>
           <t>GIABA - Member States</t>
         </is>
       </c>
-      <c r="G17" s="58" t="inlineStr">
+      <c r="G17" s="60" t="inlineStr">
         <is>
           <t>https://www.giaba.org/member-states/pages_faq.html</t>
         </is>
       </c>
-      <c r="H17" s="35" t="inlineStr">
+      <c r="H17" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I17" s="35" t="inlineStr">
+      <c r="I17" s="59" t="inlineStr">
         <is>
           <t>ECOWAS member-state pages with MERs and follow-up reports (Nigeria, Ghana, CI, Senegal, Mali, Togo)</t>
         </is>
       </c>
-      <c r="J17" s="35" t="inlineStr">
+      <c r="J17" s="59" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="K17" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L17" s="35" t="inlineStr">
+      <c r="K17" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L17" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox).</t>
         </is>
       </c>
     </row>
     <row r="18" ht="26.85" customHeight="1" s="31">
-      <c r="B18" s="35" t="inlineStr">
+      <c r="B18" s="59" t="inlineStr">
         <is>
           <t>Regional</t>
         </is>
       </c>
-      <c r="C18" s="35" t="inlineStr">
+      <c r="C18" s="59" t="inlineStr">
         <is>
           <t>GIABA</t>
         </is>
       </c>
-      <c r="D18" s="35" t="inlineStr">
+      <c r="D18" s="59" t="inlineStr">
         <is>
           <t>FATF/regional</t>
         </is>
       </c>
-      <c r="E18" s="35" t="inlineStr">
+      <c r="E18" s="59" t="inlineStr">
         <is>
           <t>GIABA</t>
         </is>
       </c>
-      <c r="F18" s="35" t="inlineStr">
+      <c r="F18" s="59" t="inlineStr">
         <is>
           <t>GIABA - Publications (mutual evaluations)</t>
         </is>
       </c>
-      <c r="G18" s="58" t="inlineStr">
+      <c r="G18" s="60" t="inlineStr">
         <is>
           <t>https://www.giaba.org/publications/index.html?cat=4</t>
         </is>
       </c>
-      <c r="H18" s="35" t="inlineStr">
+      <c r="H18" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I18" s="35" t="inlineStr">
+      <c r="I18" s="59" t="inlineStr">
         <is>
           <t>Mutual evaluation and enhanced follow-up reports; 2026 FURs for Niger, Mali, CI</t>
         </is>
       </c>
-      <c r="J18" s="35" t="inlineStr">
+      <c r="J18" s="59" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="K18" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L18" s="35" t="inlineStr">
+      <c r="K18" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L18" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox).</t>
         </is>
       </c>
     </row>
     <row r="19" ht="26.85" customHeight="1" s="31">
-      <c r="B19" s="35" t="inlineStr">
+      <c r="B19" s="59" t="inlineStr">
         <is>
           <t>Regional</t>
         </is>
       </c>
-      <c r="C19" s="35" t="inlineStr">
+      <c r="C19" s="59" t="inlineStr">
         <is>
           <t>ESAAMLG</t>
         </is>
       </c>
-      <c r="D19" s="35" t="inlineStr">
+      <c r="D19" s="59" t="inlineStr">
         <is>
           <t>FATF/regional</t>
         </is>
       </c>
-      <c r="E19" s="35" t="inlineStr">
+      <c r="E19" s="59" t="inlineStr">
         <is>
           <t>Eastern and Southern Africa Anti-Money Laundering Group</t>
         </is>
       </c>
-      <c r="F19" s="35" t="inlineStr">
+      <c r="F19" s="59" t="inlineStr">
         <is>
           <t>ESAAMLG - Countries</t>
         </is>
       </c>
-      <c r="G19" s="58" t="inlineStr">
+      <c r="G19" s="60" t="inlineStr">
         <is>
           <t>https://www.esaamlg.org/index.php/countries</t>
         </is>
       </c>
-      <c r="H19" s="35" t="inlineStr">
+      <c r="H19" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I19" s="35" t="inlineStr">
+      <c r="I19" s="59" t="inlineStr">
         <is>
           <t>Member countries (22) incl. Kenya, Rwanda; links to MERs</t>
         </is>
       </c>
-      <c r="J19" s="35" t="inlineStr">
+      <c r="J19" s="59" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="K19" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L19" s="35" t="inlineStr">
+      <c r="K19" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L19" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox).</t>
         </is>
       </c>
     </row>
     <row r="20" ht="26.85" customHeight="1" s="31">
-      <c r="B20" s="35" t="inlineStr">
+      <c r="B20" s="59" t="inlineStr">
         <is>
           <t>Regional</t>
         </is>
       </c>
-      <c r="C20" s="35" t="inlineStr">
+      <c r="C20" s="59" t="inlineStr">
         <is>
           <t>ESAAMLG</t>
         </is>
       </c>
-      <c r="D20" s="35" t="inlineStr">
+      <c r="D20" s="59" t="inlineStr">
         <is>
           <t>FATF/regional</t>
         </is>
       </c>
-      <c r="E20" s="35" t="inlineStr">
+      <c r="E20" s="59" t="inlineStr">
         <is>
           <t>ESAAMLG</t>
         </is>
       </c>
-      <c r="F20" s="35" t="inlineStr">
+      <c r="F20" s="59" t="inlineStr">
         <is>
           <t>Second Round MER of Rwanda (July 2024)</t>
         </is>
       </c>
-      <c r="G20" s="58" t="inlineStr">
+      <c r="G20" s="60" t="inlineStr">
         <is>
           <t>https://www.esaamlg.org/reports/Second%20Round%20MER%20of%20Rwanda-July%202024.pdf</t>
         </is>
       </c>
-      <c r="H20" s="35" t="inlineStr">
+      <c r="H20" s="59" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="I20" s="35" t="inlineStr">
+      <c r="I20" s="59" t="inlineStr">
         <is>
           <t>Rwanda mutual evaluation report - sector-by-sector AML/CFT gaps (useful for sales pitch)</t>
         </is>
       </c>
-      <c r="J20" s="35" t="inlineStr">
+      <c r="J20" s="59" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="K20" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L20" s="35" t="inlineStr">
+      <c r="K20" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L20" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox).</t>
         </is>
       </c>
     </row>
     <row r="21" ht="52.2" customHeight="1" s="31">
-      <c r="B21" s="35" t="inlineStr">
+      <c r="B21" s="59" t="inlineStr">
         <is>
           <t>Regional</t>
         </is>
       </c>
-      <c r="C21" s="35" t="inlineStr">
+      <c r="C21" s="59" t="inlineStr">
         <is>
           <t>GABAC</t>
         </is>
       </c>
-      <c r="D21" s="35" t="inlineStr">
+      <c r="D21" s="59" t="inlineStr">
         <is>
           <t>FATF/regional</t>
         </is>
       </c>
-      <c r="E21" s="35" t="inlineStr">
+      <c r="E21" s="59" t="inlineStr">
         <is>
           <t>GABAC (Groupe d'Action contre le Blanchiment d'Argent en Afrique Centrale)</t>
         </is>
       </c>
-      <c r="F21" s="35" t="inlineStr">
+      <c r="F21" s="59" t="inlineStr">
         <is>
           <t>Rapports d'évaluation mutuelle</t>
         </is>
       </c>
-      <c r="G21" s="58" t="inlineStr">
+      <c r="G21" s="60" t="inlineStr">
         <is>
           <t>https://gabac.org/rapports-devaluation-mutuelle/</t>
         </is>
       </c>
-      <c r="H21" s="35" t="inlineStr">
+      <c r="H21" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I21" s="35" t="inlineStr">
+      <c r="I21" s="59" t="inlineStr">
         <is>
           <t>MERs and follow-up reports for Cameroon, Gabon, Congo, DRC, Chad, CAR, Eq. Guinea</t>
         </is>
       </c>
-      <c r="J21" s="35" t="inlineStr">
+      <c r="J21" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K21" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L21" s="35" t="inlineStr">
+      <c r="K21" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L21" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox). DRC is a GABAC member (not ESAAMLG).</t>
         </is>
       </c>
     </row>
     <row r="22" ht="26.85" customHeight="1" s="31">
-      <c r="B22" s="35" t="inlineStr">
+      <c r="B22" s="59" t="inlineStr">
         <is>
           <t>Regional</t>
         </is>
       </c>
-      <c r="C22" s="35" t="inlineStr">
+      <c r="C22" s="59" t="inlineStr">
         <is>
           <t>BCEAO</t>
         </is>
       </c>
-      <c r="D22" s="35" t="inlineStr">
+      <c r="D22" s="59" t="inlineStr">
         <is>
           <t>Forex/Money transfer</t>
         </is>
       </c>
-      <c r="E22" s="35" t="inlineStr">
+      <c r="E22" s="59" t="inlineStr">
         <is>
           <t>BCEAO</t>
         </is>
       </c>
-      <c r="F22" s="35" t="inlineStr">
+      <c r="F22" s="59" t="inlineStr">
         <is>
           <t>Liste des intermédiaires en opérations de banque agréés dans l'UMOA en 2025</t>
         </is>
       </c>
-      <c r="G22" s="58" t="inlineStr">
+      <c r="G22" s="60" t="inlineStr">
         <is>
           <t>https://www.bceao.int/sites/default/files/inline-files/Liste-des-Intermediaires-en-Operation-de-Banque-au-31-decembre-2025.pdf</t>
         </is>
       </c>
-      <c r="H22" s="35" t="inlineStr">
+      <c r="H22" s="59" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="I22" s="35" t="inlineStr">
+      <c r="I22" s="59" t="inlineStr">
         <is>
           <t>Licensed banking intermediaries (IOB) incl. money-transfer sub-agents, by country</t>
         </is>
       </c>
-      <c r="J22" s="35" t="inlineStr">
+      <c r="J22" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K22" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L22" s="35" t="inlineStr">
+      <c r="K22" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L22" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox).</t>
         </is>
       </c>
     </row>
     <row r="23" ht="52.2" customHeight="1" s="31">
-      <c r="B23" s="35" t="inlineStr">
+      <c r="B23" s="59" t="inlineStr">
         <is>
           <t>Regional</t>
         </is>
       </c>
-      <c r="C23" s="35" t="inlineStr">
+      <c r="C23" s="59" t="inlineStr">
         <is>
           <t>CIMA</t>
         </is>
       </c>
-      <c r="D23" s="35" t="inlineStr">
+      <c r="D23" s="59" t="inlineStr">
         <is>
           <t>Industry association</t>
         </is>
       </c>
-      <c r="E23" s="35" t="inlineStr">
+      <c r="E23" s="59" t="inlineStr">
         <is>
           <t>FANAF</t>
         </is>
       </c>
-      <c r="F23" s="35" t="inlineStr">
+      <c r="F23" s="59" t="inlineStr">
         <is>
           <t>Annuaire FANAF 2023 (32e édition)</t>
         </is>
       </c>
-      <c r="G23" s="58" t="inlineStr">
+      <c r="G23" s="60" t="inlineStr">
         <is>
           <t>https://fanaf.org/wp-content/uploads/2025/04/ANNUAIRE_FANAF_2023_32e_Edition.pdf</t>
         </is>
       </c>
-      <c r="H23" s="35" t="inlineStr">
+      <c r="H23" s="59" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="I23" s="35" t="inlineStr">
+      <c r="I23" s="59" t="inlineStr">
         <is>
           <t>Directory of member insurers/reinsurers in 27 African countries with contacts, plus national insurance associations</t>
         </is>
       </c>
-      <c r="J23" s="35" t="inlineStr">
+      <c r="J23" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K23" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L23" s="35" t="inlineStr">
+      <c r="K23" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L23" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox). Good contact source for insurer compliance teams.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="52.2" customHeight="1" s="31">
-      <c r="B24" s="35" t="inlineStr">
+      <c r="B24" s="59" t="inlineStr">
         <is>
           <t>Regional</t>
         </is>
       </c>
-      <c r="C24" s="35" t="inlineStr">
+      <c r="C24" s="59" t="inlineStr">
         <is>
           <t>CIMA</t>
         </is>
       </c>
-      <c r="D24" s="35" t="inlineStr">
+      <c r="D24" s="59" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="E24" s="35" t="inlineStr">
+      <c r="E24" s="59" t="inlineStr">
         <is>
           <t>CIMA (Conférence Interafricaine des Marchés d'Assurances)</t>
         </is>
       </c>
-      <c r="F24" s="35" t="inlineStr">
+      <c r="F24" s="59" t="inlineStr">
         <is>
           <t>Bulletin Officiel 30e édition (31 déc. 2024)</t>
         </is>
       </c>
-      <c r="G24" s="58" t="inlineStr">
+      <c r="G24" s="60" t="inlineStr">
         <is>
           <t>https://cima-afrique.org/wp-content/uploads/2025/03/Bulletin-Officiel-30eme-Edition_compressed.pdf</t>
         </is>
       </c>
-      <c r="H24" s="35" t="inlineStr">
+      <c r="H24" s="59" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="I24" s="35" t="inlineStr">
+      <c r="I24" s="59" t="inlineStr">
         <is>
           <t>Official bulletin of licensing decisions, extensions and withdrawals for insurers across 14 CFA-zone states</t>
         </is>
       </c>
-      <c r="J24" s="35" t="inlineStr">
+      <c r="J24" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K24" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L24" s="35" t="inlineStr">
+      <c r="K24" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L24" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox). No single consolidated register; ~181 licensed insurers (2022).</t>
         </is>
       </c>
     </row>
     <row r="25" ht="26.85" customHeight="1" s="31">
-      <c r="B25" s="35" t="inlineStr">
+      <c r="B25" s="59" t="inlineStr">
         <is>
           <t>Regional</t>
         </is>
       </c>
-      <c r="C25" s="35" t="inlineStr">
+      <c r="C25" s="59" t="inlineStr">
         <is>
           <t>CIMA</t>
         </is>
       </c>
-      <c r="D25" s="35" t="inlineStr">
+      <c r="D25" s="59" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="E25" s="35" t="inlineStr">
+      <c r="E25" s="59" t="inlineStr">
         <is>
           <t>CIMA</t>
         </is>
       </c>
-      <c r="F25" s="35" t="inlineStr">
+      <c r="F25" s="59" t="inlineStr">
         <is>
           <t>Rapport des marchés CIMA 2022</t>
         </is>
       </c>
-      <c r="G25" s="58" t="inlineStr">
+      <c r="G25" s="60" t="inlineStr">
         <is>
           <t>https://cima-afrique.org/wp-content/uploads/2024/10/rapport-des-marches-CIMA-2022.pdf</t>
         </is>
       </c>
-      <c r="H25" s="35" t="inlineStr">
+      <c r="H25" s="59" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="I25" s="35" t="inlineStr">
+      <c r="I25" s="59" t="inlineStr">
         <is>
           <t>Market report naming insurers by country (181 companies: 116 non-life, 65 life)</t>
         </is>
       </c>
-      <c r="J25" s="35" t="inlineStr">
+      <c r="J25" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K25" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L25" s="35" t="inlineStr">
+      <c r="K25" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L25" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox).</t>
         </is>
       </c>
     </row>
     <row r="26" ht="52.2" customHeight="1" s="31">
-      <c r="B26" s="35" t="inlineStr">
+      <c r="B26" s="59" t="inlineStr">
         <is>
           <t>Regional</t>
         </is>
       </c>
-      <c r="C26" s="35" t="inlineStr">
+      <c r="C26" s="59" t="inlineStr">
         <is>
           <t>BCEAO</t>
         </is>
       </c>
-      <c r="D26" s="35" t="inlineStr">
+      <c r="D26" s="59" t="inlineStr">
         <is>
           <t>Microfinance</t>
         </is>
       </c>
-      <c r="E26" s="35" t="inlineStr">
+      <c r="E26" s="59" t="inlineStr">
         <is>
           <t>Commission Bancaire de l'UMOA</t>
         </is>
       </c>
-      <c r="F26" s="35" t="inlineStr">
+      <c r="F26" s="59" t="inlineStr">
         <is>
           <t>Landscape of reporting institutions</t>
         </is>
       </c>
-      <c r="G26" s="58" t="inlineStr">
+      <c r="G26" s="60" t="inlineStr">
         <is>
           <t>https://cb-umoa.org/en/landscape-reporting-institutions</t>
         </is>
       </c>
-      <c r="H26" s="35" t="inlineStr">
+      <c r="H26" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I26" s="35" t="inlineStr">
+      <c r="I26" s="59" t="inlineStr">
         <is>
           <t>Counts of banks/FIs per country and Article 44 SFDs (286 large MFIs under BCEAO/CB supervision)</t>
         </is>
       </c>
-      <c r="J26" s="35" t="inlineStr">
+      <c r="J26" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K26" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L26" s="35" t="inlineStr">
+      <c r="K26" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L26" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox). Named Art.44 SFD list not located; see BCEAO 'Crédit et Microfinance' page.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="64.90000000000001" customHeight="1" s="31">
-      <c r="B27" s="35" t="inlineStr">
+      <c r="B27" s="59" t="inlineStr">
         <is>
           <t>Regional</t>
         </is>
       </c>
-      <c r="C27" s="35" t="inlineStr">
+      <c r="C27" s="59" t="inlineStr">
         <is>
           <t>BCEAO</t>
         </is>
       </c>
-      <c r="D27" s="35" t="inlineStr">
+      <c r="D27" s="59" t="inlineStr">
         <is>
           <t>Microfinance</t>
         </is>
       </c>
-      <c r="E27" s="35" t="inlineStr">
+      <c r="E27" s="59" t="inlineStr">
         <is>
           <t>BCEAO</t>
         </is>
       </c>
-      <c r="F27" s="35" t="inlineStr">
+      <c r="F27" s="59" t="inlineStr">
         <is>
           <t>Crédit et Microfinance (documents)</t>
         </is>
       </c>
-      <c r="G27" s="58" t="inlineStr">
+      <c r="G27" s="60" t="inlineStr">
         <is>
           <t>https://www.bceao.int/fr/documents/credit-et-microfinance</t>
         </is>
       </c>
-      <c r="H27" s="35" t="inlineStr">
+      <c r="H27" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I27" s="35" t="inlineStr">
+      <c r="I27" s="59" t="inlineStr">
         <is>
           <t>SFD indicators (to 30 June 2025) and microfinance documents; source for SFD statistics</t>
         </is>
       </c>
-      <c r="J27" s="35" t="inlineStr">
+      <c r="J27" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K27" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L27" s="35" t="inlineStr">
+      <c r="K27" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L27" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox). Named SFD lists are held by national ministry units (DRS-SFD Senegal, DRSSFD CI, CCS-SFD Mali).</t>
         </is>
       </c>
     </row>
     <row r="28" ht="52.2" customHeight="1" s="31">
-      <c r="B28" s="35" t="inlineStr">
+      <c r="B28" s="59" t="inlineStr">
         <is>
           <t>Regional</t>
         </is>
       </c>
-      <c r="C28" s="35" t="inlineStr">
+      <c r="C28" s="59" t="inlineStr">
         <is>
           <t>BCEAO</t>
         </is>
       </c>
-      <c r="D28" s="35" t="inlineStr">
+      <c r="D28" s="59" t="inlineStr">
         <is>
           <t>Payments/E-money</t>
         </is>
       </c>
-      <c r="E28" s="35" t="inlineStr">
+      <c r="E28" s="59" t="inlineStr">
         <is>
           <t>BCEAO</t>
         </is>
       </c>
-      <c r="F28" s="35" t="inlineStr">
+      <c r="F28" s="59" t="inlineStr">
         <is>
           <t>Liste des établissements de paiement agréés dans l'UMOA (au 28 février 2026)</t>
         </is>
       </c>
-      <c r="G28" s="58" t="inlineStr">
+      <c r="G28" s="60" t="inlineStr">
         <is>
           <t>https://www.bceao.int/sites/default/files/2026-03/LISTE%20DES%20ETABLISSEMENTS%20DE%20PAIEMENT%20AGR%C3%89%C3%89S%20DANS%20L%E2%80%99UMOA%20au%2031%20janvier%202026.pdf</t>
         </is>
       </c>
-      <c r="H28" s="35" t="inlineStr">
+      <c r="H28" s="59" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="I28" s="35" t="inlineStr">
+      <c r="I28" s="59" t="inlineStr">
         <is>
           <t>31 licensed payment institutions (CI 9, Senegal 11, Togo 3, Mali 1...) with registration no. and date</t>
         </is>
       </c>
-      <c r="J28" s="35" t="inlineStr">
+      <c r="J28" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K28" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L28" s="35" t="inlineStr">
+      <c r="K28" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L28" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox). BCEAO homepage mentions a 31 Aug 2026 update.</t>
         </is>
       </c>
     </row>
     <row r="29" ht="52.2" customHeight="1" s="31">
-      <c r="B29" s="35" t="inlineStr">
+      <c r="B29" s="59" t="inlineStr">
         <is>
           <t>Regional</t>
         </is>
       </c>
-      <c r="C29" s="35" t="inlineStr">
+      <c r="C29" s="59" t="inlineStr">
         <is>
           <t>BCEAO</t>
         </is>
       </c>
-      <c r="D29" s="35" t="inlineStr">
+      <c r="D29" s="59" t="inlineStr">
         <is>
           <t>Payments/E-money</t>
         </is>
       </c>
-      <c r="E29" s="35" t="inlineStr">
+      <c r="E29" s="59" t="inlineStr">
         <is>
           <t>BCEAO</t>
         </is>
       </c>
-      <c r="F29" s="35" t="inlineStr">
+      <c r="F29" s="59" t="inlineStr">
         <is>
           <t>Etablissements de Monnaie Electronique</t>
         </is>
       </c>
-      <c r="G29" s="58" t="inlineStr">
+      <c r="G29" s="60" t="inlineStr">
         <is>
           <t>https://www.bceao.int/fr/content/etablissements-de-monnaie-electronique</t>
         </is>
       </c>
-      <c r="H29" s="35" t="inlineStr">
+      <c r="H29" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I29" s="35" t="inlineStr">
+      <c r="I29" s="59" t="inlineStr">
         <is>
           <t>82 e-money initiatives: 18 EMEs, 4 Treasuries, 1 SFD, 59 bank-telco partnerships, by country</t>
         </is>
       </c>
-      <c r="J29" s="35" t="inlineStr">
+      <c r="J29" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K29" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L29" s="35" t="inlineStr">
+      <c r="K29" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L29" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox). English version: /en/content/electronic-money-issuing-institutions-0</t>
         </is>
       </c>
     </row>
     <row r="30" ht="26.85" customHeight="1" s="31">
-      <c r="B30" s="35" t="inlineStr">
+      <c r="B30" s="59" t="inlineStr">
         <is>
           <t>Regional</t>
         </is>
       </c>
-      <c r="C30" s="35" t="inlineStr">
+      <c r="C30" s="59" t="inlineStr">
         <is>
           <t>BCEAO</t>
         </is>
       </c>
-      <c r="D30" s="35" t="inlineStr">
+      <c r="D30" s="59" t="inlineStr">
         <is>
           <t>Payments/E-money</t>
         </is>
       </c>
-      <c r="E30" s="35" t="inlineStr">
+      <c r="E30" s="59" t="inlineStr">
         <is>
           <t>Commission Bancaire de l'UMOA</t>
         </is>
       </c>
-      <c r="F30" s="35" t="inlineStr">
+      <c r="F30" s="59" t="inlineStr">
         <is>
           <t>UMOA - Liste des EME et EP de l'UMOA 2026</t>
         </is>
       </c>
-      <c r="G30" s="58" t="inlineStr">
+      <c r="G30" s="60" t="inlineStr">
         <is>
           <t>https://www.cb-umoa.org/sites/default/files/Liste%20%20des%20EME%20ET%20EP%20de%20l%27UMOA%202026.pdf</t>
         </is>
       </c>
-      <c r="H30" s="35" t="inlineStr">
+      <c r="H30" s="59" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="I30" s="35" t="inlineStr">
+      <c r="I30" s="59" t="inlineStr">
         <is>
           <t>Consolidated e-money issuers and payment institutions across UMOA (as at 29 June 2026)</t>
         </is>
       </c>
-      <c r="J30" s="35" t="inlineStr">
+      <c r="J30" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K30" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L30" s="35" t="inlineStr">
+      <c r="K30" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L30" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox).</t>
         </is>
       </c>
     </row>
     <row r="31" ht="52.2" customHeight="1" s="31">
-      <c r="B31" s="35" t="inlineStr">
+      <c r="B31" s="59" t="inlineStr">
         <is>
           <t>Regional</t>
         </is>
       </c>
-      <c r="C31" s="35" t="inlineStr">
+      <c r="C31" s="59" t="inlineStr">
         <is>
           <t>COBAC/BEAC</t>
         </is>
       </c>
-      <c r="D31" s="35" t="inlineStr">
+      <c r="D31" s="59" t="inlineStr">
         <is>
           <t>Payments/E-money</t>
         </is>
       </c>
-      <c r="E31" s="35" t="inlineStr">
+      <c r="E31" s="59" t="inlineStr">
         <is>
           <t>BEAC</t>
         </is>
       </c>
-      <c r="F31" s="35" t="inlineStr">
+      <c r="F31" s="59" t="inlineStr">
         <is>
           <t>Rapport sur les services de paiement dans la CEMAC 2024</t>
         </is>
       </c>
-      <c r="G31" s="58" t="inlineStr">
+      <c r="G31" s="60" t="inlineStr">
         <is>
           <t>https://www.beac.int/wp-content/uploads/2026/04/RAPPORT-SUR-LES-SERVICES-DE-PAIEMENT-DANS-LA-CEMAC-2024-.pdf</t>
         </is>
       </c>
-      <c r="H31" s="35" t="inlineStr">
+      <c r="H31" s="59" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="I31" s="35" t="inlineStr">
+      <c r="I31" s="59" t="inlineStr">
         <is>
           <t>Payment service providers / e-money in CEMAC (aggregate; annexes may name institutions)</t>
         </is>
       </c>
-      <c r="J31" s="35" t="inlineStr">
+      <c r="J31" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K31" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L31" s="35" t="inlineStr">
+      <c r="K31" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L31" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox). No standalone named list of payment institutions found.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="39.55" customHeight="1" s="31">
-      <c r="B32" s="35" t="inlineStr">
+      <c r="B32" s="59" t="inlineStr">
         <is>
           <t>DR Congo</t>
         </is>
       </c>
-      <c r="C32" s="35" t="inlineStr">
+      <c r="C32" s="59" t="inlineStr">
         <is>
           <t>GABAC</t>
         </is>
       </c>
-      <c r="D32" s="35" t="inlineStr">
+      <c r="D32" s="59" t="inlineStr">
         <is>
           <t>Banks</t>
         </is>
       </c>
-      <c r="E32" s="35" t="inlineStr">
+      <c r="E32" s="59" t="inlineStr">
         <is>
           <t>Banque Centrale du Congo (BCC)</t>
         </is>
       </c>
-      <c r="F32" s="35" t="inlineStr">
+      <c r="F32" s="59" t="inlineStr">
         <is>
           <t>Banques agréées : intermédiaires financiers en RDC</t>
         </is>
       </c>
-      <c r="G32" s="58" t="inlineStr">
+      <c r="G32" s="60" t="inlineStr">
         <is>
           <t>https://www.bcc.cd/intermediaires-financiers/banques-agreees</t>
         </is>
       </c>
-      <c r="H32" s="35" t="inlineStr">
+      <c r="H32" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I32" s="35" t="inlineStr">
+      <c r="I32" s="59" t="inlineStr">
         <is>
           <t>~15-16 licensed commercial banks (Equity BCDC, Rawbank, TMB, Ecobank, FirstBank, UBA, BGFI...) with licence refs</t>
         </is>
       </c>
-      <c r="J32" s="35" t="inlineStr">
+      <c r="J32" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K32" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L32" s="35" t="inlineStr">
+      <c r="K32" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L32" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox).</t>
         </is>
       </c>
     </row>
     <row r="33" ht="39.55" customHeight="1" s="31">
-      <c r="B33" s="35" t="inlineStr">
+      <c r="B33" s="59" t="inlineStr">
         <is>
           <t>DR Congo</t>
         </is>
       </c>
-      <c r="C33" s="35" t="inlineStr">
+      <c r="C33" s="59" t="inlineStr">
         <is>
           <t>GABAC</t>
         </is>
       </c>
-      <c r="D33" s="35" t="inlineStr">
+      <c r="D33" s="59" t="inlineStr">
         <is>
           <t>Banks</t>
         </is>
       </c>
-      <c r="E33" s="35" t="inlineStr">
+      <c r="E33" s="59" t="inlineStr">
         <is>
           <t>Banque Centrale du Congo (BCC)</t>
         </is>
       </c>
-      <c r="F33" s="35" t="inlineStr">
+      <c r="F33" s="59" t="inlineStr">
         <is>
           <t>Stabilité financière - Intermédiaires financiers (hub)</t>
         </is>
       </c>
-      <c r="G33" s="58" t="inlineStr">
+      <c r="G33" s="60" t="inlineStr">
         <is>
           <t>https://www.bcc.cd/intermediaires-financiers</t>
         </is>
       </c>
-      <c r="H33" s="35" t="inlineStr">
+      <c r="H33" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I33" s="35" t="inlineStr">
+      <c r="I33" s="59" t="inlineStr">
         <is>
           <t>Hub of BCC registers: banks, microfinance, COOPEC, e-money, messageries financières, bureaux de change, ancillary PSPs</t>
         </is>
       </c>
-      <c r="J33" s="35" t="inlineStr">
+      <c r="J33" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K33" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L33" s="35" t="inlineStr">
+      <c r="K33" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L33" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox).</t>
         </is>
       </c>
     </row>
     <row r="34" ht="26.85" customHeight="1" s="31">
-      <c r="B34" s="35" t="inlineStr">
+      <c r="B34" s="59" t="inlineStr">
         <is>
           <t>DR Congo</t>
         </is>
       </c>
-      <c r="C34" s="35" t="inlineStr">
+      <c r="C34" s="59" t="inlineStr">
         <is>
           <t>GABAC</t>
         </is>
       </c>
-      <c r="D34" s="35" t="inlineStr">
+      <c r="D34" s="59" t="inlineStr">
         <is>
           <t>FIU</t>
         </is>
       </c>
-      <c r="E34" s="35" t="inlineStr">
+      <c r="E34" s="59" t="inlineStr">
         <is>
           <t>CENAREF (Cellule Nationale des Renseignements Financiers)</t>
         </is>
       </c>
-      <c r="F34" s="35" t="inlineStr">
+      <c r="F34" s="59" t="inlineStr">
         <is>
           <t>CENAREF - no official website located</t>
         </is>
       </c>
-      <c r="G34" s="35" t="n"/>
-      <c r="H34" s="35" t="inlineStr">
+      <c r="G34" s="59" t="n"/>
+      <c r="H34" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I34" s="35" t="inlineStr">
+      <c r="I34" s="59" t="inlineStr">
         <is>
           <t>FIU (joined Egmont July 2026); regulations via Loi 22/068 AML/CFT</t>
         </is>
       </c>
-      <c r="J34" s="35" t="inlineStr">
+      <c r="J34" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K34" s="35" t="inlineStr">
+      <c r="K34" s="59" t="inlineStr">
         <is>
           <t>nein</t>
         </is>
       </c>
-      <c r="L34" s="35" t="inlineStr">
+      <c r="L34" s="59" t="inlineStr">
         <is>
           <t>No official domain found in search; contact via Ministry of Finance. Not invented.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="52.2" customHeight="1" s="31">
-      <c r="B35" s="35" t="inlineStr">
+      <c r="B35" s="59" t="inlineStr">
         <is>
           <t>DR Congo</t>
         </is>
       </c>
-      <c r="C35" s="35" t="inlineStr">
+      <c r="C35" s="59" t="inlineStr">
         <is>
           <t>GABAC</t>
         </is>
       </c>
-      <c r="D35" s="35" t="inlineStr">
+      <c r="D35" s="59" t="inlineStr">
         <is>
           <t>Forex/Money transfer</t>
         </is>
       </c>
-      <c r="E35" s="35" t="inlineStr">
+      <c r="E35" s="59" t="inlineStr">
         <is>
           <t>Banque Centrale du Congo (BCC)</t>
         </is>
       </c>
-      <c r="F35" s="35" t="inlineStr">
+      <c r="F35" s="59" t="inlineStr">
         <is>
           <t>Messageries financières agréées</t>
         </is>
       </c>
-      <c r="G35" s="58" t="inlineStr">
+      <c r="G35" s="60" t="inlineStr">
         <is>
           <t>https://www.bcc.cd/intermediaires-financiers/messageries-financieres</t>
         </is>
       </c>
-      <c r="H35" s="35" t="inlineStr">
+      <c r="H35" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I35" s="35" t="inlineStr">
+      <c r="I35" s="59" t="inlineStr">
         <is>
           <t>Licensed money-transfer operators (messageries financières)</t>
         </is>
       </c>
-      <c r="J35" s="35" t="inlineStr">
+      <c r="J35" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K35" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L35" s="35" t="inlineStr">
+      <c r="K35" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L35" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox). Bureaux de change register is a sub-section of the same hub.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="39.55" customHeight="1" s="31">
-      <c r="B36" s="35" t="inlineStr">
+      <c r="B36" s="59" t="inlineStr">
         <is>
           <t>DR Congo</t>
         </is>
       </c>
-      <c r="C36" s="35" t="inlineStr">
+      <c r="C36" s="59" t="inlineStr">
         <is>
           <t>GABAC</t>
         </is>
       </c>
-      <c r="D36" s="35" t="inlineStr">
+      <c r="D36" s="59" t="inlineStr">
         <is>
           <t>Industry association</t>
         </is>
       </c>
-      <c r="E36" s="35" t="inlineStr">
+      <c r="E36" s="59" t="inlineStr">
         <is>
           <t>Association Congolaise des Banques (ACB)</t>
         </is>
       </c>
-      <c r="F36" s="35" t="inlineStr">
+      <c r="F36" s="59" t="inlineStr">
         <is>
           <t>ACB - site officiel</t>
         </is>
       </c>
-      <c r="G36" s="58" t="inlineStr">
+      <c r="G36" s="60" t="inlineStr">
         <is>
           <t>https://www.acb-rdc.cd</t>
         </is>
       </c>
-      <c r="H36" s="35" t="inlineStr">
+      <c r="H36" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I36" s="35" t="inlineStr">
+      <c r="I36" s="59" t="inlineStr">
         <is>
           <t>Mandatory association of all DRC credit institutions (membership compulsory by law)</t>
         </is>
       </c>
-      <c r="J36" s="35" t="inlineStr">
+      <c r="J36" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K36" s="35" t="inlineStr">
+      <c r="K36" s="59" t="inlineStr">
         <is>
           <t>nein</t>
         </is>
       </c>
-      <c r="L36" s="35" t="inlineStr">
+      <c r="L36" s="59" t="inlineStr">
         <is>
           <t>Domain cited in ACB LinkedIn announcement; not confirmed by search index.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="39.55" customHeight="1" s="31">
-      <c r="B37" s="35" t="inlineStr">
+      <c r="B37" s="59" t="inlineStr">
         <is>
           <t>DR Congo</t>
         </is>
       </c>
-      <c r="C37" s="35" t="inlineStr">
+      <c r="C37" s="59" t="inlineStr">
         <is>
           <t>GABAC</t>
         </is>
       </c>
-      <c r="D37" s="35" t="inlineStr">
+      <c r="D37" s="59" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="E37" s="35" t="inlineStr">
+      <c r="E37" s="59" t="inlineStr">
         <is>
           <t>ARCA (Autorité de Régulation et de Contrôle des Assurances)</t>
         </is>
       </c>
-      <c r="F37" s="35" t="inlineStr">
+      <c r="F37" s="59" t="inlineStr">
         <is>
           <t>Sociétés d'assurances - Arca</t>
         </is>
       </c>
-      <c r="G37" s="58" t="inlineStr">
+      <c r="G37" s="60" t="inlineStr">
         <is>
           <t>https://arca.cd/societes-dassurances-2/</t>
         </is>
       </c>
-      <c r="H37" s="35" t="inlineStr">
+      <c r="H37" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I37" s="35" t="inlineStr">
+      <c r="I37" s="59" t="inlineStr">
         <is>
           <t>Licensed life &amp; non-life insurers with approval numbers (Rawsur, Activa, SFA, SUNU, Mayfair, GPA, SONAS...)</t>
         </is>
       </c>
-      <c r="J37" s="35" t="inlineStr">
+      <c r="J37" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K37" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L37" s="35" t="inlineStr">
+      <c r="K37" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L37" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox). Page copyright 2022; may lag.</t>
         </is>
       </c>
     </row>
     <row r="38" ht="26.85" customHeight="1" s="31">
-      <c r="B38" s="35" t="inlineStr">
+      <c r="B38" s="59" t="inlineStr">
         <is>
           <t>DR Congo</t>
         </is>
       </c>
-      <c r="C38" s="35" t="inlineStr">
+      <c r="C38" s="59" t="inlineStr">
         <is>
           <t>GABAC</t>
         </is>
       </c>
-      <c r="D38" s="35" t="inlineStr">
+      <c r="D38" s="59" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="E38" s="35" t="inlineStr">
+      <c r="E38" s="59" t="inlineStr">
         <is>
           <t>ARCA</t>
         </is>
       </c>
-      <c r="F38" s="35" t="inlineStr">
+      <c r="F38" s="59" t="inlineStr">
         <is>
           <t>Intermédiaires d'assurances - Arca</t>
         </is>
       </c>
-      <c r="G38" s="58" t="inlineStr">
+      <c r="G38" s="60" t="inlineStr">
         <is>
           <t>https://arca.cd/intermediaires/</t>
         </is>
       </c>
-      <c r="H38" s="35" t="inlineStr">
+      <c r="H38" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I38" s="35" t="inlineStr">
+      <c r="I38" s="59" t="inlineStr">
         <is>
           <t>Licensed insurance brokers and general agents (~29)</t>
         </is>
       </c>
-      <c r="J38" s="35" t="inlineStr">
+      <c r="J38" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K38" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L38" s="35" t="inlineStr">
+      <c r="K38" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L38" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox).</t>
         </is>
       </c>
     </row>
     <row r="39" ht="39.55" customHeight="1" s="31">
-      <c r="B39" s="35" t="inlineStr">
+      <c r="B39" s="59" t="inlineStr">
         <is>
           <t>DR Congo</t>
         </is>
       </c>
-      <c r="C39" s="35" t="inlineStr">
+      <c r="C39" s="59" t="inlineStr">
         <is>
           <t>GABAC</t>
         </is>
       </c>
-      <c r="D39" s="35" t="inlineStr">
+      <c r="D39" s="59" t="inlineStr">
         <is>
           <t>Microfinance</t>
         </is>
       </c>
-      <c r="E39" s="35" t="inlineStr">
+      <c r="E39" s="59" t="inlineStr">
         <is>
           <t>Banque Centrale du Congo (BCC)</t>
         </is>
       </c>
-      <c r="F39" s="35" t="inlineStr">
+      <c r="F39" s="59" t="inlineStr">
         <is>
           <t>Sociétés de microfinance agréées</t>
         </is>
       </c>
-      <c r="G39" s="58" t="inlineStr">
+      <c r="G39" s="60" t="inlineStr">
         <is>
           <t>https://www.bcc.cd/intermediaires-financiers/microfinance</t>
         </is>
       </c>
-      <c r="H39" s="35" t="inlineStr">
+      <c r="H39" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I39" s="35" t="inlineStr">
+      <c r="I39" s="59" t="inlineStr">
         <is>
           <t>Licensed microfinance companies (FINCA, Baobab, LOLC, SMICO...) - sector 116 institutions end-2025</t>
         </is>
       </c>
-      <c r="J39" s="35" t="inlineStr">
+      <c r="J39" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K39" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L39" s="35" t="inlineStr">
+      <c r="K39" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L39" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox).</t>
         </is>
       </c>
     </row>
     <row r="40" ht="26.85" customHeight="1" s="31">
-      <c r="B40" s="35" t="inlineStr">
+      <c r="B40" s="59" t="inlineStr">
         <is>
           <t>DR Congo</t>
         </is>
       </c>
-      <c r="C40" s="35" t="inlineStr">
+      <c r="C40" s="59" t="inlineStr">
         <is>
           <t>GABAC</t>
         </is>
       </c>
-      <c r="D40" s="35" t="inlineStr">
+      <c r="D40" s="59" t="inlineStr">
         <is>
           <t>Microfinance</t>
         </is>
       </c>
-      <c r="E40" s="35" t="inlineStr">
+      <c r="E40" s="59" t="inlineStr">
         <is>
           <t>Banque Centrale du Congo (BCC)</t>
         </is>
       </c>
-      <c r="F40" s="35" t="inlineStr">
+      <c r="F40" s="59" t="inlineStr">
         <is>
           <t>Caisses d'épargne et de crédit agréées</t>
         </is>
       </c>
-      <c r="G40" s="58" t="inlineStr">
+      <c r="G40" s="60" t="inlineStr">
         <is>
           <t>https://www.bcc.cd/intermediaires-financiers/caisse-epargne-credit</t>
         </is>
       </c>
-      <c r="H40" s="35" t="inlineStr">
+      <c r="H40" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I40" s="35" t="inlineStr">
+      <c r="I40" s="59" t="inlineStr">
         <is>
           <t>Licensed savings &amp; credit cooperatives (COOPEC)</t>
         </is>
       </c>
-      <c r="J40" s="35" t="inlineStr">
+      <c r="J40" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K40" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L40" s="35" t="inlineStr">
+      <c r="K40" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L40" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox).</t>
         </is>
       </c>
     </row>
     <row r="41" ht="39.55" customHeight="1" s="31">
-      <c r="B41" s="35" t="inlineStr">
+      <c r="B41" s="59" t="inlineStr">
         <is>
           <t>DR Congo</t>
         </is>
       </c>
-      <c r="C41" s="35" t="inlineStr">
+      <c r="C41" s="59" t="inlineStr">
         <is>
           <t>GABAC</t>
         </is>
       </c>
-      <c r="D41" s="35" t="inlineStr">
+      <c r="D41" s="59" t="inlineStr">
         <is>
           <t>Payments/E-money</t>
         </is>
       </c>
-      <c r="E41" s="35" t="inlineStr">
+      <c r="E41" s="59" t="inlineStr">
         <is>
           <t>Banque Centrale du Congo (BCC)</t>
         </is>
       </c>
-      <c r="F41" s="35" t="inlineStr">
+      <c r="F41" s="59" t="inlineStr">
         <is>
           <t>Etablissements émetteurs de monnaie électronique</t>
         </is>
       </c>
-      <c r="G41" s="58" t="inlineStr">
+      <c r="G41" s="60" t="inlineStr">
         <is>
           <t>https://www.bcc.cd/surveillance-des-intermediaires-financiers/intermediaires-financiers-assujettis/etablissements-de-credit/societes-financieres/ee</t>
         </is>
       </c>
-      <c r="H41" s="35" t="inlineStr">
+      <c r="H41" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I41" s="35" t="inlineStr">
+      <c r="I41" s="59" t="inlineStr">
         <is>
           <t>4 e-money issuers: Vodacash (M-Pesa), Airtel Money RDC, Orange Money RDC, Afrimobile Money</t>
         </is>
       </c>
-      <c r="J41" s="35" t="inlineStr">
+      <c r="J41" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K41" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L41" s="35" t="inlineStr">
+      <c r="K41" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L41" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox). Licence dates 2012-2015; may be stale.</t>
         </is>
       </c>
     </row>
     <row r="42" ht="39.55" customHeight="1" s="31">
-      <c r="B42" s="35" t="inlineStr">
+      <c r="B42" s="59" t="inlineStr">
         <is>
           <t>DR Congo</t>
         </is>
       </c>
-      <c r="C42" s="35" t="inlineStr">
+      <c r="C42" s="59" t="inlineStr">
         <is>
           <t>GABAC</t>
         </is>
       </c>
-      <c r="D42" s="35" t="inlineStr">
+      <c r="D42" s="59" t="inlineStr">
         <is>
           <t>Payments/E-money</t>
         </is>
       </c>
-      <c r="E42" s="35" t="inlineStr">
+      <c r="E42" s="59" t="inlineStr">
         <is>
           <t>Banque Centrale du Congo (BCC)</t>
         </is>
       </c>
-      <c r="F42" s="35" t="inlineStr">
+      <c r="F42" s="59" t="inlineStr">
         <is>
           <t>Prestataires des services connexes agréés</t>
         </is>
       </c>
-      <c r="G42" s="58" t="inlineStr">
+      <c r="G42" s="60" t="inlineStr">
         <is>
           <t>https://www.bcc.cd/intermediaires-financiers/prestataires-services-connexes</t>
         </is>
       </c>
-      <c r="H42" s="35" t="inlineStr">
+      <c r="H42" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I42" s="35" t="inlineStr">
+      <c r="I42" s="59" t="inlineStr">
         <is>
           <t>Licensed payment-related service providers/aggregators (Monetbil, PayWay Congo, Nomba...)</t>
         </is>
       </c>
-      <c r="J42" s="35" t="inlineStr">
+      <c r="J42" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K42" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L42" s="35" t="inlineStr">
+      <c r="K42" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L42" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox). Updated 15 July 2026.</t>
         </is>
       </c>
     </row>
     <row r="43" ht="39.55" customHeight="1" s="31">
-      <c r="B43" s="35" t="inlineStr">
+      <c r="B43" s="59" t="inlineStr">
         <is>
           <t>DR Congo</t>
         </is>
       </c>
-      <c r="C43" s="35" t="inlineStr">
+      <c r="C43" s="59" t="inlineStr">
         <is>
           <t>GABAC</t>
         </is>
       </c>
-      <c r="D43" s="35" t="inlineStr">
+      <c r="D43" s="59" t="inlineStr">
         <is>
           <t>Professional body</t>
         </is>
       </c>
-      <c r="E43" s="35" t="inlineStr">
+      <c r="E43" s="59" t="inlineStr">
         <is>
           <t>Ordre National des Experts-Comptables (ONEC RDC)</t>
         </is>
       </c>
-      <c r="F43" s="35" t="inlineStr">
+      <c r="F43" s="59" t="inlineStr">
         <is>
           <t>Loi créant l'ONEC (JO 19.02.2015)</t>
         </is>
       </c>
-      <c r="G43" s="58" t="inlineStr">
+      <c r="G43" s="60" t="inlineStr">
         <is>
           <t>https://www.leganet.cd/Legislation/JO/2015/Numeros/JOS.19.02.2015.pdf</t>
         </is>
       </c>
-      <c r="H43" s="35" t="inlineStr">
+      <c r="H43" s="59" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="I43" s="35" t="inlineStr">
+      <c r="I43" s="59" t="inlineStr">
         <is>
           <t>Founding law; ~347 active chartered accountants and 90 firms (2023); no public member list found</t>
         </is>
       </c>
-      <c r="J43" s="35" t="inlineStr">
+      <c r="J43" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K43" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L43" s="35" t="inlineStr">
+      <c r="K43" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L43" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox). Official ONEC website not found.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="52.2" customHeight="1" s="31">
-      <c r="B44" s="35" t="inlineStr">
+      <c r="B44" s="59" t="inlineStr">
         <is>
           <t>Kenya</t>
         </is>
       </c>
-      <c r="C44" s="35" t="inlineStr">
+      <c r="C44" s="59" t="inlineStr">
         <is>
           <t>ESAAMLG</t>
         </is>
       </c>
-      <c r="D44" s="35" t="inlineStr">
+      <c r="D44" s="59" t="inlineStr">
         <is>
           <t>Banks</t>
         </is>
       </c>
-      <c r="E44" s="35" t="inlineStr">
+      <c r="E44" s="59" t="inlineStr">
         <is>
           <t>Central Bank of Kenya</t>
         </is>
       </c>
-      <c r="F44" s="35" t="inlineStr">
+      <c r="F44" s="59" t="inlineStr">
         <is>
           <t>Directory of Licenced Commercial Banks, Mortgage Finance Institutions and Authorised Non-Operating Bank Holding Companies</t>
         </is>
       </c>
-      <c r="G44" s="58" t="inlineStr">
+      <c r="G44" s="60" t="inlineStr">
         <is>
           <t>https://www.centralbank.go.ke/wp-content/uploads/2026/07/Directory-of-Licenced-Commercial-Banks-Mortgage-Finance-Institutions-and-Authorised-Non-Operating-Bank-Holding-Companies.pdf</t>
         </is>
       </c>
-      <c r="H44" s="35" t="inlineStr">
+      <c r="H44" s="59" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="I44" s="35" t="inlineStr">
+      <c r="I44" s="59" t="inlineStr">
         <is>
           <t>~38 commercial banks + mortgage finance cos + NOHCs with address, phone, email, website, peer group, branches</t>
         </is>
       </c>
-      <c r="J44" s="35" t="inlineStr">
+      <c r="J44" s="59" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="K44" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L44" s="35" t="inlineStr">
+      <c r="K44" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L44" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox). July 2026 upload. Contact details YES.</t>
         </is>
       </c>
     </row>
     <row r="45" ht="26.85" customHeight="1" s="31">
-      <c r="B45" s="35" t="inlineStr">
+      <c r="B45" s="59" t="inlineStr">
         <is>
           <t>Kenya</t>
         </is>
       </c>
-      <c r="C45" s="35" t="inlineStr">
+      <c r="C45" s="59" t="inlineStr">
         <is>
           <t>ESAAMLG</t>
         </is>
       </c>
-      <c r="D45" s="35" t="inlineStr">
+      <c r="D45" s="59" t="inlineStr">
         <is>
           <t>Banks</t>
         </is>
       </c>
-      <c r="E45" s="35" t="inlineStr">
+      <c r="E45" s="59" t="inlineStr">
         <is>
           <t>Central Bank of Kenya</t>
         </is>
       </c>
-      <c r="F45" s="35" t="inlineStr">
+      <c r="F45" s="59" t="inlineStr">
         <is>
           <t>Bank Supervision (hub for all directories)</t>
         </is>
       </c>
-      <c r="G45" s="58" t="inlineStr">
+      <c r="G45" s="60" t="inlineStr">
         <is>
           <t>https://www.centralbank.go.ke/bank-supervision/</t>
         </is>
       </c>
-      <c r="H45" s="35" t="inlineStr">
+      <c r="H45" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I45" s="35" t="inlineStr">
+      <c r="I45" s="59" t="inlineStr">
         <is>
           <t>Links to directories of banks, MFBs, forex bureaus, MRPs, CRBs, representative offices</t>
         </is>
       </c>
-      <c r="J45" s="35" t="inlineStr">
+      <c r="J45" s="59" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="K45" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L45" s="35" t="inlineStr">
+      <c r="K45" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L45" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox).</t>
         </is>
       </c>
     </row>
     <row r="46" ht="39.55" customHeight="1" s="31">
-      <c r="B46" s="35" t="inlineStr">
+      <c r="B46" s="59" t="inlineStr">
         <is>
           <t>Kenya</t>
         </is>
       </c>
-      <c r="C46" s="35" t="inlineStr">
+      <c r="C46" s="59" t="inlineStr">
         <is>
           <t>ESAAMLG</t>
         </is>
       </c>
-      <c r="D46" s="35" t="inlineStr">
+      <c r="D46" s="59" t="inlineStr">
         <is>
           <t>Capital markets</t>
         </is>
       </c>
-      <c r="E46" s="35" t="inlineStr">
+      <c r="E46" s="59" t="inlineStr">
         <is>
           <t>Capital Markets Authority</t>
         </is>
       </c>
-      <c r="F46" s="35" t="inlineStr">
+      <c r="F46" s="59" t="inlineStr">
         <is>
           <t>List of licensees - Capital Markets Authority</t>
         </is>
       </c>
-      <c r="G46" s="58" t="inlineStr">
+      <c r="G46" s="60" t="inlineStr">
         <is>
           <t>https://licensees.cma.or.ke/licenses/1/</t>
         </is>
       </c>
-      <c r="H46" s="35" t="inlineStr">
+      <c r="H46" s="59" t="inlineStr">
         <is>
           <t>Search tool</t>
         </is>
       </c>
-      <c r="I46" s="35" t="inlineStr">
+      <c r="I46" s="59" t="inlineStr">
         <is>
           <t>Licensees by category: stockbrokers, investment banks, fund managers (~43+), forex brokers, exchanges, etc.</t>
         </is>
       </c>
-      <c r="J46" s="35" t="inlineStr">
+      <c r="J46" s="59" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="K46" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L46" s="35" t="inlineStr">
+      <c r="K46" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L46" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox).</t>
         </is>
       </c>
     </row>
     <row r="47" ht="39.55" customHeight="1" s="31">
-      <c r="B47" s="35" t="inlineStr">
+      <c r="B47" s="59" t="inlineStr">
         <is>
           <t>Kenya</t>
         </is>
       </c>
-      <c r="C47" s="35" t="inlineStr">
+      <c r="C47" s="59" t="inlineStr">
         <is>
           <t>ESAAMLG</t>
         </is>
       </c>
-      <c r="D47" s="35" t="inlineStr">
+      <c r="D47" s="59" t="inlineStr">
         <is>
           <t>FIU</t>
         </is>
       </c>
-      <c r="E47" s="35" t="inlineStr">
+      <c r="E47" s="59" t="inlineStr">
         <is>
           <t>Financial Reporting Centre (FRC)</t>
         </is>
       </c>
-      <c r="F47" s="35" t="inlineStr">
+      <c r="F47" s="59" t="inlineStr">
         <is>
           <t>Compliance - Financial Reporting Centre - Kenya</t>
         </is>
       </c>
-      <c r="G47" s="58" t="inlineStr">
+      <c r="G47" s="60" t="inlineStr">
         <is>
           <t>https://www.frc.go.ke/?page_id=25</t>
         </is>
       </c>
-      <c r="H47" s="35" t="inlineStr">
+      <c r="H47" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I47" s="35" t="inlineStr">
+      <c r="I47" s="59" t="inlineStr">
         <is>
           <t>AML/CFT obligations, guidance, annual compliance report (ACR), goAML registration for reporting institutions</t>
         </is>
       </c>
-      <c r="J47" s="35" t="inlineStr">
+      <c r="J47" s="59" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="K47" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L47" s="35" t="inlineStr">
+      <c r="K47" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L47" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox). Homepage https://www.frc.go.ke/</t>
         </is>
       </c>
     </row>
     <row r="48" ht="39.55" customHeight="1" s="31">
-      <c r="B48" s="35" t="inlineStr">
+      <c r="B48" s="59" t="inlineStr">
         <is>
           <t>Kenya</t>
         </is>
       </c>
-      <c r="C48" s="35" t="inlineStr">
+      <c r="C48" s="59" t="inlineStr">
         <is>
           <t>ESAAMLG</t>
         </is>
       </c>
-      <c r="D48" s="35" t="inlineStr">
+      <c r="D48" s="59" t="inlineStr">
         <is>
           <t>Forex/Money transfer</t>
         </is>
       </c>
-      <c r="E48" s="35" t="inlineStr">
+      <c r="E48" s="59" t="inlineStr">
         <is>
           <t>Central Bank of Kenya</t>
         </is>
       </c>
-      <c r="F48" s="35" t="inlineStr">
+      <c r="F48" s="59" t="inlineStr">
         <is>
           <t>Directory of Licenced Foreign Exchange Bureaus Feb 2026</t>
         </is>
       </c>
-      <c r="G48" s="58" t="inlineStr">
+      <c r="G48" s="60" t="inlineStr">
         <is>
           <t>https://www.centralbank.go.ke/wp-content/uploads/2026/02/Directory-of-Licenced-Foreign-Exchange-Bureaus-Feb-2026.pdf</t>
         </is>
       </c>
-      <c r="H48" s="35" t="inlineStr">
+      <c r="H48" s="59" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="I48" s="35" t="inlineStr">
+      <c r="I48" s="59" t="inlineStr">
         <is>
           <t>~88 forex bureaus with location, contacts, licence date</t>
         </is>
       </c>
-      <c r="J48" s="35" t="inlineStr">
+      <c r="J48" s="59" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="K48" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L48" s="35" t="inlineStr">
+      <c r="K48" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L48" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox). Contact details YES.</t>
         </is>
       </c>
     </row>
     <row r="49" ht="39.55" customHeight="1" s="31">
-      <c r="B49" s="35" t="inlineStr">
+      <c r="B49" s="59" t="inlineStr">
         <is>
           <t>Kenya</t>
         </is>
       </c>
-      <c r="C49" s="35" t="inlineStr">
+      <c r="C49" s="59" t="inlineStr">
         <is>
           <t>ESAAMLG</t>
         </is>
       </c>
-      <c r="D49" s="35" t="inlineStr">
+      <c r="D49" s="59" t="inlineStr">
         <is>
           <t>Forex/Money transfer</t>
         </is>
       </c>
-      <c r="E49" s="35" t="inlineStr">
+      <c r="E49" s="59" t="inlineStr">
         <is>
           <t>Central Bank of Kenya</t>
         </is>
       </c>
-      <c r="F49" s="35" t="inlineStr">
+      <c r="F49" s="59" t="inlineStr">
         <is>
           <t>Directory of Licenced Money Remittance Providers (MRPs) Feb 2026</t>
         </is>
       </c>
-      <c r="G49" s="58" t="inlineStr">
+      <c r="G49" s="60" t="inlineStr">
         <is>
           <t>https://www.centralbank.go.ke/wp-content/uploads/2026/02/Directory-of-Licenced-Money-Remittance-Providers-Feb-2026.pdf</t>
         </is>
       </c>
-      <c r="H49" s="35" t="inlineStr">
+      <c r="H49" s="59" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="I49" s="35" t="inlineStr">
+      <c r="I49" s="59" t="inlineStr">
         <is>
           <t>Licensed money remittance providers with address, contacts, licence date</t>
         </is>
       </c>
-      <c r="J49" s="35" t="inlineStr">
+      <c r="J49" s="59" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="K49" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L49" s="35" t="inlineStr">
+      <c r="K49" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L49" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox). Contact details YES.</t>
         </is>
       </c>
     </row>
     <row r="50" ht="26.85" customHeight="1" s="31">
-      <c r="B50" s="35" t="inlineStr">
+      <c r="B50" s="59" t="inlineStr">
         <is>
           <t>Kenya</t>
         </is>
       </c>
-      <c r="C50" s="35" t="inlineStr">
+      <c r="C50" s="59" t="inlineStr">
         <is>
           <t>ESAAMLG</t>
         </is>
       </c>
-      <c r="D50" s="35" t="inlineStr">
+      <c r="D50" s="59" t="inlineStr">
         <is>
           <t>Industry association</t>
         </is>
       </c>
-      <c r="E50" s="35" t="inlineStr">
+      <c r="E50" s="59" t="inlineStr">
         <is>
           <t>Kenya Bankers Association</t>
         </is>
       </c>
-      <c r="F50" s="35" t="inlineStr">
+      <c r="F50" s="59" t="inlineStr">
         <is>
           <t>KBA Members</t>
         </is>
       </c>
-      <c r="G50" s="58" t="inlineStr">
+      <c r="G50" s="60" t="inlineStr">
         <is>
           <t>https://www.kba.co.ke/kba-members/</t>
         </is>
       </c>
-      <c r="H50" s="35" t="inlineStr">
+      <c r="H50" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I50" s="35" t="inlineStr">
+      <c r="I50" s="59" t="inlineStr">
         <is>
           <t>46-47 member banks/MFBs</t>
         </is>
       </c>
-      <c r="J50" s="35" t="inlineStr">
+      <c r="J50" s="59" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="K50" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L50" s="35" t="inlineStr">
+      <c r="K50" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L50" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox).</t>
         </is>
       </c>
     </row>
     <row r="51" ht="52.2" customHeight="1" s="31">
-      <c r="B51" s="35" t="inlineStr">
+      <c r="B51" s="59" t="inlineStr">
         <is>
           <t>Kenya</t>
         </is>
       </c>
-      <c r="C51" s="35" t="inlineStr">
+      <c r="C51" s="59" t="inlineStr">
         <is>
           <t>ESAAMLG</t>
         </is>
       </c>
-      <c r="D51" s="35" t="inlineStr">
+      <c r="D51" s="59" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="E51" s="35" t="inlineStr">
+      <c r="E51" s="59" t="inlineStr">
         <is>
           <t>Insurance Regulatory Authority</t>
         </is>
       </c>
-      <c r="F51" s="35" t="inlineStr">
+      <c r="F51" s="59" t="inlineStr">
         <is>
           <t>List of Licensed Insurers 2025</t>
         </is>
       </c>
-      <c r="G51" s="58" t="inlineStr">
+      <c r="G51" s="60" t="inlineStr">
         <is>
           <t>https://www.ira.go.ke/lib.html?f=ira-licensed-insurers-and-intermediaries-2025</t>
         </is>
       </c>
-      <c r="H51" s="35" t="inlineStr">
+      <c r="H51" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I51" s="35" t="inlineStr">
+      <c r="I51" s="59" t="inlineStr">
         <is>
           <t>Licensed insurers, reinsurers, brokers, bancassurance, loss assessors etc.</t>
         </is>
       </c>
-      <c r="J51" s="35" t="inlineStr">
+      <c r="J51" s="59" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="K51" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L51" s="35" t="inlineStr">
+      <c r="K51" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L51" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox). 2026 list gazetted 30 Apr 2026 (633 entities) - check IRA site for 2026 version.</t>
         </is>
       </c>
     </row>
     <row r="52" ht="39.55" customHeight="1" s="31">
-      <c r="B52" s="35" t="inlineStr">
+      <c r="B52" s="59" t="inlineStr">
         <is>
           <t>Kenya</t>
         </is>
       </c>
-      <c r="C52" s="35" t="inlineStr">
+      <c r="C52" s="59" t="inlineStr">
         <is>
           <t>ESAAMLG</t>
         </is>
       </c>
-      <c r="D52" s="35" t="inlineStr">
+      <c r="D52" s="59" t="inlineStr">
         <is>
           <t>Microfinance</t>
         </is>
       </c>
-      <c r="E52" s="35" t="inlineStr">
+      <c r="E52" s="59" t="inlineStr">
         <is>
           <t>Central Bank of Kenya</t>
         </is>
       </c>
-      <c r="F52" s="35" t="inlineStr">
+      <c r="F52" s="59" t="inlineStr">
         <is>
           <t>Directory of Licenced Microfinance Banks Feb 2026</t>
         </is>
       </c>
-      <c r="G52" s="58" t="inlineStr">
+      <c r="G52" s="60" t="inlineStr">
         <is>
           <t>https://www.centralbank.go.ke/wp-content/uploads/2026/02/Directory-of-Licenced-Microfinance-Banks-Feb-2026.pdf</t>
         </is>
       </c>
-      <c r="H52" s="35" t="inlineStr">
+      <c r="H52" s="59" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="I52" s="35" t="inlineStr">
+      <c r="I52" s="59" t="inlineStr">
         <is>
           <t>~14 microfinance banks with contacts</t>
         </is>
       </c>
-      <c r="J52" s="35" t="inlineStr">
+      <c r="J52" s="59" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="K52" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L52" s="35" t="inlineStr">
+      <c r="K52" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L52" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox). Contact details YES.</t>
         </is>
       </c>
     </row>
     <row r="53" ht="52.2" customHeight="1" s="31">
-      <c r="B53" s="35" t="inlineStr">
+      <c r="B53" s="59" t="inlineStr">
         <is>
           <t>Kenya</t>
         </is>
       </c>
-      <c r="C53" s="35" t="inlineStr">
+      <c r="C53" s="59" t="inlineStr">
         <is>
           <t>ESAAMLG</t>
         </is>
       </c>
-      <c r="D53" s="35" t="inlineStr">
+      <c r="D53" s="59" t="inlineStr">
         <is>
           <t>Microfinance</t>
         </is>
       </c>
-      <c r="E53" s="35" t="inlineStr">
+      <c r="E53" s="59" t="inlineStr">
         <is>
           <t>SASRA (Sacco Societies Regulatory Authority)</t>
         </is>
       </c>
-      <c r="F53" s="35" t="inlineStr">
+      <c r="F53" s="59" t="inlineStr">
         <is>
           <t>List of Licensed and Authorized Sacco Societies in Kenya for FY ending 31 Dec 2026</t>
         </is>
       </c>
-      <c r="G53" s="58" t="inlineStr">
+      <c r="G53" s="60" t="inlineStr">
         <is>
           <t>https://www.sasra.go.ke/download/list-of-licensed-and-authorized-sacco-societies-in-kenya-for-the-financial-year-ending-31st-december-2026/</t>
         </is>
       </c>
-      <c r="H53" s="35" t="inlineStr">
+      <c r="H53" s="59" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="I53" s="35" t="inlineStr">
+      <c r="I53" s="59" t="inlineStr">
         <is>
           <t>~176 deposit-taking SACCOs + ~177 non-withdrawable DT SACCOs; restricted/revoked schedules</t>
         </is>
       </c>
-      <c r="J53" s="35" t="inlineStr">
+      <c r="J53" s="59" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="K53" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L53" s="35" t="inlineStr">
+      <c r="K53" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L53" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox). Large training market (SACCOs are reporting institutions).</t>
         </is>
       </c>
     </row>
     <row r="54" ht="39.55" customHeight="1" s="31">
-      <c r="B54" s="35" t="inlineStr">
+      <c r="B54" s="59" t="inlineStr">
         <is>
           <t>Kenya</t>
         </is>
       </c>
-      <c r="C54" s="35" t="inlineStr">
+      <c r="C54" s="59" t="inlineStr">
         <is>
           <t>ESAAMLG</t>
         </is>
       </c>
-      <c r="D54" s="35" t="inlineStr">
+      <c r="D54" s="59" t="inlineStr">
         <is>
           <t>Payments/E-money</t>
         </is>
       </c>
-      <c r="E54" s="35" t="inlineStr">
+      <c r="E54" s="59" t="inlineStr">
         <is>
           <t>Central Bank of Kenya</t>
         </is>
       </c>
-      <c r="F54" s="35" t="inlineStr">
+      <c r="F54" s="59" t="inlineStr">
         <is>
           <t>Directory of Authorized Payment Service Providers (15 May 2026)</t>
         </is>
       </c>
-      <c r="G54" s="58" t="inlineStr">
+      <c r="G54" s="60" t="inlineStr">
         <is>
           <t>https://www.centralbank.go.ke/wp-content/uploads/2026/06/Directory-of-Authorized-Payment-Service-Providers-15th-May-2026.pdf</t>
         </is>
       </c>
-      <c r="H54" s="35" t="inlineStr">
+      <c r="H54" s="59" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="I54" s="35" t="inlineStr">
+      <c r="I54" s="59" t="inlineStr">
         <is>
           <t>Authorised PSPs incl. Safaricom M-Pesa, Airtel Money, Cellulant, Pesapal, Paystack with services authorised</t>
         </is>
       </c>
-      <c r="J54" s="35" t="inlineStr">
+      <c r="J54" s="59" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="K54" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L54" s="35" t="inlineStr">
+      <c r="K54" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L54" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox).</t>
         </is>
       </c>
     </row>
     <row r="55" ht="39.55" customHeight="1" s="31">
-      <c r="B55" s="35" t="inlineStr">
+      <c r="B55" s="59" t="inlineStr">
         <is>
           <t>Kenya</t>
         </is>
       </c>
-      <c r="C55" s="35" t="inlineStr">
+      <c r="C55" s="59" t="inlineStr">
         <is>
           <t>ESAAMLG</t>
         </is>
       </c>
-      <c r="D55" s="35" t="inlineStr">
+      <c r="D55" s="59" t="inlineStr">
         <is>
           <t>Professional body</t>
         </is>
       </c>
-      <c r="E55" s="35" t="inlineStr">
+      <c r="E55" s="59" t="inlineStr">
         <is>
           <t>ICPAK</t>
         </is>
       </c>
-      <c r="F55" s="35" t="inlineStr">
+      <c r="F55" s="59" t="inlineStr">
         <is>
           <t>CPA directory (licensed firms list)</t>
         </is>
       </c>
-      <c r="G55" s="58" t="inlineStr">
+      <c r="G55" s="60" t="inlineStr">
         <is>
           <t>https://old.icpak.com/cpa-directory</t>
         </is>
       </c>
-      <c r="H55" s="35" t="inlineStr">
+      <c r="H55" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I55" s="35" t="inlineStr">
+      <c r="I55" s="59" t="inlineStr">
         <is>
           <t>Licensed audit/accountancy firms and practising members (annual list download)</t>
         </is>
       </c>
-      <c r="J55" s="35" t="inlineStr">
+      <c r="J55" s="59" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="K55" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L55" s="35" t="inlineStr">
+      <c r="K55" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L55" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox). Old site; list may be 2024.</t>
         </is>
       </c>
     </row>
     <row r="56" ht="26.85" customHeight="1" s="31">
-      <c r="B56" s="35" t="inlineStr">
+      <c r="B56" s="59" t="inlineStr">
         <is>
           <t>Kenya</t>
         </is>
       </c>
-      <c r="C56" s="35" t="inlineStr">
+      <c r="C56" s="59" t="inlineStr">
         <is>
           <t>ESAAMLG</t>
         </is>
       </c>
-      <c r="D56" s="35" t="inlineStr">
+      <c r="D56" s="59" t="inlineStr">
         <is>
           <t>Professional body</t>
         </is>
       </c>
-      <c r="E56" s="35" t="inlineStr">
+      <c r="E56" s="59" t="inlineStr">
         <is>
           <t>Law Society of Kenya</t>
         </is>
       </c>
-      <c r="F56" s="35" t="inlineStr">
+      <c r="F56" s="59" t="inlineStr">
         <is>
           <t>LSK online advocate search</t>
         </is>
       </c>
-      <c r="G56" s="58" t="inlineStr">
+      <c r="G56" s="60" t="inlineStr">
         <is>
           <t>https://online.lsk.or.ke</t>
         </is>
       </c>
-      <c r="H56" s="35" t="inlineStr">
+      <c r="H56" s="59" t="inlineStr">
         <is>
           <t>Search tool</t>
         </is>
       </c>
-      <c r="I56" s="35" t="inlineStr">
+      <c r="I56" s="59" t="inlineStr">
         <is>
           <t>Advocates with active/inactive practising certificate status</t>
         </is>
       </c>
-      <c r="J56" s="35" t="inlineStr">
+      <c r="J56" s="59" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="K56" s="35" t="inlineStr">
+      <c r="K56" s="59" t="inlineStr">
         <is>
           <t>nein</t>
         </is>
       </c>
-      <c r="L56" s="35" t="inlineStr">
+      <c r="L56" s="59" t="inlineStr">
         <is>
           <t>Portal cited by The Star/Nation; not directly confirmed in search index.</t>
         </is>
       </c>
     </row>
     <row r="57" ht="52.2" customHeight="1" s="31">
-      <c r="B57" s="35" t="inlineStr">
+      <c r="B57" s="59" t="inlineStr">
         <is>
           <t>Kenya</t>
         </is>
       </c>
-      <c r="C57" s="35" t="inlineStr">
+      <c r="C57" s="59" t="inlineStr">
         <is>
           <t>ESAAMLG</t>
         </is>
       </c>
-      <c r="D57" s="35" t="inlineStr">
+      <c r="D57" s="59" t="inlineStr">
         <is>
           <t>VASP</t>
         </is>
       </c>
-      <c r="E57" s="35" t="inlineStr">
+      <c r="E57" s="59" t="inlineStr">
         <is>
           <t>Central Bank of Kenya / CMA</t>
         </is>
       </c>
-      <c r="F57" s="35" t="inlineStr">
+      <c r="F57" s="59" t="inlineStr">
         <is>
           <t>Public Notice on the Virtual Assets Service Providers Act 2025</t>
         </is>
       </c>
-      <c r="G57" s="58" t="inlineStr">
+      <c r="G57" s="60" t="inlineStr">
         <is>
           <t>https://www.centralbank.go.ke/uploads/press_releases/665231223_Public%20Notice%20on%20the%20Virtual%20Assets%20Service%20Providers%20Act%202025.pdf</t>
         </is>
       </c>
-      <c r="H57" s="35" t="inlineStr">
+      <c r="H57" s="59" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="I57" s="35" t="inlineStr">
+      <c r="I57" s="59" t="inlineStr">
         <is>
           <t>No VASP register yet - notice confirms none licensed pending Treasury regulations</t>
         </is>
       </c>
-      <c r="J57" s="35" t="inlineStr">
+      <c r="J57" s="59" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="K57" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L57" s="35" t="inlineStr">
+      <c r="K57" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L57" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox). VASP Act 2025 in force 4 Nov 2025; watch for register.</t>
         </is>
       </c>
     </row>
     <row r="58" ht="39.55" customHeight="1" s="31">
-      <c r="B58" s="35" t="inlineStr">
+      <c r="B58" s="59" t="inlineStr">
         <is>
           <t>Nigeria</t>
         </is>
       </c>
-      <c r="C58" s="35" t="inlineStr">
+      <c r="C58" s="59" t="inlineStr">
         <is>
           <t>GIABA</t>
         </is>
       </c>
-      <c r="D58" s="35" t="inlineStr">
+      <c r="D58" s="59" t="inlineStr">
         <is>
           <t>Banks</t>
         </is>
       </c>
-      <c r="E58" s="35" t="inlineStr">
+      <c r="E58" s="59" t="inlineStr">
         <is>
           <t>Central Bank of Nigeria</t>
         </is>
       </c>
-      <c r="F58" s="35" t="inlineStr">
+      <c r="F58" s="59" t="inlineStr">
         <is>
           <t>Financial Institutions | Central Bank of Nigeria</t>
         </is>
       </c>
-      <c r="G58" s="58" t="inlineStr">
+      <c r="G58" s="60" t="inlineStr">
         <is>
           <t>https://www.cbn.gov.ng/supervision/finstitutions.html</t>
         </is>
       </c>
-      <c r="H58" s="35" t="inlineStr">
+      <c r="H58" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I58" s="35" t="inlineStr">
+      <c r="I58" s="59" t="inlineStr">
         <is>
           <t>Hub of CBN institution lists: commercial/merchant/non-interest banks, MFBs, PMBs, finance cos, BDCs, PSBs, MMOs</t>
         </is>
       </c>
-      <c r="J58" s="35" t="inlineStr">
+      <c r="J58" s="59" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="K58" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L58" s="35" t="inlineStr">
+      <c r="K58" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L58" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox).</t>
         </is>
       </c>
     </row>
     <row r="59" ht="52.2" customHeight="1" s="31">
-      <c r="B59" s="35" t="inlineStr">
+      <c r="B59" s="59" t="inlineStr">
         <is>
           <t>Nigeria</t>
         </is>
       </c>
-      <c r="C59" s="35" t="inlineStr">
+      <c r="C59" s="59" t="inlineStr">
         <is>
           <t>GIABA</t>
         </is>
       </c>
-      <c r="D59" s="35" t="inlineStr">
+      <c r="D59" s="59" t="inlineStr">
         <is>
           <t>Banks</t>
         </is>
       </c>
-      <c r="E59" s="35" t="inlineStr">
+      <c r="E59" s="59" t="inlineStr">
         <is>
           <t>Central Bank of Nigeria</t>
         </is>
       </c>
-      <c r="F59" s="35" t="inlineStr">
+      <c r="F59" s="59" t="inlineStr">
         <is>
           <t>List of Deposit Money Banks as at 26 April 2024</t>
         </is>
       </c>
-      <c r="G59" s="58" t="inlineStr">
+      <c r="G59" s="60" t="inlineStr">
         <is>
           <t>https://www.cbn.gov.ng/Out/2024/CCD/LIST%20OF%20DEPOSIT%20MONEY%20BANKS%20AS%20AT%2026TH%20APRIL,%202024%20(1).pdf</t>
         </is>
       </c>
-      <c r="H59" s="35" t="inlineStr">
+      <c r="H59" s="59" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="I59" s="35" t="inlineStr">
+      <c r="I59" s="59" t="inlineStr">
         <is>
           <t>Commercial, merchant and non-interest banks</t>
         </is>
       </c>
-      <c r="J59" s="35" t="inlineStr">
+      <c r="J59" s="59" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="K59" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L59" s="35" t="inlineStr">
+      <c r="K59" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L59" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox). Newer lists may be on the hub post-recapitalisation.</t>
         </is>
       </c>
     </row>
     <row r="60" ht="26.85" customHeight="1" s="31">
-      <c r="B60" s="35" t="inlineStr">
+      <c r="B60" s="59" t="inlineStr">
         <is>
           <t>Nigeria</t>
         </is>
       </c>
-      <c r="C60" s="35" t="inlineStr">
+      <c r="C60" s="59" t="inlineStr">
         <is>
           <t>GIABA</t>
         </is>
       </c>
-      <c r="D60" s="35" t="inlineStr">
+      <c r="D60" s="59" t="inlineStr">
         <is>
           <t>Capital markets</t>
         </is>
       </c>
-      <c r="E60" s="35" t="inlineStr">
+      <c r="E60" s="59" t="inlineStr">
         <is>
           <t>Securities and Exchange Commission Nigeria</t>
         </is>
       </c>
-      <c r="F60" s="35" t="inlineStr">
+      <c r="F60" s="59" t="inlineStr">
         <is>
           <t>SEC Nigeria website (registered capital market operators)</t>
         </is>
       </c>
-      <c r="G60" s="58" t="inlineStr">
+      <c r="G60" s="60" t="inlineStr">
         <is>
           <t>https://sec.gov.ng/</t>
         </is>
       </c>
-      <c r="H60" s="35" t="inlineStr">
+      <c r="H60" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I60" s="35" t="inlineStr">
+      <c r="I60" s="59" t="inlineStr">
         <is>
           <t>Registered CMOs (brokers, dealers, fund managers)</t>
         </is>
       </c>
-      <c r="J60" s="35" t="inlineStr">
+      <c r="J60" s="59" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="K60" s="35" t="inlineStr">
+      <c r="K60" s="59" t="inlineStr">
         <is>
           <t>nein</t>
         </is>
       </c>
-      <c r="L60" s="35" t="inlineStr">
+      <c r="L60" s="59" t="inlineStr">
         <is>
           <t>Domain verified; specific CMO register URL not confirmed in search.</t>
         </is>
       </c>
     </row>
     <row r="61" ht="26.85" customHeight="1" s="31">
-      <c r="B61" s="35" t="inlineStr">
+      <c r="B61" s="59" t="inlineStr">
         <is>
           <t>Nigeria</t>
         </is>
       </c>
-      <c r="C61" s="35" t="inlineStr">
+      <c r="C61" s="59" t="inlineStr">
         <is>
           <t>GIABA</t>
         </is>
       </c>
-      <c r="D61" s="35" t="inlineStr">
+      <c r="D61" s="59" t="inlineStr">
         <is>
           <t>FIU</t>
         </is>
       </c>
-      <c r="E61" s="35" t="inlineStr">
+      <c r="E61" s="59" t="inlineStr">
         <is>
           <t>Nigerian Financial Intelligence Unit</t>
         </is>
       </c>
-      <c r="F61" s="35" t="inlineStr">
+      <c r="F61" s="59" t="inlineStr">
         <is>
           <t>About NFIU</t>
         </is>
       </c>
-      <c r="G61" s="58" t="inlineStr">
+      <c r="G61" s="60" t="inlineStr">
         <is>
           <t>https://www.nfiu.gov.ng/index.php/nfiu</t>
         </is>
       </c>
-      <c r="H61" s="35" t="inlineStr">
+      <c r="H61" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I61" s="35" t="inlineStr">
+      <c r="I61" s="59" t="inlineStr">
         <is>
           <t>FIU; guidelines/advisories for reporting entities, goAML</t>
         </is>
       </c>
-      <c r="J61" s="35" t="inlineStr">
+      <c r="J61" s="59" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="K61" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L61" s="35" t="inlineStr">
+      <c r="K61" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L61" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox).</t>
         </is>
       </c>
     </row>
     <row r="62" ht="52.2" customHeight="1" s="31">
-      <c r="B62" s="35" t="inlineStr">
+      <c r="B62" s="59" t="inlineStr">
         <is>
           <t>Nigeria</t>
         </is>
       </c>
-      <c r="C62" s="35" t="inlineStr">
+      <c r="C62" s="59" t="inlineStr">
         <is>
           <t>GIABA</t>
         </is>
       </c>
-      <c r="D62" s="35" t="inlineStr">
+      <c r="D62" s="59" t="inlineStr">
         <is>
           <t>FIU</t>
         </is>
       </c>
-      <c r="E62" s="35" t="inlineStr">
+      <c r="E62" s="59" t="inlineStr">
         <is>
           <t>SCUML (EFCC)</t>
         </is>
       </c>
-      <c r="F62" s="35" t="inlineStr">
+      <c r="F62" s="59" t="inlineStr">
         <is>
           <t>Special Control Unit against Money Laundering</t>
         </is>
       </c>
-      <c r="G62" s="58" t="inlineStr">
+      <c r="G62" s="60" t="inlineStr">
         <is>
           <t>https://scuml.efcc.gov.ng/</t>
         </is>
       </c>
-      <c r="H62" s="35" t="inlineStr">
+      <c r="H62" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I62" s="35" t="inlineStr">
+      <c r="I62" s="59" t="inlineStr">
         <is>
           <t>DNFBP registration/supervision (lawyers, accountants, real estate, dealers) - CTR/CBTR portal</t>
         </is>
       </c>
-      <c r="J62" s="35" t="inlineStr">
+      <c r="J62" s="59" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="K62" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L62" s="35" t="inlineStr">
+      <c r="K62" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L62" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox). DNFBP supervisor - relevant for professional firms.</t>
         </is>
       </c>
     </row>
     <row r="63" ht="64.90000000000001" customHeight="1" s="31">
-      <c r="B63" s="35" t="inlineStr">
+      <c r="B63" s="59" t="inlineStr">
         <is>
           <t>Nigeria</t>
         </is>
       </c>
-      <c r="C63" s="35" t="inlineStr">
+      <c r="C63" s="59" t="inlineStr">
         <is>
           <t>GIABA</t>
         </is>
       </c>
-      <c r="D63" s="35" t="inlineStr">
+      <c r="D63" s="59" t="inlineStr">
         <is>
           <t>Forex/Money transfer</t>
         </is>
       </c>
-      <c r="E63" s="35" t="inlineStr">
+      <c r="E63" s="59" t="inlineStr">
         <is>
           <t>Central Bank of Nigeria</t>
         </is>
       </c>
-      <c r="F63" s="35" t="inlineStr">
+      <c r="F63" s="59" t="inlineStr">
         <is>
           <t>List of CBN Licenced Bureaux de Change as at December 31, 2021</t>
         </is>
       </c>
-      <c r="G63" s="58" t="inlineStr">
+      <c r="G63" s="60" t="inlineStr">
         <is>
           <t>https://www.cbn.gov.ng/Out/2022/FPRD/LIST%20OF%20CBN%20LICENCED%20BUREAUX%20DE%20CHANGE%20AS%20AT%20DECEMBER%2031,%202021.pdf</t>
         </is>
       </c>
-      <c r="H63" s="35" t="inlineStr">
+      <c r="H63" s="59" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="I63" s="35" t="inlineStr">
+      <c r="I63" s="59" t="inlineStr">
         <is>
           <t>Historic BDC list (thousands) - superseded</t>
         </is>
       </c>
-      <c r="J63" s="35" t="inlineStr">
+      <c r="J63" s="59" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="K63" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L63" s="35" t="inlineStr">
+      <c r="K63" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L63" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox). Current regime: 82 BDCs granted final licences Nov 2025 (list on CBN site per press; PDF URL not confirmed).</t>
         </is>
       </c>
     </row>
     <row r="64" ht="26.85" customHeight="1" s="31">
-      <c r="B64" s="35" t="inlineStr">
+      <c r="B64" s="59" t="inlineStr">
         <is>
           <t>Nigeria</t>
         </is>
       </c>
-      <c r="C64" s="35" t="inlineStr">
+      <c r="C64" s="59" t="inlineStr">
         <is>
           <t>GIABA</t>
         </is>
       </c>
-      <c r="D64" s="35" t="inlineStr">
+      <c r="D64" s="59" t="inlineStr">
         <is>
           <t>Industry association</t>
         </is>
       </c>
-      <c r="E64" s="35" t="inlineStr">
+      <c r="E64" s="59" t="inlineStr">
         <is>
           <t>Chartered Institute of Bankers of Nigeria</t>
         </is>
       </c>
-      <c r="F64" s="35" t="inlineStr">
+      <c r="F64" s="59" t="inlineStr">
         <is>
           <t>CIBN - overview membership</t>
         </is>
       </c>
-      <c r="G64" s="58" t="inlineStr">
+      <c r="G64" s="60" t="inlineStr">
         <is>
           <t>https://www.cibng.org/overview-membership/</t>
         </is>
       </c>
-      <c r="H64" s="35" t="inlineStr">
+      <c r="H64" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I64" s="35" t="inlineStr">
+      <c r="I64" s="59" t="inlineStr">
         <is>
           <t>Bankers' professional body (CPD duties); Bankers' Committee itself has no public roster</t>
         </is>
       </c>
-      <c r="J64" s="35" t="inlineStr">
+      <c r="J64" s="59" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="K64" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L64" s="35" t="inlineStr">
+      <c r="K64" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L64" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox).</t>
         </is>
       </c>
     </row>
     <row r="65" ht="52.2" customHeight="1" s="31">
-      <c r="B65" s="35" t="inlineStr">
+      <c r="B65" s="59" t="inlineStr">
         <is>
           <t>Nigeria</t>
         </is>
       </c>
-      <c r="C65" s="35" t="inlineStr">
+      <c r="C65" s="59" t="inlineStr">
         <is>
           <t>GIABA</t>
         </is>
       </c>
-      <c r="D65" s="35" t="inlineStr">
+      <c r="D65" s="59" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="E65" s="35" t="inlineStr">
+      <c r="E65" s="59" t="inlineStr">
         <is>
           <t>NAICOM</t>
         </is>
       </c>
-      <c r="F65" s="35" t="inlineStr">
+      <c r="F65" s="59" t="inlineStr">
         <is>
           <t>Insurance Operators - NAICOM</t>
         </is>
       </c>
-      <c r="G65" s="58" t="inlineStr">
+      <c r="G65" s="60" t="inlineStr">
         <is>
           <t>https://naicom.gov.ng/insurance-operators/</t>
         </is>
       </c>
-      <c r="H65" s="35" t="inlineStr">
+      <c r="H65" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I65" s="35" t="inlineStr">
+      <c r="I65" s="59" t="inlineStr">
         <is>
           <t>Hub: composite, general (28), life (12), reinsurance, takaful, micro-insurance (18), brokers, loss adjusters with address/website/licence no.</t>
         </is>
       </c>
-      <c r="J65" s="35" t="inlineStr">
+      <c r="J65" s="59" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="K65" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L65" s="35" t="inlineStr">
+      <c r="K65" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L65" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox).</t>
         </is>
       </c>
     </row>
     <row r="66" ht="39.55" customHeight="1" s="31">
-      <c r="B66" s="35" t="inlineStr">
+      <c r="B66" s="59" t="inlineStr">
         <is>
           <t>Nigeria</t>
         </is>
       </c>
-      <c r="C66" s="35" t="inlineStr">
+      <c r="C66" s="59" t="inlineStr">
         <is>
           <t>GIABA</t>
         </is>
       </c>
-      <c r="D66" s="35" t="inlineStr">
+      <c r="D66" s="59" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="E66" s="35" t="inlineStr">
+      <c r="E66" s="59" t="inlineStr">
         <is>
           <t>NAICOM</t>
         </is>
       </c>
-      <c r="F66" s="35" t="inlineStr">
+      <c r="F66" s="59" t="inlineStr">
         <is>
           <t>List of Insurance Companies that Complied with the MCR prescribed by NIIRA 2025</t>
         </is>
       </c>
-      <c r="G66" s="58" t="inlineStr">
+      <c r="G66" s="60" t="inlineStr">
         <is>
           <t>https://naicom.gov.ng/wp-content/uploads/2026/08/List-of-Insurance-Companies-that-Complied-with-the-MCR-Prescribed-by-NIIRA-2025.pdf</t>
         </is>
       </c>
-      <c r="H66" s="35" t="inlineStr">
+      <c r="H66" s="59" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="I66" s="35" t="inlineStr">
+      <c r="I66" s="59" t="inlineStr">
         <is>
           <t>48 insurers + 2 reinsurers verified compliant with new minimum capital (Aug 2026)</t>
         </is>
       </c>
-      <c r="J66" s="35" t="inlineStr">
+      <c r="J66" s="59" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="K66" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L66" s="35" t="inlineStr">
+      <c r="K66" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L66" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox). Most current insurer list.</t>
         </is>
       </c>
     </row>
     <row r="67" ht="52.2" customHeight="1" s="31">
-      <c r="B67" s="35" t="inlineStr">
+      <c r="B67" s="59" t="inlineStr">
         <is>
           <t>Nigeria</t>
         </is>
       </c>
-      <c r="C67" s="35" t="inlineStr">
+      <c r="C67" s="59" t="inlineStr">
         <is>
           <t>GIABA</t>
         </is>
       </c>
-      <c r="D67" s="35" t="inlineStr">
+      <c r="D67" s="59" t="inlineStr">
         <is>
           <t>Microfinance</t>
         </is>
       </c>
-      <c r="E67" s="35" t="inlineStr">
+      <c r="E67" s="59" t="inlineStr">
         <is>
           <t>Central Bank of Nigeria</t>
         </is>
       </c>
-      <c r="F67" s="35" t="inlineStr">
+      <c r="F67" s="59" t="inlineStr">
         <is>
           <t>List of Microfinance Banks as at December 31, 2021</t>
         </is>
       </c>
-      <c r="G67" s="58" t="inlineStr">
+      <c r="G67" s="60" t="inlineStr">
         <is>
           <t>https://www.cbn.gov.ng/Out/2022/FPRD/List%20of%20Microfinance%20Banks%20as%20at%20December%2031,%202021.pdf</t>
         </is>
       </c>
-      <c r="H67" s="35" t="inlineStr">
+      <c r="H67" s="59" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="I67" s="35" t="inlineStr">
+      <c r="I67" s="59" t="inlineStr">
         <is>
           <t>~900 MFBs with address, state, tier</t>
         </is>
       </c>
-      <c r="J67" s="35" t="inlineStr">
+      <c r="J67" s="59" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="K67" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L67" s="35" t="inlineStr">
+      <c r="K67" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L67" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox). Most recent named MFB list found is 2021.</t>
         </is>
       </c>
     </row>
     <row r="68" ht="39.55" customHeight="1" s="31">
-      <c r="B68" s="35" t="inlineStr">
+      <c r="B68" s="59" t="inlineStr">
         <is>
           <t>Nigeria</t>
         </is>
       </c>
-      <c r="C68" s="35" t="inlineStr">
+      <c r="C68" s="59" t="inlineStr">
         <is>
           <t>GIABA</t>
         </is>
       </c>
-      <c r="D68" s="35" t="inlineStr">
+      <c r="D68" s="59" t="inlineStr">
         <is>
           <t>Payments/E-money</t>
         </is>
       </c>
-      <c r="E68" s="35" t="inlineStr">
+      <c r="E68" s="59" t="inlineStr">
         <is>
           <t>Central Bank of Nigeria</t>
         </is>
       </c>
-      <c r="F68" s="35" t="inlineStr">
+      <c r="F68" s="59" t="inlineStr">
         <is>
           <t>Payment Service Providers</t>
         </is>
       </c>
-      <c r="G68" s="58" t="inlineStr">
+      <c r="G68" s="60" t="inlineStr">
         <is>
           <t>https://www.cbn.gov.ng/PaymentsSystem/PSPs.html</t>
         </is>
       </c>
-      <c r="H68" s="35" t="inlineStr">
+      <c r="H68" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I68" s="35" t="inlineStr">
+      <c r="I68" s="59" t="inlineStr">
         <is>
           <t>Licensed MMOs (Opay, PalmPay...), switching/processing (Interswitch, Flutterwave, Paystack), PSSPs (100+)</t>
         </is>
       </c>
-      <c r="J68" s="35" t="inlineStr">
+      <c r="J68" s="59" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="K68" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L68" s="35" t="inlineStr">
+      <c r="K68" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L68" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox).</t>
         </is>
       </c>
     </row>
     <row r="69" ht="26.85" customHeight="1" s="31">
-      <c r="B69" s="35" t="inlineStr">
+      <c r="B69" s="59" t="inlineStr">
         <is>
           <t>Nigeria</t>
         </is>
       </c>
-      <c r="C69" s="35" t="inlineStr">
+      <c r="C69" s="59" t="inlineStr">
         <is>
           <t>GIABA</t>
         </is>
       </c>
-      <c r="D69" s="35" t="inlineStr">
+      <c r="D69" s="59" t="inlineStr">
         <is>
           <t>Payments/E-money</t>
         </is>
       </c>
-      <c r="E69" s="35" t="inlineStr">
+      <c r="E69" s="59" t="inlineStr">
         <is>
           <t>Central Bank of Nigeria</t>
         </is>
       </c>
-      <c r="F69" s="35" t="inlineStr">
+      <c r="F69" s="59" t="inlineStr">
         <is>
           <t>Inst PSB (Payment Service Banks)</t>
         </is>
       </c>
-      <c r="G69" s="58" t="inlineStr">
+      <c r="G69" s="60" t="inlineStr">
         <is>
           <t>https://www.cbn.gov.ng/Supervision/Inst-PSB.asp</t>
         </is>
       </c>
-      <c r="H69" s="35" t="inlineStr">
+      <c r="H69" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I69" s="35" t="inlineStr">
+      <c r="I69" s="59" t="inlineStr">
         <is>
           <t>Payment service banks: 9PSB, Hope PSB, MoMo PSB, Moneymaster PSB</t>
         </is>
       </c>
-      <c r="J69" s="35" t="inlineStr">
+      <c r="J69" s="59" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="K69" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L69" s="35" t="inlineStr">
+      <c r="K69" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L69" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox).</t>
         </is>
       </c>
     </row>
     <row r="70" ht="39.55" customHeight="1" s="31">
-      <c r="B70" s="35" t="inlineStr">
+      <c r="B70" s="59" t="inlineStr">
         <is>
           <t>Nigeria</t>
         </is>
       </c>
-      <c r="C70" s="35" t="inlineStr">
+      <c r="C70" s="59" t="inlineStr">
         <is>
           <t>GIABA</t>
         </is>
       </c>
-      <c r="D70" s="35" t="inlineStr">
+      <c r="D70" s="59" t="inlineStr">
         <is>
           <t>Professional body</t>
         </is>
       </c>
-      <c r="E70" s="35" t="inlineStr">
+      <c r="E70" s="59" t="inlineStr">
         <is>
           <t>Nigerian Bar Association</t>
         </is>
       </c>
-      <c r="F70" s="35" t="inlineStr">
+      <c r="F70" s="59" t="inlineStr">
         <is>
           <t>NBA Find a Lawyer</t>
         </is>
       </c>
-      <c r="G70" s="58" t="inlineStr">
+      <c r="G70" s="60" t="inlineStr">
         <is>
           <t>https://nigerianbar.org.ng/find-lawyer</t>
         </is>
       </c>
-      <c r="H70" s="35" t="inlineStr">
+      <c r="H70" s="59" t="inlineStr">
         <is>
           <t>Search tool</t>
         </is>
       </c>
-      <c r="I70" s="35" t="inlineStr">
+      <c r="I70" s="59" t="inlineStr">
         <is>
           <t>Search lawyers by name/enrolment no.; NBA-SLP National Law Firms Directory (800+ firms) also launched 2026</t>
         </is>
       </c>
-      <c r="J70" s="35" t="inlineStr">
+      <c r="J70" s="59" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="K70" s="35" t="inlineStr">
+      <c r="K70" s="59" t="inlineStr">
         <is>
           <t>nein</t>
         </is>
       </c>
-      <c r="L70" s="35" t="inlineStr">
+      <c r="L70" s="59" t="inlineStr">
         <is>
           <t>URL from news report; NBA blog domain confirmed.</t>
         </is>
       </c>
     </row>
     <row r="71" ht="26.85" customHeight="1" s="31">
-      <c r="B71" s="35" t="inlineStr">
+      <c r="B71" s="59" t="inlineStr">
         <is>
           <t>Nigeria</t>
         </is>
       </c>
-      <c r="C71" s="35" t="inlineStr">
+      <c r="C71" s="59" t="inlineStr">
         <is>
           <t>GIABA</t>
         </is>
       </c>
-      <c r="D71" s="35" t="inlineStr">
+      <c r="D71" s="59" t="inlineStr">
         <is>
           <t>Professional body</t>
         </is>
       </c>
-      <c r="E71" s="35" t="inlineStr">
+      <c r="E71" s="59" t="inlineStr">
         <is>
           <t>Institute of Chartered Accountants of Nigeria</t>
         </is>
       </c>
-      <c r="F71" s="35" t="inlineStr">
+      <c r="F71" s="59" t="inlineStr">
         <is>
           <t>ICAN website</t>
         </is>
       </c>
-      <c r="G71" s="58" t="inlineStr">
+      <c r="G71" s="60" t="inlineStr">
         <is>
           <t>https://icanig.org</t>
         </is>
       </c>
-      <c r="H71" s="35" t="inlineStr">
+      <c r="H71" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I71" s="35" t="inlineStr">
+      <c r="I71" s="59" t="inlineStr">
         <is>
           <t>Member register (not publicly searchable confirmed)</t>
         </is>
       </c>
-      <c r="J71" s="35" t="inlineStr">
+      <c r="J71" s="59" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="K71" s="35" t="inlineStr">
+      <c r="K71" s="59" t="inlineStr">
         <is>
           <t>nein</t>
         </is>
       </c>
-      <c r="L71" s="35" t="inlineStr">
+      <c r="L71" s="59" t="inlineStr">
         <is>
           <t>Domain inferred from ICAN voter-list hosting; not confirmed.</t>
         </is>
       </c>
     </row>
     <row r="72" ht="52.2" customHeight="1" s="31">
-      <c r="B72" s="35" t="inlineStr">
+      <c r="B72" s="59" t="inlineStr">
         <is>
           <t>Nigeria</t>
         </is>
       </c>
-      <c r="C72" s="35" t="inlineStr">
+      <c r="C72" s="59" t="inlineStr">
         <is>
           <t>GIABA</t>
         </is>
       </c>
-      <c r="D72" s="35" t="inlineStr">
+      <c r="D72" s="59" t="inlineStr">
         <is>
           <t>VASP</t>
         </is>
       </c>
-      <c r="E72" s="35" t="inlineStr">
+      <c r="E72" s="59" t="inlineStr">
         <is>
           <t>Securities and Exchange Commission Nigeria</t>
         </is>
       </c>
-      <c r="F72" s="35" t="inlineStr">
+      <c r="F72" s="59" t="inlineStr">
         <is>
           <t>Registered FinTech Operators (RI and ARIP)</t>
         </is>
       </c>
-      <c r="G72" s="58" t="inlineStr">
+      <c r="G72" s="60" t="inlineStr">
         <is>
           <t>https://www.sec.gov.ng/fintech-and-innovation-hub-finport/registered-fintech-operators/</t>
         </is>
       </c>
-      <c r="H72" s="35" t="inlineStr">
+      <c r="H72" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I72" s="35" t="inlineStr">
+      <c r="I72" s="59" t="inlineStr">
         <is>
           <t>Digital-asset exchanges/VASPs admitted to ARIP (Busha, Quidax, Luno, KuCoin Nigeria, etc.)</t>
         </is>
       </c>
-      <c r="J72" s="35" t="inlineStr">
+      <c r="J72" s="59" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="K72" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L72" s="35" t="inlineStr">
+      <c r="K72" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L72" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox). ARIP = approval-in-principle, not full registration.</t>
         </is>
       </c>
     </row>
     <row r="73" ht="26.85" customHeight="1" s="31">
-      <c r="B73" s="35" t="inlineStr">
+      <c r="B73" s="59" t="inlineStr">
         <is>
           <t>Côte d'Ivoire</t>
         </is>
       </c>
-      <c r="C73" s="35" t="inlineStr">
+      <c r="C73" s="59" t="inlineStr">
         <is>
           <t>BCEAO</t>
         </is>
       </c>
-      <c r="D73" s="35" t="inlineStr">
+      <c r="D73" s="59" t="inlineStr">
         <is>
           <t>Banks</t>
         </is>
       </c>
-      <c r="E73" s="35" t="inlineStr">
+      <c r="E73" s="59" t="inlineStr">
         <is>
           <t>Commission Bancaire de l'UMOA</t>
         </is>
       </c>
-      <c r="F73" s="35" t="inlineStr">
+      <c r="F73" s="59" t="inlineStr">
         <is>
           <t>Liste Côte d'Ivoire 2025</t>
         </is>
       </c>
-      <c r="G73" s="58" t="inlineStr">
+      <c r="G73" s="60" t="inlineStr">
         <is>
           <t>https://www.cb-umoa.org/sites/default/files/Liste%20C%C3%B4te%20d'Ivoire%202025.pdf</t>
         </is>
       </c>
-      <c r="H73" s="35" t="inlineStr">
+      <c r="H73" s="59" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="I73" s="35" t="inlineStr">
+      <c r="I73" s="59" t="inlineStr">
         <is>
           <t>33 credit institutions licensed in CI</t>
         </is>
       </c>
-      <c r="J73" s="35" t="inlineStr">
+      <c r="J73" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K73" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L73" s="35" t="inlineStr">
+      <c r="K73" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L73" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox).</t>
         </is>
       </c>
     </row>
     <row r="74" ht="26.85" customHeight="1" s="31">
-      <c r="B74" s="35" t="inlineStr">
+      <c r="B74" s="59" t="inlineStr">
         <is>
           <t>Côte d'Ivoire</t>
         </is>
       </c>
-      <c r="C74" s="35" t="inlineStr">
+      <c r="C74" s="59" t="inlineStr">
         <is>
           <t>BCEAO</t>
         </is>
       </c>
-      <c r="D74" s="35" t="inlineStr">
+      <c r="D74" s="59" t="inlineStr">
         <is>
           <t>FIU</t>
         </is>
       </c>
-      <c r="E74" s="35" t="inlineStr">
+      <c r="E74" s="59" t="inlineStr">
         <is>
           <t>CENTIF-CI</t>
         </is>
       </c>
-      <c r="F74" s="35" t="inlineStr">
+      <c r="F74" s="59" t="inlineStr">
         <is>
           <t>Accueil - CENTIF CI</t>
         </is>
       </c>
-      <c r="G74" s="58" t="inlineStr">
+      <c r="G74" s="60" t="inlineStr">
         <is>
           <t>https://www.centif.ci/</t>
         </is>
       </c>
-      <c r="H74" s="35" t="inlineStr">
+      <c r="H74" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I74" s="35" t="inlineStr">
+      <c r="I74" s="59" t="inlineStr">
         <is>
           <t>FIU; annual reports, guidance, targeted financial sanctions list</t>
         </is>
       </c>
-      <c r="J74" s="35" t="inlineStr">
+      <c r="J74" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K74" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L74" s="35" t="inlineStr">
+      <c r="K74" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L74" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox).</t>
         </is>
       </c>
     </row>
     <row r="75" ht="26.85" customHeight="1" s="31">
-      <c r="B75" s="35" t="inlineStr">
+      <c r="B75" s="59" t="inlineStr">
         <is>
           <t>Côte d'Ivoire</t>
         </is>
       </c>
-      <c r="C75" s="35" t="inlineStr">
+      <c r="C75" s="59" t="inlineStr">
         <is>
           <t>BCEAO</t>
         </is>
       </c>
-      <c r="D75" s="35" t="inlineStr">
+      <c r="D75" s="59" t="inlineStr">
         <is>
           <t>FIU</t>
         </is>
       </c>
-      <c r="E75" s="35" t="inlineStr">
+      <c r="E75" s="59" t="inlineStr">
         <is>
           <t>CENTIF-CI</t>
         </is>
       </c>
-      <c r="F75" s="35" t="inlineStr">
+      <c r="F75" s="59" t="inlineStr">
         <is>
           <t>Liste des Sanctions Financières Ciblées (SFC)</t>
         </is>
       </c>
-      <c r="G75" s="58" t="inlineStr">
+      <c r="G75" s="60" t="inlineStr">
         <is>
           <t>https://www.centif.ci/liste-des-sanctions/</t>
         </is>
       </c>
-      <c r="H75" s="35" t="inlineStr">
+      <c r="H75" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I75" s="35" t="inlineStr">
+      <c r="I75" s="59" t="inlineStr">
         <is>
           <t>National TFS list for screening</t>
         </is>
       </c>
-      <c r="J75" s="35" t="inlineStr">
+      <c r="J75" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K75" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L75" s="35" t="inlineStr">
+      <c r="K75" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L75" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox).</t>
         </is>
       </c>
     </row>
     <row r="76" ht="26.85" customHeight="1" s="31">
-      <c r="B76" s="35" t="inlineStr">
+      <c r="B76" s="59" t="inlineStr">
         <is>
           <t>Côte d'Ivoire</t>
         </is>
       </c>
-      <c r="C76" s="35" t="inlineStr">
+      <c r="C76" s="59" t="inlineStr">
         <is>
           <t>BCEAO</t>
         </is>
       </c>
-      <c r="D76" s="35" t="inlineStr">
+      <c r="D76" s="59" t="inlineStr">
         <is>
           <t>Industry association</t>
         </is>
       </c>
-      <c r="E76" s="35" t="inlineStr">
+      <c r="E76" s="59" t="inlineStr">
         <is>
           <t>APBEF-CI</t>
         </is>
       </c>
-      <c r="F76" s="35" t="inlineStr">
+      <c r="F76" s="59" t="inlineStr">
         <is>
           <t>APBEF-CI - fiche annuaire</t>
         </is>
       </c>
-      <c r="G76" s="58" t="inlineStr">
+      <c r="G76" s="60" t="inlineStr">
         <is>
           <t>https://annuaireci.com/en/entreprises/apbef-ci-association-professionnelle-des-banques-et-etablissement-financier-de-cote-divoire/</t>
         </is>
       </c>
-      <c r="H76" s="35" t="inlineStr">
+      <c r="H76" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I76" s="35" t="inlineStr">
+      <c r="I76" s="59" t="inlineStr">
         <is>
           <t>Contact details of the bankers' association (Plateau, Abidjan)</t>
         </is>
       </c>
-      <c r="J76" s="35" t="inlineStr">
+      <c r="J76" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K76" s="35" t="inlineStr">
+      <c r="K76" s="59" t="inlineStr">
         <is>
           <t>nein</t>
         </is>
       </c>
-      <c r="L76" s="35" t="inlineStr">
+      <c r="L76" s="59" t="inlineStr">
         <is>
           <t>Third-party directory; official APBEF-CI site not found.</t>
         </is>
       </c>
     </row>
     <row r="77" ht="39.55" customHeight="1" s="31">
-      <c r="B77" s="35" t="inlineStr">
+      <c r="B77" s="59" t="inlineStr">
         <is>
           <t>Côte d'Ivoire</t>
         </is>
       </c>
-      <c r="C77" s="35" t="inlineStr">
+      <c r="C77" s="59" t="inlineStr">
         <is>
           <t>CIMA</t>
         </is>
       </c>
-      <c r="D77" s="35" t="inlineStr">
+      <c r="D77" s="59" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="E77" s="35" t="inlineStr">
+      <c r="E77" s="59" t="inlineStr">
         <is>
           <t>Direction des Assurances (Trésor CI)</t>
         </is>
       </c>
-      <c r="F77" s="35" t="inlineStr">
+      <c r="F77" s="59" t="inlineStr">
         <is>
           <t>Rapport d'activités du marché ivoirien des assurances 2019</t>
         </is>
       </c>
-      <c r="G77" s="58" t="inlineStr">
+      <c r="G77" s="60" t="inlineStr">
         <is>
           <t>https://assurances.tresor.gouv.ci/assur/wp-content/uploads/2022/01/Rapport-dactivit%C3%A9s-du-march%C3%A9-ivoirien-des-assurances_Exercice-2019-DEF-Copie-1.pdf</t>
         </is>
       </c>
-      <c r="H77" s="35" t="inlineStr">
+      <c r="H77" s="59" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="I77" s="35" t="inlineStr">
+      <c r="I77" s="59" t="inlineStr">
         <is>
           <t>Market report naming insurers (~33 companies, 305 brokers in 2021)</t>
         </is>
       </c>
-      <c r="J77" s="35" t="inlineStr">
+      <c r="J77" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K77" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L77" s="35" t="inlineStr">
+      <c r="K77" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L77" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox). Current named list not found.</t>
         </is>
       </c>
     </row>
     <row r="78" ht="52.2" customHeight="1" s="31">
-      <c r="B78" s="35" t="inlineStr">
+      <c r="B78" s="59" t="inlineStr">
         <is>
           <t>Côte d'Ivoire</t>
         </is>
       </c>
-      <c r="C78" s="35" t="inlineStr">
+      <c r="C78" s="59" t="inlineStr">
         <is>
           <t>BCEAO</t>
         </is>
       </c>
-      <c r="D78" s="35" t="inlineStr">
+      <c r="D78" s="59" t="inlineStr">
         <is>
           <t>Microfinance</t>
         </is>
       </c>
-      <c r="E78" s="35" t="inlineStr">
+      <c r="E78" s="59" t="inlineStr">
         <is>
           <t>Direction de la Réglementation et de la Surveillance des SFD (Trésor)</t>
         </is>
       </c>
-      <c r="F78" s="35" t="inlineStr">
+      <c r="F78" s="59" t="inlineStr">
         <is>
           <t>Portail microfinance du Trésor - monographies SFD</t>
         </is>
       </c>
-      <c r="G78" s="58" t="inlineStr">
+      <c r="G78" s="60" t="inlineStr">
         <is>
           <t>https://microfinance.tresor.gouv.ci/micro/wp-content/uploads/2020/07/monographie_2018.pdf</t>
         </is>
       </c>
-      <c r="H78" s="35" t="inlineStr">
+      <c r="H78" s="59" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="I78" s="35" t="inlineStr">
+      <c r="I78" s="59" t="inlineStr">
         <is>
           <t>Monograph naming SFDs (46 licensed in 2023)</t>
         </is>
       </c>
-      <c r="J78" s="35" t="inlineStr">
+      <c r="J78" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K78" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L78" s="35" t="inlineStr">
+      <c r="K78" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L78" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox). Older; site microfinance.tresor.gouv.ci hosts newer notes.</t>
         </is>
       </c>
     </row>
     <row r="79" ht="39.55" customHeight="1" s="31">
-      <c r="B79" s="35" t="inlineStr">
+      <c r="B79" s="59" t="inlineStr">
         <is>
           <t>Côte d'Ivoire</t>
         </is>
       </c>
-      <c r="C79" s="35" t="inlineStr">
+      <c r="C79" s="59" t="inlineStr">
         <is>
           <t>BCEAO</t>
         </is>
       </c>
-      <c r="D79" s="35" t="inlineStr">
+      <c r="D79" s="59" t="inlineStr">
         <is>
           <t>Payments/E-money</t>
         </is>
       </c>
-      <c r="E79" s="35" t="inlineStr">
+      <c r="E79" s="59" t="inlineStr">
         <is>
           <t>BCEAO</t>
         </is>
       </c>
-      <c r="F79" s="35" t="inlineStr">
+      <c r="F79" s="59" t="inlineStr">
         <is>
           <t>3 - Liste Côte d'Ivoire_2026 (EME)</t>
         </is>
       </c>
-      <c r="G79" s="58" t="inlineStr">
+      <c r="G79" s="60" t="inlineStr">
         <is>
           <t>https://www.bceao.int/sites/default/files/inline-files/3%20-%20Liste%20C%C3%B4te%20d_Ivoire_2026.pdf</t>
         </is>
       </c>
-      <c r="H79" s="35" t="inlineStr">
+      <c r="H79" s="59" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="I79" s="35" t="inlineStr">
+      <c r="I79" s="59" t="inlineStr">
         <is>
           <t>4 e-money issuers: Orange Money CI, MTN MFS CI, Moov Money CI, Djogana Pay (June 2026)</t>
         </is>
       </c>
-      <c r="J79" s="35" t="inlineStr">
+      <c r="J79" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K79" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L79" s="35" t="inlineStr">
+      <c r="K79" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L79" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox). Payment institutions (9) in BCEAO EP list.</t>
         </is>
       </c>
     </row>
     <row r="80" ht="26.85" customHeight="1" s="31">
-      <c r="B80" s="35" t="inlineStr">
+      <c r="B80" s="59" t="inlineStr">
         <is>
           <t>Côte d'Ivoire</t>
         </is>
       </c>
-      <c r="C80" s="35" t="inlineStr">
+      <c r="C80" s="59" t="inlineStr">
         <is>
           <t>BCEAO</t>
         </is>
       </c>
-      <c r="D80" s="35" t="inlineStr">
+      <c r="D80" s="59" t="inlineStr">
         <is>
           <t>Professional body</t>
         </is>
       </c>
-      <c r="E80" s="35" t="inlineStr">
+      <c r="E80" s="59" t="inlineStr">
         <is>
           <t>Ordre des Avocats - Barreau de Côte d'Ivoire</t>
         </is>
       </c>
-      <c r="F80" s="35" t="inlineStr">
+      <c r="F80" s="59" t="inlineStr">
         <is>
           <t>Ordre des avocats (site officiel)</t>
         </is>
       </c>
-      <c r="G80" s="58" t="inlineStr">
+      <c r="G80" s="60" t="inlineStr">
         <is>
           <t>https://web.ordredesavocats.ci/</t>
         </is>
       </c>
-      <c r="H80" s="35" t="inlineStr">
+      <c r="H80" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I80" s="35" t="inlineStr">
+      <c r="I80" s="59" t="inlineStr">
         <is>
           <t>Bar of CI; UK FCDO says detailed list of lawyers available on this site</t>
         </is>
       </c>
-      <c r="J80" s="35" t="inlineStr">
+      <c r="J80" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K80" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L80" s="35" t="inlineStr">
+      <c r="K80" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L80" s="59" t="inlineStr">
         <is>
           <t>Domain confirmed via PDF hosted on it; directory page not confirmed.</t>
         </is>
       </c>
     </row>
     <row r="81" ht="26.85" customHeight="1" s="31">
-      <c r="B81" s="35" t="inlineStr">
+      <c r="B81" s="59" t="inlineStr">
         <is>
           <t>Senegal</t>
         </is>
       </c>
-      <c r="C81" s="35" t="inlineStr">
+      <c r="C81" s="59" t="inlineStr">
         <is>
           <t>BCEAO</t>
         </is>
       </c>
-      <c r="D81" s="35" t="inlineStr">
+      <c r="D81" s="59" t="inlineStr">
         <is>
           <t>Banks</t>
         </is>
       </c>
-      <c r="E81" s="35" t="inlineStr">
+      <c r="E81" s="59" t="inlineStr">
         <is>
           <t>Commission Bancaire de l'UMOA</t>
         </is>
       </c>
-      <c r="F81" s="35" t="inlineStr">
+      <c r="F81" s="59" t="inlineStr">
         <is>
           <t>Liste Sénégal 2025</t>
         </is>
       </c>
-      <c r="G81" s="58" t="inlineStr">
+      <c r="G81" s="60" t="inlineStr">
         <is>
           <t>https://www.cb-umoa.org/sites/default/files/Liste%20S%C3%A9n%C3%A9gal%202025.pdf</t>
         </is>
       </c>
-      <c r="H81" s="35" t="inlineStr">
+      <c r="H81" s="59" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="I81" s="35" t="inlineStr">
+      <c r="I81" s="59" t="inlineStr">
         <is>
           <t>33 credit institutions licensed in Senegal</t>
         </is>
       </c>
-      <c r="J81" s="35" t="inlineStr">
+      <c r="J81" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K81" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L81" s="35" t="inlineStr">
+      <c r="K81" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L81" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox).</t>
         </is>
       </c>
     </row>
     <row r="82" ht="26.85" customHeight="1" s="31">
-      <c r="B82" s="35" t="inlineStr">
+      <c r="B82" s="59" t="inlineStr">
         <is>
           <t>Senegal</t>
         </is>
       </c>
-      <c r="C82" s="35" t="inlineStr">
+      <c r="C82" s="59" t="inlineStr">
         <is>
           <t>BCEAO</t>
         </is>
       </c>
-      <c r="D82" s="35" t="inlineStr">
+      <c r="D82" s="59" t="inlineStr">
         <is>
           <t>FIU</t>
         </is>
       </c>
-      <c r="E82" s="35" t="inlineStr">
+      <c r="E82" s="59" t="inlineStr">
         <is>
           <t>CENTIF Sénégal</t>
         </is>
       </c>
-      <c r="F82" s="35" t="inlineStr">
+      <c r="F82" s="59" t="inlineStr">
         <is>
           <t>CENTIF</t>
         </is>
       </c>
-      <c r="G82" s="58" t="inlineStr">
+      <c r="G82" s="60" t="inlineStr">
         <is>
           <t>https://www.centif.sn/fr/</t>
         </is>
       </c>
-      <c r="H82" s="35" t="inlineStr">
+      <c r="H82" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I82" s="35" t="inlineStr">
+      <c r="I82" s="59" t="inlineStr">
         <is>
           <t>FIU; activity reports, typologies, e-Delta reporting</t>
         </is>
       </c>
-      <c r="J82" s="35" t="inlineStr">
+      <c r="J82" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K82" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L82" s="35" t="inlineStr">
+      <c r="K82" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L82" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox).</t>
         </is>
       </c>
     </row>
     <row r="83" ht="26.85" customHeight="1" s="31">
-      <c r="B83" s="35" t="inlineStr">
+      <c r="B83" s="59" t="inlineStr">
         <is>
           <t>Senegal</t>
         </is>
       </c>
-      <c r="C83" s="35" t="inlineStr">
+      <c r="C83" s="59" t="inlineStr">
         <is>
           <t>BCEAO</t>
         </is>
       </c>
-      <c r="D83" s="35" t="inlineStr">
+      <c r="D83" s="59" t="inlineStr">
         <is>
           <t>FIU</t>
         </is>
       </c>
-      <c r="E83" s="35" t="inlineStr">
+      <c r="E83" s="59" t="inlineStr">
         <is>
           <t>CENTIF Sénégal</t>
         </is>
       </c>
-      <c r="F83" s="35" t="inlineStr">
+      <c r="F83" s="59" t="inlineStr">
         <is>
           <t>Rapport d'activités 2025</t>
         </is>
       </c>
-      <c r="G83" s="58" t="inlineStr">
+      <c r="G83" s="60" t="inlineStr">
         <is>
           <t>https://www.centif.sn/asset/attachements/rapports/Rapport_activite_2025.pdf.pdf</t>
         </is>
       </c>
-      <c r="H83" s="35" t="inlineStr">
+      <c r="H83" s="59" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="I83" s="35" t="inlineStr">
+      <c r="I83" s="59" t="inlineStr">
         <is>
           <t>STR statistics by sector (banks ~83%), obliged-entity scope after 2024 law</t>
         </is>
       </c>
-      <c r="J83" s="35" t="inlineStr">
+      <c r="J83" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K83" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L83" s="35" t="inlineStr">
+      <c r="K83" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L83" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox).</t>
         </is>
       </c>
     </row>
     <row r="84" ht="26.85" customHeight="1" s="31">
-      <c r="B84" s="35" t="inlineStr">
+      <c r="B84" s="59" t="inlineStr">
         <is>
           <t>Senegal</t>
         </is>
       </c>
-      <c r="C84" s="35" t="inlineStr">
+      <c r="C84" s="59" t="inlineStr">
         <is>
           <t>BCEAO</t>
         </is>
       </c>
-      <c r="D84" s="35" t="inlineStr">
+      <c r="D84" s="59" t="inlineStr">
         <is>
           <t>Microfinance</t>
         </is>
       </c>
-      <c r="E84" s="35" t="inlineStr">
+      <c r="E84" s="59" t="inlineStr">
         <is>
           <t>DRS-SFD (Ministère des Finances)</t>
         </is>
       </c>
-      <c r="F84" s="35" t="inlineStr">
+      <c r="F84" s="59" t="inlineStr">
         <is>
           <t>DRS-SFD - no list URL located</t>
         </is>
       </c>
-      <c r="G84" s="35" t="n"/>
-      <c r="H84" s="35" t="inlineStr">
+      <c r="G84" s="59" t="n"/>
+      <c r="H84" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I84" s="35" t="inlineStr">
+      <c r="I84" s="59" t="inlineStr">
         <is>
           <t>~297 licensed SFDs (Oct 2025)</t>
         </is>
       </c>
-      <c r="J84" s="35" t="inlineStr">
+      <c r="J84" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K84" s="35" t="inlineStr">
+      <c r="K84" s="59" t="inlineStr">
         <is>
           <t>nein</t>
         </is>
       </c>
-      <c r="L84" s="35" t="inlineStr">
+      <c r="L84" s="59" t="inlineStr">
         <is>
           <t>No public named list found; request from DRS-SFD.</t>
         </is>
       </c>
     </row>
     <row r="85" ht="39.55" customHeight="1" s="31">
-      <c r="B85" s="35" t="inlineStr">
+      <c r="B85" s="59" t="inlineStr">
         <is>
           <t>Senegal</t>
         </is>
       </c>
-      <c r="C85" s="35" t="inlineStr">
+      <c r="C85" s="59" t="inlineStr">
         <is>
           <t>BCEAO</t>
         </is>
       </c>
-      <c r="D85" s="35" t="inlineStr">
+      <c r="D85" s="59" t="inlineStr">
         <is>
           <t>Payments/E-money</t>
         </is>
       </c>
-      <c r="E85" s="35" t="inlineStr">
+      <c r="E85" s="59" t="inlineStr">
         <is>
           <t>Commission Bancaire de l'UMOA</t>
         </is>
       </c>
-      <c r="F85" s="35" t="inlineStr">
+      <c r="F85" s="59" t="inlineStr">
         <is>
           <t>Liste des EME SN 2025</t>
         </is>
       </c>
-      <c r="G85" s="58" t="inlineStr">
+      <c r="G85" s="60" t="inlineStr">
         <is>
           <t>https://cb-umoa.org/sites/default/files/Liste%20des%20EME%20SN_2025.pdf</t>
         </is>
       </c>
-      <c r="H85" s="35" t="inlineStr">
+      <c r="H85" s="59" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="I85" s="35" t="inlineStr">
+      <c r="I85" s="59" t="inlineStr">
         <is>
           <t>E-money issuers: Orange Finances Mobiles SN, Mobile Cash (Free Money), Wave Digital Finance, QuickPay</t>
         </is>
       </c>
-      <c r="J85" s="35" t="inlineStr">
+      <c r="J85" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K85" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L85" s="35" t="inlineStr">
+      <c r="K85" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L85" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox). 11 payment institutions in BCEAO EP list.</t>
         </is>
       </c>
     </row>
     <row r="86" ht="26.85" customHeight="1" s="31">
-      <c r="B86" s="35" t="inlineStr">
+      <c r="B86" s="59" t="inlineStr">
         <is>
           <t>Senegal</t>
         </is>
       </c>
-      <c r="C86" s="35" t="inlineStr">
+      <c r="C86" s="59" t="inlineStr">
         <is>
           <t>BCEAO</t>
         </is>
       </c>
-      <c r="D86" s="35" t="inlineStr">
+      <c r="D86" s="59" t="inlineStr">
         <is>
           <t>Professional body</t>
         </is>
       </c>
-      <c r="E86" s="35" t="inlineStr">
+      <c r="E86" s="59" t="inlineStr">
         <is>
           <t>ONECCA Sénégal</t>
         </is>
       </c>
-      <c r="F86" s="35" t="inlineStr">
+      <c r="F86" s="59" t="inlineStr">
         <is>
           <t>ONECCA - site officiel</t>
         </is>
       </c>
-      <c r="G86" s="58" t="inlineStr">
+      <c r="G86" s="60" t="inlineStr">
         <is>
           <t>https://www.onecca.sn</t>
         </is>
       </c>
-      <c r="H86" s="35" t="inlineStr">
+      <c r="H86" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I86" s="35" t="inlineStr">
+      <c r="I86" s="59" t="inlineStr">
         <is>
           <t>Chartered accountants/auditors order (mandatory registration)</t>
         </is>
       </c>
-      <c r="J86" s="35" t="inlineStr">
+      <c r="J86" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K86" s="35" t="inlineStr">
+      <c r="K86" s="59" t="inlineStr">
         <is>
           <t>nein</t>
         </is>
       </c>
-      <c r="L86" s="35" t="inlineStr">
+      <c r="L86" s="59" t="inlineStr">
         <is>
           <t>Domain cited by secondary sources; not confirmed in index.</t>
         </is>
       </c>
     </row>
     <row r="87" ht="39.55" customHeight="1" s="31">
-      <c r="B87" s="35" t="inlineStr">
+      <c r="B87" s="59" t="inlineStr">
         <is>
           <t>Cameroon</t>
         </is>
       </c>
-      <c r="C87" s="35" t="inlineStr">
+      <c r="C87" s="59" t="inlineStr">
         <is>
           <t>COBAC/BEAC</t>
         </is>
       </c>
-      <c r="D87" s="35" t="inlineStr">
+      <c r="D87" s="59" t="inlineStr">
         <is>
           <t>Banks</t>
         </is>
       </c>
-      <c r="E87" s="35" t="inlineStr">
+      <c r="E87" s="59" t="inlineStr">
         <is>
           <t>COBAC</t>
         </is>
       </c>
-      <c r="F87" s="35" t="inlineStr">
+      <c r="F87" s="59" t="inlineStr">
         <is>
           <t>COBAC - SOCIETE GENERALE CAMEROUN (example per-institution page)</t>
         </is>
       </c>
-      <c r="G87" s="58" t="inlineStr">
+      <c r="G87" s="60" t="inlineStr">
         <is>
           <t>http://www.sgcobac.org/jcms/ess_6899/en/societe-generale-cameroun</t>
         </is>
       </c>
-      <c r="H87" s="35" t="inlineStr">
+      <c r="H87" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I87" s="35" t="inlineStr">
+      <c r="I87" s="59" t="inlineStr">
         <is>
           <t>Per-bank page in COBAC directory (Cameroon ~17-19 banks)</t>
         </is>
       </c>
-      <c r="J87" s="35" t="inlineStr">
+      <c r="J87" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K87" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L87" s="35" t="inlineStr">
+      <c r="K87" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L87" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox).</t>
         </is>
       </c>
     </row>
     <row r="88" ht="26.85" customHeight="1" s="31">
-      <c r="B88" s="35" t="inlineStr">
+      <c r="B88" s="59" t="inlineStr">
         <is>
           <t>Cameroon</t>
         </is>
       </c>
-      <c r="C88" s="35" t="inlineStr">
+      <c r="C88" s="59" t="inlineStr">
         <is>
           <t>COBAC/BEAC</t>
         </is>
       </c>
-      <c r="D88" s="35" t="inlineStr">
+      <c r="D88" s="59" t="inlineStr">
         <is>
           <t>FIU</t>
         </is>
       </c>
-      <c r="E88" s="35" t="inlineStr">
+      <c r="E88" s="59" t="inlineStr">
         <is>
           <t>ANIF Cameroun</t>
         </is>
       </c>
-      <c r="F88" s="35" t="inlineStr">
+      <c r="F88" s="59" t="inlineStr">
         <is>
           <t>ANIF Cameroun - no official website located</t>
         </is>
       </c>
-      <c r="G88" s="35" t="n"/>
-      <c r="H88" s="35" t="inlineStr">
+      <c r="G88" s="59" t="n"/>
+      <c r="H88" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I88" s="35" t="inlineStr">
+      <c r="I88" s="59" t="inlineStr">
         <is>
           <t>FIU (Décret 2005/187); reporting entities per CEMAC Reg. 01/CEMAC/UMAC/CM</t>
         </is>
       </c>
-      <c r="J88" s="35" t="inlineStr">
+      <c r="J88" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K88" s="35" t="inlineStr">
+      <c r="K88" s="59" t="inlineStr">
         <is>
           <t>nein</t>
         </is>
       </c>
-      <c r="L88" s="35" t="inlineStr">
+      <c r="L88" s="59" t="inlineStr">
         <is>
           <t>No official domain found; do not guess.</t>
         </is>
       </c>
     </row>
     <row r="89" ht="26.85" customHeight="1" s="31">
-      <c r="B89" s="35" t="inlineStr">
+      <c r="B89" s="59" t="inlineStr">
         <is>
           <t>Cameroon</t>
         </is>
       </c>
-      <c r="C89" s="35" t="inlineStr">
+      <c r="C89" s="59" t="inlineStr">
         <is>
           <t>COBAC/BEAC</t>
         </is>
       </c>
-      <c r="D89" s="35" t="inlineStr">
+      <c r="D89" s="59" t="inlineStr">
         <is>
           <t>Industry association</t>
         </is>
       </c>
-      <c r="E89" s="35" t="inlineStr">
+      <c r="E89" s="59" t="inlineStr">
         <is>
           <t>APECCAM</t>
         </is>
       </c>
-      <c r="F89" s="35" t="inlineStr">
+      <c r="F89" s="59" t="inlineStr">
         <is>
           <t>L'APECCAM au fil des ans</t>
         </is>
       </c>
-      <c r="G89" s="58" t="inlineStr">
+      <c r="G89" s="60" t="inlineStr">
         <is>
           <t>https://www.osidimbea.cm/associations/patrons/apeccam-fil/</t>
         </is>
       </c>
-      <c r="H89" s="35" t="inlineStr">
+      <c r="H89" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I89" s="35" t="inlineStr">
+      <c r="I89" s="59" t="inlineStr">
         <is>
           <t>Bankers' association profile (27 member banks &amp; FIs)</t>
         </is>
       </c>
-      <c r="J89" s="35" t="inlineStr">
+      <c r="J89" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K89" s="35" t="inlineStr">
+      <c r="K89" s="59" t="inlineStr">
         <is>
           <t>nein</t>
         </is>
       </c>
-      <c r="L89" s="35" t="inlineStr">
+      <c r="L89" s="59" t="inlineStr">
         <is>
           <t>Third-party page; official site not found.</t>
         </is>
       </c>
     </row>
     <row r="90" ht="39.55" customHeight="1" s="31">
-      <c r="B90" s="35" t="inlineStr">
+      <c r="B90" s="59" t="inlineStr">
         <is>
           <t>Cameroon</t>
         </is>
       </c>
-      <c r="C90" s="35" t="inlineStr">
+      <c r="C90" s="59" t="inlineStr">
         <is>
           <t>COBAC/BEAC</t>
         </is>
       </c>
-      <c r="D90" s="35" t="inlineStr">
+      <c r="D90" s="59" t="inlineStr">
         <is>
           <t>Microfinance</t>
         </is>
       </c>
-      <c r="E90" s="35" t="inlineStr">
+      <c r="E90" s="59" t="inlineStr">
         <is>
           <t>MINFI Cameroun</t>
         </is>
       </c>
-      <c r="F90" s="35" t="inlineStr">
+      <c r="F90" s="59" t="inlineStr">
         <is>
           <t>Liste des Établissements de Microfinance Agréés au 31 décembre 2021</t>
         </is>
       </c>
-      <c r="G90" s="58" t="inlineStr">
+      <c r="G90" s="60" t="inlineStr">
         <is>
           <t>https://minfi.gov.cm/liste-des-etablissements-de-microfinance-agrees-au-31-decembre-2021/</t>
         </is>
       </c>
-      <c r="H90" s="35" t="inlineStr">
+      <c r="H90" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I90" s="35" t="inlineStr">
+      <c r="I90" s="59" t="inlineStr">
         <is>
           <t>EMFs by category &amp; region with approval ref; 2026 list (385 EMFs, as at 31 Dec 2025) published by MINFI per press</t>
         </is>
       </c>
-      <c r="J90" s="35" t="inlineStr">
+      <c r="J90" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K90" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L90" s="35" t="inlineStr">
+      <c r="K90" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L90" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox). Look for 2025 version on same site.</t>
         </is>
       </c>
     </row>
     <row r="91" ht="26.85" customHeight="1" s="31">
-      <c r="B91" s="35" t="inlineStr">
+      <c r="B91" s="59" t="inlineStr">
         <is>
           <t>Cameroon</t>
         </is>
       </c>
-      <c r="C91" s="35" t="inlineStr">
+      <c r="C91" s="59" t="inlineStr">
         <is>
           <t>COBAC/BEAC</t>
         </is>
       </c>
-      <c r="D91" s="35" t="inlineStr">
+      <c r="D91" s="59" t="inlineStr">
         <is>
           <t>Professional body</t>
         </is>
       </c>
-      <c r="E91" s="35" t="inlineStr">
+      <c r="E91" s="59" t="inlineStr">
         <is>
           <t>Barreau du Cameroun</t>
         </is>
       </c>
-      <c r="F91" s="35" t="inlineStr">
+      <c r="F91" s="59" t="inlineStr">
         <is>
           <t>Ordre des Avocats au Barreau du Cameroun</t>
         </is>
       </c>
-      <c r="G91" s="58" t="inlineStr">
+      <c r="G91" s="60" t="inlineStr">
         <is>
           <t>https://barreaucameroun.org/fr/</t>
         </is>
       </c>
-      <c r="H91" s="35" t="inlineStr">
+      <c r="H91" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I91" s="35" t="inlineStr">
+      <c r="I91" s="59" t="inlineStr">
         <is>
           <t>Bar website (communiqués; tableau not found online)</t>
         </is>
       </c>
-      <c r="J91" s="35" t="inlineStr">
+      <c r="J91" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K91" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L91" s="35" t="inlineStr">
+      <c r="K91" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L91" s="59" t="inlineStr">
         <is>
           <t>Domain confirmed via PDFs hosted on it.</t>
         </is>
       </c>
     </row>
     <row r="92" ht="26.85" customHeight="1" s="31">
-      <c r="B92" s="35" t="inlineStr">
+      <c r="B92" s="59" t="inlineStr">
         <is>
           <t>Cameroon</t>
         </is>
       </c>
-      <c r="C92" s="35" t="inlineStr">
+      <c r="C92" s="59" t="inlineStr">
         <is>
           <t>COBAC/BEAC</t>
         </is>
       </c>
-      <c r="D92" s="35" t="inlineStr">
+      <c r="D92" s="59" t="inlineStr">
         <is>
           <t>Professional body</t>
         </is>
       </c>
-      <c r="E92" s="35" t="inlineStr">
+      <c r="E92" s="59" t="inlineStr">
         <is>
           <t>ONECCA Cameroun</t>
         </is>
       </c>
-      <c r="F92" s="35" t="inlineStr">
+      <c r="F92" s="59" t="inlineStr">
         <is>
           <t>ONECCA - site officiel</t>
         </is>
       </c>
-      <c r="G92" s="58" t="inlineStr">
+      <c r="G92" s="60" t="inlineStr">
         <is>
           <t>https://www.onecca.cm</t>
         </is>
       </c>
-      <c r="H92" s="35" t="inlineStr">
+      <c r="H92" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I92" s="35" t="inlineStr">
+      <c r="I92" s="59" t="inlineStr">
         <is>
           <t>Chartered accountants order (~240 members 2017)</t>
         </is>
       </c>
-      <c r="J92" s="35" t="inlineStr">
+      <c r="J92" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K92" s="35" t="inlineStr">
+      <c r="K92" s="59" t="inlineStr">
         <is>
           <t>nein</t>
         </is>
       </c>
-      <c r="L92" s="35" t="inlineStr">
+      <c r="L92" s="59" t="inlineStr">
         <is>
           <t>Domain cited by secondary source.</t>
         </is>
       </c>
     </row>
     <row r="93" ht="39.55" customHeight="1" s="31">
-      <c r="B93" s="35" t="inlineStr">
+      <c r="B93" s="59" t="inlineStr">
         <is>
           <t>Ghana</t>
         </is>
       </c>
-      <c r="C93" s="35" t="inlineStr">
+      <c r="C93" s="59" t="inlineStr">
         <is>
           <t>GIABA</t>
         </is>
       </c>
-      <c r="D93" s="35" t="inlineStr">
+      <c r="D93" s="59" t="inlineStr">
         <is>
           <t>Banks</t>
         </is>
       </c>
-      <c r="E93" s="35" t="inlineStr">
+      <c r="E93" s="59" t="inlineStr">
         <is>
           <t>Bank of Ghana</t>
         </is>
       </c>
-      <c r="F93" s="35" t="inlineStr">
+      <c r="F93" s="59" t="inlineStr">
         <is>
           <t>Banks</t>
         </is>
       </c>
-      <c r="G93" s="58" t="inlineStr">
+      <c r="G93" s="60" t="inlineStr">
         <is>
           <t>https://www.bog.gov.gh/supervision-regulation/registered-institutions/banks/</t>
         </is>
       </c>
-      <c r="H93" s="35" t="inlineStr">
+      <c r="H93" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I93" s="35" t="inlineStr">
+      <c r="I93" s="59" t="inlineStr">
         <is>
           <t>~23 universal banks with address, phone, website, email</t>
         </is>
       </c>
-      <c r="J93" s="35" t="inlineStr">
+      <c r="J93" s="59" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="K93" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L93" s="35" t="inlineStr">
+      <c r="K93" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L93" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox). Contact details YES.</t>
         </is>
       </c>
     </row>
     <row r="94" ht="26.85" customHeight="1" s="31">
-      <c r="B94" s="35" t="inlineStr">
+      <c r="B94" s="59" t="inlineStr">
         <is>
           <t>Ghana</t>
         </is>
       </c>
-      <c r="C94" s="35" t="inlineStr">
+      <c r="C94" s="59" t="inlineStr">
         <is>
           <t>GIABA</t>
         </is>
       </c>
-      <c r="D94" s="35" t="inlineStr">
+      <c r="D94" s="59" t="inlineStr">
         <is>
           <t>Banks</t>
         </is>
       </c>
-      <c r="E94" s="35" t="inlineStr">
+      <c r="E94" s="59" t="inlineStr">
         <is>
           <t>Bank of Ghana</t>
         </is>
       </c>
-      <c r="F94" s="35" t="inlineStr">
+      <c r="F94" s="59" t="inlineStr">
         <is>
           <t>All Institutions</t>
         </is>
       </c>
-      <c r="G94" s="58" t="inlineStr">
+      <c r="G94" s="60" t="inlineStr">
         <is>
           <t>https://www.bog.gov.gh/supervision-regulation/all-institutions/</t>
         </is>
       </c>
-      <c r="H94" s="35" t="inlineStr">
+      <c r="H94" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I94" s="35" t="inlineStr">
+      <c r="I94" s="59" t="inlineStr">
         <is>
           <t>Hub: banks, savings &amp; loans, rural/community banks, deposit-taking MFIs, forex bureaux</t>
         </is>
       </c>
-      <c r="J94" s="35" t="inlineStr">
+      <c r="J94" s="59" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="K94" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L94" s="35" t="inlineStr">
+      <c r="K94" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L94" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox).</t>
         </is>
       </c>
     </row>
     <row r="95" ht="26.85" customHeight="1" s="31">
-      <c r="B95" s="35" t="inlineStr">
+      <c r="B95" s="59" t="inlineStr">
         <is>
           <t>Ghana</t>
         </is>
       </c>
-      <c r="C95" s="35" t="inlineStr">
+      <c r="C95" s="59" t="inlineStr">
         <is>
           <t>GIABA</t>
         </is>
       </c>
-      <c r="D95" s="35" t="inlineStr">
+      <c r="D95" s="59" t="inlineStr">
         <is>
           <t>Capital markets</t>
         </is>
       </c>
-      <c r="E95" s="35" t="inlineStr">
+      <c r="E95" s="59" t="inlineStr">
         <is>
           <t>SEC Ghana</t>
         </is>
       </c>
-      <c r="F95" s="35" t="inlineStr">
+      <c r="F95" s="59" t="inlineStr">
         <is>
           <t>SEC Ghana - Operator Types</t>
         </is>
       </c>
-      <c r="G95" s="58" t="inlineStr">
+      <c r="G95" s="60" t="inlineStr">
         <is>
           <t>https://licensees.sec.gov.gh/</t>
         </is>
       </c>
-      <c r="H95" s="35" t="inlineStr">
+      <c r="H95" s="59" t="inlineStr">
         <is>
           <t>Search tool</t>
         </is>
       </c>
-      <c r="I95" s="35" t="inlineStr">
+      <c r="I95" s="59" t="inlineStr">
         <is>
           <t>Licensees by type: 34 broker-dealers, 85 fund managers, custodians, etc.</t>
         </is>
       </c>
-      <c r="J95" s="35" t="inlineStr">
+      <c r="J95" s="59" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="K95" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L95" s="35" t="inlineStr">
+      <c r="K95" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L95" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox).</t>
         </is>
       </c>
     </row>
     <row r="96" ht="26.85" customHeight="1" s="31">
-      <c r="B96" s="35" t="inlineStr">
+      <c r="B96" s="59" t="inlineStr">
         <is>
           <t>Ghana</t>
         </is>
       </c>
-      <c r="C96" s="35" t="inlineStr">
+      <c r="C96" s="59" t="inlineStr">
         <is>
           <t>GIABA</t>
         </is>
       </c>
-      <c r="D96" s="35" t="inlineStr">
+      <c r="D96" s="59" t="inlineStr">
         <is>
           <t>FIU</t>
         </is>
       </c>
-      <c r="E96" s="35" t="inlineStr">
+      <c r="E96" s="59" t="inlineStr">
         <is>
           <t>Financial Intelligence Centre Ghana</t>
         </is>
       </c>
-      <c r="F96" s="35" t="inlineStr">
+      <c r="F96" s="59" t="inlineStr">
         <is>
           <t>FIC Home</t>
         </is>
       </c>
-      <c r="G96" s="58" t="inlineStr">
+      <c r="G96" s="60" t="inlineStr">
         <is>
           <t>https://www.fic.gov.gh/</t>
         </is>
       </c>
-      <c r="H96" s="35" t="inlineStr">
+      <c r="H96" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I96" s="35" t="inlineStr">
+      <c r="I96" s="59" t="inlineStr">
         <is>
           <t>FIU; guidelines for accountable institutions (Act 1044)</t>
         </is>
       </c>
-      <c r="J96" s="35" t="inlineStr">
+      <c r="J96" s="59" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="K96" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L96" s="35" t="inlineStr">
+      <c r="K96" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L96" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox).</t>
         </is>
       </c>
     </row>
     <row r="97" ht="26.85" customHeight="1" s="31">
-      <c r="B97" s="35" t="inlineStr">
+      <c r="B97" s="59" t="inlineStr">
         <is>
           <t>Ghana</t>
         </is>
       </c>
-      <c r="C97" s="35" t="inlineStr">
+      <c r="C97" s="59" t="inlineStr">
         <is>
           <t>GIABA</t>
         </is>
       </c>
-      <c r="D97" s="35" t="inlineStr">
+      <c r="D97" s="59" t="inlineStr">
         <is>
           <t>Industry association</t>
         </is>
       </c>
-      <c r="E97" s="35" t="inlineStr">
+      <c r="E97" s="59" t="inlineStr">
         <is>
           <t>Ghana Association of Banks</t>
         </is>
       </c>
-      <c r="F97" s="35" t="inlineStr">
+      <c r="F97" s="59" t="inlineStr">
         <is>
           <t>GAB - Who we are</t>
         </is>
       </c>
-      <c r="G97" s="58" t="inlineStr">
+      <c r="G97" s="60" t="inlineStr">
         <is>
           <t>https://gab.com.gh/about</t>
         </is>
       </c>
-      <c r="H97" s="35" t="inlineStr">
+      <c r="H97" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I97" s="35" t="inlineStr">
+      <c r="I97" s="59" t="inlineStr">
         <is>
           <t>25 member institutions (incl. ARB Apex Bank)</t>
         </is>
       </c>
-      <c r="J97" s="35" t="inlineStr">
+      <c r="J97" s="59" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="K97" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L97" s="35" t="inlineStr">
+      <c r="K97" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L97" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox).</t>
         </is>
       </c>
     </row>
     <row r="98" ht="26.85" customHeight="1" s="31">
-      <c r="B98" s="35" t="inlineStr">
+      <c r="B98" s="59" t="inlineStr">
         <is>
           <t>Ghana</t>
         </is>
       </c>
-      <c r="C98" s="35" t="inlineStr">
+      <c r="C98" s="59" t="inlineStr">
         <is>
           <t>GIABA</t>
         </is>
       </c>
-      <c r="D98" s="35" t="inlineStr">
+      <c r="D98" s="59" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="E98" s="35" t="inlineStr">
+      <c r="E98" s="59" t="inlineStr">
         <is>
           <t>National Insurance Commission</t>
         </is>
       </c>
-      <c r="F98" s="35" t="inlineStr">
+      <c r="F98" s="59" t="inlineStr">
         <is>
           <t>Insurers &amp; Reinsurers</t>
         </is>
       </c>
-      <c r="G98" s="58" t="inlineStr">
+      <c r="G98" s="60" t="inlineStr">
         <is>
           <t>https://nicgh.org/insurers-reinsurers/reinsurers/</t>
         </is>
       </c>
-      <c r="H98" s="35" t="inlineStr">
+      <c r="H98" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I98" s="35" t="inlineStr">
+      <c r="I98" s="59" t="inlineStr">
         <is>
           <t>Licensed reinsurers; sibling pages for life &amp; non-life insurers</t>
         </is>
       </c>
-      <c r="J98" s="35" t="inlineStr">
+      <c r="J98" s="59" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="K98" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L98" s="35" t="inlineStr">
+      <c r="K98" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L98" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox).</t>
         </is>
       </c>
     </row>
     <row r="99" ht="26.85" customHeight="1" s="31">
-      <c r="B99" s="35" t="inlineStr">
+      <c r="B99" s="59" t="inlineStr">
         <is>
           <t>Ghana</t>
         </is>
       </c>
-      <c r="C99" s="35" t="inlineStr">
+      <c r="C99" s="59" t="inlineStr">
         <is>
           <t>GIABA</t>
         </is>
       </c>
-      <c r="D99" s="35" t="inlineStr">
+      <c r="D99" s="59" t="inlineStr">
         <is>
           <t>Microfinance</t>
         </is>
       </c>
-      <c r="E99" s="35" t="inlineStr">
+      <c r="E99" s="59" t="inlineStr">
         <is>
           <t>Bank of Ghana</t>
         </is>
       </c>
-      <c r="F99" s="35" t="inlineStr">
+      <c r="F99" s="59" t="inlineStr">
         <is>
           <t>Savings &amp; Loans</t>
         </is>
       </c>
-      <c r="G99" s="58" t="inlineStr">
+      <c r="G99" s="60" t="inlineStr">
         <is>
           <t>https://www.bog.gov.gh/supervision-regulation/registered-institutions/savings-loans/</t>
         </is>
       </c>
-      <c r="H99" s="35" t="inlineStr">
+      <c r="H99" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I99" s="35" t="inlineStr">
+      <c r="I99" s="59" t="inlineStr">
         <is>
           <t>Licensed savings &amp; loans companies</t>
         </is>
       </c>
-      <c r="J99" s="35" t="inlineStr">
+      <c r="J99" s="59" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="K99" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L99" s="35" t="inlineStr">
+      <c r="K99" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L99" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox).</t>
         </is>
       </c>
     </row>
     <row r="100" ht="26.85" customHeight="1" s="31">
-      <c r="B100" s="35" t="inlineStr">
+      <c r="B100" s="59" t="inlineStr">
         <is>
           <t>Ghana</t>
         </is>
       </c>
-      <c r="C100" s="35" t="inlineStr">
+      <c r="C100" s="59" t="inlineStr">
         <is>
           <t>GIABA</t>
         </is>
       </c>
-      <c r="D100" s="35" t="inlineStr">
+      <c r="D100" s="59" t="inlineStr">
         <is>
           <t>Microfinance</t>
         </is>
       </c>
-      <c r="E100" s="35" t="inlineStr">
+      <c r="E100" s="59" t="inlineStr">
         <is>
           <t>Bank of Ghana</t>
         </is>
       </c>
-      <c r="F100" s="35" t="inlineStr">
+      <c r="F100" s="59" t="inlineStr">
         <is>
           <t>OFISD (rural/community banks, MFIs, forex bureaux)</t>
         </is>
       </c>
-      <c r="G100" s="58" t="inlineStr">
+      <c r="G100" s="60" t="inlineStr">
         <is>
           <t>https://www.bog.gov.gh/supervision-regulation/ofisd/</t>
         </is>
       </c>
-      <c r="H100" s="35" t="inlineStr">
+      <c r="H100" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I100" s="35" t="inlineStr">
+      <c r="I100" s="59" t="inlineStr">
         <is>
           <t>Other Financial Institutions databases incl. RCBs (~140), MFIs, forex bureaux</t>
         </is>
       </c>
-      <c r="J100" s="35" t="inlineStr">
+      <c r="J100" s="59" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="K100" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L100" s="35" t="inlineStr">
+      <c r="K100" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L100" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox).</t>
         </is>
       </c>
     </row>
     <row r="101" ht="52.2" customHeight="1" s="31">
-      <c r="B101" s="35" t="inlineStr">
+      <c r="B101" s="59" t="inlineStr">
         <is>
           <t>Ghana</t>
         </is>
       </c>
-      <c r="C101" s="35" t="inlineStr">
+      <c r="C101" s="59" t="inlineStr">
         <is>
           <t>GIABA</t>
         </is>
       </c>
-      <c r="D101" s="35" t="inlineStr">
+      <c r="D101" s="59" t="inlineStr">
         <is>
           <t>Payments/E-money</t>
         </is>
       </c>
-      <c r="E101" s="35" t="inlineStr">
+      <c r="E101" s="59" t="inlineStr">
         <is>
           <t>Bank of Ghana</t>
         </is>
       </c>
-      <c r="F101" s="35" t="inlineStr">
+      <c r="F101" s="59" t="inlineStr">
         <is>
           <t>List of approved Electronic Money Issuers and Payment Service Providers</t>
         </is>
       </c>
-      <c r="G101" s="58" t="inlineStr">
+      <c r="G101" s="60" t="inlineStr">
         <is>
           <t>https://www.bog.gov.gh/wp-content/uploads/2021/04/BOG-Approved-List-of-Electronic-Money-Issuers-and-Payment-Service-Providers.pdf</t>
         </is>
       </c>
-      <c r="H101" s="35" t="inlineStr">
+      <c r="H101" s="59" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="I101" s="35" t="inlineStr">
+      <c r="I101" s="59" t="inlineStr">
         <is>
           <t>DEMIs, Enhanced/Medium/Standard PSPs (2021)</t>
         </is>
       </c>
-      <c r="J101" s="35" t="inlineStr">
+      <c r="J101" s="59" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="K101" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L101" s="35" t="inlineStr">
+      <c r="K101" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L101" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox). 63 entities at Dec 2025 per FinTech Sector Report 2025.</t>
         </is>
       </c>
     </row>
     <row r="102" ht="26.85" customHeight="1" s="31">
-      <c r="B102" s="35" t="inlineStr">
+      <c r="B102" s="59" t="inlineStr">
         <is>
           <t>Ghana</t>
         </is>
       </c>
-      <c r="C102" s="35" t="inlineStr">
+      <c r="C102" s="59" t="inlineStr">
         <is>
           <t>GIABA</t>
         </is>
       </c>
-      <c r="D102" s="35" t="inlineStr">
+      <c r="D102" s="59" t="inlineStr">
         <is>
           <t>Payments/E-money</t>
         </is>
       </c>
-      <c r="E102" s="35" t="inlineStr">
+      <c r="E102" s="59" t="inlineStr">
         <is>
           <t>Bank of Ghana</t>
         </is>
       </c>
-      <c r="F102" s="35" t="inlineStr">
+      <c r="F102" s="59" t="inlineStr">
         <is>
           <t>FinTech Sector Report 2025 Full Year</t>
         </is>
       </c>
-      <c r="G102" s="58" t="inlineStr">
+      <c r="G102" s="60" t="inlineStr">
         <is>
           <t>https://www.bog.gov.gh/wp-content/uploads/2026/03/FinTech-Sector-Report-2025-FY-1.pdf</t>
         </is>
       </c>
-      <c r="H102" s="35" t="inlineStr">
+      <c r="H102" s="59" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="I102" s="35" t="inlineStr">
+      <c r="I102" s="59" t="inlineStr">
         <is>
           <t>Approved payment entities (63) - may include annex list</t>
         </is>
       </c>
-      <c r="J102" s="35" t="inlineStr">
+      <c r="J102" s="59" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="K102" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L102" s="35" t="inlineStr">
+      <c r="K102" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L102" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox).</t>
         </is>
       </c>
     </row>
     <row r="103" ht="52.2" customHeight="1" s="31">
-      <c r="B103" s="35" t="inlineStr">
+      <c r="B103" s="59" t="inlineStr">
         <is>
           <t>Ghana</t>
         </is>
       </c>
-      <c r="C103" s="35" t="inlineStr">
+      <c r="C103" s="59" t="inlineStr">
         <is>
           <t>GIABA</t>
         </is>
       </c>
-      <c r="D103" s="35" t="inlineStr">
+      <c r="D103" s="59" t="inlineStr">
         <is>
           <t>Professional body</t>
         </is>
       </c>
-      <c r="E103" s="35" t="inlineStr">
+      <c r="E103" s="59" t="inlineStr">
         <is>
           <t>ICAG</t>
         </is>
       </c>
-      <c r="F103" s="35" t="inlineStr">
+      <c r="F103" s="59" t="inlineStr">
         <is>
           <t>2026 List of Licensed Firms in Good Standing (22.07.2026)</t>
         </is>
       </c>
-      <c r="G103" s="58" t="inlineStr">
+      <c r="G103" s="60" t="inlineStr">
         <is>
           <t>https://www.icagh.org/wp-content/uploads/2026/07/2026-List-of-Licensed-Firms-in-Good-Standing-22.07.2026-Updated.pdf</t>
         </is>
       </c>
-      <c r="H103" s="35" t="inlineStr">
+      <c r="H103" s="59" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="I103" s="35" t="inlineStr">
+      <c r="I103" s="59" t="inlineStr">
         <is>
           <t>Licensed accountancy/audit firms with licence no., address, managing partner</t>
         </is>
       </c>
-      <c r="J103" s="35" t="inlineStr">
+      <c r="J103" s="59" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="K103" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L103" s="35" t="inlineStr">
+      <c r="K103" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L103" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox). Contact details partly (detailed 31.12.2025 list has emails).</t>
         </is>
       </c>
     </row>
     <row r="104" ht="26.85" customHeight="1" s="31">
-      <c r="B104" s="35" t="inlineStr">
+      <c r="B104" s="59" t="inlineStr">
         <is>
           <t>Ghana</t>
         </is>
       </c>
-      <c r="C104" s="35" t="inlineStr">
+      <c r="C104" s="59" t="inlineStr">
         <is>
           <t>GIABA</t>
         </is>
       </c>
-      <c r="D104" s="35" t="inlineStr">
+      <c r="D104" s="59" t="inlineStr">
         <is>
           <t>Professional body</t>
         </is>
       </c>
-      <c r="E104" s="35" t="inlineStr">
+      <c r="E104" s="59" t="inlineStr">
         <is>
           <t>General Legal Council</t>
         </is>
       </c>
-      <c r="F104" s="35" t="inlineStr">
+      <c r="F104" s="59" t="inlineStr">
         <is>
           <t>Lawyers in good standing</t>
         </is>
       </c>
-      <c r="G104" s="58" t="inlineStr">
+      <c r="G104" s="60" t="inlineStr">
         <is>
           <t>https://www.glc.gov.gh/lawyers-in-good-standing</t>
         </is>
       </c>
-      <c r="H104" s="35" t="inlineStr">
+      <c r="H104" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I104" s="35" t="inlineStr">
+      <c r="I104" s="59" t="inlineStr">
         <is>
           <t>Lawyers with current practising licence; also Roll of Lawyers and Find a Lawyer</t>
         </is>
       </c>
-      <c r="J104" s="35" t="inlineStr">
+      <c r="J104" s="59" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="K104" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L104" s="35" t="inlineStr">
+      <c r="K104" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L104" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox).</t>
         </is>
       </c>
     </row>
     <row r="105" ht="39.55" customHeight="1" s="31">
-      <c r="B105" s="35" t="inlineStr">
+      <c r="B105" s="59" t="inlineStr">
         <is>
           <t>Ghana</t>
         </is>
       </c>
-      <c r="C105" s="35" t="inlineStr">
+      <c r="C105" s="59" t="inlineStr">
         <is>
           <t>GIABA</t>
         </is>
       </c>
-      <c r="D105" s="35" t="inlineStr">
+      <c r="D105" s="59" t="inlineStr">
         <is>
           <t>VASP</t>
         </is>
       </c>
-      <c r="E105" s="35" t="inlineStr">
+      <c r="E105" s="59" t="inlineStr">
         <is>
           <t>SEC Ghana</t>
         </is>
       </c>
-      <c r="F105" s="35" t="inlineStr">
+      <c r="F105" s="59" t="inlineStr">
         <is>
           <t>Public Notice: Full List of Virtual Asset Sandbox Participants</t>
         </is>
       </c>
-      <c r="G105" s="58" t="inlineStr">
+      <c r="G105" s="60" t="inlineStr">
         <is>
           <t>https://sec.gov.gh/public-notice-full-list-of-virtual-asset-sandbox-participants/</t>
         </is>
       </c>
-      <c r="H105" s="35" t="inlineStr">
+      <c r="H105" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I105" s="35" t="inlineStr">
+      <c r="I105" s="59" t="inlineStr">
         <is>
           <t>VA sandbox participants (Yellow Card, WhiteBIT, KoinKoin...)</t>
         </is>
       </c>
-      <c r="J105" s="35" t="inlineStr">
+      <c r="J105" s="59" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="K105" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L105" s="35" t="inlineStr">
+      <c r="K105" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L105" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox). Sandbox, not full licences.</t>
         </is>
       </c>
     </row>
     <row r="106" ht="26.85" customHeight="1" s="31">
-      <c r="B106" s="35" t="inlineStr">
+      <c r="B106" s="59" t="inlineStr">
         <is>
           <t>Rwanda</t>
         </is>
       </c>
-      <c r="C106" s="35" t="inlineStr">
+      <c r="C106" s="59" t="inlineStr">
         <is>
           <t>ESAAMLG</t>
         </is>
       </c>
-      <c r="D106" s="35" t="inlineStr">
+      <c r="D106" s="59" t="inlineStr">
         <is>
           <t>Banks</t>
         </is>
       </c>
-      <c r="E106" s="35" t="inlineStr">
+      <c r="E106" s="59" t="inlineStr">
         <is>
           <t>National Bank of Rwanda</t>
         </is>
       </c>
-      <c r="F106" s="35" t="inlineStr">
+      <c r="F106" s="59" t="inlineStr">
         <is>
           <t>List of Supervised Banks</t>
         </is>
       </c>
-      <c r="G106" s="58" t="inlineStr">
+      <c r="G106" s="60" t="inlineStr">
         <is>
           <t>https://www.bnr.rw/documents/LIST_OF_SUPERVISED_BANKS.pdf</t>
         </is>
       </c>
-      <c r="H106" s="35" t="inlineStr">
+      <c r="H106" s="59" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="I106" s="35" t="inlineStr">
+      <c r="I106" s="59" t="inlineStr">
         <is>
           <t>11 banks (9 commercial, 1 development, 1 cooperative)</t>
         </is>
       </c>
-      <c r="J106" s="35" t="inlineStr">
+      <c r="J106" s="59" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="K106" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L106" s="35" t="inlineStr">
+      <c r="K106" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L106" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox).</t>
         </is>
       </c>
     </row>
     <row r="107" ht="39.55" customHeight="1" s="31">
-      <c r="B107" s="35" t="inlineStr">
+      <c r="B107" s="59" t="inlineStr">
         <is>
           <t>Rwanda</t>
         </is>
       </c>
-      <c r="C107" s="35" t="inlineStr">
+      <c r="C107" s="59" t="inlineStr">
         <is>
           <t>ESAAMLG</t>
         </is>
       </c>
-      <c r="D107" s="35" t="inlineStr">
+      <c r="D107" s="59" t="inlineStr">
         <is>
           <t>Capital markets</t>
         </is>
       </c>
-      <c r="E107" s="35" t="inlineStr">
+      <c r="E107" s="59" t="inlineStr">
         <is>
           <t>Capital Market Authority Rwanda</t>
         </is>
       </c>
-      <c r="F107" s="35" t="inlineStr">
+      <c r="F107" s="59" t="inlineStr">
         <is>
           <t>Licensees</t>
         </is>
       </c>
-      <c r="G107" s="58" t="inlineStr">
+      <c r="G107" s="60" t="inlineStr">
         <is>
           <t>https://www.cma.rw/licensing/licensees</t>
         </is>
       </c>
-      <c r="H107" s="35" t="inlineStr">
+      <c r="H107" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I107" s="35" t="inlineStr">
+      <c r="I107" s="59" t="inlineStr">
         <is>
           <t>Brokers, investment managers, custodians, CIS, advisers with contact person/address</t>
         </is>
       </c>
-      <c r="J107" s="35" t="inlineStr">
+      <c r="J107" s="59" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="K107" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L107" s="35" t="inlineStr">
+      <c r="K107" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L107" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox). VASP law passed; no VASP register yet.</t>
         </is>
       </c>
     </row>
     <row r="108" ht="26.85" customHeight="1" s="31">
-      <c r="B108" s="35" t="inlineStr">
+      <c r="B108" s="59" t="inlineStr">
         <is>
           <t>Rwanda</t>
         </is>
       </c>
-      <c r="C108" s="35" t="inlineStr">
+      <c r="C108" s="59" t="inlineStr">
         <is>
           <t>ESAAMLG</t>
         </is>
       </c>
-      <c r="D108" s="35" t="inlineStr">
+      <c r="D108" s="59" t="inlineStr">
         <is>
           <t>FIU</t>
         </is>
       </c>
-      <c r="E108" s="35" t="inlineStr">
+      <c r="E108" s="59" t="inlineStr">
         <is>
           <t>Financial Intelligence Centre Rwanda</t>
         </is>
       </c>
-      <c r="F108" s="35" t="inlineStr">
+      <c r="F108" s="59" t="inlineStr">
         <is>
           <t>Compliance</t>
         </is>
       </c>
-      <c r="G108" s="58" t="inlineStr">
+      <c r="G108" s="60" t="inlineStr">
         <is>
           <t>https://www.fic.gov.rw/compliance</t>
         </is>
       </c>
-      <c r="H108" s="35" t="inlineStr">
+      <c r="H108" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I108" s="35" t="inlineStr">
+      <c r="I108" s="59" t="inlineStr">
         <is>
           <t>Reporting-person obligations, guidelines, domestic sanctions list</t>
         </is>
       </c>
-      <c r="J108" s="35" t="inlineStr">
+      <c r="J108" s="59" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="K108" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L108" s="35" t="inlineStr">
+      <c r="K108" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L108" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox).</t>
         </is>
       </c>
     </row>
     <row r="109" ht="26.85" customHeight="1" s="31">
-      <c r="B109" s="35" t="inlineStr">
+      <c r="B109" s="59" t="inlineStr">
         <is>
           <t>Rwanda</t>
         </is>
       </c>
-      <c r="C109" s="35" t="inlineStr">
+      <c r="C109" s="59" t="inlineStr">
         <is>
           <t>ESAAMLG</t>
         </is>
       </c>
-      <c r="D109" s="35" t="inlineStr">
+      <c r="D109" s="59" t="inlineStr">
         <is>
           <t>Forex/Money transfer</t>
         </is>
       </c>
-      <c r="E109" s="35" t="inlineStr">
+      <c r="E109" s="59" t="inlineStr">
         <is>
           <t>National Bank of Rwanda</t>
         </is>
       </c>
-      <c r="F109" s="35" t="inlineStr">
+      <c r="F109" s="59" t="inlineStr">
         <is>
           <t>Forex Bureaus</t>
         </is>
       </c>
-      <c r="G109" s="58" t="inlineStr">
+      <c r="G109" s="60" t="inlineStr">
         <is>
           <t>https://www.bnr.rw/Forexbureaus</t>
         </is>
       </c>
-      <c r="H109" s="35" t="inlineStr">
+      <c r="H109" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I109" s="35" t="inlineStr">
+      <c r="I109" s="59" t="inlineStr">
         <is>
           <t>Forex bureau regulation page (~13 bureaus)</t>
         </is>
       </c>
-      <c r="J109" s="35" t="inlineStr">
+      <c r="J109" s="59" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="K109" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L109" s="35" t="inlineStr">
+      <c r="K109" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L109" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox).</t>
         </is>
       </c>
     </row>
     <row r="110" ht="26.85" customHeight="1" s="31">
-      <c r="B110" s="35" t="inlineStr">
+      <c r="B110" s="59" t="inlineStr">
         <is>
           <t>Rwanda</t>
         </is>
       </c>
-      <c r="C110" s="35" t="inlineStr">
+      <c r="C110" s="59" t="inlineStr">
         <is>
           <t>ESAAMLG</t>
         </is>
       </c>
-      <c r="D110" s="35" t="inlineStr">
+      <c r="D110" s="59" t="inlineStr">
         <is>
           <t>Industry association</t>
         </is>
       </c>
-      <c r="E110" s="35" t="inlineStr">
+      <c r="E110" s="59" t="inlineStr">
         <is>
           <t>Rwanda Bankers Association</t>
         </is>
       </c>
-      <c r="F110" s="35" t="inlineStr">
+      <c r="F110" s="59" t="inlineStr">
         <is>
           <t>RBA team page</t>
         </is>
       </c>
-      <c r="G110" s="58" t="inlineStr">
+      <c r="G110" s="60" t="inlineStr">
         <is>
           <t>https://rba.rw/our-team-2/</t>
         </is>
       </c>
-      <c r="H110" s="35" t="inlineStr">
+      <c r="H110" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I110" s="35" t="inlineStr">
+      <c r="I110" s="59" t="inlineStr">
         <is>
           <t>Association of all BNR-licensed banks (~12 members)</t>
         </is>
       </c>
-      <c r="J110" s="35" t="inlineStr">
+      <c r="J110" s="59" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="K110" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L110" s="35" t="inlineStr">
+      <c r="K110" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L110" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox).</t>
         </is>
       </c>
     </row>
     <row r="111" ht="39.55" customHeight="1" s="31">
-      <c r="B111" s="35" t="inlineStr">
+      <c r="B111" s="59" t="inlineStr">
         <is>
           <t>Rwanda</t>
         </is>
       </c>
-      <c r="C111" s="35" t="inlineStr">
+      <c r="C111" s="59" t="inlineStr">
         <is>
           <t>ESAAMLG</t>
         </is>
       </c>
-      <c r="D111" s="35" t="inlineStr">
+      <c r="D111" s="59" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="E111" s="35" t="inlineStr">
+      <c r="E111" s="59" t="inlineStr">
         <is>
           <t>National Bank of Rwanda</t>
         </is>
       </c>
-      <c r="F111" s="35" t="inlineStr">
+      <c r="F111" s="59" t="inlineStr">
         <is>
           <t>List of Licensed Insurers (updated Jan 2025)</t>
         </is>
       </c>
-      <c r="G111" s="58" t="inlineStr">
+      <c r="G111" s="60" t="inlineStr">
         <is>
           <t>https://www.bnr.rw/documents/LIST_OF_LICENSED_INSURERS-UPDATED-Jan_2025_aQrLsOj.pdf</t>
         </is>
       </c>
-      <c r="H111" s="35" t="inlineStr">
+      <c r="H111" s="59" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="I111" s="35" t="inlineStr">
+      <c r="I111" s="59" t="inlineStr">
         <is>
           <t>18 insurers with emails</t>
         </is>
       </c>
-      <c r="J111" s="35" t="inlineStr">
+      <c r="J111" s="59" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="K111" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L111" s="35" t="inlineStr">
+      <c r="K111" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L111" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox). Contact details YES.</t>
         </is>
       </c>
     </row>
     <row r="112" ht="26.85" customHeight="1" s="31">
-      <c r="B112" s="35" t="inlineStr">
+      <c r="B112" s="59" t="inlineStr">
         <is>
           <t>Rwanda</t>
         </is>
       </c>
-      <c r="C112" s="35" t="inlineStr">
+      <c r="C112" s="59" t="inlineStr">
         <is>
           <t>ESAAMLG</t>
         </is>
       </c>
-      <c r="D112" s="35" t="inlineStr">
+      <c r="D112" s="59" t="inlineStr">
         <is>
           <t>Insurance</t>
         </is>
       </c>
-      <c r="E112" s="35" t="inlineStr">
+      <c r="E112" s="59" t="inlineStr">
         <is>
           <t>National Bank of Rwanda</t>
         </is>
       </c>
-      <c r="F112" s="35" t="inlineStr">
+      <c r="F112" s="59" t="inlineStr">
         <is>
           <t>List of Licensed Insurance and Reinsurance Brokers (April 2026)</t>
         </is>
       </c>
-      <c r="G112" s="58" t="inlineStr">
+      <c r="G112" s="60" t="inlineStr">
         <is>
           <t>https://www.bnr.rw/documents/LIST_OF_LICENSED_INSURANCE_AND_REINSURANCE_BROKERS-April_2026_DG6v9R9.pdf</t>
         </is>
       </c>
-      <c r="H112" s="35" t="inlineStr">
+      <c r="H112" s="59" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="I112" s="35" t="inlineStr">
+      <c r="I112" s="59" t="inlineStr">
         <is>
           <t>Licensed insurance/reinsurance brokers</t>
         </is>
       </c>
-      <c r="J112" s="35" t="inlineStr">
+      <c r="J112" s="59" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="K112" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L112" s="35" t="inlineStr">
+      <c r="K112" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L112" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox).</t>
         </is>
       </c>
     </row>
     <row r="113" ht="26.85" customHeight="1" s="31">
-      <c r="B113" s="35" t="inlineStr">
+      <c r="B113" s="59" t="inlineStr">
         <is>
           <t>Rwanda</t>
         </is>
       </c>
-      <c r="C113" s="35" t="inlineStr">
+      <c r="C113" s="59" t="inlineStr">
         <is>
           <t>ESAAMLG</t>
         </is>
       </c>
-      <c r="D113" s="35" t="inlineStr">
+      <c r="D113" s="59" t="inlineStr">
         <is>
           <t>Microfinance</t>
         </is>
       </c>
-      <c r="E113" s="35" t="inlineStr">
+      <c r="E113" s="59" t="inlineStr">
         <is>
           <t>National Bank of Rwanda</t>
         </is>
       </c>
-      <c r="F113" s="35" t="inlineStr">
+      <c r="F113" s="59" t="inlineStr">
         <is>
           <t>List of Deposit-Taking Microfinance Institutions supervised by BNR</t>
         </is>
       </c>
-      <c r="G113" s="58" t="inlineStr">
+      <c r="G113" s="60" t="inlineStr">
         <is>
           <t>https://www.bnr.rw/documents/LIST_OF_DEPOSIT_TAKING_MICROFINANCE_INSTITUTIONS_SUPERVISED_BY_BNR.pdf</t>
         </is>
       </c>
-      <c r="H113" s="35" t="inlineStr">
+      <c r="H113" s="59" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="I113" s="35" t="inlineStr">
+      <c r="I113" s="59" t="inlineStr">
         <is>
           <t>Deposit-taking MFIs and SACCOs by location</t>
         </is>
       </c>
-      <c r="J113" s="35" t="inlineStr">
+      <c r="J113" s="59" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="K113" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L113" s="35" t="inlineStr">
+      <c r="K113" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L113" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox).</t>
         </is>
       </c>
     </row>
     <row r="114" ht="26.85" customHeight="1" s="31">
-      <c r="B114" s="35" t="inlineStr">
+      <c r="B114" s="59" t="inlineStr">
         <is>
           <t>Rwanda</t>
         </is>
       </c>
-      <c r="C114" s="35" t="inlineStr">
+      <c r="C114" s="59" t="inlineStr">
         <is>
           <t>ESAAMLG</t>
         </is>
       </c>
-      <c r="D114" s="35" t="inlineStr">
+      <c r="D114" s="59" t="inlineStr">
         <is>
           <t>Microfinance</t>
         </is>
       </c>
-      <c r="E114" s="35" t="inlineStr">
+      <c r="E114" s="59" t="inlineStr">
         <is>
           <t>National Bank of Rwanda</t>
         </is>
       </c>
-      <c r="F114" s="35" t="inlineStr">
+      <c r="F114" s="59" t="inlineStr">
         <is>
           <t>Licensed NDFSPs as of 1 October 2025</t>
         </is>
       </c>
-      <c r="G114" s="58" t="inlineStr">
+      <c r="G114" s="60" t="inlineStr">
         <is>
           <t>https://www.bnr.rw/documents/Licensed_NDFSPs_as_of_01st__October_2025_002_for_Update_to_Website_Final.pdf</t>
         </is>
       </c>
-      <c r="H114" s="35" t="inlineStr">
+      <c r="H114" s="59" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="I114" s="35" t="inlineStr">
+      <c r="I114" s="59" t="inlineStr">
         <is>
           <t>Non-deposit-taking financial service providers (lenders, etc.)</t>
         </is>
       </c>
-      <c r="J114" s="35" t="inlineStr">
+      <c r="J114" s="59" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="K114" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L114" s="35" t="inlineStr">
+      <c r="K114" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L114" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox).</t>
         </is>
       </c>
     </row>
     <row r="115" ht="26.85" customHeight="1" s="31">
-      <c r="B115" s="35" t="inlineStr">
+      <c r="B115" s="59" t="inlineStr">
         <is>
           <t>Rwanda</t>
         </is>
       </c>
-      <c r="C115" s="35" t="inlineStr">
+      <c r="C115" s="59" t="inlineStr">
         <is>
           <t>ESAAMLG</t>
         </is>
       </c>
-      <c r="D115" s="35" t="inlineStr">
+      <c r="D115" s="59" t="inlineStr">
         <is>
           <t>Payments/E-money</t>
         </is>
       </c>
-      <c r="E115" s="35" t="inlineStr">
+      <c r="E115" s="59" t="inlineStr">
         <is>
           <t>National Bank of Rwanda</t>
         </is>
       </c>
-      <c r="F115" s="35" t="inlineStr">
+      <c r="F115" s="59" t="inlineStr">
         <is>
           <t>Licensed Institutions - November 2025</t>
         </is>
       </c>
-      <c r="G115" s="58" t="inlineStr">
+      <c r="G115" s="60" t="inlineStr">
         <is>
           <t>https://www.bnr.rw/documents/Licensed_Institutions_-_November_2025_96EyafM.pdf</t>
         </is>
       </c>
-      <c r="H115" s="35" t="inlineStr">
+      <c r="H115" s="59" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="I115" s="35" t="inlineStr">
+      <c r="I115" s="59" t="inlineStr">
         <is>
           <t>PSPs, e-money issuers (MTN MoMo, Airtel), aggregators, remittance cos, forex bureaus, PSO</t>
         </is>
       </c>
-      <c r="J115" s="35" t="inlineStr">
+      <c r="J115" s="59" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="K115" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L115" s="35" t="inlineStr">
+      <c r="K115" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L115" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox).</t>
         </is>
       </c>
     </row>
     <row r="116" ht="39.55" customHeight="1" s="31">
-      <c r="B116" s="35" t="inlineStr">
+      <c r="B116" s="59" t="inlineStr">
         <is>
           <t>Rwanda</t>
         </is>
       </c>
-      <c r="C116" s="35" t="inlineStr">
+      <c r="C116" s="59" t="inlineStr">
         <is>
           <t>ESAAMLG</t>
         </is>
       </c>
-      <c r="D116" s="35" t="inlineStr">
+      <c r="D116" s="59" t="inlineStr">
         <is>
           <t>Professional body</t>
         </is>
       </c>
-      <c r="E116" s="35" t="inlineStr">
+      <c r="E116" s="59" t="inlineStr">
         <is>
           <t>ICPAR</t>
         </is>
       </c>
-      <c r="F116" s="35" t="inlineStr">
+      <c r="F116" s="59" t="inlineStr">
         <is>
           <t>List of Firms 2026</t>
         </is>
       </c>
-      <c r="G116" s="58" t="inlineStr">
+      <c r="G116" s="60" t="inlineStr">
         <is>
           <t>https://icparwanda.com/wp-content/uploads/2025/12/List-of-Firms-2026.pdf</t>
         </is>
       </c>
-      <c r="H116" s="35" t="inlineStr">
+      <c r="H116" s="59" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="I116" s="35" t="inlineStr">
+      <c r="I116" s="59" t="inlineStr">
         <is>
           <t>Licensed audit/accounting firms with managing partner, phone, email</t>
         </is>
       </c>
-      <c r="J116" s="35" t="inlineStr">
+      <c r="J116" s="59" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="K116" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L116" s="35" t="inlineStr">
+      <c r="K116" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L116" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox). Contact details YES.</t>
         </is>
       </c>
     </row>
     <row r="117" ht="26.85" customHeight="1" s="31">
-      <c r="B117" s="35" t="inlineStr">
+      <c r="B117" s="59" t="inlineStr">
         <is>
           <t>Rwanda</t>
         </is>
       </c>
-      <c r="C117" s="35" t="inlineStr">
+      <c r="C117" s="59" t="inlineStr">
         <is>
           <t>ESAAMLG</t>
         </is>
       </c>
-      <c r="D117" s="35" t="inlineStr">
+      <c r="D117" s="59" t="inlineStr">
         <is>
           <t>Professional body</t>
         </is>
       </c>
-      <c r="E117" s="35" t="inlineStr">
+      <c r="E117" s="59" t="inlineStr">
         <is>
           <t>Rwanda Bar Association</t>
         </is>
       </c>
-      <c r="F117" s="35" t="inlineStr">
+      <c r="F117" s="59" t="inlineStr">
         <is>
           <t>Rwanda Bar Association (list of advocates)</t>
         </is>
       </c>
-      <c r="G117" s="58" t="inlineStr">
+      <c r="G117" s="60" t="inlineStr">
         <is>
           <t>https://www.rwandabar.org.rw</t>
         </is>
       </c>
-      <c r="H117" s="35" t="inlineStr">
+      <c r="H117" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I117" s="35" t="inlineStr">
+      <c r="I117" s="59" t="inlineStr">
         <is>
           <t>List of practising advocates and interns</t>
         </is>
       </c>
-      <c r="J117" s="35" t="inlineStr">
+      <c r="J117" s="59" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="K117" s="35" t="inlineStr">
+      <c r="K117" s="59" t="inlineStr">
         <is>
           <t>nein</t>
         </is>
       </c>
-      <c r="L117" s="35" t="inlineStr">
+      <c r="L117" s="59" t="inlineStr">
         <is>
           <t>Domain from practitioner profile; not confirmed.</t>
         </is>
       </c>
     </row>
     <row r="118" ht="39.55" customHeight="1" s="31">
-      <c r="B118" s="35" t="inlineStr">
+      <c r="B118" s="59" t="inlineStr">
         <is>
           <t>Gabon</t>
         </is>
       </c>
-      <c r="C118" s="35" t="inlineStr">
+      <c r="C118" s="59" t="inlineStr">
         <is>
           <t>COBAC/BEAC</t>
         </is>
       </c>
-      <c r="D118" s="35" t="inlineStr">
+      <c r="D118" s="59" t="inlineStr">
         <is>
           <t>Banks</t>
         </is>
       </c>
-      <c r="E118" s="35" t="inlineStr">
+      <c r="E118" s="59" t="inlineStr">
         <is>
           <t>COBAC</t>
         </is>
       </c>
-      <c r="F118" s="35" t="inlineStr">
+      <c r="F118" s="59" t="inlineStr">
         <is>
           <t>COBAC - Banque Internationale pour le Commerce et l'Industrie du Gabon (directory)</t>
         </is>
       </c>
-      <c r="G118" s="58" t="inlineStr">
+      <c r="G118" s="60" t="inlineStr">
         <is>
           <t>http://sgcobac.org/jcms/ess_7052/fr/banque-internationale-pour-le-commerce-et-l-industrie-du-gabon?opLetterSearch=true&amp;directoryLetter=B&amp;memberId=&amp;directory_start=10&amp;directory_pageSize=20</t>
         </is>
       </c>
-      <c r="H118" s="35" t="inlineStr">
+      <c r="H118" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I118" s="35" t="inlineStr">
+      <c r="I118" s="59" t="inlineStr">
         <is>
           <t>COBAC directory entries for Gabonese banks (~10 banks)</t>
         </is>
       </c>
-      <c r="J118" s="35" t="inlineStr">
+      <c r="J118" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K118" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L118" s="35" t="inlineStr">
+      <c r="K118" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L118" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox).</t>
         </is>
       </c>
     </row>
     <row r="119" ht="26.85" customHeight="1" s="31">
-      <c r="B119" s="35" t="inlineStr">
+      <c r="B119" s="59" t="inlineStr">
         <is>
           <t>Gabon</t>
         </is>
       </c>
-      <c r="C119" s="35" t="inlineStr">
+      <c r="C119" s="59" t="inlineStr">
         <is>
           <t>GABAC</t>
         </is>
       </c>
-      <c r="D119" s="35" t="inlineStr">
+      <c r="D119" s="59" t="inlineStr">
         <is>
           <t>FATF/regional</t>
         </is>
       </c>
-      <c r="E119" s="35" t="inlineStr">
+      <c r="E119" s="59" t="inlineStr">
         <is>
           <t>FATF / GABAC</t>
         </is>
       </c>
-      <c r="F119" s="35" t="inlineStr">
+      <c r="F119" s="59" t="inlineStr">
         <is>
           <t>Gabon 2nd enhanced follow-up report 2026</t>
         </is>
       </c>
-      <c r="G119" s="58" t="inlineStr">
+      <c r="G119" s="60" t="inlineStr">
         <is>
           <t>https://www.fatf-gafi.org/content/dam/fatf-gafi/fsrb-fur/gabon-fur-2026.pdf.coredownload.inline.pdf</t>
         </is>
       </c>
-      <c r="H119" s="35" t="inlineStr">
+      <c r="H119" s="59" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="I119" s="35" t="inlineStr">
+      <c r="I119" s="59" t="inlineStr">
         <is>
           <t>AML/CFT follow-up with re-rating request</t>
         </is>
       </c>
-      <c r="J119" s="35" t="inlineStr">
+      <c r="J119" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K119" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L119" s="35" t="inlineStr">
+      <c r="K119" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L119" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox).</t>
         </is>
       </c>
     </row>
     <row r="120" ht="26.85" customHeight="1" s="31">
-      <c r="B120" s="35" t="inlineStr">
+      <c r="B120" s="59" t="inlineStr">
         <is>
           <t>Gabon</t>
         </is>
       </c>
-      <c r="C120" s="35" t="inlineStr">
+      <c r="C120" s="59" t="inlineStr">
         <is>
           <t>COBAC/BEAC</t>
         </is>
       </c>
-      <c r="D120" s="35" t="inlineStr">
+      <c r="D120" s="59" t="inlineStr">
         <is>
           <t>FIU</t>
         </is>
       </c>
-      <c r="E120" s="35" t="inlineStr">
+      <c r="E120" s="59" t="inlineStr">
         <is>
           <t>ANIF Gabon</t>
         </is>
       </c>
-      <c r="F120" s="35" t="inlineStr">
+      <c r="F120" s="59" t="inlineStr">
         <is>
           <t>ANIF Gabon - no official website located</t>
         </is>
       </c>
-      <c r="G120" s="35" t="n"/>
-      <c r="H120" s="35" t="inlineStr">
+      <c r="G120" s="59" t="n"/>
+      <c r="H120" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I120" s="35" t="inlineStr">
+      <c r="I120" s="59" t="inlineStr">
         <is>
           <t>FIU reorganised by decree (Nov 2024 / Dec 2025)</t>
         </is>
       </c>
-      <c r="J120" s="35" t="inlineStr">
+      <c r="J120" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K120" s="35" t="inlineStr">
+      <c r="K120" s="59" t="inlineStr">
         <is>
           <t>nein</t>
         </is>
       </c>
-      <c r="L120" s="35" t="inlineStr">
+      <c r="L120" s="59" t="inlineStr">
         <is>
           <t>No official domain found.</t>
         </is>
       </c>
     </row>
     <row r="121" ht="26.85" customHeight="1" s="31">
-      <c r="B121" s="35" t="inlineStr">
+      <c r="B121" s="59" t="inlineStr">
         <is>
           <t>Gabon</t>
         </is>
       </c>
-      <c r="C121" s="35" t="inlineStr">
+      <c r="C121" s="59" t="inlineStr">
         <is>
           <t>COBAC/BEAC</t>
         </is>
       </c>
-      <c r="D121" s="35" t="inlineStr">
+      <c r="D121" s="59" t="inlineStr">
         <is>
           <t>Industry association</t>
         </is>
       </c>
-      <c r="E121" s="35" t="inlineStr">
+      <c r="E121" s="59" t="inlineStr">
         <is>
           <t>APEC Gabon</t>
         </is>
       </c>
-      <c r="F121" s="35" t="inlineStr">
+      <c r="F121" s="59" t="inlineStr">
         <is>
           <t>APEC Gabon</t>
         </is>
       </c>
-      <c r="G121" s="58" t="inlineStr">
+      <c r="G121" s="60" t="inlineStr">
         <is>
           <t>https://www.apecgabon.com</t>
         </is>
       </c>
-      <c r="H121" s="35" t="inlineStr">
+      <c r="H121" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I121" s="35" t="inlineStr">
+      <c r="I121" s="59" t="inlineStr">
         <is>
           <t>Bankers' association member list</t>
         </is>
       </c>
-      <c r="J121" s="35" t="inlineStr">
+      <c r="J121" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K121" s="35" t="inlineStr">
+      <c r="K121" s="59" t="inlineStr">
         <is>
           <t>nein</t>
         </is>
       </c>
-      <c r="L121" s="35" t="inlineStr">
+      <c r="L121" s="59" t="inlineStr">
         <is>
           <t>Domain cited via Wikipedia; not confirmed.</t>
         </is>
       </c>
     </row>
     <row r="122" ht="52.2" customHeight="1" s="31">
-      <c r="B122" s="35" t="inlineStr">
+      <c r="B122" s="59" t="inlineStr">
         <is>
           <t>Gabon</t>
         </is>
       </c>
-      <c r="C122" s="35" t="inlineStr">
+      <c r="C122" s="59" t="inlineStr">
         <is>
           <t>COBAC/BEAC</t>
         </is>
       </c>
-      <c r="D122" s="35" t="inlineStr">
+      <c r="D122" s="59" t="inlineStr">
         <is>
           <t>Professional body</t>
         </is>
       </c>
-      <c r="E122" s="35" t="inlineStr">
+      <c r="E122" s="59" t="inlineStr">
         <is>
           <t>ONEC Gabon</t>
         </is>
       </c>
-      <c r="F122" s="35" t="inlineStr">
+      <c r="F122" s="59" t="inlineStr">
         <is>
           <t>ONEC tableau de l'ordre 2022</t>
         </is>
       </c>
-      <c r="G122" s="58" t="inlineStr">
+      <c r="G122" s="60" t="inlineStr">
         <is>
           <t>https://onecgabon.org/wp-content/uploads/pdf/ONEC_tableau_de_lordre_2022.pdf</t>
         </is>
       </c>
-      <c r="H122" s="35" t="inlineStr">
+      <c r="H122" s="59" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="I122" s="35" t="inlineStr">
+      <c r="I122" s="59" t="inlineStr">
         <is>
           <t>Registered chartered accountants &amp; firms</t>
         </is>
       </c>
-      <c r="J122" s="35" t="inlineStr">
+      <c r="J122" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K122" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L122" s="35" t="inlineStr">
+      <c r="K122" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L122" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox). Newer (3rd edition) tableau announced in press.</t>
         </is>
       </c>
     </row>
     <row r="123" ht="39.55" customHeight="1" s="31">
-      <c r="B123" s="35" t="inlineStr">
+      <c r="B123" s="59" t="inlineStr">
         <is>
           <t>Mali</t>
         </is>
       </c>
-      <c r="C123" s="35" t="inlineStr">
+      <c r="C123" s="59" t="inlineStr">
         <is>
           <t>BCEAO</t>
         </is>
       </c>
-      <c r="D123" s="35" t="inlineStr">
+      <c r="D123" s="59" t="inlineStr">
         <is>
           <t>Banks</t>
         </is>
       </c>
-      <c r="E123" s="35" t="inlineStr">
+      <c r="E123" s="59" t="inlineStr">
         <is>
           <t>Commission Bancaire de l'UMOA</t>
         </is>
       </c>
-      <c r="F123" s="35" t="inlineStr">
+      <c r="F123" s="59" t="inlineStr">
         <is>
           <t>Liste EC Mali 2026</t>
         </is>
       </c>
-      <c r="G123" s="58" t="inlineStr">
+      <c r="G123" s="60" t="inlineStr">
         <is>
           <t>https://www.cb-umoa.org/sites/default/files/Liste%20EC%20Mali_2026.pdf</t>
         </is>
       </c>
-      <c r="H123" s="35" t="inlineStr">
+      <c r="H123" s="59" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="I123" s="35" t="inlineStr">
+      <c r="I123" s="59" t="inlineStr">
         <is>
           <t>Credit institutions licensed in Mali (14 banks + FIs)</t>
         </is>
       </c>
-      <c r="J123" s="35" t="inlineStr">
+      <c r="J123" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K123" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L123" s="35" t="inlineStr">
+      <c r="K123" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L123" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox). 2025 version: Liste%20Mali%202025.pdf</t>
         </is>
       </c>
     </row>
     <row r="124" ht="26.85" customHeight="1" s="31">
-      <c r="B124" s="35" t="inlineStr">
+      <c r="B124" s="59" t="inlineStr">
         <is>
           <t>Mali</t>
         </is>
       </c>
-      <c r="C124" s="35" t="inlineStr">
+      <c r="C124" s="59" t="inlineStr">
         <is>
           <t>BCEAO</t>
         </is>
       </c>
-      <c r="D124" s="35" t="inlineStr">
+      <c r="D124" s="59" t="inlineStr">
         <is>
           <t>FIU</t>
         </is>
       </c>
-      <c r="E124" s="35" t="inlineStr">
+      <c r="E124" s="59" t="inlineStr">
         <is>
           <t>CENTIF Mali</t>
         </is>
       </c>
-      <c r="F124" s="35" t="inlineStr">
+      <c r="F124" s="59" t="inlineStr">
         <is>
           <t>Présentation - CENTIF Mali</t>
         </is>
       </c>
-      <c r="G124" s="58" t="inlineStr">
+      <c r="G124" s="60" t="inlineStr">
         <is>
           <t>https://centif.ml/presentation/</t>
         </is>
       </c>
-      <c r="H124" s="35" t="inlineStr">
+      <c r="H124" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I124" s="35" t="inlineStr">
+      <c r="I124" s="59" t="inlineStr">
         <is>
           <t>FIU; mandate and reporting</t>
         </is>
       </c>
-      <c r="J124" s="35" t="inlineStr">
+      <c r="J124" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K124" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L124" s="35" t="inlineStr">
+      <c r="K124" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L124" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox).</t>
         </is>
       </c>
     </row>
     <row r="125" ht="26.85" customHeight="1" s="31">
-      <c r="B125" s="35" t="inlineStr">
+      <c r="B125" s="59" t="inlineStr">
         <is>
           <t>Mali</t>
         </is>
       </c>
-      <c r="C125" s="35" t="inlineStr">
+      <c r="C125" s="59" t="inlineStr">
         <is>
           <t>BCEAO</t>
         </is>
       </c>
-      <c r="D125" s="35" t="inlineStr">
+      <c r="D125" s="59" t="inlineStr">
         <is>
           <t>Payments/E-money</t>
         </is>
       </c>
-      <c r="E125" s="35" t="inlineStr">
+      <c r="E125" s="59" t="inlineStr">
         <is>
           <t>BCEAO</t>
         </is>
       </c>
-      <c r="F125" s="35" t="inlineStr">
+      <c r="F125" s="59" t="inlineStr">
         <is>
           <t>5 - Liste Mali_2026</t>
         </is>
       </c>
-      <c r="G125" s="58" t="inlineStr">
+      <c r="G125" s="60" t="inlineStr">
         <is>
           <t>https://www.bceao.int/sites/default/files/inline-files/5%20-%20Liste%20Mali_2026.pdf</t>
         </is>
       </c>
-      <c r="H125" s="35" t="inlineStr">
+      <c r="H125" s="59" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="I125" s="35" t="inlineStr">
+      <c r="I125" s="59" t="inlineStr">
         <is>
           <t>E-money issuers in Mali (Orange Finances Mobiles Mali, Sama Money)</t>
         </is>
       </c>
-      <c r="J125" s="35" t="inlineStr">
+      <c r="J125" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K125" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L125" s="35" t="inlineStr">
+      <c r="K125" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L125" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox).</t>
         </is>
       </c>
     </row>
     <row r="126" ht="26.85" customHeight="1" s="31">
-      <c r="B126" s="35" t="inlineStr">
+      <c r="B126" s="59" t="inlineStr">
         <is>
           <t>Togo</t>
         </is>
       </c>
-      <c r="C126" s="35" t="inlineStr">
+      <c r="C126" s="59" t="inlineStr">
         <is>
           <t>BCEAO</t>
         </is>
       </c>
-      <c r="D126" s="35" t="inlineStr">
+      <c r="D126" s="59" t="inlineStr">
         <is>
           <t>Banks</t>
         </is>
       </c>
-      <c r="E126" s="35" t="inlineStr">
+      <c r="E126" s="59" t="inlineStr">
         <is>
           <t>Commission Bancaire de l'UMOA</t>
         </is>
       </c>
-      <c r="F126" s="35" t="inlineStr">
+      <c r="F126" s="59" t="inlineStr">
         <is>
           <t>Liste Togo 2025</t>
         </is>
       </c>
-      <c r="G126" s="58" t="inlineStr">
+      <c r="G126" s="60" t="inlineStr">
         <is>
           <t>https://cb-umoa.org/sites/default/files/Liste%20Togo%202025.pdf</t>
         </is>
       </c>
-      <c r="H126" s="35" t="inlineStr">
+      <c r="H126" s="59" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="I126" s="35" t="inlineStr">
+      <c r="I126" s="59" t="inlineStr">
         <is>
           <t>11 banks + 3 branches + 3 FIs licensed in Togo</t>
         </is>
       </c>
-      <c r="J126" s="35" t="inlineStr">
+      <c r="J126" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K126" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L126" s="35" t="inlineStr">
+      <c r="K126" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L126" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox).</t>
         </is>
       </c>
     </row>
     <row r="127" ht="26.85" customHeight="1" s="31">
-      <c r="B127" s="35" t="inlineStr">
+      <c r="B127" s="59" t="inlineStr">
         <is>
           <t>Togo</t>
         </is>
       </c>
-      <c r="C127" s="35" t="inlineStr">
+      <c r="C127" s="59" t="inlineStr">
         <is>
           <t>BCEAO</t>
         </is>
       </c>
-      <c r="D127" s="35" t="inlineStr">
+      <c r="D127" s="59" t="inlineStr">
         <is>
           <t>FIU</t>
         </is>
       </c>
-      <c r="E127" s="35" t="inlineStr">
+      <c r="E127" s="59" t="inlineStr">
         <is>
           <t>CENTIF Togo</t>
         </is>
       </c>
-      <c r="F127" s="35" t="inlineStr">
+      <c r="F127" s="59" t="inlineStr">
         <is>
           <t>Centif.tg</t>
         </is>
       </c>
-      <c r="G127" s="58" t="inlineStr">
+      <c r="G127" s="60" t="inlineStr">
         <is>
           <t>https://www.centif.tg/</t>
         </is>
       </c>
-      <c r="H127" s="35" t="inlineStr">
+      <c r="H127" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I127" s="35" t="inlineStr">
+      <c r="I127" s="59" t="inlineStr">
         <is>
           <t>FIU; activity reports and legal texts</t>
         </is>
       </c>
-      <c r="J127" s="35" t="inlineStr">
+      <c r="J127" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K127" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L127" s="35" t="inlineStr">
+      <c r="K127" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L127" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox).</t>
         </is>
       </c>
     </row>
     <row r="128" ht="26.85" customHeight="1" s="31">
-      <c r="B128" s="35" t="inlineStr">
+      <c r="B128" s="59" t="inlineStr">
         <is>
           <t>Republic of Congo</t>
         </is>
       </c>
-      <c r="C128" s="35" t="inlineStr">
+      <c r="C128" s="59" t="inlineStr">
         <is>
           <t>COBAC/BEAC</t>
         </is>
       </c>
-      <c r="D128" s="35" t="inlineStr">
+      <c r="D128" s="59" t="inlineStr">
         <is>
           <t>Banks</t>
         </is>
       </c>
-      <c r="E128" s="35" t="inlineStr">
+      <c r="E128" s="59" t="inlineStr">
         <is>
           <t>COBAC</t>
         </is>
       </c>
-      <c r="F128" s="35" t="inlineStr">
+      <c r="F128" s="59" t="inlineStr">
         <is>
           <t>COBAC - Ecobank Congo (directory)</t>
         </is>
       </c>
-      <c r="G128" s="58" t="inlineStr">
+      <c r="G128" s="60" t="inlineStr">
         <is>
           <t>http://www.sgcobac.org/jcms/ess_6863/en/ecobank-congo</t>
         </is>
       </c>
-      <c r="H128" s="35" t="inlineStr">
+      <c r="H128" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I128" s="35" t="inlineStr">
+      <c r="I128" s="59" t="inlineStr">
         <is>
           <t>COBAC directory entries for Congolese banks (~11 banks)</t>
         </is>
       </c>
-      <c r="J128" s="35" t="inlineStr">
+      <c r="J128" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K128" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L128" s="35" t="inlineStr">
+      <c r="K128" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L128" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox).</t>
         </is>
       </c>
     </row>
     <row r="129" ht="26.85" customHeight="1" s="31">
-      <c r="B129" s="35" t="inlineStr">
+      <c r="B129" s="59" t="inlineStr">
         <is>
           <t>Republic of Congo</t>
         </is>
       </c>
-      <c r="C129" s="35" t="inlineStr">
+      <c r="C129" s="59" t="inlineStr">
         <is>
           <t>GABAC</t>
         </is>
       </c>
-      <c r="D129" s="35" t="inlineStr">
+      <c r="D129" s="59" t="inlineStr">
         <is>
           <t>FATF/regional</t>
         </is>
       </c>
-      <c r="E129" s="35" t="inlineStr">
+      <c r="E129" s="59" t="inlineStr">
         <is>
           <t>GABAC</t>
         </is>
       </c>
-      <c r="F129" s="35" t="inlineStr">
+      <c r="F129" s="59" t="inlineStr">
         <is>
           <t>Mutual Evaluation Report April 2022 - Congo</t>
         </is>
       </c>
-      <c r="G129" s="58" t="inlineStr">
+      <c r="G129" s="60" t="inlineStr">
         <is>
           <t>https://gabac.org/wp-content/uploads/2022/10/REM-CONGO-ANGLAIS.pdf</t>
         </is>
       </c>
-      <c r="H129" s="35" t="inlineStr">
+      <c r="H129" s="59" t="inlineStr">
         <is>
           <t>PDF</t>
         </is>
       </c>
-      <c r="I129" s="35" t="inlineStr">
+      <c r="I129" s="59" t="inlineStr">
         <is>
           <t>Congo MER - lists obliged sectors and gaps</t>
         </is>
       </c>
-      <c r="J129" s="35" t="inlineStr">
+      <c r="J129" s="59" t="inlineStr">
         <is>
           <t>EN</t>
         </is>
       </c>
-      <c r="K129" s="35" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
-      <c r="L129" s="35" t="inlineStr">
+      <c r="K129" s="59" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
+      <c r="L129" s="59" t="inlineStr">
         <is>
           <t>Confirmed in search index on official domain (direct fetch blocked in sandbox).</t>
         </is>
       </c>
     </row>
     <row r="130" ht="26.85" customHeight="1" s="31">
-      <c r="B130" s="35" t="inlineStr">
+      <c r="B130" s="59" t="inlineStr">
         <is>
           <t>Republic of Congo</t>
         </is>
       </c>
-      <c r="C130" s="35" t="inlineStr">
+      <c r="C130" s="59" t="inlineStr">
         <is>
           <t>COBAC/BEAC</t>
         </is>
       </c>
-      <c r="D130" s="35" t="inlineStr">
+      <c r="D130" s="59" t="inlineStr">
         <is>
           <t>FIU</t>
         </is>
       </c>
-      <c r="E130" s="35" t="inlineStr">
+      <c r="E130" s="59" t="inlineStr">
         <is>
           <t>ANIF Congo</t>
         </is>
       </c>
-      <c r="F130" s="35" t="inlineStr">
+      <c r="F130" s="59" t="inlineStr">
         <is>
           <t>ANIF Congo - no official website located</t>
         </is>
       </c>
-      <c r="G130" s="35" t="n"/>
-      <c r="H130" s="35" t="inlineStr">
+      <c r="G130" s="59" t="n"/>
+      <c r="H130" s="59" t="inlineStr">
         <is>
           <t>HTML</t>
         </is>
       </c>
-      <c r="I130" s="35" t="inlineStr">
+      <c r="I130" s="59" t="inlineStr">
         <is>
           <t>FIU (DG Fred Ursus Otsoa Andely); EU SecFin programme 2026-28</t>
         </is>
       </c>
-      <c r="J130" s="35" t="inlineStr">
+      <c r="J130" s="59" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="K130" s="35" t="inlineStr">
+      <c r="K130" s="59" t="inlineStr">
         <is>
           <t>nein</t>
         </is>
       </c>
-      <c r="L130" s="35" t="inlineStr">
+      <c r="L130" s="59" t="inlineStr">
         <is>
           <t>No official domain found.</t>
         </is>
